--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,17 +801,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JVGLOTC0113619121</t>
+          <t>CY254064248DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>dhl-germany</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>Deutsche Post DHL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6001659976</t>
+          <t>6001664166</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -833,18 +833,22 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-02T10:57:01+01:00</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>2026-02-05T14:01:00+01:00</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-02T10:58:15+00:00</t>
+          <t>2026-03-02T01:58:14+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JVGLOTC0113619121</t>
+          <t>CY254064248DE</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -856,17 +860,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>67721300002823</t>
+          <t>JJD149990121180200257</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hermes-de</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hermes Germany</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -876,7 +880,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6001662826</t>
+          <t>6001658918</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -888,14 +892,10 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-02-23T17:07:10+01:00</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
+          <t>2026-02-13T10:25:00+01:00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>2026-03-02T01:58:14+00:00</t>
@@ -903,7 +903,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>67721300002823</t>
+          <t>JJD149990121180200257</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -915,17 +915,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CY429881982DE</t>
+          <t>YV6RE2R4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dhl-germany</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Deutsche Post DHL</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6001659732</t>
+          <t>6001658661</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -947,22 +947,22 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-02-16T13:00:00+01:00</t>
+          <t>2026-02-16T15:00:00+01:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL, Netherlands</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-02T01:58:14+00:00</t>
+          <t>2026-03-02T01:58:21+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CY429881982DE</t>
+          <t>YV6RE2R4</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -974,17 +974,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>66045117400493</t>
+          <t>JVGLOTC0114408022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hermes-de</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hermes Germany</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6001659078</t>
+          <t>6001659976</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1006,22 +1006,18 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-02-24T11:28:45+01:00</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
+          <t>2026-03-02T10:57:01+01:00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-02T01:58:14+00:00</t>
+          <t>2026-03-02T10:58:16+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>66045117400493</t>
+          <t>JVGLOTC0114408022</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1033,17 +1029,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>YV6RE2R4</t>
+          <t>JVGLOTC0113619121</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1053,7 +1049,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6001658661</t>
+          <t>6001659976</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1065,22 +1061,18 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-02-16T15:00:00+01:00</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>NL, Netherlands</t>
-        </is>
-      </c>
+          <t>2026-03-02T10:57:01+01:00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-02T01:58:21+00:00</t>
+          <t>2026-03-02T10:58:15+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>YV6RE2R4</t>
+          <t>JVGLOTC0113619121</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1092,17 +1084,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>66051117400128</t>
+          <t>YV6RF1WX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hermes-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hermes Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1112,7 +1104,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6001659012</t>
+          <t>6001658774</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1124,22 +1116,22 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-02-24T11:28:45+01:00</t>
+          <t>2026-02-26T16:00:00+01:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>NL, Netherlands</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-02T01:58:13+00:00</t>
+          <t>2026-03-02T01:58:20+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>66051117400128</t>
+          <t>YV6RF1WX</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1151,17 +1143,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JJD149990121180200257</t>
+          <t>CY429881982DE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>dhl-germany</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>Deutsche Post DHL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1171,7 +1163,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6001658918</t>
+          <t>6001659732</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1183,10 +1175,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-02-13T10:25:00+01:00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>2026-02-16T13:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>2026-03-02T01:58:14+00:00</t>
@@ -1194,301 +1190,10 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JJD149990121180200257</t>
+          <t>CY429881982DE</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>YV6RF1WX</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>gls</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GLS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>6001658774</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>csv_importer</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-02-26T16:00:00+01:00</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>NL, Netherlands</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-03-02T01:58:20+00:00</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>YV6RF1WX</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>66040117401334</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>hermes-de</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Hermes Germany</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>6001663147</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>csv_importer</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-02-26T11:26:31+01:00</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-03-02T01:58:15+00:00</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>66040117401334</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AA007903003763</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>brt-it-parcelid</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>BRT Bartolini(Parcel ID)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>6001662164</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>csv_importer</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-02-10T12:00:00+01:00</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>MILANO SEDRIANO (050)</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-03-02T02:58:15+00:00</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>AA007903003763</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>JVGLOTC0114408022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>dhlparcel-nl</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DHL Parcel NL</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>6001659976</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>csv_importer</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-03-02T10:57:01+01:00</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-03-02T10:58:16+00:00</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>JVGLOTC0114408022</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CY254064248DE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>dhl-germany</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Deutsche Post DHL</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>6001664166</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>csv_importer</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-02-05T14:01:00+01:00</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-03-02T01:58:14+00:00</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>CY254064248DE</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
         <is>
           <t>{}</t>
         </is>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,17 +801,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CY254064248DE</t>
+          <t>3366515581131</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dhl-germany</t>
+          <t>directfreight-au-ref</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Deutsche Post DHL</t>
+          <t>Direct Freight Express</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -821,56 +821,60 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6001664166</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>358326939</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-02-05T14:01:00+01:00</t>
+          <t>2026-03-03T08:41:00+11:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Warrnambool, Australia</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-02T01:58:14+00:00</t>
+          <t>2026-03-02T21:50:09+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CY254064248DE</t>
+          <t>3366515581131</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "358326939", "sales_office_id": "4131"}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JJD149990121180200257</t>
+          <t>3366515581136</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>directfreight-au-ref</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>Direct Freight Express</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -880,52 +884,60 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6001658918</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>503-6034946-5107853</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4272</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-02-13T10:25:00+01:00</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>2026-03-03T08:41:00+11:00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bendigo, Australia</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-02T01:58:14+00:00</t>
+          <t>2026-03-02T21:50:09+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>JJD149990121180200257</t>
+          <t>3366515581136</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "503-6034946-5107853", "sales_office_id": "4272"}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>YV6RE2R4</t>
+          <t>3366515581284</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>directfreight-au-ref</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Direct Freight Express</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -935,56 +947,60 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6001658661</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>358348062</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-02-16T15:00:00+01:00</t>
+          <t>2026-03-03T08:40:00+11:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>NL, Netherlands</t>
+          <t>Warrnambool, Australia</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-02T01:58:21+00:00</t>
+          <t>2026-03-02T21:50:09+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>YV6RE2R4</t>
+          <t>3366515581284</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "358348062", "sales_office_id": "4131"}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JVGLOTC0114408022</t>
+          <t>YV6RF1WX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -994,7 +1010,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6001659976</t>
+          <t>6001658774</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1006,18 +1022,22 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-02T10:57:01+01:00</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>2026-02-26T16:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NL, Netherlands</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-02T10:58:16+00:00</t>
+          <t>2026-03-02T01:58:20+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JVGLOTC0114408022</t>
+          <t>YV6RF1WX</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1029,17 +1049,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JVGLOTC0113619121</t>
+          <t>YV6RE2R4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,7 +1069,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6001659976</t>
+          <t>6001658661</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1061,139 +1081,25 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-02T10:57:01+01:00</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>2026-02-16T15:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NL, Netherlands</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-02T10:58:15+00:00</t>
+          <t>2026-03-02T01:58:21+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>JVGLOTC0113619121</t>
+          <t>YV6RE2R4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>YV6RF1WX</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>gls</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>GLS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>6001658774</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>csv_importer</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-02-26T16:00:00+01:00</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NL, Netherlands</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-03-02T01:58:20+00:00</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>YV6RF1WX</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CY429881982DE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>dhl-germany</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Deutsche Post DHL</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>6001659732</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>csv_importer</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-02-16T13:00:00+01:00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-03-02T01:58:14+00:00</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>CY429881982DE</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
         <is>
           <t>{}</t>
         </is>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>957140554393</t>
+          <t>JVGLOTC0112289839</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sending</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sending Transporte Urgente y Comunicacion</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,60 +506,52 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>408-5300258-6528314</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4562</t>
-        </is>
-      </c>
+          <t>6001667307</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-02T10:01:35</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>CARTAGENA</t>
-        </is>
-      </c>
+          <t>2026-03-02T10:57:01+01:00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-02T12:56:11+00:00</t>
+          <t>2026-03-03T01:02:39+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>957140554393</t>
+          <t>JVGLOTC0112289839</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"external_order_id": "408-5300258-6528314", "sales_office_id": "4562"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UTV338518600</t>
+          <t>MDPRPD8ML2X</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -569,50 +561,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0031009959437</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001666416</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-02-28T09:02:26+01:00</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>,Netherlands</t>
-        </is>
-      </c>
+          <t>2026-02-26T12:58:11+01:00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:47+00:00</t>
+          <t>2026-03-03T01:02:39+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>UTV338518600</t>
+          <t>MDPRPD8ML2X</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009959437", "sales_office_id": "0303"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>YVMMYQ75</t>
+          <t>12120741894</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -632,23 +616,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0049010167538</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0301</t>
-        </is>
-      </c>
+          <t>6001666123</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-02-24T12:12:07+01:00</t>
+          <t>2026-02-12T14:00:00+01:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -658,34 +638,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-02T09:32:01+00:00</t>
+          <t>2026-03-03T01:02:44+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>YVMMYQ75</t>
+          <t>12120741894</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010167538", "sales_office_id": "0301"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05228742844301</t>
+          <t>ZDDO3NPO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -695,60 +675,56 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0031009968238</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001664941</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-02T11:30:10+01:00</t>
+          <t>2026-03-02T14:00:00+01:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-02T11:31:04+00:00</t>
+          <t>2026-03-03T01:02:41+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>05228742844301</t>
+          <t>ZDDO3NPO</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009968238", "sales_office_id": "0303"}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05228742840818</t>
+          <t>ZDDO3I9H</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -758,60 +734,56 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0032005561679</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001666716</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-02T13:04:29+01:00</t>
+          <t>2026-02-05T13:30:00+01:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lummen, BE, Belgium</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-02T12:31:38+00:00</t>
+          <t>2026-03-03T01:02:41+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>05228742840818</t>
+          <t>ZDDO3I9H</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005561679", "sales_office_id": "0303"}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3366515581131</t>
+          <t>05222006538534</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>directfreight-au-ref</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Direct Freight Express</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -821,60 +793,56 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>358326939</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4131</t>
-        </is>
-      </c>
+          <t>6001664575</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-03T08:41:00+11:00</t>
+          <t>2026-03-02T15:00:27+01:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Warrnambool, Australia</t>
+          <t>Malmoe, SE, Sweden</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-02T21:50:09+00:00</t>
+          <t>2026-03-03T05:02:27+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3366515581131</t>
+          <t>05222006538534</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"external_order_id": "358326939", "sales_office_id": "4131"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3366515581136</t>
+          <t>00093275103238022821</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>directfreight-au-ref</t>
+          <t>toll-ipec</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Direct Freight Express</t>
+          <t>toll-ipec</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -884,12 +852,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>503-6034946-5107853</t>
+          <t>358352811</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -900,44 +868,44 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-03T08:41:00+11:00</t>
+          <t>2026-03-03T14:35:00+11:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Bendigo, Australia</t>
+          <t>MELBOURNE</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-02T21:50:09+00:00</t>
+          <t>2026-03-03T04:14:55+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3366515581136</t>
+          <t>00093275103238022821</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"external_order_id": "503-6034946-5107853", "sales_office_id": "4272"}</t>
+          <t>{"external_order_id": "358352811", "sales_office_id": "4131"}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3366515581284</t>
+          <t>00093275103238022814</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>directfreight-au-ref</t>
+          <t>toll-ipec</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Direct Freight Express</t>
+          <t>toll-ipec</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -947,7 +915,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>358348062</t>
+          <t>358352811</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -963,44 +931,44 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-03T08:40:00+11:00</t>
+          <t>2026-03-03T14:35:00+11:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Warrnambool, Australia</t>
+          <t>MELBOURNE</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-02T21:50:09+00:00</t>
+          <t>2026-03-03T04:14:54+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3366515581284</t>
+          <t>00093275103238022814</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"external_order_id": "358348062", "sales_office_id": "4131"}</t>
+          <t>{"external_order_id": "358352811", "sales_office_id": "4131"}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>YV6RF1WX</t>
+          <t>957140554393</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>sending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Sending Transporte Urgente y Comunicacion</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1010,56 +978,60 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6001658774</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>408-5300258-6528314</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4562</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-02-26T16:00:00+01:00</t>
+          <t>2026-03-02T10:01:35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NL, Netherlands</t>
+          <t>CARTAGENA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-02T01:58:20+00:00</t>
+          <t>2026-03-02T12:56:11+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>YV6RF1WX</t>
+          <t>957140554393</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "408-5300258-6528314", "sales_office_id": "4562"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>YV6RE2R4</t>
+          <t>UTV338518600</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1069,39 +1041,3067 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6001658661</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>0031009959437</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-02-16T15:00:00+01:00</t>
+          <t>2026-02-28T09:02:26+01:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>NL, Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-02T01:58:21+00:00</t>
+          <t>2026-03-02T11:25:47+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>YV6RE2R4</t>
+          <t>UTV338518600</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "0031009959437", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>YVMMYQ75</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0049010167538</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-02-24T12:12:07+01:00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-03-02T09:32:01+00:00</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>YVMMYQ75</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010167538", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>518157128215</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>503-8911242-3355807</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:43:00+09:00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>城南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:49:13+00:00</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>518157128215</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-8911242-3355807", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>518157127191</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>503-8911242-3355807</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:43:00+09:00</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>城南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:49:04+00:00</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>518157127191</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-8911242-3355807", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>518157126605</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>503-8911242-3355807</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:46:00+09:00</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>城南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:49:06+00:00</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>518157126605</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-8911242-3355807", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>518157127180</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>503-8911242-3355807</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:46:00+09:00</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>城南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:49:04+00:00</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>518157127180</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-8911242-3355807", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>518157126616</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>503-8911242-3355807</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:46:00+09:00</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>城南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:49:05+00:00</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>518157126616</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-8911242-3355807", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>518157127541</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>503-8911242-3355807</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:46:00+09:00</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>城南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:49:06+00:00</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>518157127541</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-8911242-3355807", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>518157125080</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>503-8911242-3355807</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:45:00+09:00</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>城南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:49:03+00:00</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>518157125080</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-8911242-3355807", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>518157127224</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>250-8062494-2544631</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:09:00+09:00</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>栃木営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:48:22+00:00</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>518157127224</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-8062494-2544631", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>518157127176</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>250-4385628-8979003</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:11:00+09:00</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>名古屋南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:48:12+00:00</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>518157127176</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-4385628-8979003", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>518157127471</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>503-8412600-1026205</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:29:00+09:00</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>長野営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:48:07+00:00</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>518157127471</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-8412600-1026205", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>518157127526</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>250-5936530-6917433</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:42:00+09:00</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>港営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:18:08+00:00</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>518157127526</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-5936530-6917433", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>518157127515</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>250-5936530-6917433</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:42:00+09:00</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>港営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:18:08+00:00</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>518157127515</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-5936530-6917433", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>518157127530</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>250-5936530-6917433</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:42:00+09:00</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>港営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:18:10+00:00</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>518157127530</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-5936530-6917433", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>518157126852</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>249-5561769-2825444</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:38:00+09:00</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>栃木営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-03-03T04:18:11+00:00</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>518157126852</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-5561769-2825444", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>518157126841</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>249-5561769-2825444</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:38:00+09:00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>栃木営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-03-03T04:18:09+00:00</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>518157126841</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-5561769-2825444", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>518157127751</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>250-6068332-6431831</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:16:00+09:00</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>渋谷営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:48:05+00:00</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>518157127751</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-6068332-6431831", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>518157127762</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>250-6068332-6431831</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:16:00+09:00</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>渋谷営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:47:57+00:00</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>518157127762</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-6068332-6431831", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>518157127773</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>250-6068332-6431831</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:16:00+09:00</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>渋谷営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:48:03+00:00</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>518157127773</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-6068332-6431831", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>518157127740</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>250-6068332-6431831</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:16:00+09:00</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>渋谷営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:47:58+00:00</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>518157127740</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-6068332-6431831", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>518157127784</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>503-4893740-1277464</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:34:00+09:00</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>湘南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-03-03T04:18:05+00:00</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>518157127784</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-4893740-1277464", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>518157127795</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>503-2261261-8993412</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:37:00+09:00</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>白石営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:47:59+00:00</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>518157127795</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-2261261-8993412", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>518157126152</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>503-4893740-1277464</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:34:00+09:00</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>湘南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-03-03T04:18:06+00:00</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>518157126152</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-4893740-1277464", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>518157127736</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>250-6068332-6431831</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:16:00+09:00</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>渋谷営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:47:58+00:00</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>518157127736</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-6068332-6431831", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>518157127692</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>249-6244601-4150243</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:12:00+09:00</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>筑西営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:45:54+00:00</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>518157127692</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-6244601-4150243", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>518157127681</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>249-6244601-4150243</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:12:00+09:00</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>筑西営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:45:54+00:00</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>518157127681</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-6244601-4150243", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>518157125091</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>249-6244601-4150243</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:12:00+09:00</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>筑西営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:45:50+00:00</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>518157125091</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-6244601-4150243", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>518157128182</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>249-8218733-0983841</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:15:00+09:00</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>枚方営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:45:58+00:00</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>518157128182</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-8218733-0983841", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>518157128145</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>503-6061539-6711805</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:21:00+09:00</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>福井営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:45:49+00:00</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>518157128145</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-6061539-6711805", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>518157128134</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>249-5783021-9663032</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:43:00+09:00</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>千葉中央営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-03-03T03:14:10+00:00</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>518157128134</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-5783021-9663032", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>518157127482</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>503-8967288-0087009</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>南大阪営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>518157127482</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-8967288-0087009", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>518157127493</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>250-5708238-8036645</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:35:00+09:00</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>柏営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-03-03T03:14:06+00:00</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>518157127493</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-5708238-8036645", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>518157127611</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>250-7272885-7567036</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:51:00+09:00</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>北大阪営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:13:05+00:00</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>518157127611</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-7272885-7567036", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>518157127600</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>250-7272885-7567036</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:51:00+09:00</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>北大阪営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>518157127600</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-7272885-7567036", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>518157127095</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>250-0741793-0439812</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:27:00+09:00</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>八幡営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-03-03T04:42:14+00:00</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>518157127095</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-0741793-0439812", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>518157127504</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>250-6747922-4619061</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-03-03T08:50:00+09:00</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>横浜鶴見営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:12:15+00:00</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>518157127504</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-6747922-4619061", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>518157127154</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>250-4394154-4275832</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:41:00+09:00</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>名古屋営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-03-03T03:12:18+00:00</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>518157127154</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-4394154-4275832", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>518157127375</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>250-4042695-6809413</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:11:00+09:00</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>荒川営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-03-03T03:42:15+00:00</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>518157127375</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-4042695-6809413", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>518157127110</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>250-8153573-0629443</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:19:00+09:00</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>小田原営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:42:10+00:00</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>518157127110</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-8153573-0629443", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>518157127121</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>249-9853683-1440666</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:26:00+09:00</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>静岡営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:42:11+00:00</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>518157127121</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-9853683-1440666", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>518157127935</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>250-8588162-8527809</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:33:00+09:00</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>鈴鹿営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:12:08+00:00</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>518157127935</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-8588162-8527809", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>518157127714</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>250-0935762-0354202</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:13:00+09:00</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>いわき営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:42:04+00:00</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>518157127714</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-0935762-0354202", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>518157127972</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>250-8962251-9398210</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:45:00+09:00</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>西埼玉営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-03-03T04:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>518157127972</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-8962251-9398210", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>518157127961</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>249-7651640-2001456</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:04:00+09:00</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>御所営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-03-03T03:42:06+00:00</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>518157127961</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-7651640-2001456", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>518157127983</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>250-8677854-5407821</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:53:00+09:00</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>岐阜営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-03-03T01:12:00+00:00</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>518157127983</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-8677854-5407821", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>05228742844301</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0031009968238</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:30:10+01:00</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Veenendaal, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:31:04+00:00</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>05228742844301</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009968238", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>05228742840818</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0032005561679</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-03-02T13:04:29+01:00</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Lummen, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-03-02T12:31:38+00:00</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>05228742840818</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005561679", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>518157126211</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>503-6933450-7752667</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:56:00+09:00</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>御所営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-03-03T02:32:10+00:00</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>518157126211</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-6933450-7752667", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01475240782282</t>
+          <t>UTV891040271</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0049010214437</t>
+          <t>0031009971763</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -522,44 +522,44 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-02-27T12:59:11+01:00</t>
+          <t>2026-03-03T16:08:08+01:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:25+00:00</t>
+          <t>2026-03-03T16:05:37+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>01475240782282</t>
+          <t>UTV891040271</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009971763", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01475240781789</t>
+          <t>UTV843312405</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -569,12 +569,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0049010214437</t>
+          <t>0031009973750</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,44 +585,44 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-02-27T12:59:11+01:00</t>
+          <t>2026-03-03T14:58:12+01:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:25+00:00</t>
+          <t>2026-03-03T16:05:28+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>01475240781789</t>
+          <t>UTV843312405</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009973750", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01475240782918</t>
+          <t>UTV789524873</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0049010214437</t>
+          <t>0031009973750</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -648,44 +648,44 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-02-27T12:59:11+01:00</t>
+          <t>2026-03-03T14:57:23+01:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:27+00:00</t>
+          <t>2026-03-03T16:05:28+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01475240782918</t>
+          <t>UTV789524873</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009973750", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01475240790578</t>
+          <t>UTV480312775</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B2BDS11345064</t>
+          <t>0031009968160</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -711,44 +711,44 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-03T13:19:35+01:00</t>
+          <t>2026-03-03T12:11:24+01:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Würzburg (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:21+00:00</t>
+          <t>2026-03-03T16:05:04+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>01475240790578</t>
+          <t>UTV480312775</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11345064", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009968160", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01475240790254</t>
+          <t>UTV924437683</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>0031009968403</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -774,44 +774,44 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T12:51:28+01:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:23+00:00</t>
+          <t>2026-03-03T16:05:00+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>01475240790254</t>
+          <t>UTV924437683</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0031009968403", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01475240790277</t>
+          <t>UTV545163780</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>0031009968403</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -837,44 +837,44 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T12:51:28+01:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:18+00:00</t>
+          <t>2026-03-03T16:05:00+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01475240790277</t>
+          <t>UTV545163780</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0031009968403", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01475240790255</t>
+          <t>00KNRRRV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>0031009973032</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -900,44 +900,44 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T15:39:03+01:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:17+00:00</t>
+          <t>2026-03-03T16:04:35+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>01475240790255</t>
+          <t>00KNRRRV</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0031009973032", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01475240790280</t>
+          <t>ZD1RIO18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>0049010246892</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -963,44 +963,44 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T09:36:55+01:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:16+00:00</t>
+          <t>2026-03-03T16:03:46+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>01475240790280</t>
+          <t>ZD1RIO18</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0049010246892", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01475240790279</t>
+          <t>ZD1RINXY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>cbn4wjx6gs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1026,44 +1026,44 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T09:44:39+01:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:16+00:00</t>
+          <t>2026-03-03T16:03:30+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>01475240790279</t>
+          <t>ZD1RINXY</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "cbn4wjx6gs", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01475240790278</t>
+          <t>YNQAF97V</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>B2BDS11273657</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1089,44 +1089,44 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T06:31:54+01:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:16+00:00</t>
+          <t>2026-03-03T16:03:25+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>01475240790278</t>
+          <t>YNQAF97V</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "B2BDS11273657", "sales_office_id": "4437"}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05228742845732</t>
+          <t>YNQAF9A3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>402-6214259-5084345</t>
+          <t>0045005253023</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1152,44 +1152,44 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-03T11:03:41+01:00</t>
+          <t>2026-03-03T11:18:40+01:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-03T11:23:14+00:00</t>
+          <t>2026-03-03T16:03:17+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>05228742845732</t>
+          <t>YNQAF9A3</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"external_order_id": "402-6214259-5084345", "sales_office_id": "4647"}</t>
+          <t>{"external_order_id": "0045005253023", "sales_office_id": "3017"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05228742846812</t>
+          <t>YNQAF99E</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0032005565675</t>
+          <t>0045005253082</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1215,44 +1215,44 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-03T11:44:18+01:00</t>
+          <t>2026-03-03T11:46:35+01:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-03T11:22:19+00:00</t>
+          <t>2026-03-03T16:03:15+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>05228742846812</t>
+          <t>YNQAF99E</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0045005253082", "sales_office_id": "3017"}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05228742846188</t>
+          <t>ZD1RINXZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0032005565675</t>
+          <t>0049010238785</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1278,44 +1278,44 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-03-03T11:44:18+01:00</t>
+          <t>2026-03-03T09:31:03+01:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-03T14:22:37+00:00</t>
+          <t>2026-03-03T16:01:29+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>05228742846188</t>
+          <t>ZD1RINXZ</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010238785", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05228742847138</t>
+          <t>YNQAF8UK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0032005565675</t>
+          <t>B2BDS11224002</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1341,44 +1341,44 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-03T11:44:18+01:00</t>
+          <t>2026-03-03T10:12:17+01:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-03-03T11:22:18+00:00</t>
+          <t>2026-03-03T16:01:19+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>05228742847138</t>
+          <t>YNQAF8UK</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11224002", "sales_office_id": "4437"}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05228742846050</t>
+          <t>ZD1RINUZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0032005564138</t>
+          <t>cbn4wg7vq3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1404,44 +1404,44 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-03-03T11:13:10+01:00</t>
+          <t>2026-03-03T12:30:27+01:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sint-Niklaas, BE, Belgium</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-03-03T14:22:23+00:00</t>
+          <t>2026-03-03T16:01:17+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>05228742846050</t>
+          <t>ZD1RINUZ</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05228742847174</t>
+          <t>ZD1RIN6L</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0032005564138</t>
+          <t>cbn4wg7vq3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1467,44 +1467,44 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-03T11:13:10+01:00</t>
+          <t>2026-03-03T12:30:27+01:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sint-Niklaas, BE, Belgium</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-03-03T14:22:24+00:00</t>
+          <t>2026-03-03T16:01:18+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>05228742847174</t>
+          <t>ZD1RIN6L</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UTV544822779</t>
+          <t>ZD1RINJ3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C0001H46LJ</t>
+          <t>cbn4wg7vq3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1530,44 +1530,44 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-03T10:58:07+01:00</t>
+          <t>2026-03-03T12:30:27+01:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-03-03T10:12:11+00:00</t>
+          <t>2026-03-03T16:01:16+00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>UTV544822779</t>
+          <t>ZD1RINJ3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>{"external_order_id": "C0001H46LJ", "sales_office_id": "4002"}</t>
+          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UTV830382349</t>
+          <t>01475240788588</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0031009972930</t>
+          <t>1116346471-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1593,44 +1593,44 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-03T11:08:50+01:00</t>
+          <t>2026-03-03T11:43:56+01:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Geretsried - Gelting (DE), Germany</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-03T10:11:28+00:00</t>
+          <t>2026-03-03T15:59:25+00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>UTV830382349</t>
+          <t>01475240788588</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009972930", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "1116346471-01", "sales_office_id": "4677"}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UTV591963001</t>
+          <t>01475240787644</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0031009972485</t>
+          <t>1116346471-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1656,44 +1656,44 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-03-03T13:28:06+01:00</t>
+          <t>2026-03-03T11:43:56+01:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Geretsried - Gelting (DE), Germany</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-03-03T13:11:09+00:00</t>
+          <t>2026-03-03T15:59:23+00:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>UTV591963001</t>
+          <t>01475240787644</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009972485", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "1116346471-01", "sales_office_id": "4677"}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01475240790240</t>
+          <t>05228742846341</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>cbn4wkbm99</t>
+          <t>0032005564933</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1719,25 +1719,2167 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
+          <t>2026-03-03T16:42:34+01:00</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sint-Niklaas, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-03-03T15:57:43+00:00</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>05228742846341</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005564933", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00KNRRNP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>gls-netherlands-api</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GLS Netherlands</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0031009975797</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-03-03T13:15:15+01:00</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:39:25+00:00</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>00KNRRNP</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009975797", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00KNRRNQ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>gls-netherlands-api</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GLS Netherlands</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0031009975797</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-03-03T13:15:15+01:00</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:39:25+00:00</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>00KNRRNQ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009975797", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ZD1RINHK</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0049010233172</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:02:25+01:00</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:38:52+00:00</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>ZD1RINHK</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010233172", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ZD1RIOPD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0049010244426</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:37:39+01:00</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:37:27+00:00</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>ZD1RIOPD</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ZD1RIOPC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0049010244426</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:37:39+01:00</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:37:26+00:00</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ZD1RIOPC</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ZD1RIOPA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0049010244426</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:37:39+01:00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:37:26+00:00</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ZD1RIOPA</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ZD1RINOK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0049010233654</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:13:09+01:00</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:37:20+00:00</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>ZD1RINOK</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010233654", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ZD1RINQ1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0049010233654</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:13:09+01:00</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:37:20+00:00</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ZD1RINQ1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010233654", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>01475240782282</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0049010214437</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-02-27T12:59:11+01:00</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Essen (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:37:25+00:00</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>01475240782282</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>01475240782918</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0049010214437</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-02-27T12:59:11+01:00</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Essen (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:37:27+00:00</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>01475240782918</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>01475240781789</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0049010214437</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-02-27T12:59:11+01:00</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Essen (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:37:25+00:00</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>01475240781789</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>01475240790578</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>B2BDS11345064</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-03-03T13:19:35+01:00</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Würzburg (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:37:21+00:00</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>01475240790578</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "B2BDS11345064", "sales_office_id": "4436"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>01475240790254</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1024905387-A</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:19:39+01:00</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Walsrode (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:37:23+00:00</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>01475240790254</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>01475240790255</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1024905387-A</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:19:39+01:00</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Walsrode (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:37:17+00:00</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>01475240790255</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>01475240790277</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1024905387-A</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:19:39+01:00</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Walsrode (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:37:18+00:00</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>01475240790277</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>01475240790280</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1024905387-A</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:19:39+01:00</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Walsrode (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:37:16+00:00</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>01475240790280</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>01475240790279</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1024905387-A</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:19:39+01:00</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Walsrode (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:37:16+00:00</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>01475240790279</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>01475240790278</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1024905387-A</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:19:39+01:00</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Walsrode (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:37:16+00:00</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>01475240790278</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>05228742844449</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0033005727379</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:42:42+01:00</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>La Crau, FR, France</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:35:13+00:00</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>05228742844449</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0033005727379", "sales_office_id": "0302"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>05228742845732</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>402-6214259-5084345</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4647</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:03:41+01:00</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Veenendaal, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:23:14+00:00</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>05228742845732</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "402-6214259-5084345", "sales_office_id": "4647"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>05228742846812</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0032005565675</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:44:18+01:00</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Courcelles, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:22:19+00:00</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>05228742846812</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>05228742846188</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0032005565675</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:44:18+01:00</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Courcelles, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:22:37+00:00</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>05228742846188</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>05228742847138</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0032005565675</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:44:18+01:00</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Courcelles, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:22:18+00:00</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>05228742847138</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>05228742846050</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0032005564138</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:13:10+01:00</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sint-Niklaas, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:22:23+00:00</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>05228742846050</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>05228742847174</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0032005564138</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:13:10+01:00</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sint-Niklaas, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:22:24+00:00</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>05228742847174</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>UTV544822779</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>C0001H46LJ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:58:07+01:00</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:12:11+00:00</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>UTV544822779</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "C0001H46LJ", "sales_office_id": "4002"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>UTV013236806</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0031009973241</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:21:49+01:00</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:12:11+00:00</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>UTV013236806</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009973241", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>UTV830382349</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0031009972930</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:08:50+01:00</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:11:28+00:00</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>UTV830382349</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009972930", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>UTV050109541</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0031009972803</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-03-03T15:23:08+01:00</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>UTV050109541</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009972803", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>UTV591963001</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0031009972485</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-03-03T13:28:06+01:00</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-03-03T13:11:09+00:00</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>UTV591963001</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009972485", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>UTV765135406</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0031009973435</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:52:36+01:00</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:10:58+00:00</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>UTV765135406</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009973435", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>UTV206686788</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0031009973435</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:52:44+01:00</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:10:58+00:00</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>UTV206686788</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009973435", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>UTV592496096</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0031009967821</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:21:53+01:00</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:10:58+00:00</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>UTV592496096</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009967821", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>01475240790240</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>cbn4wkbm99</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>2026-03-03T09:32:51+01:00</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Vechta (DE), Germany</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>2026-03-03T09:40:36+00:00</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>01475240790240</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>{"external_order_id": "cbn4wkbm99", "sales_office_id": "4316"}</t>
         </is>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UTV891040271</t>
+          <t>889198934549</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0031009971763</t>
+          <t>PO-211-14108184515190485</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -522,44 +522,44 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-03T16:08:08+01:00</t>
+          <t>2026-03-03T13:21:39-05:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Palmerton, PA, 18071, US, United States</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:37+00:00</t>
+          <t>2026-03-03T19:47:15+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>UTV891040271</t>
+          <t>889198934549</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009971763", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-211-14108184515190485", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UTV843312405</t>
+          <t>889202241879</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -569,12 +569,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0031009973750</t>
+          <t>PO-211-14319247032951275</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,44 +585,44 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-03T14:58:12+01:00</t>
+          <t>2026-03-03T11:59:39-05:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Buffalo, NY, 14207, US, United States</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:28+00:00</t>
+          <t>2026-03-03T19:47:16+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>UTV843312405</t>
+          <t>889202241879</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973750", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-211-14319247032951275", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UTV789524873</t>
+          <t>889203009432</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0031009973750</t>
+          <t>200014573095565</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -648,44 +648,44 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-03-03T14:57:23+01:00</t>
+          <t>2026-03-03T12:27:06-05:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Plainfield, NJ, 07063, US, United States</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:28+00:00</t>
+          <t>2026-03-03T19:47:13+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>UTV789524873</t>
+          <t>889203009432</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973750", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "200014573095565", "sales_office_id": "4260"}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UTV480312775</t>
+          <t>889209388370</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0031009968160</t>
+          <t>B2BDS11382021</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -711,44 +711,44 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-03T12:11:24+01:00</t>
+          <t>2026-03-03T13:21:09-05:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Upper Marlboro, MD, 20772, US, United States</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:04+00:00</t>
+          <t>2026-03-03T19:47:12+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>UTV480312775</t>
+          <t>889209388370</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009968160", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11382021", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UTV924437683</t>
+          <t>889202240703</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0031009968403</t>
+          <t>PO-211-14319247032951275</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -774,44 +774,44 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-03T12:51:28+01:00</t>
+          <t>2026-03-03T11:59:39-05:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Buffalo, NY, 14207, US, United States</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:00+00:00</t>
+          <t>2026-03-03T19:47:13+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>UTV924437683</t>
+          <t>889202240703</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009968403", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-211-14319247032951275", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UTV545163780</t>
+          <t>889202237464</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0031009968403</t>
+          <t>PO-211-14319247032951275</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -837,44 +837,44 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-03T12:51:28+01:00</t>
+          <t>2026-03-03T11:59:39-05:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Buffalo, NY, 14207, US, United States</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:00+00:00</t>
+          <t>2026-03-03T19:47:12+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UTV545163780</t>
+          <t>889202237464</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009968403", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-211-14319247032951275", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00KNRRRV</t>
+          <t>889214689915</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0031009973032</t>
+          <t>CS641101802</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -900,44 +900,44 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-03T15:39:03+01:00</t>
+          <t>2026-03-03T10:22:10-05:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Easton, PA, 18040, US, United States</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-03T16:04:35+00:00</t>
+          <t>2026-03-03T19:47:06+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>00KNRRRV</t>
+          <t>889214689915</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973032", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "CS641101802", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ZD1RIO18</t>
+          <t>889210750316</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0049010246892</t>
+          <t>102003306324304-8634765723</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -963,44 +963,44 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-03T09:36:55+01:00</t>
+          <t>2026-03-03T10:31:39-05:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Clarence, NY, 14031, US, United States</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-03T16:03:46+00:00</t>
+          <t>2026-03-03T19:47:04+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ZD1RIO18</t>
+          <t>889210750316</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010246892", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "102003306324304-8634765723", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZD1RINXY</t>
+          <t>889214692863</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>cbn4wjx6gs</t>
+          <t>CS641101802</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1026,44 +1026,44 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-03T09:44:39+01:00</t>
+          <t>2026-03-03T10:22:10-05:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Easton, PA, 18040, US, United States</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-03T16:03:30+00:00</t>
+          <t>2026-03-03T19:47:05+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ZD1RINXY</t>
+          <t>889214692863</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wjx6gs", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "CS641101802", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>YNQAF97V</t>
+          <t>889219210202</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B2BDS11273657</t>
+          <t>912003162972935-8634780397</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1089,44 +1089,44 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-03T06:31:54+01:00</t>
+          <t>2026-03-03T15:32:38-05:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DK, Denmark</t>
+          <t>Philadelphia, PA, 19111, US, United States</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-03T16:03:25+00:00</t>
+          <t>2026-03-03T20:47:09+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>YNQAF97V</t>
+          <t>889219210202</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11273657", "sales_office_id": "4437"}</t>
+          <t>{"external_order_id": "912003162972935-8634780397", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>YNQAF9A3</t>
+          <t>889198428138</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0045005253023</t>
+          <t>912003162972935-8634780397</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1152,44 +1152,44 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-03T11:18:40+01:00</t>
+          <t>2026-03-03T15:32:38-05:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>DK, Denmark</t>
+          <t>Philadelphia, PA, 19111, US, United States</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-03T16:03:17+00:00</t>
+          <t>2026-03-03T20:47:06+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>YNQAF9A3</t>
+          <t>889198428138</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0045005253023", "sales_office_id": "3017"}</t>
+          <t>{"external_order_id": "912003162972935-8634780397", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>YNQAF99E</t>
+          <t>889211139848</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0045005253082</t>
+          <t>102003306324304-8634765723</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1215,44 +1215,44 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-03T11:46:35+01:00</t>
+          <t>2026-03-03T10:31:39-05:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>DK, Denmark</t>
+          <t>Clarence, NY, 14031, US, United States</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-03T16:03:15+00:00</t>
+          <t>2026-03-03T19:47:02+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>YNQAF99E</t>
+          <t>889211139848</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0045005253082", "sales_office_id": "3017"}</t>
+          <t>{"external_order_id": "102003306324304-8634765723", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ZD1RINXZ</t>
+          <t>889220116131</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0049010238785</t>
+          <t>PO-211-14202330081910818</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1278,44 +1278,44 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-03-03T09:31:03+01:00</t>
+          <t>2026-03-03T10:08:55-05:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Woodbridge, VA, 22192, US, United States</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-03T16:01:29+00:00</t>
+          <t>2026-03-03T19:47:00+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ZD1RINXZ</t>
+          <t>889220116131</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010238785", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "PO-211-14202330081910818", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>YNQAF8UK</t>
+          <t>889211140462</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B2BDS11224002</t>
+          <t>102003306324304-8634765723</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1341,44 +1341,44 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-03T10:12:17+01:00</t>
+          <t>2026-03-03T10:31:39-05:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>DK, Denmark</t>
+          <t>Clarence, NY, 14031, US, United States</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-03-03T16:01:19+00:00</t>
+          <t>2026-03-03T19:46:59+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>YNQAF8UK</t>
+          <t>889211140462</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11224002", "sales_office_id": "4437"}</t>
+          <t>{"external_order_id": "102003306324304-8634765723", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ZD1RINUZ</t>
+          <t>889208514573</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>cbn4wg7vq3</t>
+          <t>912003307917567-8615578363</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1404,44 +1404,44 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-03-03T12:30:27+01:00</t>
+          <t>2026-03-03T11:20:34-05:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>New York, NY, 10280, US, United States</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-03-03T16:01:17+00:00</t>
+          <t>2026-03-03T19:47:00+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ZD1RINUZ</t>
+          <t>889208514573</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "912003307917567-8615578363", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ZD1RIN6L</t>
+          <t>889215570082</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>cbn4wg7vq3</t>
+          <t>912003307917567-8615578363</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1467,44 +1467,44 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-03T12:30:27+01:00</t>
+          <t>2026-03-03T11:07:29-05:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>New York, NY, 10280, US, United States</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-03-03T16:01:18+00:00</t>
+          <t>2026-03-03T19:46:58+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ZD1RIN6L</t>
+          <t>889215570082</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "912003307917567-8615578363", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ZD1RINJ3</t>
+          <t>UTV891040271</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>cbn4wg7vq3</t>
+          <t>0031009971763</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1530,44 +1530,44 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-03T12:30:27+01:00</t>
+          <t>2026-03-03T16:08:08+01:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-03-03T16:01:16+00:00</t>
+          <t>2026-03-03T16:05:37+00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ZD1RINJ3</t>
+          <t>UTV891040271</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0031009971763", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01475240788588</t>
+          <t>UTV843312405</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1116346471-01</t>
+          <t>0031009973750</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1593,44 +1593,44 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-03T11:43:56+01:00</t>
+          <t>2026-03-03T14:58:12+01:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Geretsried - Gelting (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-03T15:59:25+00:00</t>
+          <t>2026-03-03T16:05:28+00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>01475240788588</t>
+          <t>UTV843312405</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1116346471-01", "sales_office_id": "4677"}</t>
+          <t>{"external_order_id": "0031009973750", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01475240787644</t>
+          <t>UTV789524873</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1116346471-01</t>
+          <t>0031009973750</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1656,44 +1656,44 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-03-03T11:43:56+01:00</t>
+          <t>2026-03-03T14:57:23+01:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Geretsried - Gelting (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-03-03T15:59:23+00:00</t>
+          <t>2026-03-03T16:05:28+00:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>01475240787644</t>
+          <t>UTV789524873</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1116346471-01", "sales_office_id": "4677"}</t>
+          <t>{"external_order_id": "0031009973750", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05228742846341</t>
+          <t>UTV480312775</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0032005564933</t>
+          <t>0031009968160</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1719,44 +1719,44 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-03-03T16:42:34+01:00</t>
+          <t>2026-03-03T12:11:24+01:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sint-Niklaas, BE, Belgium</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-03-03T15:57:43+00:00</t>
+          <t>2026-03-03T16:05:04+00:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>05228742846341</t>
+          <t>UTV480312775</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005564933", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009968160", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00KNRRNP</t>
+          <t>UTV924437683</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0031009975797</t>
+          <t>0031009968403</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1782,44 +1782,44 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-03T13:15:15+01:00</t>
+          <t>2026-03-03T12:51:28+01:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-03-03T14:39:25+00:00</t>
+          <t>2026-03-03T16:05:00+00:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>00KNRRNP</t>
+          <t>UTV924437683</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009975797", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009968403", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00KNRRNQ</t>
+          <t>UTV545163780</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0031009975797</t>
+          <t>0031009968403</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1845,44 +1845,44 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-03-03T13:15:15+01:00</t>
+          <t>2026-03-03T12:51:28+01:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-03-03T14:39:25+00:00</t>
+          <t>2026-03-03T16:05:00+00:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>00KNRRNQ</t>
+          <t>UTV545163780</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009975797", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009968403", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZD1RINHK</t>
+          <t>UTV991396507</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0049010233172</t>
+          <t>0031009968645</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1908,44 +1908,44 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-03-03T11:02:25+01:00</t>
+          <t>2026-03-03T19:24:51+01:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-03-03T14:38:52+00:00</t>
+          <t>2026-03-03T19:05:02+00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ZD1RINHK</t>
+          <t>UTV991396507</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010233172", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009968645", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZD1RIOPD</t>
+          <t>00KNRRRV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0049010244426</t>
+          <t>0031009973032</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1971,34 +1971,34 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:39+01:00</t>
+          <t>2026-03-03T15:39:03+01:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:27+00:00</t>
+          <t>2026-03-03T16:04:35+00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ZD1RIOPD</t>
+          <t>00KNRRRV</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009973032", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZD1RIOPC</t>
+          <t>ZD1RIO18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0049010244426</t>
+          <t>0049010246892</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2034,7 +2034,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:39+01:00</t>
+          <t>2026-03-03T09:36:55+01:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2044,24 +2044,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:26+00:00</t>
+          <t>2026-03-03T16:03:46+00:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ZD1RIOPC</t>
+          <t>ZD1RIO18</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010246892", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ZD1RIOPA</t>
+          <t>ZD1RINXY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0049010244426</t>
+          <t>cbn4wjx6gs</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2097,7 +2097,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:39+01:00</t>
+          <t>2026-03-03T09:44:39+01:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:26+00:00</t>
+          <t>2026-03-03T20:03:33+00:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ZD1RIOPA</t>
+          <t>ZD1RINXY</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "cbn4wjx6gs", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ZD1RINOK</t>
+          <t>YNQAF97V</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0049010233654</t>
+          <t>B2BDS11273657</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2160,34 +2160,34 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-03-03T10:13:09+01:00</t>
+          <t>2026-03-03T06:31:54+01:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:20+00:00</t>
+          <t>2026-03-03T16:03:25+00:00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ZD1RINOK</t>
+          <t>YNQAF97V</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010233654", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11273657", "sales_office_id": "4437"}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ZD1RINQ1</t>
+          <t>YNQAF9A3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0049010233654</t>
+          <t>0045005253023</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2223,44 +2223,44 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-03-03T10:13:09+01:00</t>
+          <t>2026-03-03T11:18:40+01:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:20+00:00</t>
+          <t>2026-03-03T16:03:17+00:00</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ZD1RINQ1</t>
+          <t>YNQAF9A3</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010233654", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0045005253023", "sales_office_id": "3017"}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>01475240782282</t>
+          <t>YNQAF99E</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0049010214437</t>
+          <t>0045005253082</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2286,44 +2286,44 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-02-27T12:59:11+01:00</t>
+          <t>2026-03-03T11:46:35+01:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:25+00:00</t>
+          <t>2026-03-03T16:03:15+00:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>01475240782282</t>
+          <t>YNQAF99E</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0045005253082", "sales_office_id": "3017"}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>01475240782918</t>
+          <t>ZD1RINXZ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0049010214437</t>
+          <t>0049010238785</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2349,44 +2349,44 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-02-27T12:59:11+01:00</t>
+          <t>2026-03-03T09:31:03+01:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:27+00:00</t>
+          <t>2026-03-03T16:01:29+00:00</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>01475240782918</t>
+          <t>ZD1RINXZ</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010238785", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>01475240781789</t>
+          <t>YNQAF8UK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0049010214437</t>
+          <t>B2BDS11224002</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2412,44 +2412,44 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-02-27T12:59:11+01:00</t>
+          <t>2026-03-03T10:12:17+01:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:25+00:00</t>
+          <t>2026-03-03T16:01:19+00:00</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>01475240781789</t>
+          <t>YNQAF8UK</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11224002", "sales_office_id": "4437"}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>01475240790578</t>
+          <t>ZD1RINUZ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B2BDS11345064</t>
+          <t>cbn4wg7vq3</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2475,44 +2475,44 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-03T13:19:35+01:00</t>
+          <t>2026-03-03T12:30:27+01:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Würzburg (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:21+00:00</t>
+          <t>2026-03-03T16:01:17+00:00</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>01475240790578</t>
+          <t>ZD1RINUZ</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11345064", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>01475240790254</t>
+          <t>ZD1RIN6L</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>cbn4wg7vq3</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2538,44 +2538,44 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T12:30:27+01:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:23+00:00</t>
+          <t>2026-03-03T16:01:18+00:00</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>01475240790254</t>
+          <t>ZD1RIN6L</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>01475240790255</t>
+          <t>ZD1RINJ3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>cbn4wg7vq3</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,34 +2601,34 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T12:30:27+01:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:17+00:00</t>
+          <t>2026-03-03T16:01:16+00:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>01475240790255</t>
+          <t>ZD1RINJ3</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>01475240790277</t>
+          <t>01475240788588</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>1116346471-01</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2664,34 +2664,34 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T11:43:56+01:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>Geretsried - Gelting (DE), Germany</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:18+00:00</t>
+          <t>2026-03-03T15:59:25+00:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>01475240790277</t>
+          <t>01475240788588</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "1116346471-01", "sales_office_id": "4677"}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01475240790280</t>
+          <t>01475240787644</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>1116346471-01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2727,44 +2727,44 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T11:43:56+01:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>Geretsried - Gelting (DE), Germany</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:16+00:00</t>
+          <t>2026-03-03T15:59:23+00:00</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>01475240790280</t>
+          <t>01475240787644</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "1116346471-01", "sales_office_id": "4677"}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>01475240790279</t>
+          <t>05228742846342</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>0032005564933</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2790,44 +2790,44 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T16:42:34+01:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>Sint-Niklaas, BE, Belgium</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:16+00:00</t>
+          <t>2026-03-03T18:58:02+00:00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>01475240790279</t>
+          <t>05228742846342</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0032005564933", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>01475240790278</t>
+          <t>05228742846341</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>0032005564933</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2853,44 +2853,44 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T16:42:34+01:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>Sint-Niklaas, BE, Belgium</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:16+00:00</t>
+          <t>2026-03-03T15:57:43+00:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>01475240790278</t>
+          <t>05228742846341</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0032005564933", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05228742844449</t>
+          <t>00KNRRNP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0033005727379</t>
+          <t>0031009975797</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0302</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2916,44 +2916,44 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-03T12:42:42+01:00</t>
+          <t>2026-03-03T13:15:15+01:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>La Crau, FR, France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-03-03T14:35:13+00:00</t>
+          <t>2026-03-03T14:39:25+00:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>05228742844449</t>
+          <t>00KNRRNP</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005727379", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "0031009975797", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05228742845732</t>
+          <t>00KNRRF6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>402-6214259-5084345</t>
+          <t>0031009969354</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2979,44 +2979,44 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-03T11:03:41+01:00</t>
+          <t>2026-03-03T19:39:59+01:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-03-03T11:23:14+00:00</t>
+          <t>2026-03-03T19:09:49+00:00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>05228742845732</t>
+          <t>00KNRRF6</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{"external_order_id": "402-6214259-5084345", "sales_office_id": "4647"}</t>
+          <t>{"external_order_id": "0031009969354", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05228742846812</t>
+          <t>00KNRRNQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0032005565675</t>
+          <t>0031009975797</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3042,44 +3042,44 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-03T11:44:18+01:00</t>
+          <t>2026-03-03T13:15:15+01:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-03-03T11:22:19+00:00</t>
+          <t>2026-03-03T14:39:25+00:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>05228742846812</t>
+          <t>00KNRRNQ</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009975797", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05228742846188</t>
+          <t>ZD1RINHK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0032005565675</t>
+          <t>0049010233172</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3105,44 +3105,44 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-03T11:44:18+01:00</t>
+          <t>2026-03-03T11:02:25+01:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-03T14:22:37+00:00</t>
+          <t>2026-03-03T18:38:53+00:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>05228742846188</t>
+          <t>ZD1RINHK</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010233172", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05228742847138</t>
+          <t>ZD1RIOPD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0032005565675</t>
+          <t>0049010244426</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3168,44 +3168,44 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-03T11:44:18+01:00</t>
+          <t>2026-03-03T14:37:39+01:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-03T11:22:18+00:00</t>
+          <t>2026-03-03T14:37:27+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>05228742847138</t>
+          <t>ZD1RIOPD</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05228742846050</t>
+          <t>ZD1RIOPC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3215,12 +3215,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0032005564138</t>
+          <t>0049010244426</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3231,44 +3231,44 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-03T11:13:10+01:00</t>
+          <t>2026-03-03T14:37:39+01:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sint-Niklaas, BE, Belgium</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-03-03T14:22:23+00:00</t>
+          <t>2026-03-03T14:37:26+00:00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>05228742846050</t>
+          <t>ZD1RIOPC</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>05228742847174</t>
+          <t>ZD1RIOPA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0032005564138</t>
+          <t>0049010244426</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3294,44 +3294,44 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-03T11:13:10+01:00</t>
+          <t>2026-03-03T14:37:39+01:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Sint-Niklaas, BE, Belgium</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-03-03T14:22:24+00:00</t>
+          <t>2026-03-03T14:37:26+00:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>05228742847174</t>
+          <t>ZD1RIOPA</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UTV544822779</t>
+          <t>ZD1RINQ1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>C0001H46LJ</t>
+          <t>0049010233654</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3357,44 +3357,44 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-03T10:58:07+01:00</t>
+          <t>2026-03-03T10:13:09+01:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-03T10:12:11+00:00</t>
+          <t>2026-03-03T14:37:20+00:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>UTV544822779</t>
+          <t>ZD1RINQ1</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{"external_order_id": "C0001H46LJ", "sales_office_id": "4002"}</t>
+          <t>{"external_order_id": "0049010233654", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UTV013236806</t>
+          <t>ZD1RINOK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0031009973241</t>
+          <t>0049010233654</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3420,44 +3420,44 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-03T14:21:49+01:00</t>
+          <t>2026-03-03T10:13:09+01:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-03-03T16:12:11+00:00</t>
+          <t>2026-03-03T14:37:20+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>UTV013236806</t>
+          <t>ZD1RINOK</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973241", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010233654", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>UTV830382349</t>
+          <t>01475240782282</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0031009972930</t>
+          <t>0049010214437</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3483,44 +3483,44 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-03T11:08:50+01:00</t>
+          <t>2026-02-27T12:59:11+01:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Essen (DE), Germany</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-03-03T10:11:28+00:00</t>
+          <t>2026-03-03T11:37:25+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>UTV830382349</t>
+          <t>01475240782282</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009972930", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>UTV050109541</t>
+          <t>01475240782918</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0031009972803</t>
+          <t>0049010214437</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3546,44 +3546,44 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-03-03T15:23:08+01:00</t>
+          <t>2026-02-27T12:59:11+01:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Essen (DE), Germany</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-03-03T16:11:29+00:00</t>
+          <t>2026-03-03T12:37:27+00:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>UTV050109541</t>
+          <t>01475240782918</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009972803", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>UTV591963001</t>
+          <t>01475240781789</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0031009972485</t>
+          <t>0049010214437</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3609,44 +3609,44 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-03-03T13:28:06+01:00</t>
+          <t>2026-02-27T12:59:11+01:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Essen (DE), Germany</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-03-03T13:11:09+00:00</t>
+          <t>2026-03-03T11:37:25+00:00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>UTV591963001</t>
+          <t>01475240781789</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009972485", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>UTV765135406</t>
+          <t>01475240790578</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0031009973435</t>
+          <t>B2BDS11345064</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3672,44 +3672,44 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-03T14:52:36+01:00</t>
+          <t>2026-03-03T13:19:35+01:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Würzburg (DE), Germany</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-03-03T16:10:58+00:00</t>
+          <t>2026-03-03T12:37:21+00:00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>UTV765135406</t>
+          <t>01475240790578</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973435", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11345064", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>UTV206686788</t>
+          <t>01475240790254</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0031009973435</t>
+          <t>1024905387-A</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3735,44 +3735,44 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-03T14:52:44+01:00</t>
+          <t>2026-03-03T12:19:39+01:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Walsrode (DE), Germany</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-03T16:10:58+00:00</t>
+          <t>2026-03-03T12:37:23+00:00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>UTV206686788</t>
+          <t>01475240790254</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973435", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>UTV592496096</t>
+          <t>01475240790277</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0031009967821</t>
+          <t>1024905387-A</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3798,34 +3798,34 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-03T14:21:53+01:00</t>
+          <t>2026-03-03T12:19:39+01:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Walsrode (DE), Germany</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-03T16:10:58+00:00</t>
+          <t>2026-03-03T11:37:18+00:00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>UTV592496096</t>
+          <t>01475240790277</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009967821", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>01475240790240</t>
+          <t>01475240790255</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>cbn4wkbm99</t>
+          <t>1024905387-A</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3861,25 +3861,1348 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
+          <t>2026-03-03T12:19:39+01:00</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Walsrode (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:37:17+00:00</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>01475240790255</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>01475240790280</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1024905387-A</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:19:39+01:00</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Walsrode (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:37:16+00:00</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>01475240790280</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>01475240790279</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1024905387-A</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:19:39+01:00</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Walsrode (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:37:16+00:00</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>01475240790279</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>01475240790278</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1024905387-A</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:19:39+01:00</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Walsrode (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:37:16+00:00</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>01475240790278</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>05228742844449</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0033005727379</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-03-03T12:42:42+01:00</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>La Crau, FR, France</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:35:18+00:00</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>05228742844449</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0033005727379", "sales_office_id": "0302"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>05228742845732</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>402-6214259-5084345</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>4647</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:03:41+01:00</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Veenendaal, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:23:14+00:00</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>05228742845732</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "402-6214259-5084345", "sales_office_id": "4647"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>05228742846812</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0032005565675</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:44:18+01:00</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Courcelles, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:22:19+00:00</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>05228742846812</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>05228742846188</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0032005565675</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:44:18+01:00</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Courcelles, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:22:37+00:00</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>05228742846188</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>05228742847138</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0032005565675</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:44:18+01:00</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Courcelles, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:22:18+00:00</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>05228742847138</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>05228742844439</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0031009969234</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-03-03T19:41:07+01:00</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Veenendaal, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-03-03T18:52:36+00:00</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>05228742844439</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009969234", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>05228742846050</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0032005564138</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:13:10+01:00</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sint-Niklaas, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:22:23+00:00</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>05228742846050</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>05228742847174</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0032005564138</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:13:10+01:00</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sint-Niklaas, BE, Belgium</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:22:24+00:00</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>05228742847174</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UTV544822779</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>C0001H46LJ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:58:07+01:00</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:12:11+00:00</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>UTV544822779</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "C0001H46LJ", "sales_office_id": "4002"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UTV013236806</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0031009973241</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:21:49+01:00</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:12:11+00:00</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>UTV013236806</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009973241", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>UTV050109541</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0031009972803</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-03-03T15:23:08+01:00</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>UTV050109541</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009972803", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>UTV830382349</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0031009972930</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-03-03T11:08:50+01:00</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-03-03T10:11:28+00:00</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>UTV830382349</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009972930", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>UTV282537285</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0031009965250</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-03-03T19:40:26+01:00</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-03-03T19:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>UTV282537285</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009965250", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>UTV591963001</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0031009972485</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-03-03T13:28:06+01:00</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-03-03T13:11:09+00:00</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>UTV591963001</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009972485", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>UTV765135406</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0031009973435</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:52:36+01:00</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:10:58+00:00</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>UTV765135406</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009973435", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>UTV206686788</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0031009973435</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:52:44+01:00</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:10:58+00:00</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>UTV206686788</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009973435", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>UTV592496096</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0031009967821</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:21:53+01:00</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-03-03T20:10:58+00:00</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>UTV592496096</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009967821", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>01475240790240</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>cbn4wkbm99</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
           <t>2026-03-03T09:32:51+01:00</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Vechta (DE), Germany</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>2026-03-03T09:40:36+00:00</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>01475240790240</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>{"external_order_id": "cbn4wkbm99", "sales_office_id": "4316"}</t>
         </is>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>889198934549</t>
+          <t>889202241879</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PO-211-14108184515190485</t>
+          <t>PO-211-14319247032951275</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -522,34 +522,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-03T13:21:39-05:00</t>
+          <t>2026-03-03T11:59:39-05:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Palmerton, PA, 18071, US, United States</t>
+          <t>Buffalo, NY, 14207, US, United States</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:15+00:00</t>
+          <t>2026-03-03T23:47:17+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>889198934549</t>
+          <t>889202241879</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-14108184515190485", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "PO-211-14319247032951275", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>889202241879</t>
+          <t>889198934549</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PO-211-14319247032951275</t>
+          <t>PO-211-14108184515190485</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -585,27 +585,27 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-03T11:59:39-05:00</t>
+          <t>2026-03-03T13:21:39-05:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Buffalo, NY, 14207, US, United States</t>
+          <t>Palmerton, PA, 18071, US, United States</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:16+00:00</t>
+          <t>2026-03-03T23:47:20+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>889202241879</t>
+          <t>889198934549</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-14319247032951275", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "PO-211-14108184515190485", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:13+00:00</t>
+          <t>2026-03-03T23:47:15+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:12+00:00</t>
+          <t>2026-03-03T23:47:13+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:13+00:00</t>
+          <t>2026-03-03T23:47:15+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:12+00:00</t>
+          <t>2026-03-03T23:47:15+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>889214689915</t>
+          <t>889214392096</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS641101802</t>
+          <t>912003162972935-8634780397</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -900,34 +900,34 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-03T10:22:10-05:00</t>
+          <t>2026-03-03T15:32:38-05:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Easton, PA, 18040, US, United States</t>
+          <t>Philadelphia, PA, 19111, US, United States</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:06+00:00</t>
+          <t>2026-03-04T02:47:13+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>889214689915</t>
+          <t>889214392096</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641101802", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "912003162972935-8634780397", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>889210750316</t>
+          <t>889214689915</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>102003306324304-8634765723</t>
+          <t>CS641101802</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -963,34 +963,34 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-03T10:31:39-05:00</t>
+          <t>2026-03-03T10:22:10-05:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Clarence, NY, 14031, US, United States</t>
+          <t>Easton, PA, 18040, US, United States</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:04+00:00</t>
+          <t>2026-03-03T23:47:08+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>889210750316</t>
+          <t>889214689915</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"external_order_id": "102003306324304-8634765723", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "CS641101802", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>889214692863</t>
+          <t>889219210202</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS641101802</t>
+          <t>912003162972935-8634780397</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1026,34 +1026,34 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-03T10:22:10-05:00</t>
+          <t>2026-03-03T15:32:38-05:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Easton, PA, 18040, US, United States</t>
+          <t>Philadelphia, PA, 19111, US, United States</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:05+00:00</t>
+          <t>2026-03-03T20:47:09+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>889214692863</t>
+          <t>889219210202</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641101802", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "912003162972935-8634780397", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>889219210202</t>
+          <t>889214692863</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>912003162972935-8634780397</t>
+          <t>CS641101802</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1089,34 +1089,34 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-03T15:32:38-05:00</t>
+          <t>2026-03-03T10:22:10-05:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, 19111, US, United States</t>
+          <t>Easton, PA, 18040, US, United States</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-03T20:47:09+00:00</t>
+          <t>2026-03-03T23:47:06+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>889219210202</t>
+          <t>889214692863</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"external_order_id": "912003162972935-8634780397", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "CS641101802", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>889198428138</t>
+          <t>889210750316</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>912003162972935-8634780397</t>
+          <t>102003306324304-8634765723</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1152,34 +1152,34 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-03T15:32:38-05:00</t>
+          <t>2026-03-03T10:31:39-05:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, 19111, US, United States</t>
+          <t>Clarence, NY, 14031, US, United States</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-03T20:47:06+00:00</t>
+          <t>2026-03-03T23:47:06+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>889198428138</t>
+          <t>889210750316</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"external_order_id": "912003162972935-8634780397", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "102003306324304-8634765723", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>889211139848</t>
+          <t>889214391402</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>102003306324304-8634765723</t>
+          <t>902003307904501-8615577028</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1215,34 +1215,34 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-03T10:31:39-05:00</t>
+          <t>2026-03-03T17:49:51-05:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Clarence, NY, 14031, US, United States</t>
+          <t>Ephrata, PA, 17522, US, United States</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:02+00:00</t>
+          <t>2026-03-03T23:47:13+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>889211139848</t>
+          <t>889214391402</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"external_order_id": "102003306324304-8634765723", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "902003307904501-8615577028", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>889220116131</t>
+          <t>889198428138</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PO-211-14202330081910818</t>
+          <t>912003162972935-8634780397</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1278,34 +1278,34 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-03-03T10:08:55-05:00</t>
+          <t>2026-03-03T15:32:38-05:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Woodbridge, VA, 22192, US, United States</t>
+          <t>Philadelphia, PA, 19111, US, United States</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:00+00:00</t>
+          <t>2026-03-03T20:47:06+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>889220116131</t>
+          <t>889198428138</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-14202330081910818", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "912003162972935-8634780397", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>889211140462</t>
+          <t>889198423695</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>102003306324304-8634765723</t>
+          <t>902003307904501-8615577028</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1341,34 +1341,34 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-03T10:31:39-05:00</t>
+          <t>2026-03-03T17:49:51-05:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Clarence, NY, 14031, US, United States</t>
+          <t>Ephrata, PA, 17522, US, United States</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-03-03T19:46:59+00:00</t>
+          <t>2026-03-03T23:47:11+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>889211140462</t>
+          <t>889198423695</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>{"external_order_id": "102003306324304-8634765723", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "902003307904501-8615577028", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>889208514573</t>
+          <t>889211139848</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>912003307917567-8615578363</t>
+          <t>102003306324304-8634765723</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1404,34 +1404,34 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-03-03T11:20:34-05:00</t>
+          <t>2026-03-03T10:31:39-05:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>New York, NY, 10280, US, United States</t>
+          <t>Clarence, NY, 14031, US, United States</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-03-03T19:47:00+00:00</t>
+          <t>2026-03-03T23:47:02+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>889208514573</t>
+          <t>889211139848</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>{"external_order_id": "912003307917567-8615578363", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "102003306324304-8634765723", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>889215570082</t>
+          <t>889211140462</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>912003307917567-8615578363</t>
+          <t>102003306324304-8634765723</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1467,44 +1467,44 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-03T11:07:29-05:00</t>
+          <t>2026-03-03T10:31:39-05:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>New York, NY, 10280, US, United States</t>
+          <t>Clarence, NY, 14031, US, United States</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-03-03T19:46:58+00:00</t>
+          <t>2026-03-03T23:47:02+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>889215570082</t>
+          <t>889211140462</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>{"external_order_id": "912003307917567-8615578363", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "102003306324304-8634765723", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UTV891040271</t>
+          <t>889208514573</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0031009971763</t>
+          <t>912003307917567-8615578363</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1530,44 +1530,44 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-03T16:08:08+01:00</t>
+          <t>2026-03-03T11:20:34-05:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>New York, NY, 10280, US, United States</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:37+00:00</t>
+          <t>2026-03-03T23:47:03+00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>UTV891040271</t>
+          <t>889208514573</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009971763", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "912003307917567-8615578363", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UTV843312405</t>
+          <t>889220116131</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0031009973750</t>
+          <t>PO-211-14202330081910818</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1593,44 +1593,44 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-03T14:58:12+01:00</t>
+          <t>2026-03-03T10:08:55-05:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Woodbridge, VA, 22192, US, United States</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:28+00:00</t>
+          <t>2026-03-03T23:47:02+00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>UTV843312405</t>
+          <t>889220116131</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973750", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-211-14202330081910818", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UTV789524873</t>
+          <t>889215570082</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0031009973750</t>
+          <t>912003307917567-8615578363</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1656,34 +1656,34 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-03-03T14:57:23+01:00</t>
+          <t>2026-03-03T11:07:29-05:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>New York, NY, 10280, US, United States</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:28+00:00</t>
+          <t>2026-03-03T23:46:59+00:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>UTV789524873</t>
+          <t>889215570082</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973750", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "912003307917567-8615578363", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UTV480312775</t>
+          <t>UTV891040271</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0031009968160</t>
+          <t>0031009971763</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1719,7 +1719,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-03-03T12:11:24+01:00</t>
+          <t>2026-03-03T16:08:08+01:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:04+00:00</t>
+          <t>2026-03-03T16:05:37+00:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>UTV480312775</t>
+          <t>UTV891040271</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009968160", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009971763", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UTV924437683</t>
+          <t>UTV623304688</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0031009968403</t>
+          <t>0031009974820</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1782,7 +1782,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-03T12:51:28+01:00</t>
+          <t>2026-03-03T21:31:31+01:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1792,24 +1792,24 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:00+00:00</t>
+          <t>2026-03-03T22:05:38+00:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>UTV924437683</t>
+          <t>UTV623304688</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009968403", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009974820", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UTV545163780</t>
+          <t>UTV843312405</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0031009968403</t>
+          <t>0031009973750</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1845,7 +1845,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-03-03T12:51:28+01:00</t>
+          <t>2026-03-03T14:58:12+01:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1855,24 +1855,24 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:00+00:00</t>
+          <t>2026-03-03T16:05:28+00:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>UTV545163780</t>
+          <t>UTV843312405</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009968403", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009973750", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UTV991396507</t>
+          <t>UTV789524873</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0031009968645</t>
+          <t>0031009973750</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1908,7 +1908,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-03-03T19:24:51+01:00</t>
+          <t>2026-03-03T14:57:23+01:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1918,34 +1918,34 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-03-03T19:05:02+00:00</t>
+          <t>2026-03-03T16:05:28+00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>UTV991396507</t>
+          <t>UTV789524873</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009968645", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009973750", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00KNRRRV</t>
+          <t>UTV480312775</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0031009973032</t>
+          <t>0031009968160</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1971,44 +1971,44 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-03T15:39:03+01:00</t>
+          <t>2026-03-03T12:11:24+01:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-03T16:04:35+00:00</t>
+          <t>2026-03-03T16:05:04+00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>00KNRRRV</t>
+          <t>UTV480312775</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973032", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009968160", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZD1RIO18</t>
+          <t>UTV924437683</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0049010246892</t>
+          <t>0031009968403</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2034,44 +2034,44 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-03-03T09:36:55+01:00</t>
+          <t>2026-03-03T12:51:28+01:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-03-03T16:03:46+00:00</t>
+          <t>2026-03-03T16:05:00+00:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ZD1RIO18</t>
+          <t>UTV924437683</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010246892", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009968403", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ZD1RINXY</t>
+          <t>UTV545163780</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>cbn4wjx6gs</t>
+          <t>0031009968403</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2097,44 +2097,44 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-03-03T09:44:39+01:00</t>
+          <t>2026-03-03T12:51:28+01:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-03-03T20:03:33+00:00</t>
+          <t>2026-03-03T16:05:00+00:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ZD1RINXY</t>
+          <t>UTV545163780</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wjx6gs", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0031009968403", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>YNQAF97V</t>
+          <t>UTV991396507</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>B2BDS11273657</t>
+          <t>0031009968645</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2160,44 +2160,44 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-03-03T06:31:54+01:00</t>
+          <t>2026-03-03T19:24:51+01:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>DK, Denmark</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-03-03T16:03:25+00:00</t>
+          <t>2026-03-03T19:05:02+00:00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>YNQAF97V</t>
+          <t>UTV991396507</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11273657", "sales_office_id": "4437"}</t>
+          <t>{"external_order_id": "0031009968645", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>YNQAF9A3</t>
+          <t>00KNRRRV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0045005253023</t>
+          <t>0031009973032</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2223,34 +2223,34 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-03-03T11:18:40+01:00</t>
+          <t>2026-03-03T15:39:03+01:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>DK, Denmark</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-03-03T16:03:17+00:00</t>
+          <t>2026-03-03T16:04:35+00:00</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>YNQAF9A3</t>
+          <t>00KNRRRV</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0045005253023", "sales_office_id": "3017"}</t>
+          <t>{"external_order_id": "0031009973032", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>YNQAF99E</t>
+          <t>ZD1RIO18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0045005253082</t>
+          <t>0049010246892</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2286,34 +2286,34 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-03T11:46:35+01:00</t>
+          <t>2026-03-03T09:36:55+01:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>DK, Denmark</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-03-03T16:03:15+00:00</t>
+          <t>2026-03-04T04:03:49+00:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>YNQAF99E</t>
+          <t>ZD1RIO18</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0045005253082", "sales_office_id": "3017"}</t>
+          <t>{"external_order_id": "0049010246892", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ZD1RINXZ</t>
+          <t>ZD1RINXY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0049010238785</t>
+          <t>cbn4wjx6gs</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-03-03T09:31:03+01:00</t>
+          <t>2026-03-03T09:44:39+01:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2359,24 +2359,24 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-03-03T16:01:29+00:00</t>
+          <t>2026-03-04T04:03:33+00:00</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ZD1RINXZ</t>
+          <t>ZD1RINXY</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010238785", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "cbn4wjx6gs", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>YNQAF8UK</t>
+          <t>YNQAF97V</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B2BDS11224002</t>
+          <t>B2BDS11273657</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2412,7 +2412,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-03-03T10:12:17+01:00</t>
+          <t>2026-03-03T06:31:54+01:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2422,24 +2422,24 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-03-03T16:01:19+00:00</t>
+          <t>2026-03-04T04:03:31+00:00</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>YNQAF8UK</t>
+          <t>YNQAF97V</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11224002", "sales_office_id": "4437"}</t>
+          <t>{"external_order_id": "B2BDS11273657", "sales_office_id": "4437"}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ZD1RINUZ</t>
+          <t>YNQAF9A3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>cbn4wg7vq3</t>
+          <t>0045005253023</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2475,34 +2475,34 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-03T12:30:27+01:00</t>
+          <t>2026-03-03T11:18:40+01:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-03-03T16:01:17+00:00</t>
+          <t>2026-03-04T04:03:21+00:00</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ZD1RINUZ</t>
+          <t>YNQAF9A3</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0045005253023", "sales_office_id": "3017"}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ZD1RIN6L</t>
+          <t>YNQAF99E</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>cbn4wg7vq3</t>
+          <t>0045005253082</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2538,34 +2538,34 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-03T12:30:27+01:00</t>
+          <t>2026-03-03T11:46:35+01:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-03T16:01:18+00:00</t>
+          <t>2026-03-04T04:03:21+00:00</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ZD1RIN6L</t>
+          <t>YNQAF99E</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0045005253082", "sales_office_id": "3017"}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ZD1RINJ3</t>
+          <t>ZD1RINXZ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>cbn4wg7vq3</t>
+          <t>0049010238785</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,7 +2601,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-03T12:30:27+01:00</t>
+          <t>2026-03-03T09:31:03+01:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2611,34 +2611,34 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-03-03T16:01:16+00:00</t>
+          <t>2026-03-04T04:01:32+00:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ZD1RINJ3</t>
+          <t>ZD1RINXZ</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0049010238785", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>01475240788588</t>
+          <t>YNQAF8UK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1116346471-01</t>
+          <t>B2BDS11224002</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2664,44 +2664,44 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-03T11:43:56+01:00</t>
+          <t>2026-03-03T10:12:17+01:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Geretsried - Gelting (DE), Germany</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-03T15:59:25+00:00</t>
+          <t>2026-03-04T04:01:22+00:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>01475240788588</t>
+          <t>YNQAF8UK</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1116346471-01", "sales_office_id": "4677"}</t>
+          <t>{"external_order_id": "B2BDS11224002", "sales_office_id": "4437"}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01475240787644</t>
+          <t>ZD1RINUZ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1116346471-01</t>
+          <t>cbn4wg7vq3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2727,44 +2727,44 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-03T11:43:56+01:00</t>
+          <t>2026-03-03T12:30:27+01:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Geretsried - Gelting (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-03-03T15:59:23+00:00</t>
+          <t>2026-03-04T04:01:20+00:00</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>01475240787644</t>
+          <t>ZD1RINUZ</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1116346471-01", "sales_office_id": "4677"}</t>
+          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05228742846342</t>
+          <t>ZD1RIN6L</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0032005564933</t>
+          <t>cbn4wg7vq3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2790,44 +2790,44 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-03T16:42:34+01:00</t>
+          <t>2026-03-03T12:30:27+01:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sint-Niklaas, BE, Belgium</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-03-03T18:58:02+00:00</t>
+          <t>2026-03-04T04:01:20+00:00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>05228742846342</t>
+          <t>ZD1RIN6L</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005564933", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05228742846341</t>
+          <t>ZD1RINJ3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0032005564933</t>
+          <t>cbn4wg7vq3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2853,44 +2853,44 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-03T16:42:34+01:00</t>
+          <t>2026-03-03T12:30:27+01:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sint-Niklaas, BE, Belgium</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-03T15:57:43+00:00</t>
+          <t>2026-03-04T04:01:19+00:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>05228742846341</t>
+          <t>ZD1RINJ3</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005564933", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "cbn4wg7vq3", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00KNRRNP</t>
+          <t>01475240788588</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0031009975797</t>
+          <t>1116346471-01</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2916,44 +2916,44 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-03T13:15:15+01:00</t>
+          <t>2026-03-03T11:43:56+01:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Geretsried - Gelting (DE), Germany</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-03-03T14:39:25+00:00</t>
+          <t>2026-03-03T15:59:25+00:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>00KNRRNP</t>
+          <t>01475240788588</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009975797", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "1116346471-01", "sales_office_id": "4677"}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00KNRRF6</t>
+          <t>01475240787644</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0031009969354</t>
+          <t>1116346471-01</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2979,44 +2979,44 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-03T19:39:59+01:00</t>
+          <t>2026-03-03T11:43:56+01:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Geretsried - Gelting (DE), Germany</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-03-03T19:09:49+00:00</t>
+          <t>2026-03-03T15:59:23+00:00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>00KNRRF6</t>
+          <t>01475240787644</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009969354", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "1116346471-01", "sales_office_id": "4677"}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00KNRRNQ</t>
+          <t>05228742846342</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0031009975797</t>
+          <t>0032005564933</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3042,44 +3042,44 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-03T13:15:15+01:00</t>
+          <t>2026-03-03T16:42:34+01:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sint-Niklaas, BE, Belgium</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-03-03T14:39:25+00:00</t>
+          <t>2026-03-03T18:58:02+00:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>00KNRRNQ</t>
+          <t>05228742846342</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009975797", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005564933", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ZD1RINHK</t>
+          <t>05228742846341</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0049010233172</t>
+          <t>0032005564933</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3105,44 +3105,44 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-03T11:02:25+01:00</t>
+          <t>2026-03-03T16:42:34+01:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Sint-Niklaas, BE, Belgium</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-03T18:38:53+00:00</t>
+          <t>2026-03-03T15:57:43+00:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ZD1RINHK</t>
+          <t>05228742846341</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010233172", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0032005564933", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ZD1RIOPD</t>
+          <t>00KNRRNP</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0049010244426</t>
+          <t>0031009975797</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3168,44 +3168,44 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:39+01:00</t>
+          <t>2026-03-03T13:15:15+01:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:27+00:00</t>
+          <t>2026-03-03T14:39:25+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ZD1RIOPD</t>
+          <t>00KNRRNP</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009975797", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ZD1RIOPC</t>
+          <t>00KNRRF6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3215,12 +3215,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0049010244426</t>
+          <t>0031009969354</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3231,44 +3231,44 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:39+01:00</t>
+          <t>2026-03-03T19:39:59+01:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:26+00:00</t>
+          <t>2026-03-03T19:09:49+00:00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ZD1RIOPC</t>
+          <t>00KNRRF6</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009969354", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ZD1RIOPA</t>
+          <t>00KNRRNQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0049010244426</t>
+          <t>0031009975797</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3294,34 +3294,34 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:39+01:00</t>
+          <t>2026-03-03T13:15:15+01:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:26+00:00</t>
+          <t>2026-03-03T14:39:25+00:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ZD1RIOPA</t>
+          <t>00KNRRNQ</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009975797", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ZD1RINQ1</t>
+          <t>ZD1RINHK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0049010233654</t>
+          <t>0049010233172</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3357,7 +3357,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-03T10:13:09+01:00</t>
+          <t>2026-03-03T11:02:25+01:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3367,24 +3367,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:20+00:00</t>
+          <t>2026-03-04T02:38:53+00:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ZD1RINQ1</t>
+          <t>ZD1RINHK</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010233654", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010233172", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ZD1RINOK</t>
+          <t>ZD1RIOPD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0049010233654</t>
+          <t>0049010244426</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-03T10:13:09+01:00</t>
+          <t>2026-03-03T14:37:39+01:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3430,34 +3430,34 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-03-03T14:37:20+00:00</t>
+          <t>2026-03-04T02:37:29+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ZD1RINOK</t>
+          <t>ZD1RIOPD</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010233654", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>01475240782282</t>
+          <t>ZD1RIOPA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0049010214437</t>
+          <t>0049010244426</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3483,44 +3483,44 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-02-27T12:59:11+01:00</t>
+          <t>2026-03-03T14:37:39+01:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:25+00:00</t>
+          <t>2026-03-04T02:37:29+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>01475240782282</t>
+          <t>ZD1RIOPA</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>01475240782918</t>
+          <t>ZD1RIOPC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0049010214437</t>
+          <t>0049010244426</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3546,44 +3546,44 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-02-27T12:59:11+01:00</t>
+          <t>2026-03-03T14:37:39+01:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:27+00:00</t>
+          <t>2026-03-04T02:37:29+00:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>01475240782918</t>
+          <t>ZD1RIOPC</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010244426", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>01475240781789</t>
+          <t>ZD1RINQ1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0049010214437</t>
+          <t>0049010233654</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3609,44 +3609,44 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-02-27T12:59:11+01:00</t>
+          <t>2026-03-03T10:13:09+01:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:25+00:00</t>
+          <t>2026-03-04T02:37:22+00:00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>01475240781789</t>
+          <t>ZD1RINQ1</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010233654", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>01475240790578</t>
+          <t>ZD1RINOK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>B2BDS11345064</t>
+          <t>0049010233654</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3672,34 +3672,34 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-03T13:19:35+01:00</t>
+          <t>2026-03-03T10:13:09+01:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Würzburg (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:21+00:00</t>
+          <t>2026-03-04T02:37:25+00:00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>01475240790578</t>
+          <t>ZD1RINOK</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11345064", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010233654", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01475240790254</t>
+          <t>01475240782282</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>0049010214437</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3735,34 +3735,34 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-02-27T12:59:11+01:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>Essen (DE), Germany</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:23+00:00</t>
+          <t>2026-03-03T11:37:25+00:00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>01475240790254</t>
+          <t>01475240782282</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01475240790277</t>
+          <t>01475240782918</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>0049010214437</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3798,34 +3798,34 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-02-27T12:59:11+01:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>Essen (DE), Germany</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:18+00:00</t>
+          <t>2026-03-03T12:37:27+00:00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>01475240790277</t>
+          <t>01475240782918</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>01475240790255</t>
+          <t>01475240781789</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>0049010214437</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3861,34 +3861,34 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-02-27T12:59:11+01:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>Essen (DE), Germany</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:17+00:00</t>
+          <t>2026-03-03T11:37:25+00:00</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>01475240790255</t>
+          <t>01475240781789</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0049010214437", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>01475240790280</t>
+          <t>01475240790578</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1024905387-A</t>
+          <t>B2BDS11345064</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3924,34 +3924,34 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-03T12:19:39+01:00</t>
+          <t>2026-03-03T13:19:35+01:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>Würzburg (DE), Germany</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:16+00:00</t>
+          <t>2026-03-03T12:37:21+00:00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>01475240790280</t>
+          <t>01475240790578</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "B2BDS11345064", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01475240790279</t>
+          <t>01475240790254</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-03-03T12:37:16+00:00</t>
+          <t>2026-03-03T12:37:23+00:00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>01475240790279</t>
+          <t>01475240790254</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>01475240790278</t>
+          <t>01475240790255</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-03T11:37:16+00:00</t>
+          <t>2026-03-03T11:37:17+00:00</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>01475240790278</t>
+          <t>01475240790255</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4077,17 +4077,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>05228742844449</t>
+          <t>01475240790277</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0033005727379</t>
+          <t>1024905387-A</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0302</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4113,44 +4113,44 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-03-03T12:42:42+01:00</t>
+          <t>2026-03-03T12:19:39+01:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>La Crau, FR, France</t>
+          <t>Walsrode (DE), Germany</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-03-03T18:35:18+00:00</t>
+          <t>2026-03-03T11:37:18+00:00</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>05228742844449</t>
+          <t>01475240790277</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005727379", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>05228742845732</t>
+          <t>01475240790280</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>402-6214259-5084345</t>
+          <t>1024905387-A</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4176,44 +4176,44 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-03-03T11:03:41+01:00</t>
+          <t>2026-03-03T12:19:39+01:00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>Walsrode (DE), Germany</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-03-03T11:23:14+00:00</t>
+          <t>2026-03-03T11:37:16+00:00</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>05228742845732</t>
+          <t>01475240790280</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>{"external_order_id": "402-6214259-5084345", "sales_office_id": "4647"}</t>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>05228742846812</t>
+          <t>01475240790278</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0032005565675</t>
+          <t>1024905387-A</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4239,44 +4239,44 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-03T11:44:18+01:00</t>
+          <t>2026-03-03T12:19:39+01:00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>Walsrode (DE), Germany</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-03-03T11:22:19+00:00</t>
+          <t>2026-03-03T11:37:16+00:00</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>05228742846812</t>
+          <t>01475240790278</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>05228742846188</t>
+          <t>01475240790279</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0032005565675</t>
+          <t>1024905387-A</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4302,34 +4302,34 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-03-03T11:44:18+01:00</t>
+          <t>2026-03-03T12:19:39+01:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>Walsrode (DE), Germany</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-03T14:22:37+00:00</t>
+          <t>2026-03-03T12:37:16+00:00</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>05228742846188</t>
+          <t>01475240790279</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "1024905387-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>05228742847138</t>
+          <t>05228742844449</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0032005565675</t>
+          <t>0033005727379</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0302</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4365,34 +4365,34 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-03-03T11:44:18+01:00</t>
+          <t>2026-03-03T12:42:42+01:00</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>La Crau, FR, France</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-03T11:22:18+00:00</t>
+          <t>2026-03-03T18:35:18+00:00</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>05228742847138</t>
+          <t>05228742844449</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0033005727379", "sales_office_id": "0302"}</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>05228742844439</t>
+          <t>05228742845732</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0031009969234</t>
+          <t>402-6214259-5084345</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4428,7 +4428,7 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-03T19:41:07+01:00</t>
+          <t>2026-03-03T11:03:41+01:00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4438,24 +4438,24 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-03-03T18:52:36+00:00</t>
+          <t>2026-03-03T11:23:14+00:00</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>05228742844439</t>
+          <t>05228742845732</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009969234", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "402-6214259-5084345", "sales_office_id": "4647"}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>05228742846050</t>
+          <t>05228742846812</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0032005564138</t>
+          <t>0032005565675</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4491,34 +4491,34 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-03T11:13:10+01:00</t>
+          <t>2026-03-03T11:44:18+01:00</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Sint-Niklaas, BE, Belgium</t>
+          <t>Courcelles, BE, Belgium</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-03-03T14:22:23+00:00</t>
+          <t>2026-03-03T11:22:19+00:00</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>05228742846050</t>
+          <t>05228742846812</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>05228742847174</t>
+          <t>05228742847138</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0032005564138</t>
+          <t>0032005565675</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4554,44 +4554,44 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-03-03T11:13:10+01:00</t>
+          <t>2026-03-03T11:44:18+01:00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Sint-Niklaas, BE, Belgium</t>
+          <t>Courcelles, BE, Belgium</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-03-03T14:22:24+00:00</t>
+          <t>2026-03-03T11:22:18+00:00</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>05228742847174</t>
+          <t>05228742847138</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>UTV544822779</t>
+          <t>05228742846188</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>C0001H46LJ</t>
+          <t>0032005565675</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4617,44 +4617,44 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-03-03T10:58:07+01:00</t>
+          <t>2026-03-03T11:44:18+01:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Courcelles, BE, Belgium</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-03-03T10:12:11+00:00</t>
+          <t>2026-03-03T14:22:37+00:00</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>UTV544822779</t>
+          <t>05228742846188</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>{"external_order_id": "C0001H46LJ", "sales_office_id": "4002"}</t>
+          <t>{"external_order_id": "0032005565675", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UTV013236806</t>
+          <t>05228742844439</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0031009973241</t>
+          <t>0031009969234</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4680,44 +4680,44 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-03T14:21:49+01:00</t>
+          <t>2026-03-03T19:41:07+01:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Veenendaal, NL, Netherlands</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-03-03T16:12:11+00:00</t>
+          <t>2026-03-03T18:52:36+00:00</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>UTV013236806</t>
+          <t>05228742844439</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973241", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009969234", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UTV050109541</t>
+          <t>05228742846050</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0031009972803</t>
+          <t>0032005564138</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4743,44 +4743,44 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-03T15:23:08+01:00</t>
+          <t>2026-03-03T11:13:10+01:00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Sint-Niklaas, BE, Belgium</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-03-03T16:11:29+00:00</t>
+          <t>2026-03-03T14:22:23+00:00</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>UTV050109541</t>
+          <t>05228742846050</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009972803", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>UTV830382349</t>
+          <t>05228742847174</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0031009972930</t>
+          <t>0032005564138</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4806,34 +4806,34 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-03-03T11:08:50+01:00</t>
+          <t>2026-03-03T11:13:10+01:00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Sint-Niklaas, BE, Belgium</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-03-03T10:11:28+00:00</t>
+          <t>2026-03-03T14:22:24+00:00</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>UTV830382349</t>
+          <t>05228742847174</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009972930", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005564138", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>UTV282537285</t>
+          <t>UTV544822779</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0031009965250</t>
+          <t>C0001H46LJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4869,7 +4869,7 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-03T19:40:26+01:00</t>
+          <t>2026-03-03T10:58:07+01:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4879,24 +4879,24 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-03-03T19:11:10+00:00</t>
+          <t>2026-03-03T10:12:11+00:00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>UTV282537285</t>
+          <t>UTV544822779</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009965250", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "C0001H46LJ", "sales_office_id": "4002"}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>UTV591963001</t>
+          <t>UTV013236806</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0031009972485</t>
+          <t>0031009973241</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4932,7 +4932,7 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-03T13:28:06+01:00</t>
+          <t>2026-03-03T14:21:49+01:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4942,24 +4942,24 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-03-03T13:11:09+00:00</t>
+          <t>2026-03-03T16:12:11+00:00</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>UTV591963001</t>
+          <t>UTV013236806</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009972485", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009973241", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>UTV765135406</t>
+          <t>UTV830382349</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0031009973435</t>
+          <t>0031009972930</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4995,7 +4995,7 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-03T14:52:36+01:00</t>
+          <t>2026-03-03T11:08:50+01:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5005,24 +5005,24 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-03-03T16:10:58+00:00</t>
+          <t>2026-03-03T10:11:28+00:00</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>UTV765135406</t>
+          <t>UTV830382349</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973435", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009972930", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>UTV206686788</t>
+          <t>UTV050109541</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0031009973435</t>
+          <t>0031009972803</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5058,7 +5058,7 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-03T14:52:44+01:00</t>
+          <t>2026-03-03T15:23:08+01:00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5068,24 +5068,24 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-03-03T16:10:58+00:00</t>
+          <t>2026-03-03T16:11:29+00:00</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>UTV206686788</t>
+          <t>UTV050109541</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973435", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009972803", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>UTV592496096</t>
+          <t>UTV282537285</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0031009967821</t>
+          <t>0031009965250</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5121,7 +5121,7 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-03T14:21:53+01:00</t>
+          <t>2026-03-03T19:40:26+01:00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5131,34 +5131,34 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-03-03T20:10:58+00:00</t>
+          <t>2026-03-03T23:11:11+00:00</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>UTV592496096</t>
+          <t>UTV282537285</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009967821", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009965250", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>01475240790240</t>
+          <t>UTV591963001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>cbn4wkbm99</t>
+          <t>0031009972485</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5184,27 +5184,3492 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
+          <t>2026-03-03T13:28:06+01:00</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-03-03T13:11:09+00:00</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>UTV591963001</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009972485", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>UTV765135406</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0031009973435</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:52:36+01:00</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:10:58+00:00</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>UTV765135406</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009973435", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>UTV206686788</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0031009973435</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:52:44+01:00</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:10:58+00:00</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>UTV206686788</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009973435", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>UTV592496096</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0031009967821</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-03-03T14:21:53+01:00</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-03-03T20:10:58+00:00</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>UTV592496096</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009967821", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>01475240790240</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>cbn4wkbm99</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
           <t>2026-03-03T09:32:51+01:00</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Vechta (DE), Germany</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>2026-03-03T09:40:36+00:00</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>01475240790240</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>{"external_order_id": "cbn4wkbm99", "sales_office_id": "4316"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>518157125872</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>250-2890326-8235029</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:26:00+09:00</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>羽島営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:03:39+00:00</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>518157125872</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-2890326-8235029", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>518157125485</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>B2BDS11190714</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:05:00+09:00</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>小田原営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-03-04T03:33:09+00:00</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>518157125485</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "B2BDS11190714", "sales_office_id": "4468"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>518157128171</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>250-9779157-6404619</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:04:00+09:00</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>横浜営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:33:05+00:00</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>518157128171</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-9779157-6404619", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>518157126535</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>B2BDS11065500</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:19:00+09:00</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>神戸営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-03-04T04:03:10+00:00</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>518157126535</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "B2BDS11065500", "sales_office_id": "4468"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>518157126583</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>250-9779157-6404619</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:04:00+09:00</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>横浜営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:33:14+00:00</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>518157126583</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-9779157-6404619", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>518157125883</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>B2BDS11065531</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-03-04T08:11:00+09:00</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>城西営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-03-04T00:02:15+00:00</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>518157125883</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "B2BDS11065531", "sales_office_id": "4468"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>518157126196</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>503-1014298-5339840</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:19:00+09:00</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>飯田営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:31:05+00:00</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>518157126196</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-1014298-5339840", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>518157128086</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>503-3479228-1748637</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:17:00+09:00</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>十和田営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-03-04T04:30:44+00:00</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>518157128086</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-3479228-1748637", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>518157127810</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>B2BDS11065416</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:01:00+09:00</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>八幡営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-03-04T03:30:44+00:00</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>518157127810</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "B2BDS11065416", "sales_office_id": "4468"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>518157126955</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>B2BDS11065432</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:45:00+09:00</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>練馬営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:00:34+00:00</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>518157126955</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "B2BDS11065432", "sales_office_id": "4468"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>518157128226</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>503-2840489-1123048</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:09:00+09:00</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>小山営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-03-04T01:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>518157128226</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-2840489-1123048", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>518157129803</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0081000027796</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:20:00+09:00</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>横浜営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-03-04T04:50:12+00:00</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>518157129803</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0081000027796", "sales_office_id": "4414"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>518157129615</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0081000027801</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:32:00+09:00</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>目黒営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:48:18+00:00</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>518157129615</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0081000027801", "sales_office_id": "4414"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>518157129280</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0081000027801</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:32:00+09:00</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>目黒営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:48:15+00:00</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>518157129280</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0081000027801", "sales_office_id": "4414"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>518157129394</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>249-0137111-3371842</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:12:00+09:00</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>豊田営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:18:17+00:00</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>518157129394</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-0137111-3371842", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>518157128661</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>249-0137111-3371842</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:12:00+09:00</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>豊田営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:18:17+00:00</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>518157128661</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-0137111-3371842", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>518157128624</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>249-0137111-3371842</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:12:00+09:00</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>豊田営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:18:16+00:00</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>518157128624</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-0137111-3371842", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>518157129630</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>249-2155586-0739856</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:47:00+09:00</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>木更津営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:18:19+00:00</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>518157129630</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-2155586-0739856", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>518157129081</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>503-9415910-3841460</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:04:00+09:00</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>名古屋南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-03-04T04:18:21+00:00</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>518157129081</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-9415910-3841460", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>518157129453</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0081000027800</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:35:00+09:00</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>和歌山営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-03-04T01:48:13+00:00</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>518157129453</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0081000027800", "sales_office_id": "4414"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>518157129641</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>503-6055084-4258225</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:03:00+09:00</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>群馬営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-03-04T03:48:21+00:00</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>518157129641</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-6055084-4258225", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>518157129733</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>503-0160047-5426207</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:29:00+09:00</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>名古屋営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-03-04T01:48:11+00:00</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>518157129733</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-0160047-5426207", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>518157129442</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0081000027800</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:35:00+09:00</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>和歌山営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-03-04T01:48:12+00:00</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>518157129442</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0081000027800", "sales_office_id": "4414"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>518157129825</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>249-9645383-5441404</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:50:00+09:00</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>和歌山営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-03-04T01:18:19+00:00</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>518157129825</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-9645383-5441404", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>518157128403</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>249-3684307-9827841</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-03-04T08:52:00+09:00</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>東松山営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-03-04T00:18:08+00:00</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>518157128403</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-3684307-9827841", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>518157129431</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0081000027800</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:35:00+09:00</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>和歌山営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-03-04T01:48:08+00:00</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>518157129431</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0081000027800", "sales_office_id": "4414"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>518157129092</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>249-6717009-0613423</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:34:00+09:00</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>木更津営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-03-04T00:47:05+00:00</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>518157129092</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-6717009-0613423", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>518157128591</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>10001475</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>4595</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:44:00+09:00</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>本荘営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-03-04T04:16:50+00:00</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>518157128591</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "10001475", "sales_office_id": "4595"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>518157129033</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>503-1128978-1491858</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:21:00+09:00</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>亀岡営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:46:26+00:00</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>518157129033</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-1128978-1491858", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>518157129011</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>250-6382180-5476642</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:34:00+09:00</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>松本営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:46:26+00:00</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>518157129011</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-6382180-5476642", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>518157128576</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>503-4928941-5064611</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:29:00+09:00</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>名東営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-03-04T01:46:21+00:00</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>518157128576</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-4928941-5064611", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>518157128565</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>503-4928941-5064611</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:29:00+09:00</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>名東営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-03-04T01:46:19+00:00</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>518157128565</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-4928941-5064611", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>518157128322</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>249-1375739-0439835</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:11:00+09:00</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>堺営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:46:19+00:00</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>518157128322</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-1375739-0439835", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>518157128554</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>503-4928941-5064611</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:29:00+09:00</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>名東営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-03-04T01:46:19+00:00</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>518157128554</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-4928941-5064611", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>518157128930</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>250-0621125-8559862</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:12:00+09:00</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>鎌倉営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-03-04T03:46:11+00:00</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>518157128930</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-0621125-8559862", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>518157128436</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>10001474</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>4595</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:29:00+09:00</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>練馬営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-03-04T00:46:12+00:00</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>518157128436</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "10001474", "sales_office_id": "4595"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>518157128521</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0081000027793</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:34:00+09:00</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>杉並営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-03-04T04:46:13+00:00</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>518157128521</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0081000027793", "sales_office_id": "4414"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>518157129313</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>249-8542780-6651859</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:22:00+09:00</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>目黒営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-03-04T04:14:46+00:00</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>518157129313</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "249-8542780-6651859", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>518157128510</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>250-8677768-3947856</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:20:00+09:00</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>東京営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2026-03-04T00:44:40+00:00</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>518157128510</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-8677768-3947856", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>518157128506</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>250-8677768-3947856</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:20:00+09:00</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>東京営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-03-04T00:44:41+00:00</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>518157128506</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-8677768-3947856", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>518157128495</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>250-8677768-3947856</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:20:00+09:00</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>東京営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2026-03-04T00:44:38+00:00</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>518157128495</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-8677768-3947856", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>518157128484</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>250-8677768-3947856</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:20:00+09:00</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>東京営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2026-03-04T00:44:37+00:00</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>518157128484</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-8677768-3947856", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>518157128996</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>10001473</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>4595</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:18:00+09:00</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>三多摩営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-03-04T04:44:44+00:00</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>518157128996</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "10001473", "sales_office_id": "4595"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>518157129416</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>250-5508752-1426236</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:26:00+09:00</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>羽島営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:44:41+00:00</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>518157129416</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-5508752-1426236", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>518157128311</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>503-8507764-1491833</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:00:00+09:00</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>さいたま営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:14:41+00:00</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>518157128311</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-8507764-1491833", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>518157129405</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>250-5508752-1426236</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:26:00+09:00</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>羽島営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:44:39+00:00</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>518157129405</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-5508752-1426236", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>518157128801</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>250-3671123-8580610</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:56:00+09:00</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>山梨営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2026-03-04T02:14:39+00:00</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>518157128801</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-3671123-8580610", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>518157129000</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>503-5687415-6370205</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:47:00+09:00</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>仙台南営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2026-03-04T03:14:40+00:00</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>518157129000</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-5687415-6370205", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>518157129232</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>250-0791481-8851848</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:07:00+09:00</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>杉並Ｂ営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2026-03-04T04:44:22+00:00</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>518157129232</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-0791481-8851848", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>518157129044</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>503-6640443-7610207</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:30:00+09:00</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>深谷営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2026-03-04T04:44:20+00:00</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>518157129044</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "503-6640443-7610207", "sales_office_id": "4564"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>518157128650</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>sagawa</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Sagawa</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>250-8403747-6355814</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:23:00+09:00</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>さいたま営業所, Japan</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2026-03-04T01:44:08+00:00</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>518157128650</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "250-8403747-6355814", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05228742846313</t>
+          <t>00KNRSZY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0032005563865</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -522,44 +522,44 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-03T11:47:07+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Aalter, BE, Belgium</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-04T13:53:29+00:00</t>
+          <t>2026-03-04T15:54:33+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05228742846313</t>
+          <t>00KNRSZY</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005563865", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05228742843747</t>
+          <t>00KNRSZS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0032005563865</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -585,44 +585,44 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-03T11:47:07+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Aalter, BE, Belgium</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-04T13:53:29+00:00</t>
+          <t>2026-03-04T15:54:30+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05228742843747</t>
+          <t>00KNRSZS</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005563865", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05228742854716</t>
+          <t>00KNRT00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0032005569225</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -648,44 +648,44 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-03-04T13:49:56+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Vilvoorde, BE, Belgium</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-04T13:53:15+00:00</t>
+          <t>2026-03-04T15:54:32+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05228742854716</t>
+          <t>00KNRT00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005569225", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UTV107113681</t>
+          <t>00KNRSZX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0031009971989</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -711,44 +711,44 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-04T10:54:01+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-04T13:04:28+00:00</t>
+          <t>2026-03-04T15:54:34+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>UTV107113681</t>
+          <t>00KNRSZX</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009971989", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UTV572230723</t>
+          <t>00KNRSZR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0031009971989</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -774,44 +774,44 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-04T10:54:14+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-04T13:04:30+00:00</t>
+          <t>2026-03-04T15:54:30+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>UTV572230723</t>
+          <t>00KNRSZR</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009971989", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00KOQNFF</t>
+          <t>00KNRSZU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0033005729405</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0302</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -837,44 +837,44 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-04T09:40:46+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FR, France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-04T13:04:11+00:00</t>
+          <t>2026-03-04T15:54:31+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>00KOQNFF</t>
+          <t>00KNRSZU</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005729405", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00KNSBZ6</t>
+          <t>00KNRSZV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B2BDS11325687</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -900,44 +900,44 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-04T08:29:43+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FR, France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-04T13:03:45+00:00</t>
+          <t>2026-03-04T15:54:29+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>00KNSBZ6</t>
+          <t>00KNRSZV</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11325687", "sales_office_id": "4452"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00KNSBZ5</t>
+          <t>00KNRSZT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B2BDS11325687</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -963,44 +963,44 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-04T08:29:43+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FR, France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-04T13:03:44+00:00</t>
+          <t>2026-03-04T15:54:30+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>00KNSBZ5</t>
+          <t>00KNRSZT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11325687", "sales_office_id": "4452"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UTV232918983</t>
+          <t>00KNRSZW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0031009973557</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1026,34 +1026,34 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-03T12:39:56+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-04T13:03:23+00:00</t>
+          <t>2026-03-04T15:54:31+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UTV232918983</t>
+          <t>00KNRSZW</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009973557", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UTV631726295</t>
+          <t>UTV662060404</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0031009974227</t>
+          <t>B2B25351563</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1089,7 +1089,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-04T11:11:04+01:00</t>
+          <t>2026-03-04T08:11:22+01:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1099,34 +1099,34 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-04T13:03:23+00:00</t>
+          <t>2026-03-04T15:53:38+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UTV631726295</t>
+          <t>UTV662060404</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009974227", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2B25351563", "sales_office_id": "4238"}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UTV630687814</t>
+          <t>00KNRPLC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0031009974227</t>
+          <t>0031009964033</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1152,44 +1152,44 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-04T11:08:20+01:00</t>
+          <t>2026-03-03T14:13:05+01:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-04T13:03:23+00:00</t>
+          <t>2026-03-04T15:53:30+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>UTV630687814</t>
+          <t>00KNRPLC</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009974227", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009964033", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UTV981141134</t>
+          <t>00KNRPD1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0031009974227</t>
+          <t>0031009964033</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1215,44 +1215,44 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-04T11:11:30+01:00</t>
+          <t>2026-03-03T14:13:05+01:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-04T13:03:19+00:00</t>
+          <t>2026-03-04T15:53:30+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UTV981141134</t>
+          <t>00KNRPD1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009974227", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009964033", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00KNRU6M</t>
+          <t>UTV019744791</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0031009980890</t>
+          <t>0031009967076</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1278,44 +1278,44 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-03-04T13:19:34+01:00</t>
+          <t>2026-03-04T10:51:21+01:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-04T13:00:25+00:00</t>
+          <t>2026-03-04T15:53:24+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>00KNRU6M</t>
+          <t>UTV019744791</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009980890", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009967076", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00KNRU6B</t>
+          <t>UTV541200300</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0031009980890</t>
+          <t>0031009967076</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1341,34 +1341,34 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-04T13:19:34+01:00</t>
+          <t>2026-03-03T12:29:01+01:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-03-04T13:00:23+00:00</t>
+          <t>2026-03-04T15:53:22+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>00KNRU6B</t>
+          <t>UTV541200300</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009980890", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009967076", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00KNRU3I</t>
+          <t>00KNRU4R</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0031009977643</t>
+          <t>0031009979003</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:16+01:00</t>
+          <t>2026-03-04T13:23:51+01:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1414,34 +1414,34 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-03-04T12:24:28+00:00</t>
+          <t>2026-03-04T15:53:03+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>00KNRU3I</t>
+          <t>00KNRU4R</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977643", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009979003", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00KNRU46</t>
+          <t>UTV348607012</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0031009977643</t>
+          <t>0031009961530</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1467,44 +1467,44 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:16+01:00</t>
+          <t>2026-03-03T15:29:43+01:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-03-04T12:24:28+00:00</t>
+          <t>2026-03-04T15:52:54+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>00KNRU46</t>
+          <t>UTV348607012</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977643", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009961530", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00KNRT87</t>
+          <t>ZI67DV4F</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0031009977643</t>
+          <t>0032005568229</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1530,44 +1530,44 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:16+01:00</t>
+          <t>2026-03-04T15:33:13+01:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>BE, Belgium</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-03-04T12:24:28+00:00</t>
+          <t>2026-03-04T15:52:15+00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>00KNRT87</t>
+          <t>ZI67DV4F</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977643", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005568229", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00KNRTCT</t>
+          <t>ZI67DV4E</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0031009978276</t>
+          <t>0032005568229</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1593,44 +1593,44 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-04T12:00:43+01:00</t>
+          <t>2026-03-04T15:33:13+01:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>BE, Belgium</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-04T12:24:26+00:00</t>
+          <t>2026-03-04T15:52:16+00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>00KNRTCT</t>
+          <t>ZI67DV4E</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009978276", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005568229", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00KNRTAS</t>
+          <t>ZI67DV4D</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0031009978276</t>
+          <t>0032005568229</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1656,44 +1656,44 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-03-04T12:00:43+01:00</t>
+          <t>2026-03-04T15:33:13+01:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>BE, Belgium</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-03-04T12:24:25+00:00</t>
+          <t>2026-03-04T15:52:15+00:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>00KNRTAS</t>
+          <t>ZI67DV4D</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009978276", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005568229", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00KNRUGF</t>
+          <t>ZI67DUT3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0031009982259</t>
+          <t>0032005565058</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1719,44 +1719,44 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-03-04T10:16:46+01:00</t>
+          <t>2026-03-04T09:07:32+01:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>BE, Belgium</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-03-04T12:24:02+00:00</t>
+          <t>2026-03-04T15:51:57+00:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>00KNRUGF</t>
+          <t>ZI67DUT3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009982259", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005565058", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00KNRUGH</t>
+          <t>ZB8W8KFW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0031009982259</t>
+          <t>B2BDS11357350</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1782,44 +1782,44 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-04T10:16:46+01:00</t>
+          <t>2026-03-04T14:19:20+01:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-03-04T12:24:06+00:00</t>
+          <t>2026-03-04T15:51:56+00:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>00KNRUGH</t>
+          <t>ZB8W8KFW</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009982259", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11357350", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00KNRU62</t>
+          <t>YNQAF937</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0031009982031</t>
+          <t>0045005252204</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1845,44 +1845,44 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-03-04T14:03:56+01:00</t>
+          <t>2026-03-03T10:44:08+01:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-03-04T13:24:01+00:00</t>
+          <t>2026-03-04T15:51:08+00:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>00KNRU62</t>
+          <t>YNQAF937</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009982031", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0045005252204", "sales_office_id": "3017"}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01475240794415</t>
+          <t>YNQAF93O</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>B2BDS11396937</t>
+          <t>0045005252204</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1908,44 +1908,44 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-03-04T12:01:34+01:00</t>
+          <t>2026-03-03T10:44:08+01:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Föhren (DE), Germany</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-03-04T12:52:56+00:00</t>
+          <t>2026-03-04T15:51:07+00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>01475240794415</t>
+          <t>YNQAF93O</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11396937", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0045005252204", "sales_office_id": "3017"}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01475240794595</t>
+          <t>ZB8W8KIE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>B2BDS11396937</t>
+          <t>B2BDS11372451</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1971,44 +1971,44 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-04T12:01:34+01:00</t>
+          <t>2026-03-04T12:56:26+01:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Föhren (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-04T12:22:59+00:00</t>
+          <t>2026-03-04T15:51:05+00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>01475240794595</t>
+          <t>ZB8W8KIE</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11396937", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11372451", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>01475240792974</t>
+          <t>05228742850751</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0049010248060</t>
+          <t>B2BDS11299677</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2034,44 +2034,44 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-03-04T11:14:15+01:00</t>
+          <t>2026-03-04T10:46:02+01:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Hagen (DE), Germany</t>
+          <t>Carhaix Plouguer, FR, France</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-03-04T12:22:43+00:00</t>
+          <t>2026-03-04T15:50:26+00:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>01475240792974</t>
+          <t>05228742850751</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010248060", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11299677", "sales_office_id": "4452"}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>01475240792242</t>
+          <t>06245165501732</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-at-sftp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD Austria</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0049010248060</t>
+          <t>0043000968791</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2097,44 +2097,40 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-03-04T11:14:15+01:00</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Hagen (DE), Germany</t>
-        </is>
-      </c>
+          <t>2026-03-04T12:17:00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-03-04T12:22:41+00:00</t>
+          <t>2026-03-04T15:47:36+00:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>01475240792242</t>
+          <t>06245165501732</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010248060", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0043000968791", "sales_office_id": "3009"}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>01475240791007</t>
+          <t>06245165502472</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-at-sftp</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD Austria</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2144,12 +2140,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1024909717-A</t>
+          <t>0043000968792</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2160,34 +2156,30 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-03-03T17:48:39+01:00</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Hamburg (DE), Germany</t>
-        </is>
-      </c>
+          <t>2026-03-04T11:09:00</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-03-04T12:22:38+00:00</t>
+          <t>2026-03-04T15:47:08+00:00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>01475240791007</t>
+          <t>06245165502472</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024909717-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0043000968792", "sales_office_id": "3009"}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>01475240794378</t>
+          <t>01475240792815</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2207,12 +2199,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>B2BDS11360678</t>
+          <t>0049010235402</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2223,44 +2215,44 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-03-04T11:35:13+01:00</t>
+          <t>2026-03-04T12:21:39+01:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>Föhren (DE), Germany</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-03-04T12:22:31+00:00</t>
+          <t>2026-03-04T14:56:09+00:00</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>01475240794378</t>
+          <t>01475240792815</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11360678", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010235402", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>01475240787147</t>
+          <t>ZD1RIPL5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2270,12 +2262,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0049010230663</t>
+          <t>B2BDS11419817</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2286,44 +2278,44 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-03T12:52:50+01:00</t>
+          <t>2026-03-04T12:15:04+01:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-03-04T12:22:28+00:00</t>
+          <t>2026-03-04T14:54:33+00:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>01475240787147</t>
+          <t>ZD1RIPL5</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010230663", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11419817", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>01475240794399</t>
+          <t>ZD1RIPQW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2333,12 +2325,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B2BDS11408485</t>
+          <t>1116415483-01</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2349,34 +2341,34 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-03-04T09:13:22+01:00</t>
+          <t>2026-03-04T10:50:00+01:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Koblenz (DE), Germany</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-03-04T12:21:43+00:00</t>
+          <t>2026-03-04T14:54:05+00:00</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>01475240794399</t>
+          <t>ZD1RIPQW</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11408485", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "1116415483-01", "sales_office_id": "4677"}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ZD1RIPRJ</t>
+          <t>ZD1RIPQV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2396,12 +2388,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0049010257313</t>
+          <t>1116415483-01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2412,7 +2404,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-03-04T12:05:28+01:00</t>
+          <t>2026-03-04T10:50:00+01:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2422,24 +2414,24 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-03-04T12:19:52+00:00</t>
+          <t>2026-03-04T14:54:03+00:00</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ZD1RIPRJ</t>
+          <t>ZD1RIPQV</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010257313", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "1116415483-01", "sales_office_id": "4677"}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ZD1RIPWM</t>
+          <t>ZD1RIPQU</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2459,12 +2451,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B2BDS11440221</t>
+          <t>1116415483-01</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2475,7 +2467,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-04T09:13:58+01:00</t>
+          <t>2026-03-04T10:50:00+01:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2485,24 +2477,24 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-03-04T12:19:23+00:00</t>
+          <t>2026-03-04T14:54:02+00:00</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ZD1RIPWM</t>
+          <t>ZD1RIPQU</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11440221", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "1116415483-01", "sales_office_id": "4677"}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ZD1RIPVP</t>
+          <t>ZD1RIPN9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2522,12 +2514,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0049010258612</t>
+          <t>PO-076-18644055267190905</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2538,7 +2530,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-04T11:32:26+01:00</t>
+          <t>2026-03-04T12:59:22+01:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2548,24 +2540,24 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-04T12:19:19+00:00</t>
+          <t>2026-03-04T14:53:39+00:00</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ZD1RIPVP</t>
+          <t>ZD1RIPN9</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010258612", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "PO-076-18644055267190905", "sales_office_id": "4670"}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05228742843490</t>
+          <t>05228742846313</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2585,7 +2577,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0031009965309</t>
+          <t>0032005563865</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2601,34 +2593,34 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-03T18:29:19+01:00</t>
+          <t>2026-03-03T11:47:07+01:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Meppel, NL, Netherlands</t>
+          <t>Aalter, BE, Belgium</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-03-04T11:57:09+00:00</t>
+          <t>2026-03-04T13:53:29+00:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>05228742843490</t>
+          <t>05228742846313</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009965309", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005563865", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05228742854152</t>
+          <t>05228742843747</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2648,7 +2640,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0032005568844</t>
+          <t>0032005563865</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2664,7 +2656,7 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-04T12:46:47+01:00</t>
+          <t>2026-03-03T11:47:07+01:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2674,34 +2666,34 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-04T11:57:06+00:00</t>
+          <t>2026-03-04T13:53:29+00:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>05228742854152</t>
+          <t>05228742843747</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005568844", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005563865", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05228742852679</t>
+          <t>957140555605</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>sending</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Sending Transporte Urgente y Comunicacion</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2711,12 +2703,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0032005567806</t>
+          <t>0034001430646</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2727,44 +2719,44 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-04T10:42:02+01:00</t>
+          <t>2026-03-04T17:56:38</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>BARCELONA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-03-04T13:55:32+00:00</t>
+          <t>2026-03-04T17:23:32+00:00</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>05228742852679</t>
+          <t>957140555605</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005567806", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0034001430646", "sales_office_id": "3018"}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>01475240790475</t>
+          <t>05228742854716</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2774,12 +2766,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0049010244719</t>
+          <t>0032005569225</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2790,44 +2782,44 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-03T08:57:01+01:00</t>
+          <t>2026-03-04T13:49:56+01:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Duisburg (DE), Germany</t>
+          <t>Vilvoorde, BE, Belgium</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-03-04T09:44:09+00:00</t>
+          <t>2026-03-04T13:53:15+00:00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>01475240790475</t>
+          <t>05228742854716</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010244719", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0032005569225", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ZL200086359426270</t>
+          <t>05228742854037</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>colis-prive</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Colis Privé</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2837,12 +2829,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0033005731185</t>
+          <t>0032005569225</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0302</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2853,40 +2845,44 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:36+00:00</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>2026-03-04T13:49:56+01:00</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Vilvoorde, BE, Belgium</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:37+00:00</t>
+          <t>2026-03-04T16:53:24+00:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ZL200086359426270</t>
+          <t>05228742854037</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005731185", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "0032005569225", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ZL200086359126270</t>
+          <t>UTV572230723</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>colis-prive</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Colis Privé</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2896,12 +2892,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0033005731185</t>
+          <t>0031009971989</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0302</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2912,40 +2908,44 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:36+00:00</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>2026-03-04T10:54:14+01:00</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:36+00:00</t>
+          <t>2026-03-04T13:04:30+00:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ZL200086359126270</t>
+          <t>UTV572230723</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005731185", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "0031009971989", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ZL200086358926270</t>
+          <t>UTV107113681</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>colis-prive</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Colis Privé</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0033005731185</t>
+          <t>0031009971989</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0302</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2971,40 +2971,44 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:33+00:00</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>2026-03-04T10:54:01+01:00</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:35+00:00</t>
+          <t>2026-03-04T13:04:28+00:00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ZL200086358926270</t>
+          <t>UTV107113681</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005731185", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "0031009971989", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ZL200086373926270</t>
+          <t>00KOQNFF</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>colis-prive</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Colis Privé</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3014,7 +3018,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0033005731185</t>
+          <t>0033005729405</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3030,40 +3034,44 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:34+00:00</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>2026-03-04T09:40:46+01:00</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>FR, France</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:37+00:00</t>
+          <t>2026-03-04T13:04:11+00:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ZL200086373926270</t>
+          <t>00KOQNFF</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005731185", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "0033005729405", "sales_office_id": "0302"}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ZL200086373826270</t>
+          <t>00KNSBZ5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>colis-prive</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Colis Privé</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3073,12 +3081,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0033005731185</t>
+          <t>B2BDS11325687</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0302</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3089,40 +3097,44 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:34+00:00</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>2026-03-04T08:29:43+01:00</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>FR, France</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:34+00:00</t>
+          <t>2026-03-04T13:03:44+00:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ZL200086373826270</t>
+          <t>00KNSBZ5</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005731185", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "B2BDS11325687", "sales_office_id": "4452"}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06245165503412</t>
+          <t>00KNSBZ6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>dpd-at-sftp</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DPD Austria</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3132,12 +3144,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0043000969824</t>
+          <t>B2BDS11325687</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3148,40 +3160,44 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-04T13:07:00</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>2026-03-04T08:29:43+01:00</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>FR, France</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-04T12:11:07+00:00</t>
+          <t>2026-03-04T13:03:45+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>06245165503412</t>
+          <t>00KNSBZ6</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0043000969824", "sales_office_id": "3009"}</t>
+          <t>{"external_order_id": "B2BDS11325687", "sales_office_id": "4452"}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>01475240794662</t>
+          <t>UTV232918983</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3191,12 +3207,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>cbn4wkrk4y</t>
+          <t>0031009973557</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3207,44 +3223,44 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-04T11:54:46+01:00</t>
+          <t>2026-03-03T12:39:56+01:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Uplengen-Jübberde (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-03-04T11:54:48+00:00</t>
+          <t>2026-03-04T13:03:23+00:00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>01475240794662</t>
+          <t>UTV232918983</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wkrk4y", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0031009973557", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>01475240795023</t>
+          <t>UTV630687814</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3254,12 +3270,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0049010256899</t>
+          <t>0031009974227</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3270,44 +3286,44 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-04T12:49:17+01:00</t>
+          <t>2026-03-04T11:08:20+01:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Mittenwalde (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-03-04T12:54:02+00:00</t>
+          <t>2026-03-04T13:03:23+00:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>01475240795023</t>
+          <t>UTV630687814</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010256899", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009974227", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>01475240794620</t>
+          <t>UTV631726295</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3317,12 +3333,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0049010255767</t>
+          <t>0031009974227</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3333,44 +3349,44 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-04T08:34:14+01:00</t>
+          <t>2026-03-04T11:11:04+01:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>St. Ingbert (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-04T08:53:54+00:00</t>
+          <t>2026-03-04T13:03:23+00:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>01475240794620</t>
+          <t>UTV631726295</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010255767", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009974227", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ZD1RIPBV</t>
+          <t>UTV981141134</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3380,12 +3396,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>B2BDS11376184</t>
+          <t>0031009974227</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3396,44 +3412,44 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-04T12:05:57+01:00</t>
+          <t>2026-03-04T11:11:30+01:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-03-04T11:46:34+00:00</t>
+          <t>2026-03-04T13:03:19+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ZD1RIPBV</t>
+          <t>UTV981141134</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11376184", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009974227", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ZD1RIP55</t>
+          <t>00KNRU6M</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3443,12 +3459,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>B2BDS11358873</t>
+          <t>0031009980890</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3459,44 +3475,44 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-04T09:00:26+01:00</t>
+          <t>2026-03-04T13:19:34+01:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-03-04T12:20:07+00:00</t>
+          <t>2026-03-04T14:49:41+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ZD1RIP55</t>
+          <t>00KNRU6M</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11358873", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009980890", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>01475240792807</t>
+          <t>00KNRU6B</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3506,12 +3522,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>B2BDS11364055</t>
+          <t>0031009980890</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3522,44 +3538,44 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-03-04T10:26:15+01:00</t>
+          <t>2026-03-04T13:19:34+01:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Hamm (DE), Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-03-04T09:47:00+00:00</t>
+          <t>2026-03-04T14:49:41+00:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>01475240792807</t>
+          <t>00KNRU6B</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11364055", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009980890", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>80840147987802</t>
+          <t>00KNRUAL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3569,12 +3585,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0351001381540</t>
+          <t>0031009980632</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3585,40 +3601,44 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-03-04T12:04:00</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>2026-03-04T15:17:11+01:00</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-03-04T13:20:07+00:00</t>
+          <t>2026-03-04T14:54:52+00:00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>80840147987802</t>
+          <t>00KNRUAL</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0351001381540", "sales_office_id": "3024"}</t>
+          <t>{"external_order_id": "0031009980632", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>UTV861289583</t>
+          <t>00KNRU3P</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3628,7 +3648,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0031009978686</t>
+          <t>0031009980632</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3644,44 +3664,44 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-04T13:12:13+01:00</t>
+          <t>2026-03-04T15:17:11+01:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-03-04T13:49:12+00:00</t>
+          <t>2026-03-04T14:54:53+00:00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>UTV861289583</t>
+          <t>00KNRU3P</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009978686", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009980632", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>UTV765312164</t>
+          <t>00KNRTMP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3691,7 +3711,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0031009978686</t>
+          <t>0031009978568</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3707,44 +3727,44 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-04T13:11:58+01:00</t>
+          <t>2026-03-04T12:02:01+01:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-04T13:49:12+00:00</t>
+          <t>2026-03-04T17:25:18+00:00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>UTV765312164</t>
+          <t>00KNRTMP</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009978686", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009978568", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06086432953429</t>
+          <t>00KNRU3I</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>dpd-ch-sftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DPD Switzerland</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3754,12 +3774,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0041006360823</t>
+          <t>0031009977643</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0323</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3770,44 +3790,44 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-04T10:11:45+01:00</t>
+          <t>2026-03-04T12:42:16+01:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>,Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-04T09:37:54+00:00</t>
+          <t>2026-03-04T12:24:28+00:00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>06086432953429</t>
+          <t>00KNRU3I</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0041006360823", "sales_office_id": "0323"}</t>
+          <t>{"external_order_id": "0031009977643", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JVGLOTC0098890097</t>
+          <t>00KNRU46</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3817,52 +3837,60 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6001670971</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>0031009977643</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-03-04T13:02:11+01:00</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+          <t>2026-03-04T12:42:16+01:00</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-03-04T12:13:56+00:00</t>
+          <t>2026-03-04T12:24:28+00:00</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>JVGLOTC0098890097</t>
+          <t>00KNRU46</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "0031009977643", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>02057856002373</t>
+          <t>00KNRT87</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>hermes-de</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hermes Germany</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3872,56 +3900,60 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6001672020</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>0031009977643</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-03T16:46:05+01:00</t>
+          <t>2026-03-04T12:42:16+01:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:48+00:00</t>
+          <t>2026-03-04T12:24:28+00:00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>02057856002373</t>
+          <t>00KNRT87</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "0031009977643", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>05222069750950</t>
+          <t>00KNRUH1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3931,56 +3963,60 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6001668620</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>0031009982544</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-02-24T15:14:55+01:00</t>
+          <t>2026-03-04T14:51:25+01:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Joure, NL, Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:52+00:00</t>
+          <t>2026-03-04T14:24:33+00:00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>05222069750950</t>
+          <t>00KNRUH1</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "0031009982544", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>REC000080955752</t>
+          <t>00KNRUH0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3990,52 +4026,60 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6001668765</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>0031009982544</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-03-04T10:49:00</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>2026-03-04T14:51:25+01:00</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-04T11:20:02+00:00</t>
+          <t>2026-03-04T14:24:37+00:00</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>REC000080955752</t>
+          <t>00KNRUH0</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "0031009982544", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>REC000080962198</t>
+          <t>00KNRTCT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4045,52 +4089,60 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6001670166</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>0031009978276</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-03-04T11:37:00</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>2026-03-04T12:00:43+01:00</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:44+00:00</t>
+          <t>2026-03-04T12:24:26+00:00</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>REC000080962198</t>
+          <t>00KNRTCT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "0031009978276", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>REC000080960938</t>
+          <t>00KNRTAS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4100,52 +4152,60 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>6001670080</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>0031009978276</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-03-04T11:24:00</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>2026-03-04T12:00:43+01:00</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:42+00:00</t>
+          <t>2026-03-04T12:24:25+00:00</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>REC000080960938</t>
+          <t>00KNRTAS</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "0031009978276", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>REC000080989257</t>
+          <t>00KNRUGH</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4155,52 +4215,60 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6001671464</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>0031009982259</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-04T11:24:00</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>2026-03-04T10:16:46+01:00</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:42+00:00</t>
+          <t>2026-03-04T12:24:06+00:00</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>REC000080989257</t>
+          <t>00KNRUGH</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "0031009982259", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>REC000080956839</t>
+          <t>00KNRUGF</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4210,52 +4278,60 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>6001669414</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>0031009982259</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-03-04T10:37:00</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>2026-03-04T10:16:46+01:00</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-04T10:17:39+00:00</t>
+          <t>2026-03-04T12:24:02+00:00</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>REC000080956839</t>
+          <t>00KNRUGF</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "0031009982259", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>REC000080956030</t>
+          <t>00KNRU3D</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4265,52 +4341,60 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>6001669121</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>0031009981113</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-03-04T11:59:00</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>2026-03-04T12:39:26+01:00</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-04T11:20:02+00:00</t>
+          <t>2026-03-04T14:54:06+00:00</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>REC000080956030</t>
+          <t>00KNRU3D</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "0031009981113", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>REC000080959604</t>
+          <t>00KNRU62</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4320,52 +4404,60 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6001669920</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>0031009982031</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-04T11:37:00</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
+          <t>2026-03-04T14:03:56+01:00</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:42+00:00</t>
+          <t>2026-03-04T13:24:01+00:00</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>REC000080959604</t>
+          <t>00KNRU62</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "0031009982031", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>REC000080958055</t>
+          <t>01475240794415</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4375,52 +4467,60 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>6001669687</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>B2BDS11396937</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-04T10:24:00</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
+          <t>2026-03-04T12:01:34+01:00</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Föhren (DE), Germany</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-03-04T10:17:39+00:00</t>
+          <t>2026-03-04T12:52:56+00:00</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>REC000080958055</t>
+          <t>01475240794415</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "B2BDS11396937", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>REC000080962144</t>
+          <t>01475240794595</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4430,52 +4530,60 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>6001670154</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>B2BDS11396937</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-03-04T11:15:00</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
+          <t>2026-03-04T12:01:34+01:00</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Föhren (DE), Germany</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:43+00:00</t>
+          <t>2026-03-04T12:22:59+00:00</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>REC000080962144</t>
+          <t>01475240794595</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "B2BDS11396937", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ZDDO3PDO</t>
+          <t>01475240792974</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4485,56 +4593,60 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>6001670023</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>0049010248060</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T11:14:15+01:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Hagen (DE), Germany</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T12:22:43+00:00</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ZDDO3PDO</t>
+          <t>01475240792974</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0049010248060", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ZDDO3P9M</t>
+          <t>01475240792242</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4544,56 +4656,60 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>6001668541</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+          <t>0049010248060</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T11:14:15+01:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Hagen (DE), Germany</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T12:22:41+00:00</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ZDDO3P9M</t>
+          <t>01475240792242</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0049010248060", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ZDDO3PFP</t>
+          <t>01475240791007</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4603,56 +4719,60 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>6001670644</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>1024909717-A</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-03T17:48:39+01:00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Hamburg (DE), Germany</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T12:22:38+00:00</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>ZDDO3PFP</t>
+          <t>01475240791007</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "1024909717-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ZDDO3PBL</t>
+          <t>01475240794378</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4662,56 +4782,60 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>6001669288</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>B2BDS11360678</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T11:35:13+01:00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T12:22:31+00:00</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>ZDDO3PBL</t>
+          <t>01475240794378</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "B2BDS11360678", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ZDDO3PFS</t>
+          <t>01475240787147</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4721,56 +4845,60 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>6001670644</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>0049010230663</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-03T12:52:50+01:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T12:22:28+00:00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ZDDO3PFS</t>
+          <t>01475240787147</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0049010230663", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ZDDO3PFR</t>
+          <t>01475240794399</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4780,46 +4908,50 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6001670644</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+          <t>B2BDS11408485</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T09:13:22+01:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Koblenz (DE), Germany</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T12:21:43+00:00</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>ZDDO3PFR</t>
+          <t>01475240794399</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "B2BDS11408485", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ZDDO3PDQ</t>
+          <t>ZD1RIPRJ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4839,19 +4971,23 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6001670023</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
+          <t>0049010257313</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T12:05:28+01:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4861,24 +4997,24 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-03-04T13:05:59+00:00</t>
+          <t>2026-03-04T12:19:52+00:00</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ZDDO3PDQ</t>
+          <t>ZD1RIPRJ</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0049010257313", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ZDDO3PGP</t>
+          <t>ZD1RIPWM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4898,19 +5034,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6001671274</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>B2BDS11440221</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T09:13:58+01:00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4920,24 +5060,24 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T12:19:23+00:00</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ZDDO3PGP</t>
+          <t>ZD1RIPWM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "B2BDS11440221", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>YVX879MT</t>
+          <t>ZD1RIPVP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4957,19 +5097,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>6001670301</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+          <t>0049010258612</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T11:32:26+01:00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4979,34 +5123,34 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:04+00:00</t>
+          <t>2026-03-04T12:19:19+00:00</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>YVX879MT</t>
+          <t>ZD1RIPVP</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0049010258612", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Z7V7CSVI</t>
+          <t>05228742853589</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5016,56 +5160,60 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>6001670000</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>0032005569348</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-03-04T07:30:48+01:00</t>
+          <t>2026-03-04T17:34:33+01:00</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>AT, Austria</t>
+          <t>Kortrijk, BE, Belgium</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-03-04T11:26:18+00:00</t>
+          <t>2026-03-04T16:58:21+00:00</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Z7V7CSVI</t>
+          <t>05228742853589</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0032005569348", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ZDDO3PDN</t>
+          <t>05228742853565</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5075,56 +5223,60 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>6001670023</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+          <t>0032005569348</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T17:34:33+01:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Kortrijk, BE, Belgium</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T16:58:40+00:00</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>ZDDO3PDN</t>
+          <t>05228742853565</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0032005569348", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ZDDO3PDP</t>
+          <t>05228742843490</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5134,56 +5286,60 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>6001670023</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>0031009965309</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-03T18:29:19+01:00</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Meppel, NL, Netherlands</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T11:57:09+00:00</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>ZDDO3PDP</t>
+          <t>05228742843490</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0031009965309", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ZDDO3PF5</t>
+          <t>05228742854704</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5193,56 +5349,60 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>6001670411</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+          <t>0031009973161</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T16:12:48+01:00</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Vijfhuizen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-03-04T13:05:58+00:00</t>
+          <t>2026-03-04T15:57:42+00:00</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>ZDDO3PF5</t>
+          <t>05228742854704</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0031009973161", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ZDDO3PFQ</t>
+          <t>05228742854152</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5252,56 +5412,60 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>6001670644</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+          <t>0032005568844</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T12:46:47+01:00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Aalter, BE, Belgium</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-03-04T13:05:58+00:00</t>
+          <t>2026-03-04T11:57:06+00:00</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>ZDDO3PFQ</t>
+          <t>05228742854152</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0032005568844", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>YVX879MS</t>
+          <t>05228742854586</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5311,51 +5475,55 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>6001670301</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>0032005568863</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
+          <t>2026-03-04T14:59:05+01:00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Lummen, BE, Belgium</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:06+00:00</t>
+          <t>2026-03-04T14:57:08+00:00</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>YVX879MS</t>
+          <t>05228742854586</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "0032005568863", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>05222006538667</t>
+          <t>05228742848586</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5370,51 +5538,55 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>6001671419</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
+          <t>0031009967281</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:22+01:00</t>
+          <t>2026-03-04T14:35:52+01:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Maastricht, NL, Netherlands</t>
+          <t>Etten-Leur, NL, Netherlands</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:37+00:00</t>
+          <t>2026-03-04T14:27:35+00:00</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>05222006538667</t>
+          <t>05228742848586</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0031009967281", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>05222006538652</t>
+          <t>05228742852679</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5429,56 +5601,60 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>6001670937</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
+          <t>0032005567806</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-03T15:00:39+01:00</t>
+          <t>2026-03-04T10:42:02+01:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Taulov, DK, Denmark</t>
+          <t>Courcelles, BE, Belgium</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:35+00:00</t>
+          <t>2026-03-04T13:55:32+00:00</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>05222006538652</t>
+          <t>05228742852679</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0032005567806", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>05222006538620</t>
+          <t>01475240792048</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5488,56 +5664,60 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>6001668303</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
+          <t>0049010244719</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-03-03T15:00:42+01:00</t>
+          <t>2026-03-04T17:01:51+01:00</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Broendby, DK, Denmark</t>
+          <t>Duisburg (DE), Germany</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:34+00:00</t>
+          <t>2026-03-04T16:44:13+00:00</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>05222006538620</t>
+          <t>01475240792048</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0049010244719", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>05222006538633</t>
+          <t>01475240790475</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5547,56 +5727,60 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>6001669766</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
+          <t>0049010244719</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-03-03T09:44:57+01:00</t>
+          <t>2026-03-03T08:57:01+01:00</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Tynaarlo, NL, Netherlands</t>
+          <t>Duisburg (DE), Germany</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-03-04T10:43:40+00:00</t>
+          <t>2026-03-04T09:44:09+00:00</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>05222006538633</t>
+          <t>01475240790475</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0049010244719", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>05222006538651</t>
+          <t>ZL200086359426270</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>colis-prive</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Colis Privé</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5606,56 +5790,56 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>6001670937</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+          <t>0033005731185</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-03-03T15:00:39+01:00</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Taulov, DK, Denmark</t>
-        </is>
-      </c>
+          <t>2026-03-04T12:42:36+00:00</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-03-04T10:43:40+00:00</t>
+          <t>2026-03-04T12:42:37+00:00</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>05222006538651</t>
+          <t>ZL200086359426270</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0033005731185", "sales_office_id": "0302"}</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>05222006538683</t>
+          <t>ZL200086359126270</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>colis-prive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Colis Privé</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5665,56 +5849,56 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>6001671710</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
+          <t>0033005731185</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-03-04T10:13:38+01:00</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>NL, Netherlands</t>
-        </is>
-      </c>
+          <t>2026-03-04T12:42:36+00:00</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-03-04T09:43:42+00:00</t>
+          <t>2026-03-04T12:42:36+00:00</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>05222006538683</t>
+          <t>ZL200086359126270</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0033005731185", "sales_office_id": "0302"}</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0053231072667W</t>
+          <t>ZL200086358926270</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>colis-prive</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Colis Privé</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5724,56 +5908,56 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>6001669793</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
+          <t>0033005731185</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>ROSANOW, PL, Poland</t>
-        </is>
-      </c>
+          <t>2026-03-04T12:42:33+00:00</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-04T09:43:45+00:00</t>
+          <t>2026-03-04T12:42:35+00:00</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0053231072667W</t>
+          <t>ZL200086358926270</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0033005731185", "sales_office_id": "0302"}</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>05222006538684</t>
+          <t>ZL200086373926270</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>colis-prive</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Colis Privé</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5783,56 +5967,56 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>6001671763</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
+          <t>0033005731185</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-03-04T12:36:55+01:00</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Oirschot, NL, Netherlands</t>
-        </is>
-      </c>
+          <t>2026-03-04T12:42:34+00:00</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-03-04T12:43:47+00:00</t>
+          <t>2026-03-04T12:42:37+00:00</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>05222006538684</t>
+          <t>ZL200086373926270</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0033005731185", "sales_office_id": "0302"}</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>05222006538629</t>
+          <t>ZL200086373826270</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>colis-prive</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Colis Privé</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5842,56 +6026,56 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>6001669193</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>0033005731185</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-03-04T08:46:41+01:00</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Oirschot, NL, Netherlands</t>
-        </is>
-      </c>
+          <t>2026-03-04T12:42:34+00:00</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-03-04T09:43:40+00:00</t>
+          <t>2026-03-04T12:42:34+00:00</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>05222006538629</t>
+          <t>ZL200086373826270</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0033005731185", "sales_office_id": "0302"}</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>05222006538662</t>
+          <t>00370733747468331301</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>posten-norge</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Posten Norge / Bring</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5901,56 +6085,60 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>6001671228</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+          <t>0046006020717</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-03-04T10:27:10+01:00</t>
+          <t>2026-03-04T15:47:50+01:00</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Vijfhuizen, NL, Netherlands</t>
+          <t>,Sweden</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-03-04T13:44:10+00:00</t>
+          <t>2026-03-04T17:35:16+00:00</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>05222006538662</t>
+          <t>00370733747468331301</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0046006020717", "sales_office_id": "0307"}</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>05222069771183</t>
+          <t>00370733747468330106</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>posten-norge</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Posten Norge / Bring</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5960,56 +6148,60 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>6001668953</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
+          <t>0046006020717</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-02T14:27:11+01:00</t>
+          <t>2026-03-04T15:47:50+01:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Beverwijk, NL, Netherlands</t>
+          <t>,Sweden</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:34+00:00</t>
+          <t>2026-03-04T17:35:31+00:00</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>05222069771183</t>
+          <t>00370733747468330106</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0046006020717", "sales_office_id": "0307"}</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1Z6X581R6895891837</t>
+          <t>06245165503412</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>dpd-at-sftp</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>DPD Austria</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6019,12 +6211,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0353000395812</t>
+          <t>0043000969824</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6035,25 +6227,3270 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
+          <t>2026-03-04T13:07:00</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:11:07+00:00</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>06245165503412</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0043000969824", "sales_office_id": "3009"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>05228742852986</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>79466283-A</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>4322</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:17:46+01:00</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Berkel en Rodenrijs, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:55:15+00:00</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>05228742852986</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "79466283-A", "sales_office_id": "4322"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>01475240794662</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>cbn4wkrk4y</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:54:46+01:00</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Uplengen-Jübberde (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:54:48+00:00</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>01475240794662</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "cbn4wkrk4y", "sales_office_id": "4316"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>05228742848490</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>dpd-api</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0031009967904</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-03-04T15:35:54+01:00</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Vijfhuizen, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-03-04T16:55:59+00:00</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>05228742848490</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009967904", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>01475240795023</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0049010256899</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:49:17+01:00</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Mittenwalde (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:54:02+00:00</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>01475240795023</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010256899", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>01475240794620</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0049010255767</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-03-04T08:34:14+01:00</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>St. Ingbert (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-03-04T08:53:54+00:00</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>01475240794620</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0049010255767", "sales_office_id": "0301"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ZD1RIPBV</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>B2BDS11376184</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:05:57+01:00</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>ZD1RIPBV</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "B2BDS11376184", "sales_office_id": "4436"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ZD1RIP55</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>B2BDS11358873</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:00:26+01:00</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:20:07+00:00</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>ZD1RIP55</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "B2BDS11358873", "sales_office_id": "4436"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>01475240792807</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>dpd-de</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>DPD Germany</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>B2BDS11364055</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:26:15+01:00</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Hamm (DE), Germany</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:47:00+00:00</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>01475240792807</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "B2BDS11364055", "sales_office_id": "4436"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>80840147987802</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0351001381540</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:04:00</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:20:07+00:00</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>80840147987802</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0351001381540", "sales_office_id": "3024"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>80870147980933</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>82189342-A</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>4313</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-03-04T16:50:00</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-03-04T17:20:53+00:00</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>80870147980933</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "82189342-A", "sales_office_id": "4313"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>80870147980940</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>82189342-A</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>4313</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-03-04T16:50:00</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-03-04T17:20:53+00:00</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>80870147980940</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "82189342-A", "sales_office_id": "4313"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>UTV765312164</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0031009978686</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:11:58+01:00</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:49:12+00:00</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>UTV765312164</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009978686", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>UTV861289583</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Packs</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0031009978686</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:12:13+01:00</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>,Netherlands</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:49:12+00:00</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>UTV861289583</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0031009978686", "sales_office_id": "0303"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>06086432953429</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>dpd-ch-sftp</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>DPD Switzerland</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0041006360823</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0323</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:11:45+01:00</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>,Switzerland</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-03-04T15:31:18+00:00</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>06086432953429</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>{"external_order_id": "0041006360823", "sales_office_id": "0323"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>02057856002373</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>hermes-de</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Hermes Germany</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>6001672020</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:46:05+01:00</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-03-04T06:43:48+00:00</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>02057856002373</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>JVGLOTC0098890097</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>dhlparcel-nl</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>DHL Parcel NL</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>6001670971</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:02:11+01:00</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>JVGLOTC0098890097</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>05222069750950</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>6001668620</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-02-24T15:14:55+01:00</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Joure, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-03-04T06:43:52+00:00</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>05222069750950</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>REC000080958055</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>6001669687</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:24:00</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:17:39+00:00</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>REC000080958055</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>REC000080989257</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>6001671464</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:24:00</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:19:42+00:00</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>REC000080989257</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>REC000080960938</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>6001670080</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:24:00</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:19:42+00:00</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>REC000080960938</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>REC000080956030</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>6001669121</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:59:00</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:20:02+00:00</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>REC000080956030</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>REC000080956839</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>6001669414</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:37:00</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:17:39+00:00</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>REC000080956839</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>REC000080962198</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>6001670166</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:37:00</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>REC000080962198</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>REC000080959604</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>6001669920</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:37:00</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:19:42+00:00</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>REC000080959604</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>REC000080955752</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>6001668765</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:49:00</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-03-04T17:20:09+00:00</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>REC000080955752</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>REC000080956766</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>6001669406</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-03-04T16:53:00</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2026-03-04T16:19:08+00:00</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>REC000080956766</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>REC000080962144</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>spanish-seur-ftp</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>6001670154</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:15:00</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:19:43+00:00</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>REC000080962144</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ZDDO3PFP</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>6001670644</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>ZDDO3PFP</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ZDDO3PDO</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>6001670023</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>ZDDO3PDO</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ZDDO3PBL</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>6001669288</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>ZDDO3PBL</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ZDDO3P9M</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>6001668541</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>ZDDO3P9M</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ZDDO3PFS</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>6001670644</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>ZDDO3PFS</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ZDDO3PFR</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>6001670644</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>ZDDO3PFR</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ZDDO3PDQ</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>6001670023</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>ZDDO3PDQ</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>YVX879MT</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>6001670301</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>YVX879MT</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ZDDO3PGP</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>6001671274</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>ZDDO3PGP</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Z7V7CSVI</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>6001670000</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-03-04T07:30:48+01:00</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>AT, Austria</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2026-03-04T11:26:18+00:00</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Z7V7CSVI</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ZDDO3PDN</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>6001670023</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>ZDDO3PDN</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ZDDO3PDP</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>6001670023</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>ZDDO3PDP</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ZDDO3PF5</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>6001670411</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:05:58+00:00</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>ZDDO3PF5</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>YVX879MS</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>6001670301</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:06:06+00:00</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>YVX879MS</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ZDDO3PFQ</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>gls</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>6001670644</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:00:00+01:00</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:05:58+00:00</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>ZDDO3PFQ</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>05222006538683</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>6001671710</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:13:38+01:00</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:43:42+00:00</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>05222006538683</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>05222006538684</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>6001671763</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-03-04T12:36:55+01:00</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Oirschot, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2026-03-04T16:43:52+00:00</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>05222006538684</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>0053231072667W</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>6001669793</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:05:00+01:00</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>ROSANOW, PL, Poland</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:43:45+00:00</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>0053231072667W</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>05222006538651</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>6001670937</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-03-03T15:00:39+01:00</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Taulov, DK, Denmark</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:43:40+00:00</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>05222006538651</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>05222006538667</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>6001671419</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:05:22+01:00</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Maastricht, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2026-03-04T06:43:37+00:00</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>05222006538667</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>05222006538652</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>6001670937</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-03-03T15:00:39+01:00</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Taulov, DK, Denmark</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2026-03-04T06:43:35+00:00</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>05222006538652</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>05222006538633</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>6001669766</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:44:57+01:00</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Tynaarlo, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:43:40+00:00</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>05222006538633</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>05222006538643</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>6001670502</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:28:24+01:00</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2026-03-04T15:43:52+00:00</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>05222006538643</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>05222006538620</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>6001668303</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-03-03T15:00:42+01:00</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Broendby, DK, Denmark</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-03-04T06:43:34+00:00</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>05222006538620</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>05222006538629</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>6001669193</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-03-04T08:46:41+01:00</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Oirschot, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:43:40+00:00</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>05222006538629</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>05222006538662</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>6001671228</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:27:10+01:00</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Vijfhuizen, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:44:10+00:00</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>05222006538662</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>05222069771183</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>6001668953</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-03-02T14:27:11+01:00</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Beverwijk, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2026-03-04T06:43:34+00:00</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>05222069771183</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1Z6X581R6895891837</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ups-api</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ups-api</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0353000395812</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>3027</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
           <t>2026-02-24T12:56:27+00:00</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J148" t="inlineStr">
         <is>
           <t>XXX, GOREY, Y25, IE, Ireland</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K148" t="inlineStr">
         <is>
           <t>2026-03-04T05:06:53+00:00</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t>1Z6X581R6895891837</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t>{"external_order_id": "0353000395812", "sales_office_id": "3027"}</t>
         </is>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,7 +549,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00KNRSZS</t>
+          <t>00KNRSZW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:30+00:00</t>
+          <t>2026-03-04T15:54:31+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>00KNRSZS</t>
+          <t>00KNRSZW</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00KNRT00</t>
+          <t>00KNRSZX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:32+00:00</t>
+          <t>2026-03-04T15:54:34+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>00KNRT00</t>
+          <t>00KNRSZX</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00KNRSZX</t>
+          <t>00KNRSZS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:34+00:00</t>
+          <t>2026-03-04T15:54:30+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>00KNRSZX</t>
+          <t>00KNRSZS</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -738,7 +738,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00KNRSZR</t>
+          <t>00KNRSZU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:30+00:00</t>
+          <t>2026-03-04T15:54:31+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>00KNRSZR</t>
+          <t>00KNRSZU</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00KNRSZU</t>
+          <t>00KNRT00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:31+00:00</t>
+          <t>2026-03-04T15:54:32+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>00KNRSZU</t>
+          <t>00KNRT00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00KNRSZT</t>
+          <t>00KNRSZR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>00KNRSZT</t>
+          <t>00KNRSZR</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00KNRSZW</t>
+          <t>00KNRSZT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:31+00:00</t>
+          <t>2026-03-04T15:54:30+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>00KNRSZW</t>
+          <t>00KNRSZT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ZI67DV4E</t>
+          <t>ZI67DV4D</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-04T15:52:16+00:00</t>
+          <t>2026-03-04T15:52:15+00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ZI67DV4E</t>
+          <t>ZI67DV4D</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1620,7 +1620,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ZI67DV4D</t>
+          <t>ZI67DV4E</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-03-04T15:52:15+00:00</t>
+          <t>2026-03-04T15:52:16+00:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ZI67DV4D</t>
+          <t>ZI67DV4E</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>YNQAF937</t>
+          <t>YNQAF93O</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-03-04T15:51:08+00:00</t>
+          <t>2026-03-04T15:51:07+00:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>YNQAF937</t>
+          <t>YNQAF93O</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1872,7 +1872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>YNQAF93O</t>
+          <t>YNQAF937</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-03-04T15:51:07+00:00</t>
+          <t>2026-03-04T15:51:08+00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>YNQAF93O</t>
+          <t>YNQAF937</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-03-04T15:50:26+00:00</t>
+          <t>2026-03-04T19:50:31+00:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00KNSBZ5</t>
+          <t>00KNSBZ6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-04T13:03:44+00:00</t>
+          <t>2026-03-04T13:03:45+00:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>00KNSBZ5</t>
+          <t>00KNSBZ6</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3124,7 +3124,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00KNSBZ6</t>
+          <t>00KNSBZ5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-04T13:03:45+00:00</t>
+          <t>2026-03-04T13:03:44+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>00KNSBZ6</t>
+          <t>00KNSBZ5</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00KNRU6M</t>
+          <t>00KNRU6B</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>00KNRU6M</t>
+          <t>00KNRU6B</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00KNRU6B</t>
+          <t>00KNRU6M</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>00KNRU6B</t>
+          <t>00KNRU6M</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3817,7 +3817,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>00KNRU46</t>
+          <t>00KNRT87</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>00KNRU46</t>
+          <t>00KNRT87</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3880,7 +3880,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>00KNRT87</t>
+          <t>00KNRU46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>00KNRT87</t>
+          <t>00KNRU46</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4195,7 +4195,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>00KNRUGH</t>
+          <t>00KNRUGF</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-03-04T12:24:06+00:00</t>
+          <t>2026-03-04T12:24:02+00:00</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>00KNRUGH</t>
+          <t>00KNRUGF</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4258,7 +4258,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>00KNRUGF</t>
+          <t>00KNRUGH</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-04T12:24:02+00:00</t>
+          <t>2026-03-04T12:24:06+00:00</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>00KNRUGF</t>
+          <t>00KNRUGH</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5829,7 +5829,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ZL200086359126270</t>
+          <t>ZL200086358926270</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5865,18 +5865,18 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:36+00:00</t>
+          <t>2026-03-04T12:42:33+00:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:36+00:00</t>
+          <t>2026-03-04T12:42:35+00:00</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>ZL200086359126270</t>
+          <t>ZL200086358926270</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -5888,7 +5888,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ZL200086358926270</t>
+          <t>ZL200086359126270</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5924,18 +5924,18 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:33+00:00</t>
+          <t>2026-03-04T12:42:36+00:00</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-04T12:42:35+00:00</t>
+          <t>2026-03-04T12:42:36+00:00</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>ZL200086358926270</t>
+          <t>ZL200086359126270</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>UTV765312164</t>
+          <t>UTV467285566</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0031009978686</t>
+          <t>0031009971388</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6967,7 +6967,7 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-03-04T13:11:58+01:00</t>
+          <t>2026-03-04T18:19:26+01:00</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6977,17 +6977,17 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-03-04T13:49:12+00:00</t>
+          <t>2026-03-04T19:50:05+00:00</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>UTV765312164</t>
+          <t>UTV467285566</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009978686", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009971388", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -7057,17 +7057,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>06086432953429</t>
+          <t>UTV765312164</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>dpd-ch-sftp</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DPD Switzerland</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0041006360823</t>
+          <t>0031009978686</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0323</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7093,44 +7093,44 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-04T10:11:45+01:00</t>
+          <t>2026-03-04T13:11:58+01:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>,Switzerland</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-03-04T15:31:18+00:00</t>
+          <t>2026-03-04T13:49:12+00:00</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>06086432953429</t>
+          <t>UTV765312164</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0041006360823", "sales_office_id": "0323"}</t>
+          <t>{"external_order_id": "0031009978686", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>02057856002373</t>
+          <t>06086432953429</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>hermes-de</t>
+          <t>dpd-ch-sftp</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hermes Germany</t>
+          <t>DPD Switzerland</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7140,39 +7140,43 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>6001672020</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>0041006360823</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0323</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-03T16:46:05+01:00</t>
+          <t>2026-03-04T10:11:45+01:00</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>,Switzerland</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:48+00:00</t>
+          <t>2026-03-04T15:31:18+00:00</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>02057856002373</t>
+          <t>06086432953429</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "0041006360823", "sales_office_id": "0323"}</t>
         </is>
       </c>
     </row>
@@ -7234,17 +7238,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>05222069750950</t>
+          <t>02057856002373</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>hermes-de</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Hermes Germany</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7254,7 +7258,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>6001668620</t>
+          <t>6001672020</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -7266,22 +7270,22 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-02-24T15:14:55+01:00</t>
+          <t>2026-03-03T16:46:05+01:00</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Joure, NL, Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:52+00:00</t>
+          <t>2026-03-04T06:43:48+00:00</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>05222069750950</t>
+          <t>02057856002373</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -7293,17 +7297,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>REC000080958055</t>
+          <t>05222069750950</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7313,7 +7317,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>6001669687</t>
+          <t>6001668620</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -7325,30 +7329,34 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-03-04T10:24:00</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr"/>
+          <t>2026-02-24T15:14:55+01:00</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Joure, NL, Netherlands</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-03-04T10:17:39+00:00</t>
+          <t>2026-03-04T06:43:52+00:00</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>REC000080958055</t>
+          <t>05222069750950</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>REC000080989257</t>
+          <t>REC000080959604</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7368,7 +7376,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>6001671464</t>
+          <t>6001669920</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -7380,7 +7388,7 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-04T11:24:00</t>
+          <t>2026-03-04T11:37:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -7391,7 +7399,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>REC000080989257</t>
+          <t>REC000080959604</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -7403,7 +7411,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>REC000080960938</t>
+          <t>REC000080956766</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7423,7 +7431,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>6001670080</t>
+          <t>6001669406</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -7435,18 +7443,18 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-03-04T11:24:00</t>
+          <t>2026-03-04T16:53:00</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:42+00:00</t>
+          <t>2026-03-04T16:19:08+00:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>REC000080960938</t>
+          <t>REC000080956766</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -7458,7 +7466,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>REC000080956030</t>
+          <t>REC000080989257</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7478,7 +7486,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>6001669121</t>
+          <t>6001671464</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -7490,18 +7498,18 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-04T11:59:00</t>
+          <t>2026-03-04T11:24:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-03-04T11:20:02+00:00</t>
+          <t>2026-03-04T11:19:42+00:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>REC000080956030</t>
+          <t>REC000080989257</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -7513,7 +7521,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>REC000080956839</t>
+          <t>REC000080955752</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7533,7 +7541,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>6001669414</t>
+          <t>6001668765</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -7545,18 +7553,18 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-03-04T10:37:00</t>
+          <t>2026-03-04T10:49:00</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-03-04T10:17:39+00:00</t>
+          <t>2026-03-04T17:20:09+00:00</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>REC000080956839</t>
+          <t>REC000080955752</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -7623,7 +7631,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>REC000080959604</t>
+          <t>REC000080958055</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7643,7 +7651,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>6001669920</t>
+          <t>6001669687</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -7655,18 +7663,18 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-03-04T11:37:00</t>
+          <t>2026-03-04T10:24:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:42+00:00</t>
+          <t>2026-03-04T10:17:39+00:00</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>REC000080959604</t>
+          <t>REC000080958055</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -7678,7 +7686,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>REC000080955752</t>
+          <t>REC000080956030</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7698,7 +7706,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>6001668765</t>
+          <t>6001669121</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -7710,18 +7718,18 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-03-04T10:49:00</t>
+          <t>2026-03-04T11:59:00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-03-04T17:20:09+00:00</t>
+          <t>2026-03-04T11:20:02+00:00</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>REC000080955752</t>
+          <t>REC000080956030</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -7733,7 +7741,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>REC000080956766</t>
+          <t>REC000080960938</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7753,7 +7761,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>6001669406</t>
+          <t>6001670080</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -7765,18 +7773,18 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-03-04T16:53:00</t>
+          <t>2026-03-04T11:24:00</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-03-04T16:19:08+00:00</t>
+          <t>2026-03-04T11:19:42+00:00</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>REC000080956766</t>
+          <t>REC000080960938</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -7788,7 +7796,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REC000080962144</t>
+          <t>REC000080956839</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7808,7 +7816,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>6001670154</t>
+          <t>6001669414</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -7820,18 +7828,18 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-03-04T11:15:00</t>
+          <t>2026-03-04T10:37:00</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:43+00:00</t>
+          <t>2026-03-04T10:17:39+00:00</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>REC000080962144</t>
+          <t>REC000080956839</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -7843,17 +7851,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ZDDO3PFP</t>
+          <t>REC000080962144</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7863,7 +7871,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>6001670644</t>
+          <t>6001670154</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -7875,34 +7883,30 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-04T14:00:00+01:00</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>DE, Germany</t>
-        </is>
-      </c>
+          <t>2026-03-04T11:15:00</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T11:19:43+00:00</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>ZDDO3PFP</t>
+          <t>REC000080962144</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ZDDO3PDO</t>
+          <t>ZDDO3PBL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7922,7 +7926,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>6001670023</t>
+          <t>6001669288</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -7949,7 +7953,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>ZDDO3PDO</t>
+          <t>ZDDO3PBL</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -7961,7 +7965,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ZDDO3PBL</t>
+          <t>ZDDO3PDO</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7981,7 +7985,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>6001669288</t>
+          <t>6001670023</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -8008,7 +8012,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>ZDDO3PBL</t>
+          <t>ZDDO3PDO</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -8020,7 +8024,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ZDDO3P9M</t>
+          <t>ZDDO3PFS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8040,7 +8044,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>6001668541</t>
+          <t>6001670644</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -8067,7 +8071,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>ZDDO3P9M</t>
+          <t>ZDDO3PFS</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -8079,7 +8083,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ZDDO3PFS</t>
+          <t>ZDDO3PFP</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8126,7 +8130,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>ZDDO3PFS</t>
+          <t>ZDDO3PFP</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -8138,7 +8142,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ZDDO3PFR</t>
+          <t>ZDDO3P9M</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8158,7 +8162,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>6001670644</t>
+          <t>6001668541</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -8185,7 +8189,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>ZDDO3PFR</t>
+          <t>ZDDO3P9M</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -8197,7 +8201,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ZDDO3PDQ</t>
+          <t>ZDDO3PFR</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8217,7 +8221,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>6001670023</t>
+          <t>6001670644</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -8239,12 +8243,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-03-04T13:05:59+00:00</t>
+          <t>2026-03-04T13:06:00+00:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>ZDDO3PDQ</t>
+          <t>ZDDO3PFR</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -8256,7 +8260,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>YVX879MT</t>
+          <t>ZDDO3PDQ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8276,7 +8280,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>6001670301</t>
+          <t>6001670023</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -8298,12 +8302,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:04+00:00</t>
+          <t>2026-03-04T13:05:59+00:00</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>YVX879MT</t>
+          <t>ZDDO3PDQ</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -8315,7 +8319,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ZDDO3PGP</t>
+          <t>YVX879MT</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8335,7 +8339,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>6001671274</t>
+          <t>6001670301</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -8357,12 +8361,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:00+00:00</t>
+          <t>2026-03-04T13:06:04+00:00</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>ZDDO3PGP</t>
+          <t>YVX879MT</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -8433,7 +8437,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ZDDO3PDN</t>
+          <t>ZDDO3PGP</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8453,7 +8457,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>6001670023</t>
+          <t>6001671274</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -8480,7 +8484,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>ZDDO3PDN</t>
+          <t>ZDDO3PGP</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -8551,7 +8555,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ZDDO3PF5</t>
+          <t>ZDDO3PDN</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8571,7 +8575,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>6001670411</t>
+          <t>6001670023</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -8593,12 +8597,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-03-04T13:05:58+00:00</t>
+          <t>2026-03-04T13:06:00+00:00</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>ZDDO3PF5</t>
+          <t>ZDDO3PDN</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -8610,7 +8614,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>YVX879MS</t>
+          <t>ZDDO3PF5</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8630,7 +8634,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>6001670301</t>
+          <t>6001670411</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -8652,12 +8656,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-03-04T13:06:06+00:00</t>
+          <t>2026-03-04T13:05:58+00:00</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>YVX879MS</t>
+          <t>ZDDO3PF5</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -8728,17 +8732,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>05222006538683</t>
+          <t>YVX879MS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8748,7 +8752,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>6001671710</t>
+          <t>6001670301</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -8760,34 +8764,34 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-04T10:13:38+01:00</t>
+          <t>2026-03-04T14:00:00+01:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>NL, Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-03-04T09:43:42+00:00</t>
+          <t>2026-03-04T13:06:06+00:00</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>05222006538683</t>
+          <t>YVX879MS</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>05222006538684</t>
+          <t>0053231072667W</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8807,7 +8811,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>6001671763</t>
+          <t>6001669793</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -8819,22 +8823,22 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-03-04T12:36:55+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-03-04T16:43:52+00:00</t>
+          <t>2026-03-04T09:43:45+00:00</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>05222006538684</t>
+          <t>0053231072667W</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -8846,7 +8850,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0053231072667W</t>
+          <t>05222006538633</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8866,7 +8870,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>6001669793</t>
+          <t>6001669766</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -8878,22 +8882,22 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T09:44:57+01:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Tynaarlo, NL, Netherlands</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-03-04T09:43:45+00:00</t>
+          <t>2026-03-04T10:43:40+00:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>0053231072667W</t>
+          <t>05222006538633</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -8905,7 +8909,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>05222006538651</t>
+          <t>05222006538667</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>6001670937</t>
+          <t>6001671419</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -8937,22 +8941,22 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-03-03T15:00:39+01:00</t>
+          <t>2026-03-03T16:05:22+01:00</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Taulov, DK, Denmark</t>
+          <t>Maastricht, NL, Netherlands</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-03-04T10:43:40+00:00</t>
+          <t>2026-03-04T18:43:48+00:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>05222006538651</t>
+          <t>05222006538667</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -8964,7 +8968,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>05222006538667</t>
+          <t>05222006538643</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8984,7 +8988,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>6001671419</t>
+          <t>6001670502</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -8996,22 +9000,22 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-03T16:05:22+01:00</t>
+          <t>2026-03-04T14:28:24+01:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Maastricht, NL, Netherlands</t>
+          <t>NL, Netherlands</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:37+00:00</t>
+          <t>2026-03-04T15:43:52+00:00</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>05222006538667</t>
+          <t>05222006538643</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -9023,7 +9027,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>05222006538652</t>
+          <t>05222006538630</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9043,7 +9047,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>6001670937</t>
+          <t>6001669580</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -9055,22 +9059,22 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-03T15:00:39+01:00</t>
+          <t>2026-03-04T17:36:40+01:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Taulov, DK, Denmark</t>
+          <t>Aalborg, DK, Denmark</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:35+00:00</t>
+          <t>2026-03-04T18:43:59+00:00</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>05222006538652</t>
+          <t>05222006538630</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -9082,7 +9086,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>05222006538633</t>
+          <t>05222006538684</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9102,7 +9106,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>6001669766</t>
+          <t>6001671763</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -9114,22 +9118,22 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-03-03T09:44:57+01:00</t>
+          <t>2026-03-04T12:36:55+01:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Tynaarlo, NL, Netherlands</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-03-04T10:43:40+00:00</t>
+          <t>2026-03-04T16:43:52+00:00</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>05222006538633</t>
+          <t>05222006538684</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -9141,7 +9145,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>05222006538643</t>
+          <t>05222006538652</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9161,7 +9165,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>6001670502</t>
+          <t>6001670937</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -9173,22 +9177,22 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-03-04T14:28:24+01:00</t>
+          <t>2026-03-03T15:00:39+01:00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>NL, Netherlands</t>
+          <t>Taulov, DK, Denmark</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-03-04T15:43:52+00:00</t>
+          <t>2026-03-04T18:43:59+00:00</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>05222006538643</t>
+          <t>05222006538652</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -9200,7 +9204,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>05222006538620</t>
+          <t>0053230955239W</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9220,7 +9224,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>6001668303</t>
+          <t>6001669757</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -9232,22 +9236,22 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-03-03T15:00:42+01:00</t>
+          <t>2026-03-04T14:03:49+01:00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Broendby, DK, Denmark</t>
+          <t>Torun, PL, Poland</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:34+00:00</t>
+          <t>2026-03-04T18:44:26+00:00</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>05222006538620</t>
+          <t>0053230955239W</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -9259,7 +9263,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>05222006538629</t>
+          <t>05222006538620</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9279,7 +9283,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>6001669193</t>
+          <t>6001668303</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -9291,22 +9295,22 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-03-04T08:46:41+01:00</t>
+          <t>2026-03-03T15:00:42+01:00</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Broendby, DK, Denmark</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-03-04T09:43:40+00:00</t>
+          <t>2026-03-04T18:43:46+00:00</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>05222006538629</t>
+          <t>05222006538620</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -9318,7 +9322,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>05222006538662</t>
+          <t>05222006538651</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9338,7 +9342,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>6001671228</t>
+          <t>6001670937</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -9350,22 +9354,22 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-03-04T10:27:10+01:00</t>
+          <t>2026-03-03T15:00:39+01:00</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Vijfhuizen, NL, Netherlands</t>
+          <t>Taulov, DK, Denmark</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-03-04T13:44:10+00:00</t>
+          <t>2026-03-04T10:43:40+00:00</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>05222006538662</t>
+          <t>05222006538651</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -9377,7 +9381,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>05222069771183</t>
+          <t>05222006538683</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9397,7 +9401,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>6001668953</t>
+          <t>6001671710</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -9409,22 +9413,22 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-03-02T14:27:11+01:00</t>
+          <t>2026-03-04T10:13:38+01:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Beverwijk, NL, Netherlands</t>
+          <t>NL, Netherlands</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-03-04T06:43:34+00:00</t>
+          <t>2026-03-04T09:43:42+00:00</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>05222069771183</t>
+          <t>05222006538683</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -9436,17 +9440,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1Z6X581R6895891837</t>
+          <t>05222069771183</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9456,41 +9460,277 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0353000395812</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>3027</t>
-        </is>
-      </c>
+          <t>6001668953</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
+          <t>2026-03-02T14:27:11+01:00</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Beverwijk, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2026-03-04T06:43:34+00:00</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>05222069771183</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>05222006538662</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>6001671228</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-03-04T10:27:10+01:00</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Vijfhuizen, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2026-03-04T13:44:10+00:00</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>05222006538662</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>05222006538629</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>6001669193</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-03-04T08:46:41+01:00</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Oirschot, NL, Netherlands</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>2026-03-04T09:43:40+00:00</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>05222006538629</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>05222006538625</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>dpd</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>6001668716</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>csv_importer</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-03-04T15:00:30+01:00</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Oerebro, SE, Sweden</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>2026-03-04T18:43:58+00:00</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>05222006538625</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1Z6X581R6895891837</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>ups-api</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ups-api</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0353000395812</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>3027</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
           <t>2026-02-24T12:56:27+00:00</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
+      <c r="J152" t="inlineStr">
         <is>
           <t>XXX, GOREY, Y25, IE, Ireland</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="K152" t="inlineStr">
         <is>
           <t>2026-03-04T05:06:53+00:00</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t>1Z6X581R6895891837</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>{"external_order_id": "0353000395812", "sales_office_id": "3027"}</t>
         </is>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M201"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,17 +545,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1ZR096K99094974070</t>
+          <t>16389000300699</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6001673418</t>
+          <t>6001658433</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -577,44 +577,44 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-02-24T10:18:30-08:00</t>
+          <t>2026-02-27T17:00:00+01:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>REDLANDS, CA, 92374, US, United States</t>
+          <t>Budapest, HU, Hungary</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:10+00:00</t>
+          <t>2026-03-05T04:12:15+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1ZR096K99094974070</t>
+          <t>16389000300699</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05222069697559</t>
+          <t>JD014600012504431918</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>dhl</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DHL Express</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6001674054</t>
+          <t>6001675047</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -636,44 +636,44 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-01-28T12:39:41+01:00</t>
+          <t>2026-03-04T11:27:02+01:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Meppel, NL, Netherlands</t>
+          <t>EINDHOVEN-NLD, Netherlands</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:15+00:00</t>
+          <t>2026-03-05T04:12:10+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05222069697559</t>
+          <t>JD014600012504431918</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CY431870379DE</t>
+          <t>ZDDO3M23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dhl-germany</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deutsche Post DHL</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6001670657</t>
+          <t>6001672548</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -695,44 +695,44 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-02-27T13:27:00+01:00</t>
+          <t>2026-02-24T13:30:00+01:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:10+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CY431870379DE</t>
+          <t>ZDDO3M23</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZDDO3M23</t>
+          <t>CY431870379DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dhl-germany</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Deutsche Post DHL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6001672548</t>
+          <t>6001670657</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -754,44 +754,44 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-02-24T13:30:00+01:00</t>
+          <t>2026-02-27T13:27:00+01:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:10+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ZDDO3M23</t>
+          <t>CY431870379DE</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JJD149990121180220989</t>
+          <t>05222069697559</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6001657179</t>
+          <t>6001674054</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -813,23 +813,27 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-02T14:28:00+01:00</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>2026-01-28T12:39:41+01:00</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Meppel, NL, Netherlands</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:10+00:00</t>
+          <t>2026-03-05T04:12:15+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JJD149990121180220989</t>
+          <t>05222069697559</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
@@ -954,17 +958,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JD014600012504431918</t>
+          <t>1ZR096K99094974070</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dhl</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DHL Express</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -974,7 +978,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6001675047</t>
+          <t>6001673418</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -986,12 +990,12 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-04T11:27:02+01:00</t>
+          <t>2026-02-24T10:18:30-08:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>EINDHOVEN-NLD, Netherlands</t>
+          <t>REDLANDS, CA, 92374, US, United States</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1001,29 +1005,29 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JD014600012504431918</t>
+          <t>1ZR096K99094974070</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16389000300699</t>
+          <t>502067169785</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1033,7 +1037,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6001658433</t>
+          <t>6001657770</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1045,44 +1049,44 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-02-27T17:00:00+01:00</t>
+          <t>2026-03-04T11:57:00+09:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Budapest, HU, Hungary</t>
+          <t>古河営業所, Japan</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:15+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16389000300699</t>
+          <t>502067169785</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>502067169785</t>
+          <t>JJD149990121180220989</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sagawa</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sagawa</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1092,7 +1096,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6001657770</t>
+          <t>6001657179</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1104,34 +1108,30 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-04T11:57:00+09:00</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>古河営業所, Japan</t>
-        </is>
-      </c>
+          <t>2026-03-02T14:28:00+01:00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:10+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>502067169785</t>
+          <t>JJD149990121180220989</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JJD149990121180223187</t>
+          <t>JJD149990121180223994</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6001664870</t>
+          <t>6001664198</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1169,12 +1169,12 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:11+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JJD149990121180223187</t>
+          <t>JJD149990121180223994</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JJD149990121180223622</t>
+          <t>JJD149990121180223187</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6001663145</t>
+          <t>6001664870</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1224,12 +1224,12 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:11+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JJD149990121180223622</t>
+          <t>JJD149990121180223187</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JJD149990121180221917</t>
+          <t>JJD149990121180224085</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6001660822</t>
+          <t>6001664185</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1279,12 +1279,12 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:07+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>JJD149990121180221917</t>
+          <t>JJD149990121180224085</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JJD149990121180221537</t>
+          <t>JJD149990121180221081</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6001656771</t>
+          <t>6001657127</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:11+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>JJD149990121180221537</t>
+          <t>JJD149990121180221081</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JJD149990121180221081</t>
+          <t>JJD149990121180221537</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6001657127</t>
+          <t>6001656771</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1389,12 +1389,12 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:11+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>JJD149990121180221081</t>
+          <t>JJD149990121180221537</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1406,7 +1406,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JJD149990121180223994</t>
+          <t>JJD149990121180223622</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6001664198</t>
+          <t>6001663145</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>JJD149990121180223994</t>
+          <t>JJD149990121180223622</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JJD149990121180221057</t>
+          <t>JJD149990121180221917</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6001657140</t>
+          <t>6001660822</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1499,12 +1499,12 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:11+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JJD149990121180221057</t>
+          <t>JJD149990121180221917</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JJD149990121180224085</t>
+          <t>JJD149990121180221057</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6001664185</t>
+          <t>6001657140</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:07+00:00</t>
+          <t>2026-03-05T04:12:11+00:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>JJD149990121180224085</t>
+          <t>JJD149990121180221057</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1Z6X581R9198437038</t>
+          <t>1Z6X581R9195306818</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:07+00:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1Z6X581R9198437038</t>
+          <t>1Z6X581R9195306818</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:08+00:00</t>
+          <t>2026-03-05T08:12:08+00:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1Z6X581R9193510967</t>
+          <t>JJD149990121180224481</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6001667142</t>
+          <t>6001668423</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1721,34 +1721,30 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-03-04T09:53:37+01:00</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>1 MARY KINGSLEYSTRAAT, VENLO, 5928SK, NL, Netherlands</t>
-        </is>
-      </c>
+          <t>2026-03-04T14:51:00+01:00</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:07+00:00</t>
+          <t>2026-03-05T04:12:11+00:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1Z6X581R9193510967</t>
+          <t>JJD149990121180224481</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1Z6X581R9195699207</t>
+          <t>1Z6X581R9198437038</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1790,12 +1786,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:08+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1Z6X581R9195699207</t>
+          <t>1Z6X581R9198437038</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1807,17 +1803,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JJD149990121180224481</t>
+          <t>1Z6X581R9193510967</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1827,7 +1823,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6001668423</t>
+          <t>6001667142</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1839,30 +1835,34 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-04T14:51:00+01:00</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>2026-03-04T09:53:37+01:00</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1 MARY KINGSLEYSTRAAT, VENLO, 5928SK, NL, Netherlands</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:11+00:00</t>
+          <t>2026-03-05T04:12:07+00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>JJD149990121180224481</t>
+          <t>1Z6X581R9193510967</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1Z6X581R9197898980</t>
+          <t>1Z6X581R9195699207</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:08+00:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1Z6X581R9197898980</t>
+          <t>1Z6X581R9195699207</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -1980,7 +1980,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1Z6X581R9195306818</t>
+          <t>1Z6X581R9197898980</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:07+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1Z6X581R9195306818</t>
+          <t>1Z6X581R9197898980</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2098,17 +2098,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3366573085793</t>
+          <t>996011434800773823</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>directfreight-au-ref</t>
+          <t>swiss-post</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Direct Freight Express</t>
+          <t>Swiss Post</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6001673273</t>
+          <t>6001670183</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -2130,44 +2130,44 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-03T13:09:00+09:30</t>
+          <t>2026-03-05T08:31:29+01:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Melbourne(N), Australia</t>
+          <t>CH, Switzerland</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:01+00:00</t>
+          <t>2026-03-05T09:12:13+00:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3366573085793</t>
+          <t>996011434800773823</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{"courier": "directfreight-au-ref", "custom_1": "Returns_directfreight-au-ref"}</t>
+          <t>{"courier": "swiss-post", "custom_1": "Galaxus"}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0053208782934W</t>
+          <t>REC000081043069</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6001659624</t>
+          <t>6001673088</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -2189,44 +2189,40 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>ROSANOW, PL, Poland</t>
-        </is>
-      </c>
+          <t>2026-03-05T10:11:00</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T09:20:09+00:00</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0053208782934W</t>
+          <t>REC000081043069</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0053207782018W</t>
+          <t>3366573085793</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>directfreight-au-ref</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Direct Freight Express</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2236,7 +2232,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6001659335</t>
+          <t>6001673273</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -2248,44 +2244,44 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-03T13:09:00+09:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Melbourne(N), Australia</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:01+00:00</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0053207782018W</t>
+          <t>3366573085793</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"courier": "directfreight-au-ref", "custom_1": "Returns_directfreight-au-ref"}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0053210819530W</t>
+          <t>996014994510153556</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>swiss-post</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Swiss Post</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2295,7 +2291,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6001659808</t>
+          <t>6001674739</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -2307,34 +2303,34 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-05T08:33:58+01:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>CH, Switzerland</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:03+00:00</t>
+          <t>2026-03-05T09:12:09+00:00</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0053210819530W</t>
+          <t>996014994510153556</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"courier": "swiss-post", "custom_1": "Galaxus"}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0053205297037W</t>
+          <t>0053214519488W</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2354,7 +2350,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6001658511</t>
+          <t>6001661533</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -2366,7 +2362,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2381,7 +2377,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0053205297037W</t>
+          <t>0053214519488W</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2393,7 +2389,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0053206168229W</t>
+          <t>0053208312146W</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2413,7 +2409,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6001658819</t>
+          <t>6001659474</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -2425,7 +2421,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-02T07:35:00+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2435,12 +2431,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0053206168229W</t>
+          <t>0053208312146W</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2452,7 +2448,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0053214132038W</t>
+          <t>0053213367045W</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2472,7 +2468,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6001660394</t>
+          <t>6001658654</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -2494,12 +2490,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:06+00:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0053214132038W</t>
+          <t>0053213367045W</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2511,7 +2507,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0053204699288W</t>
+          <t>0053214132038W</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2531,7 +2527,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6001658321</t>
+          <t>6001660394</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -2553,12 +2549,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0053204699288W</t>
+          <t>0053214132038W</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2570,7 +2566,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0053205219745W</t>
+          <t>0053208782934W</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2590,7 +2586,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6001658500</t>
+          <t>6001659624</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -2617,7 +2613,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0053205219745W</t>
+          <t>0053208782934W</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2629,7 +2625,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0053205219500W</t>
+          <t>0053214518101W</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2649,7 +2645,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6001658500</t>
+          <t>6001661513</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2671,12 +2667,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:07+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0053205219500W</t>
+          <t>0053214518101W</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2688,7 +2684,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0053205219805W</t>
+          <t>0053211187532W</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2708,7 +2704,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6001658500</t>
+          <t>6001659845</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -2720,22 +2716,22 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-02T18:00:15+01:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Warszawa, PL, Poland</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0053205219805W</t>
+          <t>0053211187532W</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2747,7 +2743,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0053213367045W</t>
+          <t>0053205047180W</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2767,7 +2763,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6001658654</t>
+          <t>6001658446</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -2779,7 +2775,7 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2794,7 +2790,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0053213367045W</t>
+          <t>0053205047180W</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2806,7 +2802,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0053205047180W</t>
+          <t>0053204699288W</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2826,7 +2822,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6001658446</t>
+          <t>6001658321</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -2838,7 +2834,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2848,12 +2844,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:06+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0053205047180W</t>
+          <t>0053204699288W</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2865,7 +2861,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0053214518101W</t>
+          <t>0053205219745W</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2885,7 +2881,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6001661513</t>
+          <t>6001658500</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -2907,12 +2903,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0053214518101W</t>
+          <t>0053205219745W</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -2924,7 +2920,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0053209303502W</t>
+          <t>0053205219805W</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2944,7 +2940,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6001659665</t>
+          <t>6001658500</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -2966,12 +2962,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0053209303502W</t>
+          <t>0053205219805W</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3042,7 +3038,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0053214519488W</t>
+          <t>0053205219500W</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3062,7 +3058,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6001661533</t>
+          <t>6001658500</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3074,7 +3070,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3084,12 +3080,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:07+00:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0053214519488W</t>
+          <t>0053205219500W</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3101,7 +3097,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0053208312146W</t>
+          <t>0053207782018W</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3121,7 +3117,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6001659474</t>
+          <t>6001659335</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3133,7 +3129,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3143,12 +3139,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0053208312146W</t>
+          <t>0053207782018W</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3160,7 +3156,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0053206922740W</t>
+          <t>0053204590575W</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3180,7 +3176,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6001659148</t>
+          <t>6001658123</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3192,22 +3188,22 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-02T07:35:00+01:00</t>
+          <t>2026-03-02T11:43:09+01:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Warszawa, PL, Poland</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:06+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0053206922740W</t>
+          <t>0053204590575W</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3219,7 +3215,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0053211187532W</t>
+          <t>0053206168229W</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3239,7 +3235,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6001659845</t>
+          <t>6001658819</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3251,22 +3247,22 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-02T18:00:15+01:00</t>
+          <t>2026-03-02T07:35:00+01:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Warszawa, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T08:12:09+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0053211187532W</t>
+          <t>0053206168229W</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3278,7 +3274,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0053214518024W</t>
+          <t>0053213935294W</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3298,7 +3294,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6001661513</t>
+          <t>6001660299</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3310,7 +3306,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3320,12 +3316,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T07:12:12+00:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0053214518024W</t>
+          <t>0053213935294W</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3337,7 +3333,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0053204590575W</t>
+          <t>0053214518024W</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3357,7 +3353,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6001658123</t>
+          <t>6001661513</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -3369,22 +3365,22 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-03-02T11:43:09+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Warszawa, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:06+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0053204590575W</t>
+          <t>0053214518024W</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3396,7 +3392,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0053219084596W</t>
+          <t>0053213935315W</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3416,7 +3412,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6001666305</t>
+          <t>6001660299</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -3428,7 +3424,7 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3438,12 +3434,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T07:12:09+00:00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0053219084596W</t>
+          <t>0053213935315W</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3455,7 +3451,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0053221762690W</t>
+          <t>0053205297037W</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3475,7 +3471,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>6001666846</t>
+          <t>6001658511</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -3497,12 +3493,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0053221762690W</t>
+          <t>0053205297037W</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3514,7 +3510,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0053230330362W</t>
+          <t>0053209303502W</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3534,7 +3530,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6001668645</t>
+          <t>6001659665</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -3546,22 +3542,22 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-03T17:24:38+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Opole, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:03+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0053230330362W</t>
+          <t>0053209303502W</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3573,7 +3569,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0053230441607W</t>
+          <t>0053206922740W</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3593,7 +3589,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6001669298</t>
+          <t>6001659148</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -3605,22 +3601,22 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-03-04T16:10:52+01:00</t>
+          <t>2026-03-02T07:35:00+01:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Koszalin, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T08:12:11+00:00</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0053230441607W</t>
+          <t>0053206922740W</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3632,7 +3628,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0053216195581W</t>
+          <t>0053210819530W</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3652,7 +3648,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6001665485</t>
+          <t>6001659808</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -3664,22 +3660,22 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-04T15:38:38+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Zerniki, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:03+00:00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0053216195581W</t>
+          <t>0053210819530W</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3691,7 +3687,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0053230342542W</t>
+          <t>0053230327541W</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3711,7 +3707,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6001669155</t>
+          <t>6001668512</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -3723,7 +3719,7 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3733,12 +3729,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:03+00:00</t>
+          <t>2026-03-05T07:12:10+00:00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0053230342542W</t>
+          <t>0053230327541W</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3750,7 +3746,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0053216210414W</t>
+          <t>0053240904467W</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3770,7 +3766,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6001665568</t>
+          <t>6001671456</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -3782,7 +3778,7 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3792,12 +3788,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T07:12:20+00:00</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0053216210414W</t>
+          <t>0053240904467W</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3809,7 +3805,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0053219084765W</t>
+          <t>0053221701954W</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3829,7 +3825,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6001666305</t>
+          <t>6001666791</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -3851,12 +3847,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0053219084765W</t>
+          <t>0053221701954W</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3868,7 +3864,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0053222441738W</t>
+          <t>0053219084765W</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3888,7 +3884,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>6001666941</t>
+          <t>6001666305</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -3915,7 +3911,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0053222441738W</t>
+          <t>0053219084765W</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3927,7 +3923,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0053232456444W</t>
+          <t>0053230342542W</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3947,7 +3943,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6001670198</t>
+          <t>6001669155</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -3959,22 +3955,22 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-04T12:01:43+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Gdansk Kowale / Kowale gm. Kolbudy, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:03+00:00</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0053232456444W</t>
+          <t>0053230342542W</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4104,7 +4100,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0053216668225W</t>
+          <t>0053232456444W</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4124,7 +4120,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6001665735</t>
+          <t>6001670198</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -4136,22 +4132,22 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-04T12:01:43+01:00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Gdansk Kowale / Kowale gm. Kolbudy, PL, Poland</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T08:12:10+00:00</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0053216668225W</t>
+          <t>0053232456444W</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4163,7 +4159,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0053219084616W</t>
+          <t>0053216668225W</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4183,7 +4179,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>6001666305</t>
+          <t>6001665735</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -4195,7 +4191,7 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4205,12 +4201,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0053219084616W</t>
+          <t>0053216668225W</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4222,7 +4218,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0053221701954W</t>
+          <t>0053228792542W</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4242,7 +4238,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>6001666791</t>
+          <t>6001667794</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -4254,7 +4250,7 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4264,12 +4260,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T07:12:12+00:00</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0053221701954W</t>
+          <t>0053228792542W</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4281,7 +4277,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>05286000527797</t>
+          <t>0053238476568W</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4301,7 +4297,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>6001642923</t>
+          <t>6001671219</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -4313,22 +4309,22 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-03-03T10:51:50+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T07:12:09+00:00</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>05286000527797</t>
+          <t>0053238476568W</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4340,7 +4336,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>05286000529186</t>
+          <t>0053240904518W</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4360,7 +4356,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>6001649547</t>
+          <t>6001671456</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -4372,22 +4368,22 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:35+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:01+00:00</t>
+          <t>2026-03-05T07:12:09+00:00</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>05286000529186</t>
+          <t>0053240904518W</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4399,7 +4395,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>05286000528057</t>
+          <t>0053238476676W</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4419,7 +4415,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>6001643784</t>
+          <t>6001671219</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -4431,22 +4427,22 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:30+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:01+00:00</t>
+          <t>2026-03-05T07:12:10+00:00</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>05286000528057</t>
+          <t>0053238476676W</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4458,7 +4454,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>05286000527970</t>
+          <t>0053216210414W</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4478,7 +4474,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>6001643483</t>
+          <t>6001665568</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -4490,22 +4486,22 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:29+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:02+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>05286000527970</t>
+          <t>0053216210414W</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4517,7 +4513,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>05286000528808</t>
+          <t>0053230441607W</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4537,7 +4533,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>6001648122</t>
+          <t>6001669298</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -4549,22 +4545,22 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-03T10:51:51+01:00</t>
+          <t>2026-03-04T16:10:52+01:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Koszalin, PL, Poland</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T08:12:10+00:00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>05286000528808</t>
+          <t>0053230441607W</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4576,7 +4572,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>05286000529316</t>
+          <t>0053219084616W</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4596,7 +4592,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6001651415</t>
+          <t>6001666305</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -4608,22 +4604,22 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:43+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:01+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>05286000529316</t>
+          <t>0053219084616W</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4635,7 +4631,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>05286000529201</t>
+          <t>0053221762690W</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4655,7 +4651,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6001649972</t>
+          <t>6001666846</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -4667,22 +4663,22 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:31+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>05286000529201</t>
+          <t>0053221762690W</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4694,7 +4690,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>05222006538611</t>
+          <t>0053219084596W</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4714,7 +4710,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6001667923</t>
+          <t>6001666305</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -4726,22 +4722,22 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-04T12:19:40+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Maastricht, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:12+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>05222006538611</t>
+          <t>0053219084596W</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4753,7 +4749,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>05286000528689</t>
+          <t>0053230330362W</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4773,7 +4769,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>6001647863</t>
+          <t>6001668645</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -4785,22 +4781,22 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:33+01:00</t>
+          <t>2026-03-03T17:24:38+01:00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Opole, PL, Poland</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T04:12:03+00:00</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>05286000528689</t>
+          <t>0053230330362W</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4812,7 +4808,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>05286000529187</t>
+          <t>0053223722251W</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4832,7 +4828,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>6001649900</t>
+          <t>6001667008</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -4844,22 +4840,22 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:36+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T07:12:09+00:00</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>05286000529187</t>
+          <t>0053223722251W</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4871,7 +4867,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>05286000528690</t>
+          <t>0053222441738W</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4891,7 +4887,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>6001647863</t>
+          <t>6001666941</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -4903,22 +4899,22 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:34+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>05286000528690</t>
+          <t>0053222441738W</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -4930,7 +4926,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>05286000529217</t>
+          <t>0053216195581W</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4950,7 +4946,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>6001650474</t>
+          <t>6001665485</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -4962,22 +4958,22 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:38+01:00</t>
+          <t>2026-03-04T15:38:38+01:00</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Zerniki, PL, Poland</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T08:12:14+00:00</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>05286000529217</t>
+          <t>0053216195581W</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -4989,7 +4985,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>05286000529216</t>
+          <t>05286000527970</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5009,7 +5005,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>6001650474</t>
+          <t>6001643483</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -5021,7 +5017,7 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:37+01:00</t>
+          <t>2026-03-02T11:02:29+01:00</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5031,12 +5027,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T04:12:02+00:00</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>05286000529216</t>
+          <t>05286000527970</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5048,7 +5044,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>05286000529220</t>
+          <t>05286000529217</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5068,7 +5064,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>6001650552</t>
+          <t>6001650474</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -5080,7 +5076,7 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:39+01:00</t>
+          <t>2026-03-02T11:02:38+01:00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5095,7 +5091,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>05286000529220</t>
+          <t>05286000529217</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5107,7 +5103,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>05286000528232</t>
+          <t>05286000527797</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5127,7 +5123,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>6001643932</t>
+          <t>6001642923</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -5139,7 +5135,7 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:31+01:00</t>
+          <t>2026-03-03T10:51:50+01:00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5149,12 +5145,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:03+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>05286000528232</t>
+          <t>05286000527797</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5166,7 +5162,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>05286000529945</t>
+          <t>05286000529216</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5186,7 +5182,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>6001653844</t>
+          <t>6001650474</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -5198,7 +5194,7 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:48+01:00</t>
+          <t>2026-03-02T11:02:37+01:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5208,12 +5204,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>05286000529945</t>
+          <t>05286000529216</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -5225,7 +5221,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>05286000530270</t>
+          <t>05286000528690</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5245,7 +5241,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>6001655670</t>
+          <t>6001647863</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -5257,7 +5253,7 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:49+01:00</t>
+          <t>2026-03-02T11:02:34+01:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5267,12 +5263,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:02+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>05286000530270</t>
+          <t>05286000528690</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5284,7 +5280,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>05286000531185</t>
+          <t>05286000529316</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5304,7 +5300,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>6001660060</t>
+          <t>6001651415</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -5316,7 +5312,7 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-03-03T10:51:58+01:00</t>
+          <t>2026-03-02T11:02:43+01:00</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5326,12 +5322,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T04:12:01+00:00</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>05286000531185</t>
+          <t>05286000529316</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5343,7 +5339,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>05286000529941</t>
+          <t>05286000529201</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5363,7 +5359,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>6001653229</t>
+          <t>6001649972</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -5375,7 +5371,7 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:46+01:00</t>
+          <t>2026-03-04T08:47:31+01:00</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5390,7 +5386,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>05286000529941</t>
+          <t>05286000529201</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -5402,7 +5398,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>05286000531073</t>
+          <t>05286000528057</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5422,7 +5418,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>6001659650</t>
+          <t>6001643784</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -5434,7 +5430,7 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-03-03T10:51:57+01:00</t>
+          <t>2026-03-02T11:02:30+01:00</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5444,12 +5440,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T04:12:01+00:00</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>05286000531073</t>
+          <t>05286000528057</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -5461,7 +5457,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>05326100069714</t>
+          <t>05286000528808</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5481,7 +5477,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>6001653675</t>
+          <t>6001648122</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -5493,7 +5489,7 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:51+01:00</t>
+          <t>2026-03-03T10:51:51+01:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5503,12 +5499,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>05326100069714</t>
+          <t>05286000528808</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -5520,7 +5516,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>05326100069713</t>
+          <t>05222006538611</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5540,7 +5536,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>6001653675</t>
+          <t>6001667923</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -5552,22 +5548,22 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-03-02T11:02:50+01:00</t>
+          <t>2026-03-04T12:19:40+01:00</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Maastricht, NL, Netherlands</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T04:12:12+00:00</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>05326100069713</t>
+          <t>05222006538611</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5579,7 +5575,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>05286000530946</t>
+          <t>05286000528232</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5599,7 +5595,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>6001657173</t>
+          <t>6001643932</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -5611,7 +5607,7 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-03-03T10:51:55+01:00</t>
+          <t>2026-03-02T11:02:31+01:00</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5621,12 +5617,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:01+00:00</t>
+          <t>2026-03-05T04:12:03+00:00</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>05286000530946</t>
+          <t>05286000528232</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -5638,7 +5634,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>05286000529843</t>
+          <t>05286000529186</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5658,7 +5654,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>6001652294</t>
+          <t>6001649547</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -5670,7 +5666,7 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-03-03T10:51:52+01:00</t>
+          <t>2026-03-02T11:02:35+01:00</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5685,7 +5681,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>05286000529843</t>
+          <t>05286000529186</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -5697,7 +5693,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>05326100069755</t>
+          <t>05286000528689</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5717,7 +5713,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>6001656656</t>
+          <t>6001647863</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -5729,7 +5725,7 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:38+01:00</t>
+          <t>2026-03-02T11:02:33+01:00</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5739,12 +5735,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>05326100069755</t>
+          <t>05286000528689</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -5756,7 +5752,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>05286000531446</t>
+          <t>05286000529220</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5776,7 +5772,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>6001660899</t>
+          <t>6001650552</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -5788,7 +5784,7 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:35+01:00</t>
+          <t>2026-03-02T11:02:39+01:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5798,12 +5794,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:10+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>05286000531446</t>
+          <t>05286000529220</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -5815,7 +5811,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>05286000531062</t>
+          <t>05286000529187</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5835,7 +5831,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>6001659642</t>
+          <t>6001649900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -5847,7 +5843,7 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-03-03T10:51:56+01:00</t>
+          <t>2026-03-02T11:02:36+01:00</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5857,12 +5853,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>05286000531062</t>
+          <t>05286000529187</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -5874,7 +5870,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>05286000531376</t>
+          <t>05286000530946</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5894,7 +5890,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>6001660342</t>
+          <t>6001657173</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -5906,7 +5902,7 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-03-03T10:51:59+01:00</t>
+          <t>2026-03-03T10:51:55+01:00</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5916,12 +5912,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T04:12:01+00:00</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>05286000531376</t>
+          <t>05286000530946</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -5933,7 +5929,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>05286000530944</t>
+          <t>05286000529941</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5953,7 +5949,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>6001656886</t>
+          <t>6001653229</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -5965,7 +5961,7 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-03-03T10:51:54+01:00</t>
+          <t>2026-03-02T11:02:46+01:00</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5975,12 +5971,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>05286000530944</t>
+          <t>05286000529941</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -5992,7 +5988,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>05326100069803</t>
+          <t>05286000531062</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6012,7 +6008,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>6001654870</t>
+          <t>6001659642</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -6024,7 +6020,7 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-03-03T10:52:02+01:00</t>
+          <t>2026-03-03T10:51:56+01:00</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6039,7 +6035,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>05326100069803</t>
+          <t>05286000531062</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6051,7 +6047,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>05286000531500</t>
+          <t>05286000531185</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6071,7 +6067,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>6001665231</t>
+          <t>6001660060</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -6083,7 +6079,7 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:37+01:00</t>
+          <t>2026-03-03T10:51:58+01:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6093,12 +6089,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:07+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>05286000531500</t>
+          <t>05286000531185</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -6110,7 +6106,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>05286000531377</t>
+          <t>05286000531500</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6130,7 +6126,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>6001660342</t>
+          <t>6001665231</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -6142,7 +6138,7 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-03-03T10:52:00+01:00</t>
+          <t>2026-03-04T08:47:37+01:00</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6152,12 +6148,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:01+00:00</t>
+          <t>2026-03-05T04:12:07+00:00</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>05286000531377</t>
+          <t>05286000531500</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6169,7 +6165,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>05326100069756</t>
+          <t>05286000531073</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6189,7 +6185,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>6001657633</t>
+          <t>6001659650</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -6201,7 +6197,7 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:39+01:00</t>
+          <t>2026-03-03T10:51:57+01:00</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6211,12 +6207,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>05326100069756</t>
+          <t>05286000531073</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -6228,7 +6224,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>05286000531459</t>
+          <t>05286000531377</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6248,7 +6244,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>6001662594</t>
+          <t>6001660342</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -6260,7 +6256,7 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:36+01:00</t>
+          <t>2026-03-03T10:52:00+01:00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6275,7 +6271,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>05286000531459</t>
+          <t>05286000531377</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6346,7 +6342,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>05286000530474</t>
+          <t>05286000531446</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6366,7 +6362,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>6001656104</t>
+          <t>6001660899</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -6378,7 +6374,7 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:33+01:00</t>
+          <t>2026-03-04T08:47:35+01:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6388,12 +6384,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:01+00:00</t>
+          <t>2026-03-05T04:12:10+00:00</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>05286000530474</t>
+          <t>05286000531446</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -6405,7 +6401,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>05376100046693</t>
+          <t>05286000531376</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6425,7 +6421,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>6001659775</t>
+          <t>6001660342</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -6437,7 +6433,7 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-03-03T10:52:06+01:00</t>
+          <t>2026-03-03T10:51:59+01:00</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6447,12 +6443,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:03+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>05376100046693</t>
+          <t>05286000531376</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -6464,7 +6460,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>05446100066499</t>
+          <t>05286000530270</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6484,7 +6480,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>6001648341</t>
+          <t>6001655670</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -6496,7 +6492,7 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:44+01:00</t>
+          <t>2026-03-02T11:02:49+01:00</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6506,12 +6502,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:58+00:00</t>
+          <t>2026-03-05T04:12:02+00:00</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>05446100066499</t>
+          <t>05286000530270</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -6523,7 +6519,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>05366100076329</t>
+          <t>05286000529945</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6543,7 +6539,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>6001659647</t>
+          <t>6001653844</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -6555,7 +6551,7 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:41+01:00</t>
+          <t>2026-03-02T11:02:48+01:00</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6565,12 +6561,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:01+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>05366100076329</t>
+          <t>05286000529945</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -6582,7 +6578,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>05376100046695</t>
+          <t>05286000531459</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6602,7 +6598,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>6001659789</t>
+          <t>6001662594</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -6614,7 +6610,7 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-03-03T10:52:07+01:00</t>
+          <t>2026-03-04T08:47:36+01:00</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6624,12 +6620,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T04:12:01+00:00</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>05376100046695</t>
+          <t>05286000531459</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -6641,7 +6637,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>05446100066759</t>
+          <t>05286000530474</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6661,7 +6657,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>6001660768</t>
+          <t>6001656104</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -6673,7 +6669,7 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-03T10:52:08+01:00</t>
+          <t>2026-03-04T08:47:33+01:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6683,12 +6679,12 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T04:12:01+00:00</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>05446100066759</t>
+          <t>05286000530474</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -6700,7 +6696,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>05366100076314</t>
+          <t>05286000530944</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6720,7 +6716,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>6001658834</t>
+          <t>6001656886</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -6732,7 +6728,7 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-03T10:52:03+01:00</t>
+          <t>2026-03-03T10:51:54+01:00</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6742,12 +6738,12 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:01+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>05366100076314</t>
+          <t>05286000530944</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -6759,7 +6755,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>05366100076547</t>
+          <t>05326100069713</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6779,7 +6775,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>6001667873</t>
+          <t>6001653675</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -6791,7 +6787,7 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:42+01:00</t>
+          <t>2026-03-02T11:02:50+01:00</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6801,12 +6797,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:58+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>05366100076547</t>
+          <t>05326100069713</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -6818,7 +6814,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>05366100076310</t>
+          <t>05286000529944</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6838,7 +6834,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>6001658412</t>
+          <t>6001653844</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -6850,7 +6846,7 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:40+01:00</t>
+          <t>2026-03-02T11:02:47+01:00</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6860,12 +6856,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T07:12:06+00:00</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>05366100076310</t>
+          <t>05286000529944</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -6877,7 +6873,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>05486100081140</t>
+          <t>05326100069755</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6897,7 +6893,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>6001656294</t>
+          <t>6001656656</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -6909,7 +6905,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:46+01:00</t>
+          <t>2026-03-04T08:47:38+01:00</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6919,12 +6915,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:08+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>05486100081140</t>
+          <t>05326100069755</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -6936,7 +6932,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>16029168836891</t>
+          <t>05286000529843</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6956,7 +6952,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>6001655236</t>
+          <t>6001652294</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -6968,7 +6964,7 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-02T11:03:17+01:00</t>
+          <t>2026-03-03T10:51:52+01:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6978,12 +6974,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:58+00:00</t>
+          <t>2026-03-05T04:12:01+00:00</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>16029168836891</t>
+          <t>05286000529843</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -6995,7 +6991,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>16029168836811</t>
+          <t>05326100069714</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7015,7 +7011,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>6001653217</t>
+          <t>6001653675</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -7027,7 +7023,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-03-02T11:03:13+01:00</t>
+          <t>2026-03-02T11:02:51+01:00</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7037,12 +7033,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>16029168836811</t>
+          <t>05326100069714</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -7054,7 +7050,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>16029168837171</t>
+          <t>05326100069803</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7074,7 +7070,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>6001656266</t>
+          <t>6001654870</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -7086,7 +7082,7 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-02T11:03:18+01:00</t>
+          <t>2026-03-03T10:52:02+01:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7096,12 +7092,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:58+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>16029168837171</t>
+          <t>05326100069803</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -7113,7 +7109,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>16029168836831</t>
+          <t>05326100069756</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7133,7 +7129,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>6001653815</t>
+          <t>6001657633</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -7145,7 +7141,7 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-03-02T11:03:14+01:00</t>
+          <t>2026-03-04T08:47:39+01:00</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7155,12 +7151,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:57+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>16029168836831</t>
+          <t>05326100069756</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -7172,7 +7168,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>05486100081148</t>
+          <t>05446100066759</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7192,7 +7188,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>6001657077</t>
+          <t>6001660768</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -7204,7 +7200,7 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:47+01:00</t>
+          <t>2026-03-03T10:52:08+01:00</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7214,12 +7210,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:58+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>05486100081148</t>
+          <t>05446100066759</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -7231,7 +7227,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>05486100081149</t>
+          <t>05366100076314</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7251,7 +7247,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>6001657077</t>
+          <t>6001658834</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -7263,7 +7259,7 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:48+01:00</t>
+          <t>2026-03-03T10:52:03+01:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7273,12 +7269,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:00+00:00</t>
+          <t>2026-03-05T04:12:01+00:00</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>05486100081149</t>
+          <t>05366100076314</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -7290,7 +7286,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>05486100081151</t>
+          <t>05366100076547</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7310,7 +7306,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>6001657490</t>
+          <t>6001667873</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -7322,7 +7318,7 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:49+01:00</t>
+          <t>2026-03-04T08:47:42+01:00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7337,7 +7333,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>05486100081151</t>
+          <t>05366100076547</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -7349,7 +7345,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>16029168836861</t>
+          <t>05366100076329</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7369,7 +7365,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>6001654332</t>
+          <t>6001659647</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -7381,7 +7377,7 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-03-02T11:03:15+01:00</t>
+          <t>2026-03-04T08:47:41+01:00</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7391,12 +7387,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:59+00:00</t>
+          <t>2026-03-05T04:12:01+00:00</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>16029168836861</t>
+          <t>05366100076329</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -7408,7 +7404,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>05486100081138</t>
+          <t>05376100046695</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7428,7 +7424,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>6001656294</t>
+          <t>6001659789</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -7440,7 +7436,7 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:45+01:00</t>
+          <t>2026-03-03T10:52:07+01:00</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7450,12 +7446,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:10+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>05486100081138</t>
+          <t>05376100046695</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -7467,7 +7463,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>05486100081273</t>
+          <t>05366100076310</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7487,7 +7483,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>6001666890</t>
+          <t>6001658412</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -7499,7 +7495,7 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-04T08:47:51+01:00</t>
+          <t>2026-03-04T08:47:40+01:00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7509,12 +7505,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:57+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>05486100081273</t>
+          <t>05366100076310</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -7526,7 +7522,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>05222006538735</t>
+          <t>05446100066499</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7546,7 +7542,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>6001674498</t>
+          <t>6001648341</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -7558,22 +7554,22 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:20+01:00</t>
+          <t>2026-03-04T08:47:44+01:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Goes, NL, Netherlands</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:56+00:00</t>
+          <t>2026-03-05T04:11:58+00:00</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>05222006538735</t>
+          <t>05446100066499</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -7585,7 +7581,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>05222006538712</t>
+          <t>05376100046693</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7605,7 +7601,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>6001673849</t>
+          <t>6001659775</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -7617,22 +7613,22 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-03-04T13:14:57+01:00</t>
+          <t>2026-03-03T10:52:06+01:00</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Flemalle, BE, Belgium</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:55+00:00</t>
+          <t>2026-03-05T04:12:03+00:00</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>05222006538712</t>
+          <t>05376100046693</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -7644,7 +7640,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>05222006538733</t>
+          <t>05486100081138</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7664,7 +7660,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>6001674498</t>
+          <t>6001656294</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -7676,22 +7672,22 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:20+01:00</t>
+          <t>2026-03-04T08:47:45+01:00</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Goes, NL, Netherlands</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:54+00:00</t>
+          <t>2026-03-05T04:12:10+00:00</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>05222006538733</t>
+          <t>05486100081138</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -7703,7 +7699,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>05222006538731</t>
+          <t>16029168837171</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7723,7 +7719,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>6001674498</t>
+          <t>6001656266</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -7735,22 +7731,22 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:20+01:00</t>
+          <t>2026-03-02T11:03:18+01:00</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Goes, NL, Netherlands</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:54+00:00</t>
+          <t>2026-03-05T04:11:58+00:00</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>05222006538731</t>
+          <t>16029168837171</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -7762,7 +7758,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>05222006538734</t>
+          <t>16029168836811</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7782,7 +7778,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>6001674498</t>
+          <t>6001653217</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -7794,22 +7790,22 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:20+01:00</t>
+          <t>2026-03-02T11:03:13+01:00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Goes, NL, Netherlands</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:55+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>05222006538734</t>
+          <t>16029168836811</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -7821,7 +7817,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>05222006538732</t>
+          <t>16029168836871</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7841,7 +7837,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>6001674498</t>
+          <t>6001654547</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -7853,22 +7849,22 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-03-04T11:19:20+01:00</t>
+          <t>2026-03-02T11:03:16+01:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Goes, NL, Netherlands</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:54+00:00</t>
+          <t>2026-03-05T07:12:17+00:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>05222006538732</t>
+          <t>16029168836871</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -7880,7 +7876,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>05222006538711</t>
+          <t>16029168836891</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7900,7 +7896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>6001673696</t>
+          <t>6001655236</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -7912,12 +7908,12 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-03-04T15:00:20+01:00</t>
+          <t>2026-03-02T11:03:17+01:00</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Broendby, DK, Denmark</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7927,7 +7923,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>05222006538711</t>
+          <t>16029168836891</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -7939,7 +7935,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>05222006538716</t>
+          <t>16029168836861</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7959,7 +7955,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>6001674217</t>
+          <t>6001654332</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -7971,22 +7967,22 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-03-04T12:25:03+01:00</t>
+          <t>2026-03-02T11:03:15+01:00</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Vijfhuizen, NL, Netherlands</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:55+00:00</t>
+          <t>2026-03-05T04:11:59+00:00</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>05222006538716</t>
+          <t>16029168836861</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -7998,7 +7994,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>05222006538703</t>
+          <t>05486100081140</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8018,7 +8014,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>6001672721</t>
+          <t>6001656294</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -8030,22 +8026,22 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-03-04T19:40:13+01:00</t>
+          <t>2026-03-04T08:47:46+01:00</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Rijssen, NL, Netherlands</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:54+00:00</t>
+          <t>2026-03-05T04:12:08+00:00</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>05222006538703</t>
+          <t>05486100081140</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -8057,7 +8053,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>05222006538729</t>
+          <t>16029168836831</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8077,7 +8073,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>6001674350</t>
+          <t>6001653815</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -8089,22 +8085,22 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-04T15:00:20+01:00</t>
+          <t>2026-03-02T11:03:14+01:00</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Segeltorp, SE, Sweden</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:56+00:00</t>
+          <t>2026-03-05T04:11:57+00:00</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>05222006538729</t>
+          <t>16029168836831</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -8116,7 +8112,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>05222006538707</t>
+          <t>05486100081149</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8136,7 +8132,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>6001672965</t>
+          <t>6001657077</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -8148,22 +8144,22 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-03-04T17:04:00+01:00</t>
+          <t>2026-03-04T08:47:48+01:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Berkel en Rodenrijs, NL, Netherlands</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:53+00:00</t>
+          <t>2026-03-05T04:12:00+00:00</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>05222006538707</t>
+          <t>05486100081149</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -8175,17 +8171,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ZDDO3IKL</t>
+          <t>05486100081148</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8195,7 +8191,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>6001675311</t>
+          <t>6001657077</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -8207,44 +8203,44 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-02-19T13:30:00+01:00</t>
+          <t>2026-03-04T08:47:47+01:00</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-03-05T04:11:52+00:00</t>
+          <t>2026-03-05T04:11:58+00:00</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>ZDDO3IKL</t>
+          <t>05486100081148</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>00KNRTB1</t>
+          <t>05486100081151</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8254,60 +8250,56 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0031009980266</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001657490</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-03-04T10:43:06+01:00</t>
+          <t>2026-03-04T08:47:49+01:00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-03-05T03:25:27+00:00</t>
+          <t>2026-03-05T04:11:58+00:00</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>00KNRTB1</t>
+          <t>05486100081151</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009980266", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>01475211991047</t>
+          <t>05486100081273</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8317,60 +8309,56 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>B2BDS11226242</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
+          <t>6001666890</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-03-04T09:50:42+01:00</t>
+          <t>2026-03-04T08:47:51+01:00</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Altentreptow (DE), Germany</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-03-05T03:25:20+00:00</t>
+          <t>2026-03-05T04:11:57+00:00</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>01475211991047</t>
+          <t>05486100081273</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11226242", "sales_office_id": "4436"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>H01TAA0000408746</t>
+          <t>0053243777816W</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>myhermes-uk</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>EVRi</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8380,56 +8368,56 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>204-0442560-8930761</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>4262</t>
-        </is>
-      </c>
+          <t>6001673139</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-04T17:51:45</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr"/>
+          <t>2026-03-05T07:49:00+01:00</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>ROSANOW, PL, Poland</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-03-05T03:25:19+00:00</t>
+          <t>2026-03-05T07:12:02+00:00</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>H01TAA0000408746</t>
+          <t>0053243777816W</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>{"external_order_id": "204-0442560-8930761", "sales_office_id": "4262"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>00KNRSZY</t>
+          <t>05222006538712</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8439,60 +8427,56 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>0031009977156</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001673849</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-03-04T13:20:22+01:00</t>
+          <t>2026-03-04T13:14:57+01:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Flemalle, BE, Belgium</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:33+00:00</t>
+          <t>2026-03-05T04:11:55+00:00</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>00KNRSZY</t>
+          <t>05222006538712</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>00KNRSZX</t>
+          <t>81240369878</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd-ro</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD Romania</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8502,60 +8486,56 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>0031009977156</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001663512</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-03-04T13:20:22+01:00</t>
+          <t>2026-03-05T09:16:13+02:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>S. SANTION</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:34+00:00</t>
+          <t>2026-03-05T08:12:00+00:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>00KNRSZX</t>
+          <t>81240369878</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>00KNRSZU</t>
+          <t>0053243750419W</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8565,60 +8545,56 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0031009977156</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001672832</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-03-04T13:20:22+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:31+00:00</t>
+          <t>2026-03-05T07:12:02+00:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>00KNRSZU</t>
+          <t>0053243750419W</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>00KNRSZT</t>
+          <t>05222006538735</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8628,60 +8604,56 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0031009977156</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001674498</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-04T13:20:22+01:00</t>
+          <t>2026-03-04T11:19:20+01:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Goes, NL, Netherlands</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:30+00:00</t>
+          <t>2026-03-05T08:12:02+00:00</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>00KNRSZT</t>
+          <t>05222006538735</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>00KNRSZV</t>
+          <t>05222006538733</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8691,60 +8663,56 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>0031009977156</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001674498</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-04T13:20:22+01:00</t>
+          <t>2026-03-04T11:19:20+01:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Goes, NL, Netherlands</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:29+00:00</t>
+          <t>2026-03-05T04:11:54+00:00</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>00KNRSZV</t>
+          <t>05222006538733</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>00KNRSZS</t>
+          <t>05222006538703</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8754,60 +8722,56 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>0031009977156</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001672721</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-03-04T13:20:22+01:00</t>
+          <t>2026-03-04T19:40:13+01:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Rijssen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:30+00:00</t>
+          <t>2026-03-05T04:11:54+00:00</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>00KNRSZS</t>
+          <t>05222006538703</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>00KNRT00</t>
+          <t>05222006538732</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8817,60 +8781,56 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>0031009977156</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001674498</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-03-04T13:20:22+01:00</t>
+          <t>2026-03-04T11:19:20+01:00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Goes, NL, Netherlands</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:32+00:00</t>
+          <t>2026-03-05T08:11:58+00:00</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>00KNRT00</t>
+          <t>05222006538732</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>00KNRSZR</t>
+          <t>05222006538716</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8880,60 +8840,56 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>0031009977156</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001674217</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-03-04T13:20:22+01:00</t>
+          <t>2026-03-04T12:25:03+01:00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Vijfhuizen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:30+00:00</t>
+          <t>2026-03-05T04:11:55+00:00</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>00KNRSZR</t>
+          <t>05222006538716</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>00KNRSZW</t>
+          <t>05222006538731</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8943,60 +8899,56 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>0031009977156</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001674498</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-03-04T13:20:22+01:00</t>
+          <t>2026-03-04T11:19:20+01:00</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Goes, NL, Netherlands</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-03-04T15:54:31+00:00</t>
+          <t>2026-03-05T08:12:02+00:00</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>00KNRSZW</t>
+          <t>05222006538731</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>UTV662060404</t>
+          <t>05222006538738</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9006,60 +8958,56 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>B2B25351563</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>4238</t>
-        </is>
-      </c>
+          <t>6001674591</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-03-04T08:11:22+01:00</t>
+          <t>2026-03-04T11:37:32+01:00</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Veenendaal, NL, Netherlands</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-03-04T15:53:38+00:00</t>
+          <t>2026-03-05T07:11:59+00:00</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>UTV662060404</t>
+          <t>05222006538738</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2B25351563", "sales_office_id": "4238"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>00KNRPLC</t>
+          <t>05222006538711</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9069,60 +9017,56 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0031009964033</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001673696</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-03-03T14:13:05+01:00</t>
+          <t>2026-03-04T15:00:20+01:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Broendby, DK, Denmark</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-03-04T15:53:30+00:00</t>
+          <t>2026-03-05T04:11:58+00:00</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>00KNRPLC</t>
+          <t>05222006538711</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009964033", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>00KNRPD1</t>
+          <t>05222006538734</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9132,60 +9076,56 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0031009964033</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001674498</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-03-03T14:13:05+01:00</t>
+          <t>2026-03-04T11:19:20+01:00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Goes, NL, Netherlands</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-03-04T15:53:30+00:00</t>
+          <t>2026-03-05T08:11:59+00:00</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>00KNRPD1</t>
+          <t>05222006538734</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009964033", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>UTV019744791</t>
+          <t>05222006538739</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9195,60 +9135,56 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0031009967076</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001674681</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-03-04T10:51:21+01:00</t>
+          <t>2026-03-04T11:25:19+01:00</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Rijssen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-03-04T15:53:24+00:00</t>
+          <t>2026-03-05T07:12:11+00:00</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>UTV019744791</t>
+          <t>05222006538739</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009967076", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>UTV541200300</t>
+          <t>05222006538707</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9258,60 +9194,56 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0031009967076</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001672965</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-03-03T12:29:01+01:00</t>
+          <t>2026-03-04T17:04:00+01:00</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Berkel en Rodenrijs, NL, Netherlands</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-03-04T15:53:22+00:00</t>
+          <t>2026-03-05T04:11:53+00:00</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>UTV541200300</t>
+          <t>05222006538707</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009967076", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>00KNRU4R</t>
+          <t>05222006538729</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9321,60 +9253,56 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0031009979003</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001674350</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-03-04T13:23:51+01:00</t>
+          <t>2026-03-04T15:00:20+01:00</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Segeltorp, SE, Sweden</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-03-04T15:53:03+00:00</t>
+          <t>2026-03-05T04:11:56+00:00</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>00KNRU4R</t>
+          <t>05222006538729</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009979003", "sales_office_id": "0303"}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>UTV348607012</t>
+          <t>ZDDO3IKL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9384,60 +9312,56 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0031009961530</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
+          <t>6001675311</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>csv_importer</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-03-03T15:29:43+01:00</t>
+          <t>2026-02-19T13:30:00+01:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-03-04T15:52:54+00:00</t>
+          <t>2026-03-05T04:11:52+00:00</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>UTV348607012</t>
+          <t>ZDDO3IKL</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009961530", "sales_office_id": "0303"}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ZI67DV4F</t>
+          <t>00KNRTB1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9447,7 +9371,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0032005568229</t>
+          <t>0031009980266</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9463,44 +9387,44 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-03-04T15:33:13+01:00</t>
+          <t>2026-03-04T10:43:06+01:00</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>BE, Belgium</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-03-05T03:52:17+00:00</t>
+          <t>2026-03-05T03:25:27+00:00</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>ZI67DV4F</t>
+          <t>00KNRTB1</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005568229", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009980266", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ZI67DV4D</t>
+          <t>H01TAA0000408746</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>myhermes-uk</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>EVRi</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9510,12 +9434,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0032005568229</t>
+          <t>204-0442560-8930761</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9526,44 +9450,40 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-03-04T15:33:13+01:00</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>BE, Belgium</t>
-        </is>
-      </c>
+          <t>2026-03-04T17:51:45</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-03-05T03:52:18+00:00</t>
+          <t>2026-03-05T03:25:19+00:00</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>ZI67DV4D</t>
+          <t>H01TAA0000408746</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005568229", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "204-0442560-8930761", "sales_office_id": "4262"}</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ZI67DV4E</t>
+          <t>01475211991047</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9573,12 +9493,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>0032005568229</t>
+          <t>B2BDS11226242</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9589,44 +9509,44 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-03-04T15:33:13+01:00</t>
+          <t>2026-03-04T09:50:42+01:00</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>BE, Belgium</t>
+          <t>Altentreptow (DE), Germany</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-03-05T03:52:18+00:00</t>
+          <t>2026-03-05T03:25:20+00:00</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>ZI67DV4E</t>
+          <t>01475211991047</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005568229", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11226242", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ZI67DUT3</t>
+          <t>00KNRSZY</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9636,7 +9556,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>0032005565058</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -9652,44 +9572,44 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-03-04T09:07:32+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>BE, Belgium</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-03-05T03:51:59+00:00</t>
+          <t>2026-03-04T15:54:33+00:00</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>ZI67DUT3</t>
+          <t>00KNRSZY</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005565058", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ZB8W8KFW</t>
+          <t>00KNRSZU</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9699,12 +9619,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>B2BDS11357350</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9715,44 +9635,44 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-03-04T14:19:20+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-03-05T03:51:56+00:00</t>
+          <t>2026-03-04T15:54:31+00:00</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>ZB8W8KFW</t>
+          <t>00KNRSZU</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11357350", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>YNQAF93O</t>
+          <t>00KNRSZV</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9762,12 +9682,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>0045005252204</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9778,44 +9698,44 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-03-03T10:44:08+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>DK, Denmark</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-03-05T03:51:10+00:00</t>
+          <t>2026-03-04T15:54:29+00:00</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>YNQAF93O</t>
+          <t>00KNRSZV</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0045005252204", "sales_office_id": "3017"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>YNQAF937</t>
+          <t>00KNRSZT</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9825,12 +9745,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>0045005252204</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9841,44 +9761,44 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-03T10:44:08+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>DK, Denmark</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-03-05T03:51:10+00:00</t>
+          <t>2026-03-04T15:54:30+00:00</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>YNQAF937</t>
+          <t>00KNRSZT</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0045005252204", "sales_office_id": "3017"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZB8W8KIE</t>
+          <t>00KNRSZS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9888,12 +9808,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>B2BDS11372451</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9904,44 +9824,44 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-03-04T12:56:26+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-03-05T03:51:08+00:00</t>
+          <t>2026-03-04T15:54:30+00:00</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>ZB8W8KIE</t>
+          <t>00KNRSZS</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11372451", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>05228742850751</t>
+          <t>00KNRSZR</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9951,12 +9871,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>B2BDS11299677</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9967,44 +9887,44 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-03-04T10:46:02+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Carhaix Plouguer, FR, France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-03-04T19:50:31+00:00</t>
+          <t>2026-03-04T15:54:30+00:00</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>05228742850751</t>
+          <t>00KNRSZR</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11299677", "sales_office_id": "4452"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>06245165501732</t>
+          <t>00KNRSZW</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>dpd-at-sftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DPD Austria</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10014,12 +9934,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>0043000968791</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -10030,40 +9950,44 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-03-04T12:17:00</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr"/>
+          <t>2026-03-04T13:20:22+01:00</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-03-04T15:47:36+00:00</t>
+          <t>2026-03-04T15:54:31+00:00</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>06245165501732</t>
+          <t>00KNRSZW</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0043000968791", "sales_office_id": "3009"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>06245165502472</t>
+          <t>00KNRSZX</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>dpd-at-sftp</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>DPD Austria</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10073,12 +9997,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>0043000968792</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -10089,40 +10013,44 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-03-04T11:09:00</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
+          <t>2026-03-04T13:20:22+01:00</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-03-04T15:47:08+00:00</t>
+          <t>2026-03-04T15:54:34+00:00</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>06245165502472</t>
+          <t>00KNRSZX</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0043000968792", "sales_office_id": "3009"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>01475240792815</t>
+          <t>00KNRT00</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10132,12 +10060,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>0049010235402</t>
+          <t>0031009977156</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -10148,44 +10076,44 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-03-04T12:21:39+01:00</t>
+          <t>2026-03-04T13:20:22+01:00</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Föhren (DE), Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-03-04T14:56:09+00:00</t>
+          <t>2026-03-04T15:54:32+00:00</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>01475240792815</t>
+          <t>00KNRT00</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010235402", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009977156", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ZD1RIPL5</t>
+          <t>00KNRUWD</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10195,12 +10123,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>B2BDS11419817</t>
+          <t>0031009982735</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -10211,44 +10139,44 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-03-04T12:15:04+01:00</t>
+          <t>2026-03-05T10:09:48+01:00</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-03-05T02:54:34+00:00</t>
+          <t>2026-03-05T09:54:53+00:00</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>ZD1RIPL5</t>
+          <t>00KNRUWD</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11419817", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009982735", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ZD1RIPQW</t>
+          <t>00KNRV3P</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10258,12 +10186,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1116415483-01</t>
+          <t>0031009982735</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10274,44 +10202,44 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-04T10:50:00+01:00</t>
+          <t>2026-03-05T10:09:48+01:00</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-03-05T02:54:07+00:00</t>
+          <t>2026-03-05T09:54:50+00:00</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>ZD1RIPQW</t>
+          <t>00KNRV3P</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1116415483-01", "sales_office_id": "4677"}</t>
+          <t>{"external_order_id": "0031009982735", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ZD1RIPQV</t>
+          <t>00KNRV2I</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10321,12 +10249,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1116415483-01</t>
+          <t>0031009982735</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10337,44 +10265,44 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-03-04T10:50:00+01:00</t>
+          <t>2026-03-05T10:09:48+01:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-03-05T02:54:04+00:00</t>
+          <t>2026-03-05T09:54:49+00:00</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>ZD1RIPQV</t>
+          <t>00KNRV2I</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1116415483-01", "sales_office_id": "4677"}</t>
+          <t>{"external_order_id": "0031009982735", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ZD1RIPQU</t>
+          <t>00KNRV04</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10384,12 +10312,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1116415483-01</t>
+          <t>0031009982735</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10400,44 +10328,44 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-03-04T10:50:00+01:00</t>
+          <t>2026-03-05T10:09:48+01:00</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-03-05T02:54:03+00:00</t>
+          <t>2026-03-05T09:54:48+00:00</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>ZD1RIPQU</t>
+          <t>00KNRV04</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1116415483-01", "sales_office_id": "4677"}</t>
+          <t>{"external_order_id": "0031009982735", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ZD1RIPN9</t>
+          <t>00KNRV06</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10447,12 +10375,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PO-076-18644055267190905</t>
+          <t>0031009982735</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -10463,44 +10391,44 @@
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-03-04T12:59:22+01:00</t>
+          <t>2026-03-05T10:09:48+01:00</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-03-05T02:53:43+00:00</t>
+          <t>2026-03-05T09:54:45+00:00</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>ZD1RIPN9</t>
+          <t>00KNRV06</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-076-18644055267190905", "sales_office_id": "4670"}</t>
+          <t>{"external_order_id": "0031009982735", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>05228742843747</t>
+          <t>UTV662060404</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10510,12 +10438,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0032005563865</t>
+          <t>B2B25351563</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -10526,44 +10454,44 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-03-03T11:47:07+01:00</t>
+          <t>2026-03-04T08:11:22+01:00</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Aalter, BE, Belgium</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-03-04T13:53:29+00:00</t>
+          <t>2026-03-04T15:53:38+00:00</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>05228742843747</t>
+          <t>UTV662060404</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005563865", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2B25351563", "sales_office_id": "4238"}</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>05228742846313</t>
+          <t>UTV638530092</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10573,7 +10501,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0032005563865</t>
+          <t>0031009985130</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -10589,44 +10517,44 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-03-03T11:47:07+01:00</t>
+          <t>2026-03-05T08:11:07+01:00</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Aalter, BE, Belgium</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-03-04T13:53:29+00:00</t>
+          <t>2026-03-05T09:54:00+00:00</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>05228742846313</t>
+          <t>UTV638530092</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005563865", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009985130", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>957140555605</t>
+          <t>00KNRVBD</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>sending</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Sending Transporte Urgente y Comunicacion</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10636,12 +10564,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0034001430646</t>
+          <t>0031009987751</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10652,44 +10580,44 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-04T17:56:38</t>
+          <t>2026-03-05T10:32:57+01:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>BARCELONA</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-03-04T17:23:32+00:00</t>
+          <t>2026-03-05T09:54:21+00:00</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>957140555605</t>
+          <t>00KNRVBD</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0034001430646", "sales_office_id": "3018"}</t>
+          <t>{"external_order_id": "0031009987751", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>05228742854716</t>
+          <t>00KNRVFL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10699,7 +10627,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0032005569225</t>
+          <t>0031009984296</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10715,1791 +10643,27 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-03-04T13:49:56+01:00</t>
+          <t>2026-03-05T09:58:19+01:00</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Vilvoorde, BE, Belgium</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-03-04T13:53:15+00:00</t>
+          <t>2026-03-05T09:54:01+00:00</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>05228742854716</t>
+          <t>00KNRVFL</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005569225", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>05228742854037</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>dpd-api</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>DPD</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>0032005569225</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>2026-03-04T13:49:56+01:00</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>Vilvoorde, BE, Belgium</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>2026-03-04T16:53:24+00:00</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>05228742854037</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0032005569225", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>UTV107113681</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Packs</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0031009971989</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>2026-03-04T10:54:01+01:00</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>,Netherlands</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>2026-03-04T13:04:28+00:00</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>UTV107113681</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009971989", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>UTV572230723</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Packs</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0031009971989</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>2026-03-04T10:54:14+01:00</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>,Netherlands</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>2026-03-04T13:04:30+00:00</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>UTV572230723</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009971989", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>00KOQNFF</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>gls</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>GLS</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>0033005729405</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>0302</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>2026-03-04T09:40:46+01:00</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>FR, France</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>2026-03-05T01:04:13+00:00</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>00KOQNFF</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0033005729405", "sales_office_id": "0302"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>00KNSBZ6</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>gls</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>GLS</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>B2BDS11325687</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>4452</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>2026-03-04T08:29:43+01:00</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>FR, France</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>2026-03-05T01:03:46+00:00</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>00KNSBZ6</t>
-        </is>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "B2BDS11325687", "sales_office_id": "4452"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>00KNSBZ5</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>gls</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>GLS</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>B2BDS11325687</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>4452</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>2026-03-04T08:29:43+01:00</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>FR, France</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>2026-03-05T01:03:46+00:00</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>00KNSBZ5</t>
-        </is>
-      </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "B2BDS11325687", "sales_office_id": "4452"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>UTV232918983</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Packs</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0031009973557</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>2026-03-03T12:39:56+01:00</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>,Netherlands</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>2026-03-04T13:03:23+00:00</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>UTV232918983</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009973557", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>UTV631726295</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Packs</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0031009974227</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>2026-03-04T11:11:04+01:00</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>,Netherlands</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>2026-03-05T01:03:35+00:00</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>UTV631726295</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009974227", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>UTV630687814</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Packs</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0031009974227</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>2026-03-04T11:08:20+01:00</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>,Netherlands</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>2026-03-05T01:03:23+00:00</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>UTV630687814</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009974227", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>UTV981141134</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Packs</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>0031009974227</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>2026-03-04T11:11:30+01:00</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>,Netherlands</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>2026-03-05T01:03:22+00:00</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>UTV981141134</t>
-        </is>
-      </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009974227", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>00KNRU6M</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>0031009980890</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>2026-03-04T13:19:34+01:00</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:49:41+00:00</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>00KNRU6M</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009980890", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>00KNRU6B</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0031009980890</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>2026-03-04T13:19:34+01:00</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:49:41+00:00</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>00KNRU6B</t>
-        </is>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009980890", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>00KNRU3P</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0031009980632</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2026-03-04T15:17:11+01:00</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:54:53+00:00</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>00KNRU3P</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009980632", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>00KNRUAL</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0031009980632</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>2026-03-04T15:17:11+01:00</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:54:52+00:00</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>00KNRUAL</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009980632", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>00KNRTMP</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>0031009978568</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:02:01+01:00</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>2026-03-04T17:25:18+00:00</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>00KNRTMP</t>
-        </is>
-      </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009978568", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>00KNRU3I</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>0031009977643</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:42:16+01:00</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:24:28+00:00</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>00KNRU3I</t>
-        </is>
-      </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009977643", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>00KNRT87</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>0031009977643</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:42:16+01:00</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:24:28+00:00</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>00KNRT87</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009977643", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>00KNRU46</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>0031009977643</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:42:16+01:00</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:24:28+00:00</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>00KNRU46</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009977643", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>00KNRUH1</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>0031009982544</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:51:25+01:00</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:24:33+00:00</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>00KNRUH1</t>
-        </is>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009982544", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>00KNRUH0</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>0031009982544</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:51:25+01:00</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:24:37+00:00</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>00KNRUH0</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009982544", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>00KNRTCT</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>0031009978276</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:00:43+01:00</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:24:26+00:00</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>00KNRTCT</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009978276", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>00KNRTAS</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>0031009978276</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:00:43+01:00</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:24:25+00:00</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>00KNRTAS</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009978276", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>00KNRUGH</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>0031009982259</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>2026-03-04T10:16:46+01:00</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:24:06+00:00</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>00KNRUGH</t>
-        </is>
-      </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009982259", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>00KNRUGF</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>0031009982259</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>2026-03-04T10:16:46+01:00</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:24:02+00:00</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>00KNRUGF</t>
-        </is>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009982259", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>00KNRU3D</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>0031009981113</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:39:26+01:00</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:54:06+00:00</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>00KNRU3D</t>
-        </is>
-      </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009981113", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>00KNRU62</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>gls-netherlands-api</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>GLS Netherlands</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>0031009982031</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:03:56+01:00</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>2026-03-04T13:24:01+00:00</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>00KNRU62</t>
-        </is>
-      </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "0031009982031", "sales_office_id": "0303"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>01475240794415</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>dpd-de</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>DPD Germany</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>B2BDS11396937</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:01:34+01:00</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>Föhren (DE), Germany</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:52:56+00:00</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>01475240794415</t>
-        </is>
-      </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "B2BDS11396937", "sales_office_id": "4436"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>01475240794595</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>dpd-de</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>DPD Germany</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>B2BDS11396937</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:01:34+01:00</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>Föhren (DE), Germany</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>2026-03-04T12:22:59+00:00</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>01475240794595</t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>{"external_order_id": "B2BDS11396937", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009984296", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00KNRV5G</t>
+          <t>889141001381</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0031009986262</t>
+          <t>PO-211-07922097162872541</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -522,44 +522,44 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-05T13:26:12+01:00</t>
+          <t>2026-03-01T11:01:54-05:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Lehigh Acres, FL, 33936, US, United States</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-05T16:37:49+00:00</t>
+          <t>2026-03-05T21:31:05+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>00KNRV5G</t>
+          <t>889141001381</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009986262", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-211-07922097162872541", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>YNQAF94W</t>
+          <t>889141000010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -569,12 +569,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0045005252106</t>
+          <t>PO-211-07922097162872541</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,44 +585,44 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-03T13:36:36+01:00</t>
+          <t>2026-03-01T11:01:54-05:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>DK, Denmark</t>
+          <t>Lehigh Acres, FL, 33936, US, United States</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-05T16:36:56+00:00</t>
+          <t>2026-03-05T21:31:05+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>YNQAF94W</t>
+          <t>889141000010</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0045005252106", "sales_office_id": "3017"}</t>
+          <t>{"external_order_id": "PO-211-07922097162872541", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UTV086196752</t>
+          <t>889138964329</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B2B25352339</t>
+          <t>PO-211-07922097162872541</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -648,34 +648,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-03-05T09:40:15+01:00</t>
+          <t>2026-03-02T10:48:23-05:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Lehigh Acres, FL, 33936, US, United States</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-05T16:37:09+00:00</t>
+          <t>2026-03-05T21:30:57+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>UTV086196752</t>
+          <t>889138964329</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2B25352339", "sales_office_id": "4238"}</t>
+          <t>{"external_order_id": "PO-211-07922097162872541", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00KNRV5H</t>
+          <t>00KNRV5G</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B2B25349980</t>
+          <t>0031009986262</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-05T08:47:53+01:00</t>
+          <t>2026-03-05T13:26:12+01:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,34 +721,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-05T16:37:06+00:00</t>
+          <t>2026-03-05T16:37:49+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>00KNRV5H</t>
+          <t>00KNRV5G</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2B25349980", "sales_office_id": "4238"}</t>
+          <t>{"external_order_id": "0031009986262", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00KNRV5I</t>
+          <t>YNQAF94W</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0031009985171</t>
+          <t>0045005252106</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -774,44 +774,44 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-05T12:29:22+01:00</t>
+          <t>2026-03-03T13:36:36+01:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>DK, Denmark</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-03-05T16:36:59+00:00</t>
+          <t>2026-03-05T16:36:56+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>00KNRV5I</t>
+          <t>YNQAF94W</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985171", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0045005252106", "sales_office_id": "3017"}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00KNRV5K</t>
+          <t>UTV086196752</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0031009986605</t>
+          <t>B2B25352339</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -837,34 +837,34 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-05T13:26:12+01:00</t>
+          <t>2026-03-05T09:40:15+01:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-05T16:36:53+00:00</t>
+          <t>2026-03-05T16:37:09+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>00KNRV5K</t>
+          <t>UTV086196752</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009986605", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2B25352339", "sales_office_id": "4238"}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00KNRVQF</t>
+          <t>00KNRV5H</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0031009985449</t>
+          <t>B2B25349980</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -900,7 +900,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-05T14:03:08+01:00</t>
+          <t>2026-03-05T08:47:53+01:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -910,24 +910,24 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-05T16:36:44+00:00</t>
+          <t>2026-03-05T16:37:06+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>00KNRVQF</t>
+          <t>00KNRV5H</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985449", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2B25349980", "sales_office_id": "4238"}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00KNRVQE</t>
+          <t>00KNRV5I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0031009985449</t>
+          <t>0031009985171</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -963,7 +963,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-05T14:03:08+01:00</t>
+          <t>2026-03-05T12:29:22+01:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -973,34 +973,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-05T16:36:43+00:00</t>
+          <t>2026-03-05T16:36:59+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>00KNRVQE</t>
+          <t>00KNRV5I</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985449", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009985171", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UTV349218732</t>
+          <t>00KNRV5K</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0031009982642</t>
+          <t>0031009986605</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1026,44 +1026,44 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-05T14:48:40+01:00</t>
+          <t>2026-03-05T13:26:12+01:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-05T16:36:29+00:00</t>
+          <t>2026-03-05T16:36:53+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UTV349218732</t>
+          <t>00KNRV5K</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009982642", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009986605", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UTV708632950</t>
+          <t>00KNRVQF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0031009989478</t>
+          <t>0031009985449</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1089,44 +1089,44 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-05T11:44:15+01:00</t>
+          <t>2026-03-05T14:03:08+01:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-05T16:36:21+00:00</t>
+          <t>2026-03-05T16:36:44+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UTV708632950</t>
+          <t>00KNRVQF</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009989478", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009985449", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UTV422555679</t>
+          <t>00KNRVQE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0031009989478</t>
+          <t>0031009985449</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1152,34 +1152,34 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-05T11:44:15+01:00</t>
+          <t>2026-03-05T14:03:08+01:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-05T16:36:21+00:00</t>
+          <t>2026-03-05T16:36:43+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>UTV422555679</t>
+          <t>00KNRVQE</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009989478", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009985449", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UTV032522421</t>
+          <t>UTV349218732</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0031009986900</t>
+          <t>0031009982642</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1215,7 +1215,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-05T16:46:47+01:00</t>
+          <t>2026-03-05T14:48:40+01:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1225,24 +1225,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-05T16:35:45+00:00</t>
+          <t>2026-03-05T16:36:29+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UTV032522421</t>
+          <t>UTV349218732</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009986900", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009982642", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UTV223792505</t>
+          <t>UTV708632950</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0031009985858</t>
+          <t>0031009989478</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1278,7 +1278,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-03-05T16:46:10+01:00</t>
+          <t>2026-03-05T11:44:15+01:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1288,34 +1288,34 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-05T16:35:33+00:00</t>
+          <t>2026-03-05T16:36:21+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>UTV223792505</t>
+          <t>UTV708632950</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985858", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009989478", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05228742857838</t>
+          <t>UTV422555679</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NL02K201000891</t>
+          <t>0031009989478</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1341,44 +1341,44 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-05T13:32:27+01:00</t>
+          <t>2026-03-05T11:44:15+01:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-03-05T16:34:26+00:00</t>
+          <t>2026-03-05T16:36:21+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>05228742857838</t>
+          <t>UTV422555679</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>{"external_order_id": "NL02K201000891", "sales_office_id": "8001"}</t>
+          <t>{"external_order_id": "0031009989478", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05228742843093</t>
+          <t>UTV032522421</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0032005562315</t>
+          <t>0031009986900</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1404,44 +1404,44 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-03-03T12:57:29+01:00</t>
+          <t>2026-03-05T16:46:47+01:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-03-05T16:33:54+00:00</t>
+          <t>2026-03-05T16:35:45+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>05228742843093</t>
+          <t>UTV032522421</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005562315", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009986900", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05228742843097</t>
+          <t>UTV223792505</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0032005562315</t>
+          <t>0031009985858</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1467,34 +1467,34 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-03T12:57:29+01:00</t>
+          <t>2026-03-05T16:46:10+01:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-03-05T19:34:10+00:00</t>
+          <t>2026-03-05T16:35:33+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>05228742843097</t>
+          <t>UTV223792505</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005562315", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009985858", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05228742843084</t>
+          <t>05228742857838</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0032005562315</t>
+          <t>NL02K201000891</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1530,34 +1530,34 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-03T12:57:29+01:00</t>
+          <t>2026-03-05T13:32:27+01:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-03-05T16:33:54+00:00</t>
+          <t>2026-03-05T16:34:26+00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>05228742843084</t>
+          <t>05228742857838</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005562315", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "NL02K201000891", "sales_office_id": "8001"}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05228742857827</t>
+          <t>05228742843093</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0031009987454</t>
+          <t>0032005562315</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1593,44 +1593,44 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-05T11:01:38+01:00</t>
+          <t>2026-03-03T12:57:29+01:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>Courcelles, BE, Belgium</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-05T16:33:38+00:00</t>
+          <t>2026-03-05T16:33:54+00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>05228742857827</t>
+          <t>05228742843093</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009987454", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005562315", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06245165504451</t>
+          <t>05228742843097</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dpd-at-sftp</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DPD Austria</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0043000969914</t>
+          <t>0032005562315</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1656,40 +1656,44 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-03-05T11:39:00</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>2026-03-03T12:57:29+01:00</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Courcelles, BE, Belgium</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-03-05T16:29:36+00:00</t>
+          <t>2026-03-05T19:34:10+00:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>06245165504451</t>
+          <t>05228742843097</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0043000969914", "sales_office_id": "3009"}</t>
+          <t>{"external_order_id": "0032005562315", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06245165503888</t>
+          <t>05228742843084</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dpd-at-sftp</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DPD Austria</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1699,12 +1703,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0043000969914</t>
+          <t>0032005562315</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1715,40 +1719,44 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-03-05T11:39:00</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>2026-03-03T12:57:29+01:00</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Courcelles, BE, Belgium</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-03-05T16:29:32+00:00</t>
+          <t>2026-03-05T16:33:54+00:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>06245165503888</t>
+          <t>05228742843084</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0043000969914", "sales_office_id": "3009"}</t>
+          <t>{"external_order_id": "0032005562315", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06245165503073</t>
+          <t>05228742857827</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>dpd-at-sftp</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DPD Austria</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1758,12 +1766,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0043000969914</t>
+          <t>0031009987454</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1774,30 +1782,34 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-04T12:14:00</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>2026-03-05T11:01:38+01:00</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Veenendaal, NL, Netherlands</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-03-05T16:29:33+00:00</t>
+          <t>2026-03-05T16:33:38+00:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>06245165503073</t>
+          <t>05228742857827</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0043000969914", "sales_office_id": "3009"}</t>
+          <t>{"external_order_id": "0031009987454", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06245165503331</t>
+          <t>06245165504451</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1833,18 +1845,18 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-03-04T12:14:00</t>
+          <t>2026-03-05T11:39:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-03-05T16:29:31+00:00</t>
+          <t>2026-03-05T16:29:36+00:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>06245165503331</t>
+          <t>06245165504451</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1856,7 +1868,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06245165503017</t>
+          <t>06245165503331</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1903,7 +1915,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>06245165503017</t>
+          <t>06245165503331</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1915,7 +1927,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06245165503330</t>
+          <t>06245165503888</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1951,18 +1963,18 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-04T12:14:00</t>
+          <t>2026-03-05T11:39:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-05T16:29:31+00:00</t>
+          <t>2026-03-05T16:29:32+00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>06245165503330</t>
+          <t>06245165503888</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1974,17 +1986,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05228742854642</t>
+          <t>06245165503073</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-at-sftp</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Austria</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1994,12 +2006,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>B2BDS8988338</t>
+          <t>0043000969914</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2010,44 +2022,40 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-03-05T10:06:22+01:00</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Billy Berclau, FR, France</t>
-        </is>
-      </c>
+          <t>2026-03-04T12:14:00</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-03-05T16:11:53+00:00</t>
+          <t>2026-03-05T16:29:33+00:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>05228742854642</t>
+          <t>06245165503073</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS8988338", "sales_office_id": "4452"}</t>
+          <t>{"external_order_id": "0043000969914", "sales_office_id": "3009"}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ZI67DVGW</t>
+          <t>06245165503017</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-at-sftp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD Austria</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2057,12 +2065,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0032005571392</t>
+          <t>0043000969914</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2073,44 +2081,40 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-03-05T09:23:15+01:00</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>BE, Belgium</t>
-        </is>
-      </c>
+          <t>2026-03-04T12:14:00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-03-05T13:20:56+00:00</t>
+          <t>2026-03-05T16:29:31+00:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ZI67DVGW</t>
+          <t>06245165503017</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005571392", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0043000969914", "sales_office_id": "3009"}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ZI67DV5J</t>
+          <t>06245165503330</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-at-sftp</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD Austria</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2120,12 +2124,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0032005568749</t>
+          <t>0043000969914</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2136,44 +2140,40 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-03-04T14:17:24+01:00</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>BE, Belgium</t>
-        </is>
-      </c>
+          <t>2026-03-04T12:14:00</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-03-05T13:20:52+00:00</t>
+          <t>2026-03-05T16:29:31+00:00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ZI67DV5J</t>
+          <t>06245165503330</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005568749", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0043000969914", "sales_office_id": "3009"}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>01475240792925</t>
+          <t>05228742854642</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PO-076-14235327299190751</t>
+          <t>B2BDS8988338</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2199,44 +2199,44 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-03-04T12:17:48+01:00</t>
+          <t>2026-03-05T10:06:22+01:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Wustermark (DE), Germany</t>
+          <t>Billy Berclau, FR, France</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-03-05T13:18:00+00:00</t>
+          <t>2026-03-05T16:11:53+00:00</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>01475240792925</t>
+          <t>05228742854642</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-076-14235327299190751", "sales_office_id": "4670"}</t>
+          <t>{"external_order_id": "B2BDS8988338", "sales_office_id": "4452"}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>01475240792922</t>
+          <t>ZI67DVGW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PO-076-14235327299190751</t>
+          <t>0032005571392</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2262,44 +2262,44 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-04T12:17:48+01:00</t>
+          <t>2026-03-05T09:23:15+01:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Wustermark (DE), Germany</t>
+          <t>BE, Belgium</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-03-05T12:48:00+00:00</t>
+          <t>2026-03-05T13:20:56+00:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>01475240792922</t>
+          <t>ZI67DVGW</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-076-14235327299190751", "sales_office_id": "4670"}</t>
+          <t>{"external_order_id": "0032005571392", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>01475240792924</t>
+          <t>ZI67DV5J</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PO-076-14235327299190751</t>
+          <t>0032005568749</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2325,34 +2325,34 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-03-04T12:17:48+01:00</t>
+          <t>2026-03-04T14:17:24+01:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Wustermark (DE), Germany</t>
+          <t>BE, Belgium</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-03-05T12:48:03+00:00</t>
+          <t>2026-03-05T13:20:52+00:00</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>01475240792924</t>
+          <t>ZI67DV5J</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-076-14235327299190751", "sales_office_id": "4670"}</t>
+          <t>{"external_order_id": "0032005568749", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>01475240792923</t>
+          <t>01475240792925</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-03-05T12:48:00+00:00</t>
+          <t>2026-03-05T13:18:00+00:00</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>01475240792923</t>
+          <t>01475240792925</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2415,7 +2415,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>01475240795334</t>
+          <t>01475240792924</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B2BDS11429503</t>
+          <t>PO-076-14235327299190751</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,34 +2451,34 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-05T09:52:47+01:00</t>
+          <t>2026-03-04T12:17:48+01:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Ludwigsburg (DE), Germany</t>
+          <t>Wustermark (DE), Germany</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-03-05T12:47:18+00:00</t>
+          <t>2026-03-05T12:48:03+00:00</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>01475240795334</t>
+          <t>01475240792924</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11429503", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "PO-076-14235327299190751", "sales_office_id": "4670"}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>01475240795333</t>
+          <t>01475240792923</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B2BDS11429503</t>
+          <t>PO-076-14235327299190751</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2514,44 +2514,44 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-05T09:52:47+01:00</t>
+          <t>2026-03-04T12:17:48+01:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Ludwigsburg (DE), Germany</t>
+          <t>Wustermark (DE), Germany</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-05T12:47:17+00:00</t>
+          <t>2026-03-05T12:48:00+00:00</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>01475240795333</t>
+          <t>01475240792923</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11429503", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "PO-076-14235327299190751", "sales_office_id": "4670"}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05228742856930</t>
+          <t>01475240792922</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0032005571577</t>
+          <t>PO-076-14235327299190751</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2577,44 +2577,44 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-05T11:15:23+01:00</t>
+          <t>2026-03-04T12:17:48+01:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Vilvoorde, BE, Belgium</t>
+          <t>Wustermark (DE), Germany</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-03-05T12:39:41+00:00</t>
+          <t>2026-03-05T12:48:00+00:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>05228742856930</t>
+          <t>01475240792922</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005571577", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-076-14235327299190751", "sales_office_id": "4670"}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05228742858127</t>
+          <t>01475240795334</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0032005570555</t>
+          <t>B2BDS11429503</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2640,44 +2640,44 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-05T11:12:19+01:00</t>
+          <t>2026-03-05T09:52:47+01:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Aalter, BE, Belgium</t>
+          <t>Ludwigsburg (DE), Germany</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-05T12:39:46+00:00</t>
+          <t>2026-03-05T12:47:18+00:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>05228742858127</t>
+          <t>01475240795334</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005570555", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11429503", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05228742857108</t>
+          <t>01475240795333</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>C0001D1NHF</t>
+          <t>B2BDS11429503</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2703,34 +2703,34 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-05T12:56:38+01:00</t>
+          <t>2026-03-05T09:52:47+01:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Sint-Niklaas, BE, Belgium</t>
+          <t>Ludwigsburg (DE), Germany</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-03-05T12:39:38+00:00</t>
+          <t>2026-03-05T12:47:17+00:00</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>05228742857108</t>
+          <t>01475240795333</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{"external_order_id": "C0001D1NHF", "sales_office_id": "4124"}</t>
+          <t>{"external_order_id": "B2BDS11429503", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05228742857900</t>
+          <t>05228742856930</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0032005571865</t>
+          <t>0032005571577</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2766,44 +2766,44 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-05T15:03:00+01:00</t>
+          <t>2026-03-05T11:15:23+01:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Lummen, BE, Belgium</t>
+          <t>Vilvoorde, BE, Belgium</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-03-05T14:09:37+00:00</t>
+          <t>2026-03-05T12:39:41+00:00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>05228742857900</t>
+          <t>05228742856930</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005571865", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005571577", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00KNSCLJ</t>
+          <t>05228742857108</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0033005729742</t>
+          <t>C0001D1NHF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0302</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2829,44 +2829,44 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-05T11:05:26+01:00</t>
+          <t>2026-03-05T12:56:38+01:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>FR, France</t>
+          <t>Sint-Niklaas, BE, Belgium</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-05T12:04:58+00:00</t>
+          <t>2026-03-05T12:39:38+00:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>00KNSCLJ</t>
+          <t>05228742857108</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005729742", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "C0001D1NHF", "sales_office_id": "4124"}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06086432946253</t>
+          <t>05228742858127</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dpd-ch-sftp</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DPD Switzerland</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>B2BDS10912281</t>
+          <t>0032005570555</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2892,44 +2892,44 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-02-26T15:15:32+01:00</t>
+          <t>2026-03-05T11:12:19+01:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>,Switzerland</t>
+          <t>Aalter, BE, Belgium</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-03-05T11:26:06+00:00</t>
+          <t>2026-03-05T12:39:46+00:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>06086432946253</t>
+          <t>05228742858127</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS10912281", "sales_office_id": "4493"}</t>
+          <t>{"external_order_id": "0032005570555", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06086432945142</t>
+          <t>05228742857900</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dpd-ch-sftp</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DPD Switzerland</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>B2BDS10912281</t>
+          <t>0032005571865</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2955,44 +2955,44 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-02-26T15:15:31+01:00</t>
+          <t>2026-03-05T15:03:00+01:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>,Switzerland</t>
+          <t>Lummen, BE, Belgium</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-03-05T11:26:11+00:00</t>
+          <t>2026-03-05T14:09:37+00:00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>06086432945142</t>
+          <t>05228742857900</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS10912281", "sales_office_id": "4493"}</t>
+          <t>{"external_order_id": "0032005571865", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DR5411740477U</t>
+          <t>00KNSCLJ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ceskaposta-api</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Post</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0420001017085</t>
+          <t>0033005729742</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>0302</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3018,44 +3018,44 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-05T14:22:00+01:00</t>
+          <t>2026-03-05T11:05:26+01:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>39701</t>
+          <t>FR, France</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-03-05T18:55:15+00:00</t>
+          <t>2026-03-05T12:04:58+00:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>DR5411740477U</t>
+          <t>00KNSCLJ</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0420001017085", "sales_office_id": "3015"}</t>
+          <t>{"external_order_id": "0033005729742", "sales_office_id": "0302"}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>01475240795326</t>
+          <t>06086432946253</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-ch-sftp</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD Switzerland</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PO-076-08297648215672223</t>
+          <t>B2BDS10912281</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3081,44 +3081,44 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-05T13:34:08+01:00</t>
+          <t>2026-02-26T15:15:32+01:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Bad Bentheim (DE), Germany</t>
+          <t>,Switzerland</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-05T13:14:12+00:00</t>
+          <t>2026-03-05T11:26:06+00:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>01475240795326</t>
+          <t>06086432946253</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-076-08297648215672223", "sales_office_id": "4670"}</t>
+          <t>{"external_order_id": "B2BDS10912281", "sales_office_id": "4493"}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>01475240798638</t>
+          <t>06086432945142</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-ch-sftp</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD Switzerland</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FG6ER83</t>
+          <t>B2BDS10912281</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3144,44 +3144,44 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-05T15:45:13+01:00</t>
+          <t>2026-02-26T15:15:31+01:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>,Switzerland</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-05T15:14:09+00:00</t>
+          <t>2026-03-05T11:26:11+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>01475240798638</t>
+          <t>06086432945142</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{"external_order_id": "FG6ER83", "sales_office_id": "4326"}</t>
+          <t>{"external_order_id": "B2BDS10912281", "sales_office_id": "4493"}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>01475240797659</t>
+          <t>DR5411740477U</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>ceskaposta-api</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Czech Post</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0049010265892</t>
+          <t>0420001017085</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3207,44 +3207,44 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-05T13:41:43+01:00</t>
+          <t>2026-03-05T14:22:00+01:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Duisburg (DE), Germany</t>
+          <t>39701</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-03-05T14:14:01+00:00</t>
+          <t>2026-03-05T20:55:09+00:00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>01475240797659</t>
+          <t>DR5411740477U</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010265892", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0420001017085", "sales_office_id": "3015"}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UTV524448232</t>
+          <t>01475240795326</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0031009983377</t>
+          <t>PO-076-08297648215672223</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3270,44 +3270,44 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-05T11:18:02+01:00</t>
+          <t>2026-03-05T13:34:08+01:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Bad Bentheim (DE), Germany</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-03-05T10:58:04+00:00</t>
+          <t>2026-03-05T13:14:12+00:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>UTV524448232</t>
+          <t>01475240795326</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009983377", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-076-08297648215672223", "sales_office_id": "4670"}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UTV461276896</t>
+          <t>01475240798638</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0031009983377</t>
+          <t>FG6ER83</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3333,44 +3333,44 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-05T11:19:54+01:00</t>
+          <t>2026-03-05T15:45:13+01:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-05T10:58:05+00:00</t>
+          <t>2026-03-05T15:14:09+00:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>UTV461276896</t>
+          <t>01475240798638</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009983377", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "FG6ER83", "sales_office_id": "4326"}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>05228742853559</t>
+          <t>01475240797659</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>B2BDS11245186</t>
+          <t>0049010265892</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3396,44 +3396,44 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-05T14:34:50+01:00</t>
+          <t>2026-03-05T13:41:43+01:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Trappes, FR, France</t>
+          <t>Duisburg (DE), Germany</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-03-05T17:57:47+00:00</t>
+          <t>2026-03-05T14:14:01+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>05228742853559</t>
+          <t>01475240797659</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11245186", "sales_office_id": "4452"}</t>
+          <t>{"external_order_id": "0049010265892", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>05228742851586</t>
+          <t>UTV461276896</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>B2BDS11245186</t>
+          <t>0031009983377</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3459,44 +3459,44 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-05T14:34:55+01:00</t>
+          <t>2026-03-05T11:19:54+01:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Trappes, FR, France</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-03-05T17:57:51+00:00</t>
+          <t>2026-03-05T10:58:05+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>05228742851586</t>
+          <t>UTV461276896</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11245186", "sales_office_id": "4452"}</t>
+          <t>{"external_order_id": "0031009983377", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>05228742853462</t>
+          <t>UTV524448232</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>B2BDS11245186</t>
+          <t>0031009983377</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3522,27 +3522,27 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-03-05T14:35:16+01:00</t>
+          <t>2026-03-05T11:18:02+01:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Trappes, FR, France</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-03-05T16:58:01+00:00</t>
+          <t>2026-03-05T10:58:04+00:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>05228742853462</t>
+          <t>UTV524448232</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11245186", "sales_office_id": "4452"}</t>
+          <t>{"external_order_id": "0031009983377", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>05228742852714</t>
+          <t>05228742853462</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3648,7 +3648,7 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-05T14:35:09+01:00</t>
+          <t>2026-03-05T14:35:16+01:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-03-05T17:57:59+00:00</t>
+          <t>2026-03-05T20:58:07+00:00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>05228742852714</t>
+          <t>05228742853462</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3675,17 +3675,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>UTV125856209</t>
+          <t>05228742852714</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0031009986304</t>
+          <t>B2BDS11245186</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3711,44 +3711,44 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-05T10:19:26+01:00</t>
+          <t>2026-03-05T14:35:09+01:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Trappes, FR, France</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-05T12:27:55+00:00</t>
+          <t>2026-03-05T17:57:59+00:00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>UTV125856209</t>
+          <t>05228742852714</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009986304", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11245186", "sales_office_id": "4452"}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>UTV933479259</t>
+          <t>05228742851586</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0031009985343</t>
+          <t>B2BDS11245186</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3774,44 +3774,44 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-05T13:14:35+01:00</t>
+          <t>2026-03-05T14:34:55+01:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Trappes, FR, France</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-05T12:27:56+00:00</t>
+          <t>2026-03-05T17:57:51+00:00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>UTV933479259</t>
+          <t>05228742851586</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985343", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11245186", "sales_office_id": "4452"}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>UTV035877190</t>
+          <t>05228742853559</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>C0001KK77X</t>
+          <t>B2BDS11245186</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3837,34 +3837,34 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-03-05T15:48:04+01:00</t>
+          <t>2026-03-05T14:34:50+01:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Trappes, FR, France</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-03-05T15:27:58+00:00</t>
+          <t>2026-03-05T17:57:47+00:00</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>UTV035877190</t>
+          <t>05228742853559</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{"external_order_id": "C0001KK77X", "sales_office_id": "4002"}</t>
+          <t>{"external_order_id": "B2BDS11245186", "sales_office_id": "4452"}</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>UTV925673374</t>
+          <t>UTV125856209</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0031009984956</t>
+          <t>0031009986304</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3900,7 +3900,7 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-05T13:21:49+01:00</t>
+          <t>2026-03-05T10:19:26+01:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3910,24 +3910,24 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-03-05T13:57:16+00:00</t>
+          <t>2026-03-05T12:27:55+00:00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>UTV925673374</t>
+          <t>UTV125856209</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009984956", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009986304", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>UTV656095877</t>
+          <t>UTV035877190</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0031009984956</t>
+          <t>C0001KK77X</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-03-05T13:21:39+01:00</t>
+          <t>2026-03-05T15:48:04+01:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3973,24 +3973,24 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-03-05T13:57:16+00:00</t>
+          <t>2026-03-05T15:27:58+00:00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>UTV656095877</t>
+          <t>UTV035877190</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009984956", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "C0001KK77X", "sales_office_id": "4002"}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>UTV526643716</t>
+          <t>UTV933479259</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0031009984956</t>
+          <t>0031009985343</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-03-05T13:21:59+01:00</t>
+          <t>2026-03-05T13:14:35+01:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4036,24 +4036,24 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-05T13:57:16+00:00</t>
+          <t>2026-03-05T12:27:56+00:00</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>UTV526643716</t>
+          <t>UTV933479259</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009984956", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009985343", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>UTV628205484</t>
+          <t>UTV925673374</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4089,7 +4089,7 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-03-05T13:22:10+01:00</t>
+          <t>2026-03-05T13:21:49+01:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-03-05T13:57:12+00:00</t>
+          <t>2026-03-05T13:57:16+00:00</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>UTV628205484</t>
+          <t>UTV925673374</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4116,7 +4116,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>UTV623744754</t>
+          <t>UTV656095877</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0031009988346</t>
+          <t>0031009984956</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-03-05T13:48:46+01:00</t>
+          <t>2026-03-05T13:21:39+01:00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4162,24 +4162,24 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-03-05T13:57:12+00:00</t>
+          <t>2026-03-05T13:57:16+00:00</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>UTV623744754</t>
+          <t>UTV656095877</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009988346", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009984956", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>UTV496358438</t>
+          <t>UTV526643716</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0031009988346</t>
+          <t>0031009984956</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4215,7 +4215,7 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-05T13:49:35+01:00</t>
+          <t>2026-03-05T13:21:59+01:00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4225,24 +4225,24 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-03-05T13:57:12+00:00</t>
+          <t>2026-03-05T13:57:16+00:00</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>UTV496358438</t>
+          <t>UTV526643716</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009988346", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009984956", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>UTV938392959</t>
+          <t>UTV623744754</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0031009983652</t>
+          <t>0031009988346</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-03-05T15:52:48+01:00</t>
+          <t>2026-03-05T13:48:46+01:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4288,24 +4288,24 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-05T16:57:09+00:00</t>
+          <t>2026-03-05T13:57:12+00:00</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>UTV938392959</t>
+          <t>UTV623744754</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009983652", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009988346", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>UTV506798360</t>
+          <t>UTV628205484</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0031009981799</t>
+          <t>0031009984956</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4341,7 +4341,7 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-03-05T13:34:54+01:00</t>
+          <t>2026-03-05T13:22:10+01:00</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4351,24 +4351,24 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-05T13:57:08+00:00</t>
+          <t>2026-03-05T13:57:12+00:00</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>UTV506798360</t>
+          <t>UTV628205484</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009981799", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009984956", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>UTV691066572</t>
+          <t>UTV496358438</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0031009984665</t>
+          <t>0031009988346</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4404,7 +4404,7 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-05T17:09:29+01:00</t>
+          <t>2026-03-05T13:49:35+01:00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4414,24 +4414,24 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-03-05T16:57:13+00:00</t>
+          <t>2026-03-05T13:57:12+00:00</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>UTV691066572</t>
+          <t>UTV496358438</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009984665", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009988346", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UTV162718948</t>
+          <t>UTV938392959</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4467,7 +4467,7 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-05T15:51:28+01:00</t>
+          <t>2026-03-05T15:52:48+01:00</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>UTV162718948</t>
+          <t>UTV938392959</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4620,7 +4620,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UTV900137917</t>
+          <t>UTV162718948</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0031009984072</t>
+          <t>0031009983652</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4656,7 +4656,7 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-05T16:13:14+01:00</t>
+          <t>2026-03-05T15:51:28+01:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4666,24 +4666,24 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-03-05T16:57:05+00:00</t>
+          <t>2026-03-05T16:57:09+00:00</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>UTV900137917</t>
+          <t>UTV162718948</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009984072", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009983652", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UTV119119325</t>
+          <t>UTV691066572</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0031009985362</t>
+          <t>0031009984665</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4719,7 +4719,7 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-05T11:18:21+01:00</t>
+          <t>2026-03-05T17:09:29+01:00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4729,24 +4729,24 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-03-05T10:57:02+00:00</t>
+          <t>2026-03-05T16:57:13+00:00</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>UTV119119325</t>
+          <t>UTV691066572</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985362", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009984665", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>UTV406057557</t>
+          <t>UTV506798360</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0031009985362</t>
+          <t>0031009981799</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4782,7 +4782,7 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-03-05T11:18:21+01:00</t>
+          <t>2026-03-05T13:34:54+01:00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4792,24 +4792,24 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-03-05T10:57:02+00:00</t>
+          <t>2026-03-05T13:57:08+00:00</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>UTV406057557</t>
+          <t>UTV506798360</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985362", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009981799", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>UTV617341791</t>
+          <t>UTV900137917</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0031009982316</t>
+          <t>0031009984072</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4845,7 +4845,7 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-05T11:48:45+01:00</t>
+          <t>2026-03-05T16:13:14+01:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4855,24 +4855,24 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-03-05T10:57:04+00:00</t>
+          <t>2026-03-05T16:57:05+00:00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>UTV617341791</t>
+          <t>UTV900137917</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009982316", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009984072", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>UTV320542695</t>
+          <t>UTV406057557</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0031009982316</t>
+          <t>0031009985362</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4908,7 +4908,7 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-05T11:48:56+01:00</t>
+          <t>2026-03-05T11:18:21+01:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4918,24 +4918,24 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-03-05T10:57:03+00:00</t>
+          <t>2026-03-05T10:57:02+00:00</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>UTV320542695</t>
+          <t>UTV406057557</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009982316", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009985362", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>UTV037761896</t>
+          <t>UTV119119325</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0031009983462</t>
+          <t>0031009985362</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4971,7 +4971,7 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-05T12:17:14+01:00</t>
+          <t>2026-03-05T11:18:21+01:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4981,34 +4981,34 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-03-05T13:57:03+00:00</t>
+          <t>2026-03-05T10:57:02+00:00</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>UTV037761896</t>
+          <t>UTV119119325</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009983462", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009985362", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>00KNRUWG</t>
+          <t>UTV320542695</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>B2BDS11483776</t>
+          <t>0031009982316</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5034,44 +5034,44 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-05T13:36:54+01:00</t>
+          <t>2026-03-05T11:48:56+01:00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-03-05T13:01:42+00:00</t>
+          <t>2026-03-05T10:57:03+00:00</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>00KNRUWG</t>
+          <t>UTV320542695</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11483776", "sales_office_id": "4449"}</t>
+          <t>{"external_order_id": "0031009982316", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>00KNRUYZ</t>
+          <t>UTV617341791</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>B2BDS11483776</t>
+          <t>0031009982316</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5097,44 +5097,44 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-05T13:36:54+01:00</t>
+          <t>2026-03-05T11:48:45+01:00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-03-05T13:01:41+00:00</t>
+          <t>2026-03-05T10:57:04+00:00</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>00KNRUYZ</t>
+          <t>UTV617341791</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11483776", "sales_office_id": "4449"}</t>
+          <t>{"external_order_id": "0031009982316", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>00KNRUQI</t>
+          <t>UTV037761896</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gls-netherlands-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GLS Netherlands</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>B2BDS11483776</t>
+          <t>0031009983462</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5160,44 +5160,44 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-03-05T13:36:54+01:00</t>
+          <t>2026-03-05T12:17:14+01:00</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-03-05T13:01:39+00:00</t>
+          <t>2026-03-05T13:57:03+00:00</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>00KNRUQI</t>
+          <t>UTV037761896</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11483776", "sales_office_id": "4449"}</t>
+          <t>{"external_order_id": "0031009983462", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>05228742857309</t>
+          <t>00KNRUWG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0032005570503</t>
+          <t>B2BDS11483776</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5223,44 +5223,44 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-03-05T11:24:52+01:00</t>
+          <t>2026-03-05T13:36:54+01:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Lummen, BE, Belgium</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-03-05T10:39:23+00:00</t>
+          <t>2026-03-05T13:01:42+00:00</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>05228742857309</t>
+          <t>00KNRUWG</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005570503", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11483776", "sales_office_id": "4449"}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>05228742856561</t>
+          <t>00KNRUYZ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0031009981419</t>
+          <t>B2BDS11483776</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5286,44 +5286,44 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-03-05T11:21:30+01:00</t>
+          <t>2026-03-05T13:36:54+01:00</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Vijfhuizen, NL, Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-03-05T14:34:08+00:00</t>
+          <t>2026-03-05T13:01:41+00:00</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>05228742856561</t>
+          <t>00KNRUYZ</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009981419", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11483776", "sales_office_id": "4449"}</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>05228742855617</t>
+          <t>00KNRUQI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>gls-netherlands-api</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS Netherlands</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0031009981419</t>
+          <t>B2BDS11483776</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5349,34 +5349,34 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-03-05T11:21:29+01:00</t>
+          <t>2026-03-05T13:36:54+01:00</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Vijfhuizen, NL, Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-03-05T11:33:43+00:00</t>
+          <t>2026-03-05T13:01:39+00:00</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>05228742855617</t>
+          <t>00KNRUQI</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009981419", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11483776", "sales_office_id": "4449"}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>05228742856686</t>
+          <t>05228742857309</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0032005571626</t>
+          <t>0032005570503</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5412,34 +5412,34 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-03-05T10:35:02+01:00</t>
+          <t>2026-03-05T11:24:52+01:00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Courcelles, BE, Belgium</t>
+          <t>Lummen, BE, Belgium</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-03-05T10:09:03+00:00</t>
+          <t>2026-03-05T10:39:23+00:00</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>05228742856686</t>
+          <t>05228742857309</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005571626", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005570503", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>05228742856316</t>
+          <t>05228742856561</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>B2BDS11403446</t>
+          <t>0031009981419</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5475,34 +5475,34 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-03-05T13:36:59+01:00</t>
+          <t>2026-03-05T11:21:30+01:00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Kortrijk, BE, Belgium</t>
+          <t>Vijfhuizen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-03-05T13:03:42+00:00</t>
+          <t>2026-03-05T14:34:08+00:00</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>05228742856316</t>
+          <t>05228742856561</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11403446", "sales_office_id": "4490"}</t>
+          <t>{"external_order_id": "0031009981419", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>05228742856289</t>
+          <t>05228742855617</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>B2BDS11403446</t>
+          <t>0031009981419</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5538,34 +5538,34 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-03-05T13:36:59+01:00</t>
+          <t>2026-03-05T11:21:29+01:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Kortrijk, BE, Belgium</t>
+          <t>Vijfhuizen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-03-05T13:03:42+00:00</t>
+          <t>2026-03-05T11:33:43+00:00</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>05228742856289</t>
+          <t>05228742855617</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11403446", "sales_office_id": "4490"}</t>
+          <t>{"external_order_id": "0031009981419", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>05228742855368</t>
+          <t>05228742856686</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>B2BDS11403446</t>
+          <t>0032005571626</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5601,34 +5601,34 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-05T13:36:59+01:00</t>
+          <t>2026-03-05T10:35:02+01:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Kortrijk, BE, Belgium</t>
+          <t>Courcelles, BE, Belgium</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-03-05T13:03:55+00:00</t>
+          <t>2026-03-05T10:09:03+00:00</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>05228742855368</t>
+          <t>05228742856686</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11403446", "sales_office_id": "4490"}</t>
+          <t>{"external_order_id": "0032005571626", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>05228742855926</t>
+          <t>05228742856316</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-03-05T13:03:37+00:00</t>
+          <t>2026-03-05T13:03:42+00:00</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>05228742855926</t>
+          <t>05228742856316</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5691,7 +5691,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>05228742855786</t>
+          <t>05228742855528</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5737,12 +5737,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-03-05T14:33:29+00:00</t>
+          <t>2026-03-05T13:03:25+00:00</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>05228742855786</t>
+          <t>05228742855528</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -5754,7 +5754,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>05228742855528</t>
+          <t>05228742855368</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-03-05T13:03:25+00:00</t>
+          <t>2026-03-05T13:03:55+00:00</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>05228742855528</t>
+          <t>05228742855368</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -5817,7 +5817,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>05228742856264</t>
+          <t>05228742855926</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-03-05T14:33:40+00:00</t>
+          <t>2026-03-05T13:03:37+00:00</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>05228742856264</t>
+          <t>05228742855926</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -5880,7 +5880,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>05228742858191</t>
+          <t>05228742855786</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0031009987589</t>
+          <t>B2BDS11403446</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5916,34 +5916,34 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-03-05T11:14:11+01:00</t>
+          <t>2026-03-05T13:36:59+01:00</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Goes, NL, Netherlands</t>
+          <t>Kortrijk, BE, Belgium</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-05T10:39:00+00:00</t>
+          <t>2026-03-05T14:33:29+00:00</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>05228742858191</t>
+          <t>05228742855786</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009987589", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11403446", "sales_office_id": "4490"}</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>05228742856034</t>
+          <t>05228742856289</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>B2BDS11320375</t>
+          <t>B2BDS11403446</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5979,34 +5979,34 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-03-05T11:08:11+01:00</t>
+          <t>2026-03-05T13:36:59+01:00</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>Kortrijk, BE, Belgium</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-03-05T10:39:12+00:00</t>
+          <t>2026-03-05T13:03:42+00:00</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>05228742856034</t>
+          <t>05228742856289</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11320375", "sales_office_id": "4449"}</t>
+          <t>{"external_order_id": "B2BDS11403446", "sales_office_id": "4490"}</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>05228742857634</t>
+          <t>05228742856264</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0031009987659</t>
+          <t>B2BDS11403446</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6042,44 +6042,44 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-03-05T14:27:50+01:00</t>
+          <t>2026-03-05T13:36:59+01:00</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Kortrijk, BE, Belgium</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-03-05T13:39:47+00:00</t>
+          <t>2026-03-05T14:33:40+00:00</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>05228742857634</t>
+          <t>05228742856264</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009987659", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11403446", "sales_office_id": "4490"}</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>00KNSCSS</t>
+          <t>05228742858191</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0033005731001</t>
+          <t>0031009987589</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0302</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6105,44 +6105,44 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-03-05T11:07:25+01:00</t>
+          <t>2026-03-05T11:14:11+01:00</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>FR, France</t>
+          <t>Goes, NL, Netherlands</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-03-05T10:12:39+00:00</t>
+          <t>2026-03-05T10:39:00+00:00</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>00KNSCSS</t>
+          <t>05228742858191</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005731001", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "0031009987589", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>00KNSCSR</t>
+          <t>05228742857634</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0033005731001</t>
+          <t>0031009987659</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0302</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6168,44 +6168,44 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-05T11:07:25+01:00</t>
+          <t>2026-03-05T14:27:50+01:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>FR, France</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-03-05T10:12:39+00:00</t>
+          <t>2026-03-05T13:39:47+00:00</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>00KNSCSR</t>
+          <t>05228742857634</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0033005731001", "sales_office_id": "0302"}</t>
+          <t>{"external_order_id": "0031009987659", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>YVXA6PPF</t>
+          <t>05228742856034</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6215,56 +6215,60 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>6001673740</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
+          <t>B2BDS11320375</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-02-24T13:30:53+01:00</t>
+          <t>2026-03-05T11:08:11+01:00</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>Veenendaal, NL, Netherlands</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:11+00:00</t>
+          <t>2026-03-05T10:39:12+00:00</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>YVXA6PPF</t>
+          <t>05228742856034</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "B2BDS11320375", "sales_office_id": "4449"}</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>JJD149990121180221276</t>
+          <t>00KNSCSR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6274,52 +6278,60 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>6001656843</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
+          <t>0033005731001</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-03-05T14:22:00+01:00</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
+          <t>2026-03-05T11:07:25+01:00</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>FR, France</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:22+00:00</t>
+          <t>2026-03-05T10:12:39+00:00</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>JJD149990121180221276</t>
+          <t>00KNSCSR</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "0033005731001", "sales_office_id": "0302"}</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CY431870379DE</t>
+          <t>00KNSCSS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>dhl-germany</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Deutsche Post DHL</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6329,56 +6341,60 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>6001670657</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
+          <t>0033005731001</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-02-27T13:27:00+01:00</t>
+          <t>2026-03-05T11:07:25+01:00</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>FR, France</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T10:12:39+00:00</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CY431870379DE</t>
+          <t>00KNSCSS</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "0033005731001", "sales_office_id": "0302"}</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JD014600012504431918</t>
+          <t>YVXA6PPF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>dhl</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DHL Express</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6388,7 +6404,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>6001675047</t>
+          <t>6001673740</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -6400,27 +6416,27 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-03-04T11:27:02+01:00</t>
+          <t>2026-02-24T13:30:53+01:00</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>EINDHOVEN-NLD, Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:10+00:00</t>
+          <t>2026-03-05T04:12:11+00:00</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>JD014600012504431918</t>
+          <t>YVXA6PPF</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
@@ -6482,17 +6498,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>05222069697559</t>
+          <t>CY431894273DE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>dhl-germany</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Deutsche Post DHL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6502,7 +6518,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>6001674054</t>
+          <t>6001676249</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -6514,27 +6530,27 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-01-28T12:39:41+01:00</t>
+          <t>2026-03-05T13:25:00+01:00</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Meppel, NL, Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:15+00:00</t>
+          <t>2026-03-05T13:14:01+00:00</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>05222069697559</t>
+          <t>CY431894273DE</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
@@ -6600,17 +6616,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>JD014600012546522558</t>
+          <t>845152822580</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>dhl</t>
+          <t>dhl-germany</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DHL Express</t>
+          <t>Deutsche Post DHL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6620,7 +6636,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>6001672823</t>
+          <t>6001675328</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -6632,22 +6648,22 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-03-04T11:27:02+01:00</t>
+          <t>2026-02-12T15:06:41+01:00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>EINDHOVEN-NLD, Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:10+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>JD014600012546522558</t>
+          <t>845152822580</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6718,17 +6734,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>05222069778729</t>
+          <t>CY431870379DE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>dhl-germany</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Deutsche Post DHL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6738,7 +6754,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>6001676007</t>
+          <t>6001670657</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -6750,44 +6766,44 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-03-05T08:20:00+01:00</t>
+          <t>2026-02-27T13:27:00+01:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-03-05T16:16:22+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>05222069778729</t>
+          <t>CY431870379DE</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ZDDO3M23</t>
+          <t>502067169785</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6797,7 +6813,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>6001672548</t>
+          <t>6001657770</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -6809,22 +6825,22 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-02-24T13:30:00+01:00</t>
+          <t>2026-03-04T11:57:00+09:00</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>古河営業所, Japan</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:10+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>ZDDO3M23</t>
+          <t>502067169785</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -6836,17 +6852,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CY431894273DE</t>
+          <t>JJD149990121180221276</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>dhl-germany</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Deutsche Post DHL</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6856,7 +6872,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>6001676249</t>
+          <t>6001656843</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -6868,22 +6884,18 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-03-05T13:25:00+01:00</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
+          <t>2026-03-05T14:22:00+01:00</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-03-05T13:14:01+00:00</t>
+          <t>2026-03-05T13:42:22+00:00</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CY431894273DE</t>
+          <t>JJD149990121180221276</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -6895,17 +6907,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>845152822580</t>
+          <t>05222069697559</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>dhl-germany</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Deutsche Post DHL</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6915,7 +6927,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>6001675328</t>
+          <t>6001674054</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -6927,44 +6939,44 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-02-12T15:06:41+01:00</t>
+          <t>2026-01-28T12:39:41+01:00</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Meppel, NL, Netherlands</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:15+00:00</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>845152822580</t>
+          <t>05222069697559</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>502067169785</t>
+          <t>JD014600012546522558</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>sagawa</t>
+          <t>dhl</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sagawa</t>
+          <t>DHL Express</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6974,7 +6986,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>6001657770</t>
+          <t>6001672823</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -6986,44 +6998,44 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-03-04T11:57:00+09:00</t>
+          <t>2026-03-04T11:27:02+01:00</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>古河営業所, Japan</t>
+          <t>EINDHOVEN-NLD, Netherlands</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:10+00:00</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>502067169785</t>
+          <t>JD014600012546522558</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>JJD149990121180221537</t>
+          <t>ZDDO3M23</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7033,7 +7045,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>6001656771</t>
+          <t>6001672548</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -7045,40 +7057,44 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-04T14:51:00+01:00</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>2026-02-24T13:30:00+01:00</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>DE, Germany</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:10+00:00</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>JJD149990121180221537</t>
+          <t>ZDDO3M23</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JJD149990121180223473</t>
+          <t>05222069778729</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>dpd</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7088,7 +7104,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>6001663171</t>
+          <t>6001676007</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -7100,40 +7116,44 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-05T14:22:00+01:00</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr"/>
+          <t>2026-03-05T08:20:00+01:00</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Oirschot, NL, Netherlands</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:16+00:00</t>
+          <t>2026-03-05T16:16:22+00:00</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>JJD149990121180223473</t>
+          <t>05222069778729</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>JJD149990121180223799</t>
+          <t>JD014600012504431918</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>dhl</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>DHL Express</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7143,7 +7163,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>6001664342</t>
+          <t>6001675047</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -7155,18 +7175,22 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-03-05T14:22:00+01:00</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr"/>
+          <t>2026-03-04T11:27:02+01:00</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>EINDHOVEN-NLD, Netherlands</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:20+00:00</t>
+          <t>2026-03-05T04:12:10+00:00</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>JJD149990121180223799</t>
+          <t>JD014600012504431918</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -7178,7 +7202,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>JJD149990121180221081</t>
+          <t>JJD149990121180223105</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7198,7 +7222,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>6001657127</t>
+          <t>6001665167</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -7210,18 +7234,18 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-03-04T14:51:00+01:00</t>
+          <t>2026-03-05T14:22:00+01:00</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:11+00:00</t>
+          <t>2026-03-05T13:42:21+00:00</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>JJD149990121180221081</t>
+          <t>JJD149990121180223105</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -7233,7 +7257,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>JJD149990121180221197</t>
+          <t>JJD149990121180223994</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7253,7 +7277,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>6001656849</t>
+          <t>6001664198</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -7265,18 +7289,18 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-03-05T14:22:00+01:00</t>
+          <t>2026-03-04T14:51:00+01:00</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:20+00:00</t>
+          <t>2026-03-05T04:12:11+00:00</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>JJD149990121180221197</t>
+          <t>JJD149990121180223994</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -7288,7 +7312,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>JJD149990121180221917</t>
+          <t>JJD149990121180221197</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7308,7 +7332,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>6001660822</t>
+          <t>6001656849</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -7320,18 +7344,18 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-04T14:51:00+01:00</t>
+          <t>2026-03-05T14:22:00+01:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T13:42:20+00:00</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>JJD149990121180221917</t>
+          <t>JJD149990121180221197</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -7343,7 +7367,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>JJD149990121180223187</t>
+          <t>JJD149990121180223622</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7363,7 +7387,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>6001664870</t>
+          <t>6001663145</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -7381,12 +7405,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:11+00:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>JJD149990121180223187</t>
+          <t>JJD149990121180223622</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -7398,7 +7422,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>JJD149990121180223622</t>
+          <t>JJD149990121180221385</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7418,7 +7442,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>6001663145</t>
+          <t>6001656808</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -7430,18 +7454,18 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-04T14:51:00+01:00</t>
+          <t>2026-03-05T14:22:00+01:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:11+00:00</t>
+          <t>2026-03-05T17:42:29+00:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>JJD149990121180223622</t>
+          <t>JJD149990121180221385</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -7453,7 +7477,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>JJD149990121180221057</t>
+          <t>JJD149990121180223187</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7473,7 +7497,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>6001657140</t>
+          <t>6001664870</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -7491,12 +7515,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:11+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>JJD149990121180221057</t>
+          <t>JJD149990121180223187</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -7508,7 +7532,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>JJD149990121180223324</t>
+          <t>JJD149990121180223349</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7528,7 +7552,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>6001664582</t>
+          <t>6001664555</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -7546,12 +7570,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:14+00:00</t>
+          <t>2026-03-05T13:42:13+00:00</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>JJD149990121180223324</t>
+          <t>JJD149990121180223349</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -7563,7 +7587,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>JJD149990121180221385</t>
+          <t>JJD149990121180221362</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7583,7 +7607,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>6001656808</t>
+          <t>6001656829</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -7601,12 +7625,12 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-03-05T17:42:29+00:00</t>
+          <t>2026-03-05T13:42:18+00:00</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>JJD149990121180221385</t>
+          <t>JJD149990121180221362</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -7618,7 +7642,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>JJD149990121180223105</t>
+          <t>JJD149990121180223799</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7638,7 +7662,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>6001665167</t>
+          <t>6001664342</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -7656,12 +7680,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:21+00:00</t>
+          <t>2026-03-05T13:42:20+00:00</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>JJD149990121180223105</t>
+          <t>JJD149990121180223799</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -7673,7 +7697,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>JJD149990121180222378</t>
+          <t>JJD149990121180223851</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7693,7 +7717,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>6001660819</t>
+          <t>6001664315</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -7711,12 +7735,12 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:13+00:00</t>
+          <t>2026-03-05T13:42:17+00:00</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>JJD149990121180222378</t>
+          <t>JJD149990121180223851</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -7728,7 +7752,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>JJD149990121180223349</t>
+          <t>JJD149990121180223189</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7748,7 +7772,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>6001664555</t>
+          <t>6001664847</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -7766,12 +7790,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:13+00:00</t>
+          <t>2026-03-05T13:42:16+00:00</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>JJD149990121180223349</t>
+          <t>JJD149990121180223189</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -7783,7 +7807,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>JJD149990121180221756</t>
+          <t>JJD149990121180221081</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7803,7 +7827,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>6001669139</t>
+          <t>6001657127</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -7815,18 +7839,18 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-05T14:22:00+01:00</t>
+          <t>2026-03-04T14:51:00+01:00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:17+00:00</t>
+          <t>2026-03-05T04:12:11+00:00</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>JJD149990121180221756</t>
+          <t>JJD149990121180221081</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -7838,7 +7862,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JJD149990121180224085</t>
+          <t>JJD149990121180223324</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7858,7 +7882,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>6001664185</t>
+          <t>6001664582</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -7870,18 +7894,18 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-03-04T14:51:00+01:00</t>
+          <t>2026-03-05T14:22:00+01:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:07+00:00</t>
+          <t>2026-03-05T13:42:14+00:00</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>JJD149990121180224085</t>
+          <t>JJD149990121180223324</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -7893,7 +7917,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>JJD149990121180223994</t>
+          <t>JJD149990121180221756</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7913,7 +7937,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>6001664198</t>
+          <t>6001669139</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -7925,18 +7949,18 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-03-04T14:51:00+01:00</t>
+          <t>2026-03-05T14:22:00+01:00</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:11+00:00</t>
+          <t>2026-03-05T13:42:17+00:00</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>JJD149990121180223994</t>
+          <t>JJD149990121180221756</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -7948,7 +7972,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>JJD149990121180223189</t>
+          <t>JJD149990121180221917</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7968,7 +7992,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>6001664847</t>
+          <t>6001660822</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -7980,18 +8004,18 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-03-05T14:22:00+01:00</t>
+          <t>2026-03-04T14:51:00+01:00</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:16+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>JJD149990121180223189</t>
+          <t>JJD149990121180221917</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -8003,7 +8027,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>JJD149990121180221362</t>
+          <t>JJD149990121180223473</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8023,7 +8047,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>6001656829</t>
+          <t>6001663171</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -8041,12 +8065,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:18+00:00</t>
+          <t>2026-03-05T13:42:16+00:00</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>JJD149990121180221362</t>
+          <t>JJD149990121180223473</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -8058,7 +8082,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>JJD149990121180223851</t>
+          <t>JJD149990121180221057</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8078,7 +8102,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>6001664315</t>
+          <t>6001657140</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -8090,18 +8114,18 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-03-05T14:22:00+01:00</t>
+          <t>2026-03-04T14:51:00+01:00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-03-05T13:42:17+00:00</t>
+          <t>2026-03-05T04:12:11+00:00</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>JJD149990121180223851</t>
+          <t>JJD149990121180221057</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -8113,17 +8137,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1Z6X581R9197898980</t>
+          <t>JJD149990121180222378</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8133,7 +8157,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>6001667142</t>
+          <t>6001660819</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -8145,44 +8169,40 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-03-04T09:53:37+01:00</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>1 MARY KINGSLEYSTRAAT, VENLO, 5928SK, NL, Netherlands</t>
-        </is>
-      </c>
+          <t>2026-03-05T14:22:00+01:00</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T13:42:13+00:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>1Z6X581R9197898980</t>
+          <t>JJD149990121180222378</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1Z6X581R9198437038</t>
+          <t>JJD149990121180224085</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8192,7 +8212,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>6001667142</t>
+          <t>6001664185</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -8204,34 +8224,30 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-03-04T09:53:37+01:00</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>1 MARY KINGSLEYSTRAAT, VENLO, 5928SK, NL, Netherlands</t>
-        </is>
-      </c>
+          <t>2026-03-04T14:51:00+01:00</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:07+00:00</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>1Z6X581R9198437038</t>
+          <t>JJD149990121180224085</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>JJD149990121180224481</t>
+          <t>JJD149990121180221537</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8251,7 +8267,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>6001668423</t>
+          <t>6001656771</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -8269,12 +8285,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:11+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>JJD149990121180224481</t>
+          <t>JJD149990121180221537</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -8286,7 +8302,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1Z6X581R9195306818</t>
+          <t>1Z6X581R9197898980</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8328,12 +8344,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:07+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>1Z6X581R9195306818</t>
+          <t>1Z6X581R9197898980</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -8345,17 +8361,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1Z6X581R9195699207</t>
+          <t>JJD149990121180224481</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8365,7 +8381,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>6001667142</t>
+          <t>6001668423</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -8377,44 +8393,40 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-04T09:53:37+01:00</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>1 MARY KINGSLEYSTRAAT, VENLO, 5928SK, NL, Netherlands</t>
-        </is>
-      </c>
+          <t>2026-03-04T14:51:00+01:00</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:08+00:00</t>
+          <t>2026-03-05T04:12:11+00:00</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>1Z6X581R9195699207</t>
+          <t>JJD149990121180224481</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>996011434800773180</t>
+          <t>1Z6X581R9193510967</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>swiss-post</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Swiss Post</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8424,7 +8436,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>6001670595</t>
+          <t>6001667142</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -8436,34 +8448,34 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-03-04T11:46:35+01:00</t>
+          <t>2026-03-04T09:53:37+01:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>CH, Switzerland</t>
+          <t>1 MARY KINGSLEYSTRAAT, VENLO, 5928SK, NL, Netherlands</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-03-05T08:12:08+00:00</t>
+          <t>2026-03-05T04:12:07+00:00</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>996011434800773180</t>
+          <t>1Z6X581R9193510967</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>{"courier": "swiss-post", "custom_1": "Galaxus"}</t>
+          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1Z6X581R9193510967</t>
+          <t>1Z6X581R9195699207</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8505,12 +8517,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:07+00:00</t>
+          <t>2026-03-05T04:12:08+00:00</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>1Z6X581R9193510967</t>
+          <t>1Z6X581R9195699207</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -8522,7 +8534,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1ZR096K99098019201</t>
+          <t>1Z6X581R9195306818</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8542,7 +8554,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>6001658193</t>
+          <t>6001667142</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -8554,22 +8566,22 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-03-03T12:18:34-05:00</t>
+          <t>2026-03-04T09:53:37+01:00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>MOUNT POCONO, PA, 18344, US, United States</t>
+          <t>1 MARY KINGSLEYSTRAAT, VENLO, 5928SK, NL, Netherlands</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:08+00:00</t>
+          <t>2026-03-05T04:12:07+00:00</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>1ZR096K99098019201</t>
+          <t>1Z6X581R9195306818</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -8581,7 +8593,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1Z0JA1729003969802</t>
+          <t>1ZR096K99098019201</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8601,7 +8613,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>6001673962</t>
+          <t>6001658193</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -8613,22 +8625,22 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-03-04T12:00:03-08:00</t>
+          <t>2026-03-03T12:18:34-05:00</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>REDLANDS, CA, 92374, US, United States</t>
+          <t>MOUNT POCONO, PA, 18344, US, United States</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:09+00:00</t>
+          <t>2026-03-05T04:12:08+00:00</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>1Z0JA1729003969802</t>
+          <t>1ZR096K99098019201</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -8640,17 +8652,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>996011434800773823</t>
+          <t>1Z6X581R9198437038</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>swiss-post</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Swiss Post</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8660,7 +8672,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>6001670183</t>
+          <t>6001667142</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -8672,44 +8684,44 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-05T08:31:29+01:00</t>
+          <t>2026-03-04T09:53:37+01:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>CH, Switzerland</t>
+          <t>1 MARY KINGSLEYSTRAAT, VENLO, 5928SK, NL, Netherlands</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-03-05T09:12:13+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>996011434800773823</t>
+          <t>1Z6X581R9198437038</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>{"courier": "swiss-post", "custom_1": "Galaxus"}</t>
+          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>REC000081042986</t>
+          <t>996011434800773180</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>swiss-post</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Swiss Post</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8719,7 +8731,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>6001672950</t>
+          <t>6001670595</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -8731,40 +8743,44 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-03-05T11:33:00</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr"/>
+          <t>2026-03-04T11:46:35+01:00</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>CH, Switzerland</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-03-05T11:19:51+00:00</t>
+          <t>2026-03-05T08:12:08+00:00</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>REC000081042986</t>
+          <t>996011434800773180</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"courier": "swiss-post", "custom_1": "Galaxus"}</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>REC000081048624</t>
+          <t>1Z0JA1729003969802</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8774,7 +8790,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>6001674102</t>
+          <t>6001673962</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -8786,40 +8802,44 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-03-05T13:51:00</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr"/>
+          <t>2026-03-04T12:00:03-08:00</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>REDLANDS, CA, 92374, US, United States</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-03-05T13:19:33+00:00</t>
+          <t>2026-03-05T04:12:09+00:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>REC000081048624</t>
+          <t>1Z0JA1729003969802</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>REC000081044420</t>
+          <t>996011434800773823</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>swiss-post</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Swiss Post</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8829,7 +8849,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>6001673474</t>
+          <t>6001670183</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -8841,30 +8861,34 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-03-05T16:07:00</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr"/>
+          <t>2026-03-05T08:31:29+01:00</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>CH, Switzerland</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-03-05T15:19:34+00:00</t>
+          <t>2026-03-05T09:12:13+00:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>REC000081044420</t>
+          <t>996011434800773823</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"courier": "swiss-post", "custom_1": "Galaxus"}</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>REC000081044241</t>
+          <t>REC000081046292</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8884,7 +8908,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>6001673440</t>
+          <t>6001673792</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -8896,18 +8920,18 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-05T10:18:00</t>
+          <t>2026-03-05T11:18:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-03-05T12:19:32+00:00</t>
+          <t>2026-03-05T16:18:56+00:00</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>REC000081044241</t>
+          <t>REC000081046292</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -8919,7 +8943,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>REC000081043835</t>
+          <t>REC000081043676</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8939,7 +8963,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>6001673341</t>
+          <t>6001673257</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -8951,18 +8975,18 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-05T16:01:00</t>
+          <t>2026-03-05T12:12:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-03-05T15:19:35+00:00</t>
+          <t>2026-03-05T11:20:12+00:00</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>REC000081043835</t>
+          <t>REC000081043676</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -8974,7 +8998,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>REC000081043031</t>
+          <t>REC000081053476</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8994,7 +9018,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>6001673055</t>
+          <t>6001674563</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -9006,18 +9030,18 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-03-05T17:38:00</t>
+          <t>2026-03-05T13:22:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-03-05T17:20:20+00:00</t>
+          <t>2026-03-05T13:19:52+00:00</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>REC000081043031</t>
+          <t>REC000081053476</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -9029,7 +9053,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>REC000081043069</t>
+          <t>REC000081044419</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9049,7 +9073,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>6001673088</t>
+          <t>6001673471</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -9061,18 +9085,18 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-03-05T10:11:00</t>
+          <t>2026-03-05T15:31:00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-03-05T09:20:09+00:00</t>
+          <t>2026-03-05T15:19:16+00:00</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>REC000081043069</t>
+          <t>REC000081044419</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -9084,7 +9108,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>REC000081043676</t>
+          <t>REC000081043069</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9104,7 +9128,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>6001673257</t>
+          <t>6001673088</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -9116,18 +9140,18 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-03-05T12:12:00</t>
+          <t>2026-03-05T10:11:00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-03-05T11:20:12+00:00</t>
+          <t>2026-03-05T09:20:09+00:00</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>REC000081043676</t>
+          <t>REC000081043069</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -9139,7 +9163,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>REC000081044419</t>
+          <t>REC000081042986</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9159,7 +9183,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>6001673471</t>
+          <t>6001672950</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -9171,18 +9195,18 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-03-05T15:31:00</t>
+          <t>2026-03-05T11:33:00</t>
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-03-05T15:19:16+00:00</t>
+          <t>2026-03-05T11:19:51+00:00</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>REC000081044419</t>
+          <t>REC000081042986</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -9249,7 +9273,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>REC000081046292</t>
+          <t>REC000081048624</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9269,7 +9293,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>6001673792</t>
+          <t>6001674102</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -9281,18 +9305,18 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-03-05T11:18:00</t>
+          <t>2026-03-05T13:51:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-03-05T16:18:56+00:00</t>
+          <t>2026-03-05T13:19:33+00:00</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>REC000081046292</t>
+          <t>REC000081048624</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -9304,7 +9328,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>REC000081041114</t>
+          <t>REC000081050406</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9324,7 +9348,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>6001672432</t>
+          <t>6001674313</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -9336,18 +9360,18 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-03-05T12:12:00</t>
+          <t>2026-03-05T19:48:00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-03-05T11:20:11+00:00</t>
+          <t>2026-03-05T19:19:40+00:00</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>REC000081041114</t>
+          <t>REC000081050406</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -9359,7 +9383,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>REC000081053476</t>
+          <t>REC000081041114</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9379,7 +9403,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>6001674563</t>
+          <t>6001672432</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -9391,18 +9415,18 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-03-05T13:22:00</t>
+          <t>2026-03-05T12:12:00</t>
         </is>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-03-05T13:19:52+00:00</t>
+          <t>2026-03-05T11:20:11+00:00</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>REC000081053476</t>
+          <t>REC000081041114</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -9414,7 +9438,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>REC000081050406</t>
+          <t>REC000081043835</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9434,7 +9458,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>6001674313</t>
+          <t>6001673341</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -9446,18 +9470,18 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-03-05T19:48:00</t>
+          <t>2026-03-05T16:01:00</t>
         </is>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-03-05T19:19:40+00:00</t>
+          <t>2026-03-05T15:19:35+00:00</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>REC000081050406</t>
+          <t>REC000081043835</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -9469,7 +9493,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>REC000081083270</t>
+          <t>REC000081043031</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9489,7 +9513,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>6001675719</t>
+          <t>6001673055</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -9501,18 +9525,18 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-03-05T16:11:00</t>
+          <t>2026-03-05T17:38:00</t>
         </is>
       </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-03-05T15:19:34+00:00</t>
+          <t>2026-03-05T17:20:20+00:00</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>REC000081083270</t>
+          <t>REC000081043031</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -9524,17 +9548,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>996014994510153556</t>
+          <t>REC000081044241</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>swiss-post</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Swiss Post</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9544,7 +9568,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>6001674739</t>
+          <t>6001673440</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -9556,44 +9580,40 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-03-05T08:33:58+01:00</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>CH, Switzerland</t>
-        </is>
-      </c>
+          <t>2026-03-05T10:18:00</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-03-05T09:12:09+00:00</t>
+          <t>2026-03-05T12:19:32+00:00</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>996014994510153556</t>
+          <t>REC000081044241</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>{"courier": "swiss-post", "custom_1": "Galaxus"}</t>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3366573085793</t>
+          <t>REC000081044420</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>directfreight-au-ref</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Direct Freight Express</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9603,7 +9623,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>6001673273</t>
+          <t>6001673474</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -9615,44 +9635,40 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-03-03T13:09:00+09:30</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Melbourne(N), Australia</t>
-        </is>
-      </c>
+          <t>2026-03-05T16:07:00</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:01+00:00</t>
+          <t>2026-03-05T15:19:34+00:00</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>3366573085793</t>
+          <t>REC000081044420</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>{"courier": "directfreight-au-ref", "custom_1": "Returns_directfreight-au-ref"}</t>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>0053208782934W</t>
+          <t>REC000081083270</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9662,7 +9678,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>6001659624</t>
+          <t>6001675719</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -9674,44 +9690,40 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>ROSANOW, PL, Poland</t>
-        </is>
-      </c>
+          <t>2026-03-05T16:11:00</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T15:19:34+00:00</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>0053208782934W</t>
+          <t>REC000081083270</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>0053205219805W</t>
+          <t>996014994510153556</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>swiss-post</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Swiss Post</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9721,7 +9733,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>6001658500</t>
+          <t>6001674739</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -9733,44 +9745,44 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-05T08:33:58+01:00</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>CH, Switzerland</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T09:12:09+00:00</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>0053205219805W</t>
+          <t>996014994510153556</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"courier": "swiss-post", "custom_1": "Galaxus"}</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>0053210819530W</t>
+          <t>3366573085793</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>directfreight-au-ref</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Direct Freight Express</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9780,7 +9792,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>6001659808</t>
+          <t>6001673273</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -9792,34 +9804,34 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-03T13:09:00+09:30</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Melbourne(N), Australia</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:03+00:00</t>
+          <t>2026-03-05T04:12:01+00:00</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>0053210819530W</t>
+          <t>3366573085793</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"courier": "directfreight-au-ref", "custom_1": "Returns_directfreight-au-ref"}</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>0053207782018W</t>
+          <t>0053205047180W</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9839,7 +9851,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>6001659335</t>
+          <t>6001658446</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -9851,7 +9863,7 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9861,12 +9873,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:06+00:00</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>0053207782018W</t>
+          <t>0053205047180W</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -9878,7 +9890,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>0053204699288W</t>
+          <t>0053206922740W</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9898,7 +9910,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>6001658321</t>
+          <t>6001659148</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -9910,7 +9922,7 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-02T07:35:00+01:00</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9920,12 +9932,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T08:12:11+00:00</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>0053204699288W</t>
+          <t>0053206922740W</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -9937,7 +9949,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>0053206922740W</t>
+          <t>0053214519488W</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9957,7 +9969,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>6001659148</t>
+          <t>6001661533</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -9969,7 +9981,7 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-02T07:35:00+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9979,12 +9991,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-03-05T08:12:11+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>0053206922740W</t>
+          <t>0053214519488W</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -9996,7 +10008,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>0053205219745W</t>
+          <t>0053214132038W</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10016,7 +10028,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>6001658500</t>
+          <t>6001660394</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -10043,7 +10055,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>0053205219745W</t>
+          <t>0053214132038W</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -10055,7 +10067,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>0053205219500W</t>
+          <t>0053213367045W</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10075,7 +10087,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>6001658500</t>
+          <t>6001658654</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -10097,12 +10109,12 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:07+00:00</t>
+          <t>2026-03-05T04:12:06+00:00</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>0053205219500W</t>
+          <t>0053213367045W</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -10114,7 +10126,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>0053204590575W</t>
+          <t>0053213935294W</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10134,7 +10146,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>6001658123</t>
+          <t>6001660299</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -10146,22 +10158,22 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-03-02T11:43:09+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Warszawa, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-03-05T16:12:16+00:00</t>
+          <t>2026-03-05T07:12:12+00:00</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>0053204590575W</t>
+          <t>0053213935294W</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -10173,7 +10185,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>0053205141234W</t>
+          <t>0053209303502W</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10193,7 +10205,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>6001658455</t>
+          <t>6001659665</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -10205,22 +10217,22 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-03-05T13:31:26+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Warszawa, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-03-05T13:16:11+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>0053205141234W</t>
+          <t>0053209303502W</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -10291,7 +10303,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>0053209303502W</t>
+          <t>0053205219745W</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10311,7 +10323,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>6001659665</t>
+          <t>6001658500</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -10333,12 +10345,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>0053209303502W</t>
+          <t>0053205219745W</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -10350,7 +10362,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>0053211187532W</t>
+          <t>0053204699288W</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10370,7 +10382,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>6001659845</t>
+          <t>6001658321</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -10382,12 +10394,12 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-02T18:00:15+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Warszawa, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -10397,7 +10409,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>0053211187532W</t>
+          <t>0053204699288W</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -10409,7 +10421,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>0053205219692W</t>
+          <t>0053204590575W</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10429,7 +10441,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>6001658500</t>
+          <t>6001658123</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -10441,22 +10453,22 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-02T11:43:09+01:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Warszawa, PL, Poland</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:06+00:00</t>
+          <t>2026-03-05T16:12:16+00:00</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>0053205219692W</t>
+          <t>0053204590575W</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -10468,7 +10480,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>0053214519488W</t>
+          <t>0053205141234W</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10488,7 +10500,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>6001661533</t>
+          <t>6001658455</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -10500,22 +10512,22 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-05T13:31:26+01:00</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Warszawa, PL, Poland</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T13:16:11+00:00</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>0053214519488W</t>
+          <t>0053205141234W</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -10527,7 +10539,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>0053208312146W</t>
+          <t>0053205297037W</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10547,7 +10559,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>6001659474</t>
+          <t>6001658511</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -10559,7 +10571,7 @@
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10574,7 +10586,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>0053208312146W</t>
+          <t>0053205297037W</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -10586,7 +10598,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>0053213367045W</t>
+          <t>0053205219500W</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10606,7 +10618,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>6001658654</t>
+          <t>6001658500</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -10628,12 +10640,12 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:06+00:00</t>
+          <t>2026-03-05T04:12:07+00:00</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>0053213367045W</t>
+          <t>0053205219500W</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -10645,7 +10657,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>0053205047180W</t>
+          <t>0053207782018W</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10665,7 +10677,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>6001658446</t>
+          <t>6001659335</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -10677,7 +10689,7 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10687,12 +10699,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:06+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>0053205047180W</t>
+          <t>0053207782018W</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -10704,7 +10716,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>0053214132038W</t>
+          <t>0053211187532W</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10724,7 +10736,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>6001660394</t>
+          <t>6001659845</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -10736,22 +10748,22 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-02T18:00:15+01:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Warszawa, PL, Poland</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>0053214132038W</t>
+          <t>0053211187532W</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -10763,7 +10775,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>0053213935294W</t>
+          <t>0053210819530W</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10783,7 +10795,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>6001660299</t>
+          <t>6001659808</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -10795,7 +10807,7 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-03-05T07:49:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10805,12 +10817,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-03-05T07:12:12+00:00</t>
+          <t>2026-03-05T04:12:03+00:00</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>0053213935294W</t>
+          <t>0053210819530W</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -10822,7 +10834,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>0053214518024W</t>
+          <t>0053208782934W</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10842,7 +10854,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>6001661513</t>
+          <t>6001659624</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -10869,7 +10881,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>0053214518024W</t>
+          <t>0053208782934W</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -10881,7 +10893,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>0053214518101W</t>
+          <t>0053205219692W</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10901,7 +10913,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>6001661513</t>
+          <t>6001658500</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -10923,12 +10935,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:06+00:00</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>0053214518101W</t>
+          <t>0053205219692W</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -10999,7 +11011,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>0053205297037W</t>
+          <t>0053208312146W</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11019,7 +11031,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>6001658511</t>
+          <t>6001659474</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -11031,7 +11043,7 @@
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11046,7 +11058,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>0053205297037W</t>
+          <t>0053208312146W</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -11058,7 +11070,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>0053219084596W</t>
+          <t>0053214518101W</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11078,7 +11090,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>6001666305</t>
+          <t>6001661513</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -11090,7 +11102,7 @@
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11100,12 +11112,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>0053219084596W</t>
+          <t>0053214518101W</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -11117,7 +11129,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>0053238476676W</t>
+          <t>0053205219805W</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11137,7 +11149,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>6001671219</t>
+          <t>6001658500</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -11149,7 +11161,7 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-03-05T07:49:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11159,12 +11171,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-03-05T07:12:10+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>0053238476676W</t>
+          <t>0053205219805W</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -11176,7 +11188,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>0053221762690W</t>
+          <t>0053214518024W</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11196,7 +11208,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>6001666846</t>
+          <t>6001661513</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -11223,7 +11235,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>0053221762690W</t>
+          <t>0053214518024W</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -11235,7 +11247,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>0053240904518W</t>
+          <t>0053230441607W</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11255,7 +11267,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>6001671456</t>
+          <t>6001669298</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -11267,22 +11279,22 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-03-05T07:49:00+01:00</t>
+          <t>2026-03-04T16:10:52+01:00</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Koszalin, PL, Poland</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-03-05T07:12:09+00:00</t>
+          <t>2026-03-05T08:12:10+00:00</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>0053240904518W</t>
+          <t>0053230441607W</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -11353,7 +11365,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>0053238476568W</t>
+          <t>0053238476676W</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11395,12 +11407,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-03-05T07:12:09+00:00</t>
+          <t>2026-03-05T07:12:10+00:00</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>0053238476568W</t>
+          <t>0053238476676W</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -11412,7 +11424,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>0053223722251W</t>
+          <t>0053222441738W</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11432,7 +11444,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>6001667008</t>
+          <t>6001666941</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -11444,7 +11456,7 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-03-05T07:49:00+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11454,12 +11466,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-03-05T07:12:09+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>0053223722251W</t>
+          <t>0053222441738W</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -11471,7 +11483,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>0053216210414W</t>
+          <t>0053221762690W</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11491,7 +11503,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>6001665568</t>
+          <t>6001666846</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -11503,7 +11515,7 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11513,12 +11525,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>0053216210414W</t>
+          <t>0053221762690W</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -11530,7 +11542,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>0053240904467W</t>
+          <t>0053221762715W</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11550,7 +11562,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>6001671456</t>
+          <t>6001666846</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -11562,7 +11574,7 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-03-05T07:49:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11572,12 +11584,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-03-05T07:12:20+00:00</t>
+          <t>2026-03-05T04:12:03+00:00</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>0053240904467W</t>
+          <t>0053221762715W</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -11589,7 +11601,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>0053216668225W</t>
+          <t>0053230342542W</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11609,7 +11621,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>6001665735</t>
+          <t>6001669155</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -11621,7 +11633,7 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11631,12 +11643,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:03+00:00</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>0053216668225W</t>
+          <t>0053230342542W</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -11648,7 +11660,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>0053221701954W</t>
+          <t>0053238476568W</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11668,7 +11680,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>6001666791</t>
+          <t>6001671219</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -11680,7 +11692,7 @@
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11690,12 +11702,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T07:12:09+00:00</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>0053221701954W</t>
+          <t>0053238476568W</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -11707,7 +11719,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>0053222441738W</t>
+          <t>0053230330362W</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11727,7 +11739,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>6001666941</t>
+          <t>6001668645</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -11739,22 +11751,22 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T17:24:38+01:00</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Opole, PL, Poland</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:04+00:00</t>
+          <t>2026-03-05T04:12:03+00:00</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>0053222441738W</t>
+          <t>0053230330362W</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -11766,7 +11778,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>0053216195581W</t>
+          <t>0053219084765W</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11786,7 +11798,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>6001665485</t>
+          <t>6001666305</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -11798,22 +11810,22 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-03-04T15:38:38+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Zerniki, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-03-05T08:12:14+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>0053216195581W</t>
+          <t>0053219084765W</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -11825,7 +11837,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>0053228792542W</t>
+          <t>0053223722251W</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11845,7 +11857,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>6001667794</t>
+          <t>6001667008</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -11867,12 +11879,12 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026-03-05T07:12:12+00:00</t>
+          <t>2026-03-05T07:12:09+00:00</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>0053228792542W</t>
+          <t>0053223722251W</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -11884,7 +11896,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>0053230327541W</t>
+          <t>0053228792542W</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11904,7 +11916,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>6001668512</t>
+          <t>6001667794</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -11926,12 +11938,12 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026-03-05T07:12:10+00:00</t>
+          <t>2026-03-05T07:12:12+00:00</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>0053230327541W</t>
+          <t>0053228792542W</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -11943,7 +11955,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>0053221762715W</t>
+          <t>0053219084616W</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11963,7 +11975,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>6001666846</t>
+          <t>6001666305</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -11975,7 +11987,7 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-03-03T08:49:00+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11985,12 +11997,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:03+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>0053221762715W</t>
+          <t>0053219084616W</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -12002,7 +12014,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>0053219084765W</t>
+          <t>0053216668225W</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12022,7 +12034,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>6001666305</t>
+          <t>6001665735</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -12034,7 +12046,7 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-03T08:49:00+01:00</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12049,7 +12061,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>0053219084765W</t>
+          <t>0053216668225W</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -12061,7 +12073,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>0053219084473W</t>
+          <t>0053216210414W</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12081,7 +12093,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>6001666305</t>
+          <t>6001665568</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -12103,12 +12115,12 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:03+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>0053219084473W</t>
+          <t>0053216210414W</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -12120,7 +12132,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>0053230330362W</t>
+          <t>0053230327541W</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12140,7 +12152,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>6001668645</t>
+          <t>6001668512</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -12152,22 +12164,22 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-03-03T17:24:38+01:00</t>
+          <t>2026-03-05T07:49:00+01:00</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Opole, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:03+00:00</t>
+          <t>2026-03-05T07:12:10+00:00</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>0053230330362W</t>
+          <t>0053230327541W</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -12179,7 +12191,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>0053230441607W</t>
+          <t>0053218957754W</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12199,7 +12211,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>6001669298</t>
+          <t>6001666267</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -12211,22 +12223,22 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-03-04T16:10:52+01:00</t>
+          <t>2026-03-05T14:37:17+01:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Koszalin, PL, Poland</t>
+          <t>Krakow, PL, Poland</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-03-05T08:12:10+00:00</t>
+          <t>2026-03-05T16:16:26+00:00</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>0053230441607W</t>
+          <t>0053218957754W</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -12238,7 +12250,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>0053230342542W</t>
+          <t>0053216195581W</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12258,7 +12270,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>6001669155</t>
+          <t>6001665485</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -12270,22 +12282,22 @@
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-03-04T09:05:00+01:00</t>
+          <t>2026-03-04T15:38:38+01:00</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>ROSANOW, PL, Poland</t>
+          <t>Zerniki, PL, Poland</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:03+00:00</t>
+          <t>2026-03-05T08:12:14+00:00</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>0053230342542W</t>
+          <t>0053216195581W</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -12297,7 +12309,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>0053219084616W</t>
+          <t>0053219084473W</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12339,12 +12351,12 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-03-05T04:12:05+00:00</t>
+          <t>2026-03-05T04:12:03+00:00</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>0053219084616W</t>
+          <t>0053219084473W</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -12356,7 +12368,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>0053218957754W</t>
+          <t>0053219084596W</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12376,7 +12388,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>6001666267</t>
+          <t>6001666305</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -12388,22 +12400,22 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-03-05T14:37:17+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Krakow, PL, Poland</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-03-05T16:16:26+00:00</t>
+          <t>2026-03-05T04:12:04+00:00</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>0053218957754W</t>
+          <t>0053219084596W</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -12415,7 +12427,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>05222006538611</t>
+          <t>0053221701954W</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12435,7 +12447,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>6001667923</t>
+          <t>6001666791</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -12447,22 +12459,22 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-03-04T12:19:40+01:00</t>
+          <t>2026-03-04T09:05:00+01:00</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Maastricht, NL, Netherlands</t>
+          <t>ROSANOW, PL, Poland</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-03-05T16:12:21+00:00</t>
+          <t>2026-03-05T04:12:05+00:00</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>05222006538611</t>
+          <t>0053221701954W</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -801,17 +801,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01475240801708</t>
+          <t>UTV366918661</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0049010272928</t>
+          <t>0031009994397</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -837,44 +837,44 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-06T10:47:25+01:00</t>
+          <t>2026-03-06T17:28:23+01:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-06T15:41:27+00:00</t>
+          <t>2026-03-06T18:42:45+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01475240801708</t>
+          <t>UTV366918661</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272928", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009994397", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05228742861288</t>
+          <t>UTV310660604</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0032005573112</t>
+          <t>0031009994397</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -900,44 +900,44 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-06T12:33:25+01:00</t>
+          <t>2026-03-06T17:28:36+01:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Aalter, BE, Belgium</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-06T15:41:08+00:00</t>
+          <t>2026-03-06T18:42:45+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>05228742861288</t>
+          <t>UTV310660604</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005573112", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009994397", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05228742861453</t>
+          <t>01475240801708</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0032005573112</t>
+          <t>0049010272928</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -963,34 +963,34 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-03-06T12:33:25+01:00</t>
+          <t>2026-03-06T10:47:25+01:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Aalter, BE, Belgium</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-06T15:41:09+00:00</t>
+          <t>2026-03-06T15:41:27+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>05228742861453</t>
+          <t>01475240801708</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005573112", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010272928", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05228742858322</t>
+          <t>05228742861288</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0031009985268</t>
+          <t>0032005573112</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1026,34 +1026,34 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-06T14:38:35+01:00</t>
+          <t>2026-03-06T12:33:25+01:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Berkel en Rodenrijs, NL, Netherlands</t>
+          <t>Aalter, BE, Belgium</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-06T15:19:20+00:00</t>
+          <t>2026-03-06T15:41:08+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>05228742858322</t>
+          <t>05228742861288</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985268", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005573112", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05228742857013</t>
+          <t>05228742861453</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0031009985268</t>
+          <t>0032005573112</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1089,44 +1089,44 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-06T11:35:00+01:00</t>
+          <t>2026-03-06T12:33:25+01:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Aalter, BE, Belgium</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-06T15:19:17+00:00</t>
+          <t>2026-03-06T15:41:09+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05228742857013</t>
+          <t>05228742861453</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985268", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0032005573112", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01475240796877</t>
+          <t>05228742858322</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B2BDS11383175</t>
+          <t>0031009985268</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1152,44 +1152,44 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-06T09:56:10+01:00</t>
+          <t>2026-03-06T14:38:35+01:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Föhren (DE), Germany</t>
+          <t>Berkel en Rodenrijs, NL, Netherlands</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-06T15:19:01+00:00</t>
+          <t>2026-03-06T15:19:20+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>01475240796877</t>
+          <t>05228742858322</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11383175", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009985268", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01475240795750</t>
+          <t>05228742857013</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B2BDS11383175</t>
+          <t>0031009985268</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1215,44 +1215,44 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-06T09:56:10+01:00</t>
+          <t>2026-03-06T11:35:00+01:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Föhren (DE), Germany</t>
+          <t>Oirschot, NL, Netherlands</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-06T15:19:00+00:00</t>
+          <t>2026-03-06T15:19:17+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>01475240795750</t>
+          <t>05228742857013</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11383175", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009985268", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>889065726850</t>
+          <t>01475240796877</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>200014315503148</t>
+          <t>B2BDS11383175</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1278,44 +1278,44 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-02-27T17:55:47-06:00</t>
+          <t>2026-03-06T09:56:10+01:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Blakely, GA, 39823, US, United States</t>
+          <t>Föhren (DE), Germany</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-06T14:40:55+00:00</t>
+          <t>2026-03-06T15:19:01+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>889065726850</t>
+          <t>01475240796877</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>{"external_order_id": "200014315503148", "sales_office_id": "4260"}</t>
+          <t>{"external_order_id": "B2BDS11383175", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>889064338000</t>
+          <t>01475240795750</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>200014315503148</t>
+          <t>B2BDS11383175</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1341,44 +1341,44 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-02-28T13:48:35-06:00</t>
+          <t>2026-03-06T09:56:10+01:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Blakely, GA, 39823, US, United States</t>
+          <t>Föhren (DE), Germany</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-03-06T14:40:56+00:00</t>
+          <t>2026-03-06T15:19:00+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>889064338000</t>
+          <t>01475240795750</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>{"external_order_id": "200014315503148", "sales_office_id": "4260"}</t>
+          <t>{"external_order_id": "B2BDS11383175", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05228742857143</t>
+          <t>889065726850</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B2BDS11466676</t>
+          <t>200014315503148</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1404,44 +1404,44 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-03-06T12:43:14+01:00</t>
+          <t>2026-02-27T17:55:47-06:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Montevrain, FR, France</t>
+          <t>Blakely, GA, 39823, US, United States</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-03-06T13:40:27+00:00</t>
+          <t>2026-03-06T14:40:55+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>05228742857143</t>
+          <t>889065726850</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11466676", "sales_office_id": "4452"}</t>
+          <t>{"external_order_id": "200014315503148", "sales_office_id": "4260"}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05228742857200</t>
+          <t>889064338000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B2BDS11466676</t>
+          <t>200014315503148</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1467,44 +1467,44 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-06T12:41:39+01:00</t>
+          <t>2026-02-28T13:48:35-06:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Montevrain, FR, France</t>
+          <t>Blakely, GA, 39823, US, United States</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-03-06T13:40:39+00:00</t>
+          <t>2026-03-06T14:40:56+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>05228742857200</t>
+          <t>889064338000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11466676", "sales_office_id": "4452"}</t>
+          <t>{"external_order_id": "200014315503148", "sales_office_id": "4260"}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01475240802573</t>
+          <t>05228742857143</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0049010276509</t>
+          <t>B2BDS11466676</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1530,44 +1530,44 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-06T09:37:45+01:00</t>
+          <t>2026-03-06T12:43:14+01:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Montevrain, FR, France</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-03-06T14:09:12+00:00</t>
+          <t>2026-03-06T13:40:27+00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>01475240802573</t>
+          <t>05228742857143</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276509", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11466676", "sales_office_id": "4452"}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01475240802838</t>
+          <t>05228742857200</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0049010276509</t>
+          <t>B2BDS11466676</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1593,34 +1593,34 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-06T09:37:45+01:00</t>
+          <t>2026-03-06T12:41:39+01:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Montevrain, FR, France</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-06T13:39:09+00:00</t>
+          <t>2026-03-06T13:40:39+00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>01475240802838</t>
+          <t>05228742857200</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276509", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11466676", "sales_office_id": "4452"}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01475240802746</t>
+          <t>01475240802573</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0049010275899</t>
+          <t>0049010276509</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1656,7 +1656,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-03-06T13:47:08+01:00</t>
+          <t>2026-03-06T09:37:45+01:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1666,24 +1666,24 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:49+00:00</t>
+          <t>2026-03-06T14:09:12+00:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>01475240802746</t>
+          <t>01475240802573</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275899", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010276509", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01475240801614</t>
+          <t>01475240802838</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>302-3422488-6889965</t>
+          <t>0049010276509</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1719,34 +1719,34 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-03-06T13:22:38+01:00</t>
+          <t>2026-03-06T09:37:45+01:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Mannheim (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:48+00:00</t>
+          <t>2026-03-06T13:39:09+00:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>01475240801614</t>
+          <t>01475240802838</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>{"external_order_id": "302-3422488-6889965", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "0049010276509", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01475240802747</t>
+          <t>01475240802746</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:47+00:00</t>
+          <t>2026-03-06T13:38:49+00:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>01475240802747</t>
+          <t>01475240802746</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01475240803436</t>
+          <t>01475240802747</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:48+00:00</t>
+          <t>2026-03-06T13:38:47+00:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>01475240803436</t>
+          <t>01475240802747</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1872,7 +1872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01475240803441</t>
+          <t>01475240801614</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>B2BDS11585635</t>
+          <t>302-3422488-6889965</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1908,34 +1908,34 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-03-06T09:26:06+01:00</t>
+          <t>2026-03-06T13:22:38+01:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>Mannheim (DE), Germany</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:38+00:00</t>
+          <t>2026-03-06T13:38:48+00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>01475240803441</t>
+          <t>01475240801614</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11585635", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "302-3422488-6889965", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01475240800296</t>
+          <t>01475240803436</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0049010270947</t>
+          <t>0049010275899</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1971,34 +1971,34 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-06T08:07:34+01:00</t>
+          <t>2026-03-06T13:47:08+01:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Melle (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-06T14:38:40+00:00</t>
+          <t>2026-03-06T13:38:48+00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>01475240800296</t>
+          <t>01475240803436</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010270947", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010275899", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>01475240800294</t>
+          <t>01475240803441</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0049010270947</t>
+          <t>B2BDS11585635</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2034,34 +2034,34 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-03-06T08:07:34+01:00</t>
+          <t>2026-03-06T09:26:06+01:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Melle (DE), Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:37+00:00</t>
+          <t>2026-03-06T13:38:38+00:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>01475240800294</t>
+          <t>01475240803441</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010270947", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11585635", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>01475240800295</t>
+          <t>01475240800294</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:36+00:00</t>
+          <t>2026-03-06T13:38:37+00:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>01475240800295</t>
+          <t>01475240800294</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>01475240800293</t>
+          <t>01475240800295</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>01475240800293</t>
+          <t>01475240800295</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>01475240801747</t>
+          <t>01475240800296</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0049010274508</t>
+          <t>0049010270947</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2223,34 +2223,34 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-03-06T11:09:58+01:00</t>
+          <t>2026-03-06T08:07:34+01:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Melle (DE), Germany</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-03-06T12:04:31+00:00</t>
+          <t>2026-03-06T14:38:40+00:00</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>01475240801747</t>
+          <t>01475240800296</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274508", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010270947", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>01475240801460</t>
+          <t>01475240800293</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0049010274508</t>
+          <t>0049010270947</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2286,34 +2286,34 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-06T11:09:58+01:00</t>
+          <t>2026-03-06T08:07:34+01:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Melle (DE), Germany</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-03-06T13:04:33+00:00</t>
+          <t>2026-03-06T13:38:36+00:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>01475240801460</t>
+          <t>01475240800293</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274508", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010270947", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>01475240801838</t>
+          <t>01475240801460</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B2BDS11577763</t>
+          <t>0049010274508</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2349,34 +2349,34 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-03-06T10:51:33+01:00</t>
+          <t>2026-03-06T11:09:58+01:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-03-06T12:04:20+00:00</t>
+          <t>2026-03-06T13:04:33+00:00</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>01475240801838</t>
+          <t>01475240801460</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11577763", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010274508", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>01475240802662</t>
+          <t>01475240801747</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0049010275691</t>
+          <t>0049010274508</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2412,34 +2412,34 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-03-06T10:17:07+01:00</t>
+          <t>2026-03-06T11:09:58+01:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Aichach (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-03-06T12:04:18+00:00</t>
+          <t>2026-03-06T12:04:31+00:00</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>01475240802662</t>
+          <t>01475240801747</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275691", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010274508", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>01475240801568</t>
+          <t>01475240801838</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0049010274731</t>
+          <t>B2BDS11577763</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2475,34 +2475,34 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-03-06T09:54:28+01:00</t>
+          <t>2026-03-06T10:51:33+01:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Staufenberg-Mainzlar (DE), Germany</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-03-06T12:04:12+00:00</t>
+          <t>2026-03-06T12:04:20+00:00</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>01475240801568</t>
+          <t>01475240801838</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274731", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11577763", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>01475240802518</t>
+          <t>01475240802662</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B2BDS11267109</t>
+          <t>0049010275691</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2538,34 +2538,34 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-03-06T10:58:19+01:00</t>
+          <t>2026-03-06T10:17:07+01:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>St. Ingbert (DE), Germany</t>
+          <t>Aichach (DE), Germany</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-06T12:04:05+00:00</t>
+          <t>2026-03-06T12:04:18+00:00</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>01475240802518</t>
+          <t>01475240802662</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11267109", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010275691", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>01475240802517</t>
+          <t>01475240801568</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B2BDS11260336</t>
+          <t>0049010274731</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,44 +2601,44 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-06T10:43:24+01:00</t>
+          <t>2026-03-06T09:54:28+01:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Staufenberg-Mainzlar (DE), Germany</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-03-06T12:04:02+00:00</t>
+          <t>2026-03-06T12:04:12+00:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>01475240802517</t>
+          <t>01475240801568</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11260336", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010274731", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06086432957836</t>
+          <t>01475240802518</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dpd-ch-sftp</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DPD Switzerland</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0041006369361</t>
+          <t>B2BDS11267109</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0323</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2664,44 +2664,44 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-06T14:47:42+01:00</t>
+          <t>2026-03-06T10:58:19+01:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>,Switzerland</t>
+          <t>St. Ingbert (DE), Germany</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-06T15:31:00+00:00</t>
+          <t>2026-03-06T12:04:05+00:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>06086432957836</t>
+          <t>01475240802518</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0041006369361", "sales_office_id": "0323"}</t>
+          <t>{"external_order_id": "B2BDS11267109", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06086432957837</t>
+          <t>01475240802517</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dpd-ch-sftp</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DPD Switzerland</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0041006369361</t>
+          <t>B2BDS11260336</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0323</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2727,34 +2727,34 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-06T14:47:17+01:00</t>
+          <t>2026-03-06T10:43:24+01:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>,Switzerland</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-03-06T15:31:00+00:00</t>
+          <t>2026-03-06T12:04:02+00:00</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>06086432957837</t>
+          <t>01475240802517</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0041006369361", "sales_office_id": "0323"}</t>
+          <t>{"external_order_id": "B2BDS11260336", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06086432956695</t>
+          <t>06086432957836</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2790,7 +2790,7 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-06T14:47:37+01:00</t>
+          <t>2026-03-06T14:47:42+01:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>06086432956695</t>
+          <t>06086432957836</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2817,7 +2817,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06086432956696</t>
+          <t>06086432957837</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2853,7 +2853,7 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-06T14:47:29+01:00</t>
+          <t>2026-03-06T14:47:17+01:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>06086432956696</t>
+          <t>06086432957837</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2880,17 +2880,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05228742858098</t>
+          <t>06086432956695</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-ch-sftp</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Switzerland</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0031009977881</t>
+          <t>0041006369361</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0323</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2916,44 +2916,44 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-05T15:08:18+01:00</t>
+          <t>2026-03-06T14:47:37+01:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Berkel en Rodenrijs, NL, Netherlands</t>
+          <t>,Switzerland</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-03-06T11:54:08+00:00</t>
+          <t>2026-03-06T15:31:00+00:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>05228742858098</t>
+          <t>06086432956695</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009977881", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0041006369361", "sales_office_id": "0323"}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ZB8WTKFX</t>
+          <t>06086432956696</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>dpd-ch-sftp</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DPD Switzerland</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0049010268367</t>
+          <t>0041006369361</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0323</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2979,44 +2979,44 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-06T13:20:04+01:00</t>
+          <t>2026-03-06T14:47:29+01:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>,Switzerland</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-03-06T12:25:15+00:00</t>
+          <t>2026-03-06T15:31:00+00:00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ZB8WTKFX</t>
+          <t>06086432956696</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010268367", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0041006369361", "sales_office_id": "0323"}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>UTV493491865</t>
+          <t>05228742858098</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0031009990872</t>
+          <t>0031009977881</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3042,44 +3042,44 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-06T14:06:57+01:00</t>
+          <t>2026-03-05T15:08:18+01:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Berkel en Rodenrijs, NL, Netherlands</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-03-06T15:07:16+00:00</t>
+          <t>2026-03-06T11:54:08+00:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>UTV493491865</t>
+          <t>05228742858098</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009990872", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009977881", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UTV853352890</t>
+          <t>ZB8WTKFX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0031009993546</t>
+          <t>0049010268367</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3105,34 +3105,34 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-06T14:55:07+01:00</t>
+          <t>2026-03-06T13:20:04+01:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-06T14:37:03+00:00</t>
+          <t>2026-03-06T12:25:15+00:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>UTV853352890</t>
+          <t>ZB8WTKFX</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009993546", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010268367", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>UTV652701119</t>
+          <t>UTV493491865</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0031009992963</t>
+          <t>0031009990872</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3168,7 +3168,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-06T09:08:50+01:00</t>
+          <t>2026-03-06T14:06:57+01:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3178,24 +3178,24 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-06T11:37:01+00:00</t>
+          <t>2026-03-06T15:07:16+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>UTV652701119</t>
+          <t>UTV493491865</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009992963", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009990872", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>UTV728589289</t>
+          <t>UTV853352890</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0031009987981</t>
+          <t>0031009993546</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3231,7 +3231,7 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-06T14:35:08+01:00</t>
+          <t>2026-03-06T14:55:07+01:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-03-06T14:36:59+00:00</t>
+          <t>2026-03-06T14:37:03+00:00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>UTV728589289</t>
+          <t>UTV853352890</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009987981", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009993546", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UTV442010395</t>
+          <t>UTV652701119</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0031009987981</t>
+          <t>0031009992963</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-06T14:35:34+01:00</t>
+          <t>2026-03-06T09:08:50+01:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3304,24 +3304,24 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-03-06T14:37:00+00:00</t>
+          <t>2026-03-06T11:37:01+00:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>UTV442010395</t>
+          <t>UTV652701119</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009987981", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009992963", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UTV449135726</t>
+          <t>UTV728589289</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0031009975922</t>
+          <t>0031009987981</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3357,7 +3357,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-05T12:48:31+01:00</t>
+          <t>2026-03-06T14:35:08+01:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3367,34 +3367,34 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-06T11:01:02+00:00</t>
+          <t>2026-03-06T14:36:59+00:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>UTV449135726</t>
+          <t>UTV728589289</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009975922", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009987981", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>01475240802888</t>
+          <t>UTV442010395</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>B2BDS11558406</t>
+          <t>0031009987981</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3420,44 +3420,44 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-06T09:31:54+01:00</t>
+          <t>2026-03-06T14:35:34+01:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Wuppertal (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-03-06T09:00:54+00:00</t>
+          <t>2026-03-06T14:37:00+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>01475240802888</t>
+          <t>UTV442010395</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11558406", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009987981", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>01475240802380</t>
+          <t>UTV449135726</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>B2BDS11558406</t>
+          <t>0031009975922</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3483,34 +3483,34 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-06T09:31:54+01:00</t>
+          <t>2026-03-05T12:48:31+01:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Wuppertal (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-03-06T09:00:49+00:00</t>
+          <t>2026-03-06T11:01:02+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>01475240802380</t>
+          <t>UTV449135726</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11558406", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009975922", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>01475240801922</t>
+          <t>01475240802888</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-03-06T09:00:49+00:00</t>
+          <t>2026-03-06T09:00:54+00:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>01475240801922</t>
+          <t>01475240802888</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>01475240801282</t>
+          <t>01475240802380</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0049010269409</t>
+          <t>B2BDS11558406</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3609,34 +3609,34 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-03-06T11:46:00+01:00</t>
+          <t>2026-03-06T09:31:54+01:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>Wuppertal (DE), Germany</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-03-06T11:00:49+00:00</t>
+          <t>2026-03-06T09:00:49+00:00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>01475240801282</t>
+          <t>01475240802380</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010269409", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11558406", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>01475240803152</t>
+          <t>01475240801282</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1024941722-A</t>
+          <t>0049010269409</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3672,34 +3672,34 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-06T13:19:04+01:00</t>
+          <t>2026-03-06T11:46:00+01:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Essen (DE), Germany</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-03-06T13:00:50+00:00</t>
+          <t>2026-03-06T11:00:49+00:00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>01475240803152</t>
+          <t>01475240801282</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024941722-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0049010269409", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01475240801743</t>
+          <t>01475240801922</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0049010273679</t>
+          <t>B2BDS11558406</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3735,34 +3735,34 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-06T13:52:42+01:00</t>
+          <t>2026-03-06T09:31:54+01:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Malsch (DE), Germany</t>
+          <t>Wuppertal (DE), Germany</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-06T13:00:50+00:00</t>
+          <t>2026-03-06T09:00:49+00:00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>01475240801743</t>
+          <t>01475240801922</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010273679", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11558406", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01475240801418</t>
+          <t>01475240801743</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>B2BDS11558406</t>
+          <t>0049010273679</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3798,27 +3798,27 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-06T09:31:54+01:00</t>
+          <t>2026-03-06T13:52:42+01:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Wuppertal (DE), Germany</t>
+          <t>Malsch (DE), Germany</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-06T09:00:47+00:00</t>
+          <t>2026-03-06T13:00:50+00:00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>01475240801418</t>
+          <t>01475240801743</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11558406", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010273679", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>01475240803414</t>
+          <t>01475240803152</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1024948927-A</t>
+          <t>1024941722-A</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3924,34 +3924,34 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-06T09:58:58+01:00</t>
+          <t>2026-03-06T13:19:04+01:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Duisburg (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-03-06T10:00:47+00:00</t>
+          <t>2026-03-06T13:00:50+00:00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>01475240803414</t>
+          <t>01475240803152</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024948927-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "1024941722-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01475240802618</t>
+          <t>01475240801418</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0049010276102</t>
+          <t>B2BDS11558406</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3987,34 +3987,34 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-03-06T11:41:28+01:00</t>
+          <t>2026-03-06T09:31:54+01:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Obing (DE), Germany</t>
+          <t>Wuppertal (DE), Germany</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-03-06T11:00:47+00:00</t>
+          <t>2026-03-06T09:00:47+00:00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>01475240802618</t>
+          <t>01475240801418</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276102", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11558406", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>01475240801471</t>
+          <t>01475240803414</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MPSEGD5</t>
+          <t>1024948927-A</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4050,34 +4050,34 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-03-06T12:41:00+01:00</t>
+          <t>2026-03-06T09:58:58+01:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Aschaffenburg (DE), Germany</t>
+          <t>Duisburg (DE), Germany</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-06T12:00:47+00:00</t>
+          <t>2026-03-06T10:00:47+00:00</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>01475240801471</t>
+          <t>01475240803414</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>{"external_order_id": "MPSEGD5", "sales_office_id": "4286"}</t>
+          <t>{"external_order_id": "1024948927-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>01475240801533</t>
+          <t>01475240801471</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0049010276139</t>
+          <t>MPSEGD5</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4113,34 +4113,34 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-03-06T13:16:36+01:00</t>
+          <t>2026-03-06T12:41:00+01:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Hamm (DE), Germany</t>
+          <t>Aschaffenburg (DE), Germany</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-03-06T13:00:50+00:00</t>
+          <t>2026-03-06T12:00:47+00:00</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>01475240801533</t>
+          <t>01475240801471</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276139", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "MPSEGD5", "sales_office_id": "4286"}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>01475240802595</t>
+          <t>01475240802618</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B2BDS11562072</t>
+          <t>0049010276102</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4176,27 +4176,27 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-03-06T10:52:41+01:00</t>
+          <t>2026-03-06T11:41:28+01:00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Uplengen-Jübberde (DE), Germany</t>
+          <t>Obing (DE), Germany</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-03-06T10:00:46+00:00</t>
+          <t>2026-03-06T11:00:47+00:00</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>01475240802595</t>
+          <t>01475240802618</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11562072", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010276102", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>01475240802596</t>
+          <t>01475240802595</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4312,12 +4312,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-06T10:00:48+00:00</t>
+          <t>2026-03-06T10:00:46+00:00</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>01475240802596</t>
+          <t>01475240802595</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>01475240801497</t>
+          <t>01475240801533</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-06T13:00:46+00:00</t>
+          <t>2026-03-06T13:00:50+00:00</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>01475240801497</t>
+          <t>01475240801533</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4392,7 +4392,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>01475240803010</t>
+          <t>01475240802596</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0049010276463</t>
+          <t>B2BDS11562072</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4428,34 +4428,34 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-06T10:07:49+01:00</t>
+          <t>2026-03-06T10:52:41+01:00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Hamm (DE), Germany</t>
+          <t>Uplengen-Jübberde (DE), Germany</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-03-06T10:00:42+00:00</t>
+          <t>2026-03-06T10:00:48+00:00</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>01475240803010</t>
+          <t>01475240802596</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276463", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11562072", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>01475240802287</t>
+          <t>01475240801497</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0049010274099</t>
+          <t>0049010276139</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4491,34 +4491,34 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-06T11:42:50+01:00</t>
+          <t>2026-03-06T13:16:36+01:00</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Duisburg (DE), Germany</t>
+          <t>Hamm (DE), Germany</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-03-06T11:15:00+00:00</t>
+          <t>2026-03-06T13:00:46+00:00</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>01475240802287</t>
+          <t>01475240801497</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274099", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010276139", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>01475240798966</t>
+          <t>01475240803010</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FR7ATKC</t>
+          <t>0049010276463</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4554,34 +4554,34 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-03-06T10:12:01+01:00</t>
+          <t>2026-03-06T10:07:49+01:00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Lübbenau/Spreewald (DE), Germany</t>
+          <t>Hamm (DE), Germany</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:58+00:00</t>
+          <t>2026-03-06T10:00:42+00:00</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>01475240798966</t>
+          <t>01475240803010</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>{"external_order_id": "FR7ATKC", "sales_office_id": "4326"}</t>
+          <t>{"external_order_id": "0049010276463", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>01475240803100</t>
+          <t>01475240802287</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>B2BDS11565258</t>
+          <t>0049010274099</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4617,34 +4617,34 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-03-06T10:28:43+01:00</t>
+          <t>2026-03-06T11:42:50+01:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Gudensberg (DE), Germany</t>
+          <t>Duisburg (DE), Germany</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:56+00:00</t>
+          <t>2026-03-06T11:15:00+00:00</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>01475240803100</t>
+          <t>01475240802287</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11565258", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010274099", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>01475240802651</t>
+          <t>01475240798966</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0049010269157</t>
+          <t>FR7ATKC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4680,34 +4680,34 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-06T11:53:26+01:00</t>
+          <t>2026-03-06T10:12:01+01:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Lübbenau/Spreewald (DE), Germany</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:54+00:00</t>
+          <t>2026-03-06T10:14:58+00:00</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>01475240802651</t>
+          <t>01475240798966</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010269157", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "FR7ATKC", "sales_office_id": "4326"}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>01475240802955</t>
+          <t>01475240803100</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>B2BDS11571886</t>
+          <t>B2BDS11565258</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4743,34 +4743,34 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-06T11:00:06+01:00</t>
+          <t>2026-03-06T10:28:43+01:00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>Gudensberg (DE), Germany</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:54+00:00</t>
+          <t>2026-03-06T10:14:56+00:00</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>01475240802955</t>
+          <t>01475240803100</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11571886", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11565258", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>01475240802321</t>
+          <t>01475240802651</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>B2BDS11237904</t>
+          <t>0049010269157</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4806,34 +4806,34 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-03-06T10:47:46+01:00</t>
+          <t>2026-03-06T11:53:26+01:00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Hagen (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:48+00:00</t>
+          <t>2026-03-06T11:14:54+00:00</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>01475240802321</t>
+          <t>01475240802651</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11237904", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010269157", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>01475240801414</t>
+          <t>01475240802955</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0049010269157</t>
+          <t>B2BDS11571886</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4869,34 +4869,34 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-06T11:53:26+01:00</t>
+          <t>2026-03-06T11:00:06+01:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Walsrode (DE), Germany</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:52+00:00</t>
+          <t>2026-03-06T10:44:54+00:00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>01475240801414</t>
+          <t>01475240802955</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010269157", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11571886", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>01475240800108</t>
+          <t>01475240802321</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>B2BDS11309075</t>
+          <t>B2BDS11237904</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4932,34 +4932,34 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-06T11:06:05+01:00</t>
+          <t>2026-03-06T10:47:46+01:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Föhren (DE), Germany</t>
+          <t>Hagen (DE), Germany</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:46+00:00</t>
+          <t>2026-03-06T10:14:48+00:00</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>01475240800108</t>
+          <t>01475240802321</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11309075", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11237904", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>01475240800562</t>
+          <t>01475240801414</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:47+00:00</t>
+          <t>2026-03-06T11:14:52+00:00</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>01475240800562</t>
+          <t>01475240801414</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5022,7 +5022,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>01475240801173</t>
+          <t>01475240800108</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>B2BDS11328625</t>
+          <t>B2BDS11309075</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5058,34 +5058,34 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:26+01:00</t>
+          <t>2026-03-06T11:06:05+01:00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Föhren (DE), Germany</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:41+00:00</t>
+          <t>2026-03-06T10:14:46+00:00</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>01475240801173</t>
+          <t>01475240800108</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11328625", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11309075", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>01475240802019</t>
+          <t>01475240800562</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0049010274353</t>
+          <t>0049010269157</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5121,34 +5121,34 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-06T11:08:56+01:00</t>
+          <t>2026-03-06T11:53:26+01:00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Malsch (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-03-06T11:44:43+00:00</t>
+          <t>2026-03-06T11:14:47+00:00</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>01475240802019</t>
+          <t>01475240800562</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274353", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010269157", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>01475240802496</t>
+          <t>01475240801173</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0049010272893</t>
+          <t>B2BDS11328625</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5184,34 +5184,34 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-03-06T11:17:39+01:00</t>
+          <t>2026-03-06T10:44:26+01:00</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Mannheim (DE), Germany</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:41+00:00</t>
+          <t>2026-03-06T10:14:41+00:00</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>01475240802496</t>
+          <t>01475240801173</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272893", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11328625", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>01475240801937</t>
+          <t>01475240802019</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>B2BDS11550515</t>
+          <t>0049010274353</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5247,34 +5247,34 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-03-06T11:53:09+01:00</t>
+          <t>2026-03-06T11:08:56+01:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Holzgünz (DE), Germany</t>
+          <t>Malsch (DE), Germany</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:39+00:00</t>
+          <t>2026-03-06T11:44:43+00:00</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>01475240801937</t>
+          <t>01475240802019</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11550515", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010274353", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>01475240802497</t>
+          <t>01475240802496</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>01475240802497</t>
+          <t>01475240802496</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>01475240802447</t>
+          <t>01475240801937</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0049010275462</t>
+          <t>B2BDS11550515</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5373,34 +5373,34 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-03-06T10:02:07+01:00</t>
+          <t>2026-03-06T11:53:09+01:00</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Melle (DE), Germany</t>
+          <t>Holzgünz (DE), Germany</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:34+00:00</t>
+          <t>2026-03-06T11:14:39+00:00</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>01475240802447</t>
+          <t>01475240801937</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275462", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11550515", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>01475240802688</t>
+          <t>01475240802497</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>B2BDS11572044</t>
+          <t>0049010272893</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5436,34 +5436,34 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:02+01:00</t>
+          <t>2026-03-06T11:17:39+01:00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Marl (DE), Germany</t>
+          <t>Mannheim (DE), Germany</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:38+00:00</t>
+          <t>2026-03-06T11:14:41+00:00</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>01475240802688</t>
+          <t>01475240802497</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010272893", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>01475240801535</t>
+          <t>01475240802688</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>B2BDS11564142</t>
+          <t>B2BDS11572044</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5499,27 +5499,27 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-03-06T13:22:49+01:00</t>
+          <t>2026-03-06T10:44:02+01:00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Aichach (DE), Germany</t>
+          <t>Marl (DE), Germany</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:35+00:00</t>
+          <t>2026-03-06T10:14:38+00:00</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>01475240801535</t>
+          <t>01475240802688</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11564142", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5589,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>01475240802278</t>
+          <t>01475240802447</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>B2BDS11572044</t>
+          <t>0049010275462</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5625,34 +5625,34 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:02+01:00</t>
+          <t>2026-03-06T10:02:07+01:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Marl (DE), Germany</t>
+          <t>Melle (DE), Germany</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:31+00:00</t>
+          <t>2026-03-06T09:14:34+00:00</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>01475240802278</t>
+          <t>01475240802447</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010275462", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>01475240801976</t>
+          <t>01475240801535</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0049010271798</t>
+          <t>B2BDS11564142</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5688,34 +5688,34 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-03-06T11:40:51+01:00</t>
+          <t>2026-03-06T13:22:49+01:00</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Aichach (DE), Germany</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:31+00:00</t>
+          <t>2026-03-06T13:14:35+00:00</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>01475240801976</t>
+          <t>01475240801535</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271798", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11564142", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>01475240802644</t>
+          <t>01475240802278</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0049010274849</t>
+          <t>B2BDS11572044</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5751,34 +5751,34 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-03-06T13:35:13+01:00</t>
+          <t>2026-03-06T10:44:02+01:00</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Wustermark (DE), Germany</t>
+          <t>Marl (DE), Germany</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:30+00:00</t>
+          <t>2026-03-06T10:14:31+00:00</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>01475240802644</t>
+          <t>01475240802278</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274849", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>01475240802279</t>
+          <t>01475240802644</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>B2BDS11572044</t>
+          <t>0049010274849</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5814,34 +5814,34 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:02+01:00</t>
+          <t>2026-03-06T13:35:13+01:00</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Marl (DE), Germany</t>
+          <t>Wustermark (DE), Germany</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:34+00:00</t>
+          <t>2026-03-06T13:14:30+00:00</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>01475240802279</t>
+          <t>01475240802644</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010274849", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>01475240801457</t>
+          <t>01475240801976</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0049010275056</t>
+          <t>0049010271798</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5877,34 +5877,34 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-03-06T11:13:46+01:00</t>
+          <t>2026-03-06T11:40:51+01:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:30+00:00</t>
+          <t>2026-03-06T12:14:31+00:00</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>01475240801457</t>
+          <t>01475240801976</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275056", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010271798", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>01475240802597</t>
+          <t>01475240802279</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:28+00:00</t>
+          <t>2026-03-06T10:14:34+00:00</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>01475240802597</t>
+          <t>01475240802279</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>01475240801458</t>
+          <t>01475240801457</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-03-06T11:44:31+00:00</t>
+          <t>2026-03-06T10:44:30+00:00</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>01475240801458</t>
+          <t>01475240801457</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -6030,7 +6030,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>01475240801290</t>
+          <t>01475240802597</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0049010275056</t>
+          <t>B2BDS11572044</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6066,34 +6066,34 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-03-06T11:13:46+01:00</t>
+          <t>2026-03-06T10:44:02+01:00</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>Marl (DE), Germany</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:27+00:00</t>
+          <t>2026-03-06T10:14:28+00:00</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>01475240801290</t>
+          <t>01475240802597</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275056", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>01475240801287</t>
+          <t>01475240802254</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>B2BDS11570004</t>
+          <t>B2BDS11552798</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6129,34 +6129,34 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-03-06T14:22:35+01:00</t>
+          <t>2026-03-06T10:54:49+01:00</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Marl (DE), Germany</t>
+          <t>Altentreptow (DE), Germany</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:33+00:00</t>
+          <t>2026-03-06T10:19:51+00:00</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>01475240801287</t>
+          <t>01475240802254</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11570004", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11552798", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>01475240802254</t>
+          <t>01475240801290</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>B2BDS11552798</t>
+          <t>0049010275056</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6192,34 +6192,34 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-06T10:54:49+01:00</t>
+          <t>2026-03-06T11:13:46+01:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Altentreptow (DE), Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-03-06T10:19:51+00:00</t>
+          <t>2026-03-06T11:14:27+00:00</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>01475240802254</t>
+          <t>01475240801290</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11552798", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010275056", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>01475240801566</t>
+          <t>01475240801287</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1024939145-D</t>
+          <t>B2BDS11570004</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6255,34 +6255,34 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-03-06T16:02:43+01:00</t>
+          <t>2026-03-06T14:22:35+01:00</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Staufenberg-Mainzlar (DE), Germany</t>
+          <t>Marl (DE), Germany</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-03-06T15:44:34+00:00</t>
+          <t>2026-03-06T14:14:33+00:00</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>01475240801566</t>
+          <t>01475240801287</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024939145-D", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "B2BDS11570004", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>01475240802714</t>
+          <t>01475240801458</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6302,12 +6302,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>B2BDS11552798</t>
+          <t>0049010275056</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6318,27 +6318,27 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-03-06T10:54:49+01:00</t>
+          <t>2026-03-06T11:13:46+01:00</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Altentreptow (DE), Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:25+00:00</t>
+          <t>2026-03-06T11:44:31+00:00</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>01475240802714</t>
+          <t>01475240801458</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11552798", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010275056", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>01475240801731</t>
+          <t>01475240801566</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0049010270303</t>
+          <t>1024939145-D</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6507,34 +6507,34 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-03-06T12:07:55+01:00</t>
+          <t>2026-03-06T16:02:43+01:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Bad Bentheim (DE), Germany</t>
+          <t>Staufenberg-Mainzlar (DE), Germany</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:30+00:00</t>
+          <t>2026-03-06T15:44:34+00:00</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>01475240801731</t>
+          <t>01475240801566</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010270303", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "1024939145-D", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>01475240801284</t>
+          <t>01475240802714</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>B2BDS11493428</t>
+          <t>B2BDS11552798</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6570,34 +6570,34 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-03-06T13:07:38+01:00</t>
+          <t>2026-03-06T10:54:49+01:00</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Nörten-Hardenberg (DE), Germany</t>
+          <t>Altentreptow (DE), Germany</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:31+00:00</t>
+          <t>2026-03-06T10:14:25+00:00</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>01475240801284</t>
+          <t>01475240802714</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11493428", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11552798", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>01475240801386</t>
+          <t>01475240801731</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>306-7860274-6553932</t>
+          <t>0049010270303</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6633,34 +6633,34 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-03-06T13:27:52+01:00</t>
+          <t>2026-03-06T12:07:55+01:00</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Hagen (DE), Germany</t>
+          <t>Bad Bentheim (DE), Germany</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-03-06T17:14:36+00:00</t>
+          <t>2026-03-06T12:14:30+00:00</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>01475240801386</t>
+          <t>01475240801731</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>{"external_order_id": "306-7860274-6553932", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "0049010270303", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>01475240801156</t>
+          <t>01475240801284</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0049010271706</t>
+          <t>B2BDS11493428</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6696,34 +6696,34 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-03-06T11:50:32+01:00</t>
+          <t>2026-03-06T13:07:38+01:00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Nörten-Hardenberg (DE), Germany</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:28+00:00</t>
+          <t>2026-03-06T12:14:31+00:00</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>01475240801156</t>
+          <t>01475240801284</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271706", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11493428", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>01475240803166</t>
+          <t>01475240801386</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1024947548-A</t>
+          <t>306-7860274-6553932</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6759,34 +6759,34 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-03-06T10:15:05+01:00</t>
+          <t>2026-03-06T13:27:52+01:00</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Melle (DE), Germany</t>
+          <t>Hagen (DE), Germany</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:34+00:00</t>
+          <t>2026-03-06T17:14:36+00:00</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>01475240803166</t>
+          <t>01475240801386</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024947548-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "306-7860274-6553932", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>01475240801854</t>
+          <t>01475240803166</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0049010271706</t>
+          <t>1024947548-A</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6822,34 +6822,34 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-03-06T11:50:32+01:00</t>
+          <t>2026-03-06T10:15:05+01:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Melle (DE), Germany</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:26+00:00</t>
+          <t>2026-03-06T10:14:34+00:00</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>01475240801854</t>
+          <t>01475240803166</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271706", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "1024947548-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>01475240800417</t>
+          <t>01475240801156</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0049010268109</t>
+          <t>0049010271706</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6885,34 +6885,34 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-03-06T10:18:44+01:00</t>
+          <t>2026-03-06T11:50:32+01:00</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Duisburg (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:33+00:00</t>
+          <t>2026-03-06T11:14:28+00:00</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>01475240800417</t>
+          <t>01475240801156</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010268109", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010271706", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>01475240800043</t>
+          <t>01475240800417</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0049010271156</t>
+          <t>0049010268109</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6948,34 +6948,34 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:11+01:00</t>
+          <t>2026-03-06T10:18:44+01:00</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Neuhof-Dorfborn (DE), Germany</t>
+          <t>Duisburg (DE), Germany</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:25+00:00</t>
+          <t>2026-03-06T11:14:33+00:00</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>01475240800043</t>
+          <t>01475240800417</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271156", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010268109", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>01475240803541</t>
+          <t>01475240801854</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1024946909-A</t>
+          <t>0049010271706</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7011,34 +7011,34 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-03-06T10:45:28+01:00</t>
+          <t>2026-03-06T11:50:32+01:00</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:26+00:00</t>
+          <t>2026-03-06T13:14:26+00:00</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>01475240803541</t>
+          <t>01475240801854</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024946909-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0049010271706", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>01475240802170</t>
+          <t>01475240800043</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0049010275668</t>
+          <t>0049010271156</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7074,34 +7074,34 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-03-06T12:38:58+01:00</t>
+          <t>2026-03-06T10:44:11+01:00</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Neuhof-Dorfborn (DE), Germany</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:24+00:00</t>
+          <t>2026-03-06T11:14:25+00:00</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>01475240802170</t>
+          <t>01475240800043</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275668", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010271156", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>01475240801424</t>
+          <t>01475240803541</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0049010272335</t>
+          <t>1024946909-A</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7137,34 +7137,34 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-06T13:03:15+01:00</t>
+          <t>2026-03-06T10:45:28+01:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Koblenz (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:28+00:00</t>
+          <t>2026-03-06T10:14:26+00:00</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>01475240801424</t>
+          <t>01475240803541</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272335", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "1024946909-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>01475240802694</t>
+          <t>01475240802170</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MCPPKD5</t>
+          <t>0049010275668</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7200,7 +7200,7 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-06T14:30:44+01:00</t>
+          <t>2026-03-06T12:38:58+01:00</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7210,24 +7210,24 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:27+00:00</t>
+          <t>2026-03-06T12:14:24+00:00</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>01475240802694</t>
+          <t>01475240802170</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>{"external_order_id": "MCPPKD5", "sales_office_id": "4286"}</t>
+          <t>{"external_order_id": "0049010275668", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>01475240801931</t>
+          <t>01475240801424</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0049010275668</t>
+          <t>0049010272335</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7263,34 +7263,34 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-03-06T12:38:58+01:00</t>
+          <t>2026-03-06T13:03:15+01:00</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Koblenz (DE), Germany</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:23+00:00</t>
+          <t>2026-03-06T14:14:28+00:00</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>01475240801931</t>
+          <t>01475240801424</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275668", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010272335", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>01475240802088</t>
+          <t>01475240802694</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0049010271450</t>
+          <t>MCPPKD5</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -7326,34 +7326,34 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-03-06T14:52:22+01:00</t>
+          <t>2026-03-06T14:30:44+01:00</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Neuhof-Dorfborn (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:25+00:00</t>
+          <t>2026-03-06T14:14:27+00:00</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>01475240802088</t>
+          <t>01475240802694</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271450", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "MCPPKD5", "sales_office_id": "4286"}</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>01475240802171</t>
+          <t>01475240801931</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:29+00:00</t>
+          <t>2026-03-06T12:14:23+00:00</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>01475240802171</t>
+          <t>01475240801931</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -7416,7 +7416,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>01475240802074</t>
+          <t>01475240802171</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0049010271450</t>
+          <t>0049010275668</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7452,34 +7452,34 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-06T14:52:22+01:00</t>
+          <t>2026-03-06T12:38:58+01:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Neuhof-Dorfborn (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:24+00:00</t>
+          <t>2026-03-06T12:14:29+00:00</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>01475240802074</t>
+          <t>01475240802171</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271450", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010275668", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>01475240803697</t>
+          <t>01475240802088</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0049010274335</t>
+          <t>0049010271450</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7515,34 +7515,34 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-03-06T10:19:41+01:00</t>
+          <t>2026-03-06T14:52:22+01:00</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Neuhof-Dorfborn (DE), Germany</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:21+00:00</t>
+          <t>2026-03-06T14:14:25+00:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>01475240803697</t>
+          <t>01475240802088</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274335", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010271450", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>01475240801642</t>
+          <t>01475240803697</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0049010270235</t>
+          <t>0049010274335</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7578,27 +7578,27 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-06T09:34:06+01:00</t>
+          <t>2026-03-06T10:19:41+01:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:20+00:00</t>
+          <t>2026-03-06T11:14:21+00:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>01475240801642</t>
+          <t>01475240803697</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010270235", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010274335", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>01475240800215</t>
+          <t>01475240801642</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>305-9272397-9608321</t>
+          <t>0049010270235</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7704,34 +7704,34 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-03-06T11:33:48+01:00</t>
+          <t>2026-03-06T09:34:06+01:00</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:21+00:00</t>
+          <t>2026-03-06T09:14:20+00:00</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>01475240800215</t>
+          <t>01475240801642</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>{"external_order_id": "305-9272397-9608321", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "0049010270235", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>01475240800214</t>
+          <t>01475240802074</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>305-9272397-9608321</t>
+          <t>0049010271450</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7767,34 +7767,34 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-03-06T11:33:48+01:00</t>
+          <t>2026-03-06T14:52:22+01:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Neuhof-Dorfborn (DE), Germany</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:25+00:00</t>
+          <t>2026-03-06T14:14:24+00:00</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>01475240800214</t>
+          <t>01475240802074</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>{"external_order_id": "305-9272397-9608321", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "0049010271450", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>01475240802270</t>
+          <t>01475240800214</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>B2BDS11561959</t>
+          <t>305-9272397-9608321</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7830,34 +7830,34 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-03-06T08:34:02+01:00</t>
+          <t>2026-03-06T11:33:48+01:00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Ludwigsburg (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-03-06T08:14:19+00:00</t>
+          <t>2026-03-06T11:14:25+00:00</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>01475240802270</t>
+          <t>01475240800214</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11561959", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "305-9272397-9608321", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>01475240801430</t>
+          <t>01475240800215</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>B2BDS11550954</t>
+          <t>305-9272397-9608321</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7893,34 +7893,34 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-03-06T11:00:16+01:00</t>
+          <t>2026-03-06T11:33:48+01:00</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Wuppertal (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:20+00:00</t>
+          <t>2026-03-06T11:14:21+00:00</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>01475240801430</t>
+          <t>01475240800215</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11550954", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "305-9272397-9608321", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>01475240802916</t>
+          <t>01475240802270</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1024942385-A</t>
+          <t>B2BDS11561959</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7956,34 +7956,34 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-03-06T10:40:07+01:00</t>
+          <t>2026-03-06T08:34:02+01:00</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Heilbronn (DE), Germany</t>
+          <t>Ludwigsburg (DE), Germany</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:19+00:00</t>
+          <t>2026-03-06T08:14:19+00:00</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>01475240802916</t>
+          <t>01475240802270</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024942385-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "B2BDS11561959", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>01475240801934</t>
+          <t>01475240801430</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1024942385-A</t>
+          <t>B2BDS11550954</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8019,34 +8019,34 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-06T10:40:07+01:00</t>
+          <t>2026-03-06T11:00:16+01:00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Heilbronn (DE), Germany</t>
+          <t>Wuppertal (DE), Germany</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:16+00:00</t>
+          <t>2026-03-06T10:44:20+00:00</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>01475240801934</t>
+          <t>01475240801430</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024942385-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "B2BDS11550954", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>01475240801104</t>
+          <t>01475240802916</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>B2BDS11563163</t>
+          <t>1024942385-A</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -8082,34 +8082,34 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-03-06T13:36:34+01:00</t>
+          <t>2026-03-06T10:40:07+01:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Heilbronn (DE), Germany</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-03-06T13:44:25+00:00</t>
+          <t>2026-03-06T11:14:19+00:00</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>01475240801104</t>
+          <t>01475240802916</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11563163", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "1024942385-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>01475240800442</t>
+          <t>01475240801934</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>cbn4wmb36y</t>
+          <t>1024942385-A</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8145,34 +8145,34 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-03-06T13:35:17+01:00</t>
+          <t>2026-03-06T10:40:07+01:00</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Heilbronn (DE), Germany</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-03-06T12:44:26+00:00</t>
+          <t>2026-03-06T10:14:16+00:00</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>01475240800442</t>
+          <t>01475240801934</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "1024942385-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>01475240802166</t>
+          <t>01475240801104</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>B2BDS11563858</t>
+          <t>B2BDS11563163</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -8208,34 +8208,34 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-03-06T12:07:48+01:00</t>
+          <t>2026-03-06T13:36:34+01:00</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Hagen (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:20+00:00</t>
+          <t>2026-03-06T13:44:25+00:00</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>01475240802166</t>
+          <t>01475240801104</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11563858", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11563163", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>01475240801768</t>
+          <t>01475240800442</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>27-14293-38348</t>
+          <t>cbn4wmb36y</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8271,34 +8271,34 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:06+01:00</t>
+          <t>2026-03-06T13:35:17+01:00</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:15+00:00</t>
+          <t>2026-03-06T12:44:26+00:00</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>01475240801768</t>
+          <t>01475240800442</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>{"external_order_id": "27-14293-38348", "sales_office_id": "4389"}</t>
+          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>01475240801103</t>
+          <t>01475240802166</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>B2BDS11563163</t>
+          <t>B2BDS11563858</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8334,34 +8334,34 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-03-06T13:36:34+01:00</t>
+          <t>2026-03-06T12:07:48+01:00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Hagen (DE), Germany</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:31+00:00</t>
+          <t>2026-03-06T12:14:20+00:00</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>01475240801103</t>
+          <t>01475240802166</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11563163", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11563858", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>01475240801102</t>
+          <t>01475240801768</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>B2BDS11563163</t>
+          <t>27-14293-38348</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -8397,34 +8397,34 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-03-06T13:36:34+01:00</t>
+          <t>2026-03-06T10:14:06+01:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-03-06T12:44:19+00:00</t>
+          <t>2026-03-06T10:14:15+00:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>01475240801102</t>
+          <t>01475240801768</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11563163", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "27-14293-38348", "sales_office_id": "4389"}</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>01475240799764</t>
+          <t>01475240801103</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0049010267065</t>
+          <t>B2BDS11563163</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -8460,34 +8460,34 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-03-06T13:47:00+01:00</t>
+          <t>2026-03-06T13:36:34+01:00</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Melsdorf (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:20+00:00</t>
+          <t>2026-03-06T13:14:31+00:00</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>01475240799764</t>
+          <t>01475240801103</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010267065", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11563163", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>01475240800759</t>
+          <t>01475240801102</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>cbn4wmb36y</t>
+          <t>B2BDS11563163</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8523,34 +8523,34 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-03-06T13:35:17+01:00</t>
+          <t>2026-03-06T13:36:34+01:00</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:22+00:00</t>
+          <t>2026-03-06T12:44:19+00:00</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>01475240800759</t>
+          <t>01475240801102</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "B2BDS11563163", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>01475240802479</t>
+          <t>01475240800759</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>303-3833262-5777904</t>
+          <t>cbn4wmb36y</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8586,34 +8586,34 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-03-06T14:08:03+01:00</t>
+          <t>2026-03-06T13:35:17+01:00</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:35+00:00</t>
+          <t>2026-03-06T13:14:22+00:00</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>01475240802479</t>
+          <t>01475240800759</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>{"external_order_id": "303-3833262-5777904", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>01475240801473</t>
+          <t>01475240799764</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>B2BDS11543346</t>
+          <t>0049010267065</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8649,34 +8649,34 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-06T09:53:10+01:00</t>
+          <t>2026-03-06T13:47:00+01:00</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Melsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:15+00:00</t>
+          <t>2026-03-06T13:14:20+00:00</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>01475240801473</t>
+          <t>01475240799764</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11543346", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010267065", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>01475240800410</t>
+          <t>01475240802479</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>cbn4wmb36y</t>
+          <t>303-3833262-5777904</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8712,27 +8712,27 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-03-06T13:35:17+01:00</t>
+          <t>2026-03-06T14:08:03+01:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-03-06T15:14:18+00:00</t>
+          <t>2026-03-06T14:14:35+00:00</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>01475240800410</t>
+          <t>01475240802479</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "303-3833262-5777904", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>01475240802478</t>
+          <t>01475240800410</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>303-3833262-5777904</t>
+          <t>cbn4wmb36y</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8838,34 +8838,34 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-03-06T14:08:03+01:00</t>
+          <t>2026-03-06T13:35:17+01:00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-03-06T14:44:17+00:00</t>
+          <t>2026-03-06T15:14:18+00:00</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>01475240802478</t>
+          <t>01475240800410</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>{"external_order_id": "303-3833262-5777904", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>01475240799765</t>
+          <t>01475240801473</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0049010267065</t>
+          <t>B2BDS11543346</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8901,34 +8901,34 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-03-06T13:47:00+01:00</t>
+          <t>2026-03-06T09:53:10+01:00</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Melsdorf (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:18+00:00</t>
+          <t>2026-03-06T10:14:15+00:00</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>01475240799765</t>
+          <t>01475240801473</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010267065", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11543346", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>01475240801808</t>
+          <t>01475240801433</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>0049010273457</t>
+          <t>B2BDS11564552</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8964,34 +8964,34 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-06T13:20:25+01:00</t>
+          <t>2026-03-06T09:10:30+01:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Malsch (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:20+00:00</t>
+          <t>2026-03-06T09:14:18+00:00</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>01475240801808</t>
+          <t>01475240801433</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010273457", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11564552", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>01475240801433</t>
+          <t>01475240802478</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9011,12 +9011,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>B2BDS11564552</t>
+          <t>303-3833262-5777904</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9027,7 +9027,7 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-03-06T09:10:30+01:00</t>
+          <t>2026-03-06T14:08:03+01:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9037,24 +9037,24 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:18+00:00</t>
+          <t>2026-03-06T14:44:17+00:00</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>01475240801433</t>
+          <t>01475240802478</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11564552", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "303-3833262-5777904", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>01475240802713</t>
+          <t>01475240801808</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>0049010275891</t>
+          <t>0049010273457</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9090,34 +9090,34 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-03-06T13:43:18+01:00</t>
+          <t>2026-03-06T13:20:25+01:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Malsch (DE), Germany</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:25+00:00</t>
+          <t>2026-03-06T13:14:20+00:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>01475240802713</t>
+          <t>01475240801808</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275891", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010273457", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>01475240798118</t>
+          <t>01475240799765</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:16+00:00</t>
+          <t>2026-03-06T13:14:18+00:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>01475240798118</t>
+          <t>01475240799765</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -9180,7 +9180,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>01475240801618</t>
+          <t>01475240798118</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0049010274049</t>
+          <t>0049010267065</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9216,34 +9216,34 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-06T12:49:58+01:00</t>
+          <t>2026-03-06T13:47:00+01:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Melsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:19+00:00</t>
+          <t>2026-03-06T13:14:16+00:00</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>01475240801618</t>
+          <t>01475240798118</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274049", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010267065", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>01475240801119</t>
+          <t>01475240802713</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>0049010274049</t>
+          <t>0049010275891</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9279,34 +9279,34 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-06T12:49:58+01:00</t>
+          <t>2026-03-06T13:43:18+01:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:15+00:00</t>
+          <t>2026-03-06T14:14:25+00:00</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>01475240801119</t>
+          <t>01475240802713</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274049", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010275891", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>01475240803419</t>
+          <t>01475240801618</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>0049010278629</t>
+          <t>0049010274049</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -9342,34 +9342,34 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-03-06T10:11:50+01:00</t>
+          <t>2026-03-06T12:49:58+01:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Koblenz (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:11+00:00</t>
+          <t>2026-03-06T12:14:19+00:00</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>01475240803419</t>
+          <t>01475240801618</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010278629", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010274049", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>01475240803396</t>
+          <t>01475240801119</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>B2BDS11557098</t>
+          <t>0049010274049</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -9405,34 +9405,34 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-03-06T12:42:33+01:00</t>
+          <t>2026-03-06T12:49:58+01:00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-03-06T12:44:22+00:00</t>
+          <t>2026-03-06T12:14:15+00:00</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>01475240803396</t>
+          <t>01475240801119</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11557098", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010274049", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>01475240803534</t>
+          <t>01475240803419</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>0049010274446</t>
+          <t>0049010278629</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9468,34 +9468,34 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-03-06T09:35:58+01:00</t>
+          <t>2026-03-06T10:11:50+01:00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Koblenz (DE), Germany</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:08+00:00</t>
+          <t>2026-03-06T10:14:11+00:00</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>01475240803534</t>
+          <t>01475240803419</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274446", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010278629", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>01475240801048</t>
+          <t>01475240803396</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>0049010272609</t>
+          <t>B2BDS11557098</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -9531,34 +9531,34 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-03-06T11:22:44+01:00</t>
+          <t>2026-03-06T12:42:33+01:00</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Lüneburg (DE), Germany</t>
+          <t>Essen (DE), Germany</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:07+00:00</t>
+          <t>2026-03-06T12:44:22+00:00</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>01475240801048</t>
+          <t>01475240803396</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272609", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11557098", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>01475240802668</t>
+          <t>01475240803534</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:06+00:00</t>
+          <t>2026-03-06T09:14:08+00:00</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>01475240802668</t>
+          <t>01475240803534</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -9621,7 +9621,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>01475240801047</t>
+          <t>01475240801048</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:08+00:00</t>
+          <t>2026-03-06T11:14:07+00:00</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>01475240801047</t>
+          <t>01475240801048</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -9684,7 +9684,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>01475240801186</t>
+          <t>01475240801047</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0049010272958</t>
+          <t>0049010272609</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9720,34 +9720,34 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-03-06T16:05:36+01:00</t>
+          <t>2026-03-06T11:22:44+01:00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Lüneburg (DE), Germany</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-03-06T15:44:11+00:00</t>
+          <t>2026-03-06T11:14:08+00:00</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>01475240801186</t>
+          <t>01475240801047</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272958", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010272609", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>01475240802586</t>
+          <t>01475240802668</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>01475240802586</t>
+          <t>01475240802668</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -9810,7 +9810,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>01475240801046</t>
+          <t>01475240802586</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0049010272609</t>
+          <t>0049010274446</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9846,34 +9846,34 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-03-06T11:22:44+01:00</t>
+          <t>2026-03-06T09:35:58+01:00</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Lüneburg (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:12+00:00</t>
+          <t>2026-03-06T09:14:06+00:00</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>01475240801046</t>
+          <t>01475240802586</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272609", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010274446", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>01475240802870</t>
+          <t>01475240801186</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PO-076-19546873674873714</t>
+          <t>0049010272958</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9909,34 +9909,34 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:12+01:00</t>
+          <t>2026-03-06T16:05:36+01:00</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Mannheim (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-03-06T11:44:06+00:00</t>
+          <t>2026-03-06T15:44:11+00:00</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>01475240802870</t>
+          <t>01475240801186</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-076-19546873674873714", "sales_office_id": "4670"}</t>
+          <t>{"external_order_id": "0049010272958", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>01475240801560</t>
+          <t>01475240802870</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0049010272958</t>
+          <t>PO-076-19546873674873714</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9972,34 +9972,34 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-03-06T16:05:36+01:00</t>
+          <t>2026-03-06T10:44:12+01:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Mannheim (DE), Germany</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-03-06T15:14:08+00:00</t>
+          <t>2026-03-06T11:44:06+00:00</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>01475240801560</t>
+          <t>01475240802870</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272958", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "PO-076-19546873674873714", "sales_office_id": "4670"}</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>01475240803203</t>
+          <t>01475240801046</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>B2BDS11530463</t>
+          <t>0049010272609</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -10035,34 +10035,34 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-03-06T09:21:38+01:00</t>
+          <t>2026-03-06T11:22:44+01:00</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>St. Ingbert (DE), Germany</t>
+          <t>Lüneburg (DE), Germany</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:03+00:00</t>
+          <t>2026-03-06T12:14:12+00:00</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>01475240803203</t>
+          <t>01475240801046</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11530463", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010272609", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>01475240801097</t>
+          <t>01475240801560</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>B2BDS11267180</t>
+          <t>0049010272958</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -10098,34 +10098,34 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-03-06T10:27:04+01:00</t>
+          <t>2026-03-06T16:05:36+01:00</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Duisburg (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:06+00:00</t>
+          <t>2026-03-06T15:14:08+00:00</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>01475240801097</t>
+          <t>01475240801560</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11267180", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010272958", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>01475240801045</t>
+          <t>01475240801097</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>0049010272609</t>
+          <t>B2BDS11267180</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -10161,34 +10161,34 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-03-06T11:22:44+01:00</t>
+          <t>2026-03-06T10:27:04+01:00</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Lüneburg (DE), Germany</t>
+          <t>Duisburg (DE), Germany</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:03+00:00</t>
+          <t>2026-03-06T10:14:06+00:00</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>01475240801045</t>
+          <t>01475240801097</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272609", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11267180", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>01475240802303</t>
+          <t>01475240803203</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>B2BDS11223924</t>
+          <t>B2BDS11530463</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -10224,34 +10224,34 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-03-06T14:41:17+01:00</t>
+          <t>2026-03-06T09:21:38+01:00</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>St. Ingbert (DE), Germany</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-03-06T15:14:02+00:00</t>
+          <t>2026-03-06T11:14:03+00:00</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>01475240802303</t>
+          <t>01475240803203</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11223924", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11530463", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>01475240802625</t>
+          <t>01475240801045</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>0049010276252</t>
+          <t>0049010272609</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -10287,27 +10287,27 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-03-06T11:33:48+01:00</t>
+          <t>2026-03-06T11:22:44+01:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Holzgünz (DE), Germany</t>
+          <t>Lüneburg (DE), Germany</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:04+00:00</t>
+          <t>2026-03-06T11:14:03+00:00</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>01475240802625</t>
+          <t>01475240801045</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276252", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010272609", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>01475240803333</t>
+          <t>01475240802625</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10397,12 +10397,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>cbn4wmhhxm</t>
+          <t>0049010276252</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -10413,34 +10413,34 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-06T12:43:19+01:00</t>
+          <t>2026-03-06T11:33:48+01:00</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>Holzgünz (DE), Germany</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:02+00:00</t>
+          <t>2026-03-06T11:14:04+00:00</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>01475240803333</t>
+          <t>01475240802625</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmhhxm", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0049010276252", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>01475240802234</t>
+          <t>01475240803333</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>B2BDS11553517</t>
+          <t>cbn4wmhhxm</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -10476,34 +10476,34 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-03-06T09:37:40+01:00</t>
+          <t>2026-03-06T12:43:19+01:00</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-03-06T09:13:59+00:00</t>
+          <t>2026-03-06T12:14:02+00:00</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>01475240802234</t>
+          <t>01475240803333</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11553517", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "cbn4wmhhxm", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>01475240801434</t>
+          <t>01475240802303</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>0049010271265</t>
+          <t>B2BDS11223924</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -10539,27 +10539,27 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-03-06T13:57:19+01:00</t>
+          <t>2026-03-06T14:41:17+01:00</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Anröchte (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-03-06T15:14:08+00:00</t>
+          <t>2026-03-06T15:14:02+00:00</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>01475240801434</t>
+          <t>01475240802303</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271265", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11223924", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>01475240802147</t>
+          <t>01475240801434</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>cbn4wmn8ws</t>
+          <t>0049010271265</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -10665,34 +10665,34 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-03-06T11:45:31+01:00</t>
+          <t>2026-03-06T13:57:19+01:00</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Seddiner See (DE), Germany</t>
+          <t>Anröchte (DE), Germany</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:00+00:00</t>
+          <t>2026-03-06T15:14:08+00:00</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>01475240802147</t>
+          <t>01475240801434</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmn8ws", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0049010271265", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>01475240802695</t>
+          <t>01475240802234</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>0049010271341</t>
+          <t>B2BDS11553517</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -10728,34 +10728,34 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-03-06T12:24:56+01:00</t>
+          <t>2026-03-06T09:37:40+01:00</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Duisburg (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:01+00:00</t>
+          <t>2026-03-06T09:13:59+00:00</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>01475240802695</t>
+          <t>01475240802234</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271341", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11553517", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>01475240803204</t>
+          <t>01475240802695</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>0049010267564</t>
+          <t>0049010271341</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10791,44 +10791,44 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-03-06T15:05:23+01:00</t>
+          <t>2026-03-06T12:24:56+01:00</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Mannheim (DE), Germany</t>
+          <t>Duisburg (DE), Germany</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-03-06T14:12:06+00:00</t>
+          <t>2026-03-06T12:14:01+00:00</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>01475240803204</t>
+          <t>01475240802695</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010267564", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010271341", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>06086432955679</t>
+          <t>01475240802147</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>dpd-ch-sftp</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>DPD Switzerland</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>0041006367165</t>
+          <t>cbn4wmn8ws</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>0323</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10854,44 +10854,44 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-05T13:53:18+01:00</t>
+          <t>2026-03-06T11:45:31+01:00</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>,Switzerland</t>
+          <t>Seddiner See (DE), Germany</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-03-06T05:03:28+00:00</t>
+          <t>2026-03-06T11:14:00+00:00</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>06086432955679</t>
+          <t>01475240802147</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0041006367165", "sales_office_id": "0323"}</t>
+          <t>{"external_order_id": "cbn4wmn8ws", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>JJD149990121180197968</t>
+          <t>01475240803204</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10901,52 +10901,60 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>6001677729</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr"/>
+          <t>0049010267564</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-02-25T13:36:00+01:00</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr"/>
+          <t>2026-03-06T15:05:23+01:00</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Mannheim (DE), Germany</t>
+        </is>
+      </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:30+00:00</t>
+          <t>2026-03-06T14:12:06+00:00</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>JJD149990121180197968</t>
+          <t>01475240803204</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "0049010267564", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>JVGLOTC0109732872</t>
+          <t>06086432955679</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>dpd-ch-sftp</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>DPD Switzerland</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10956,52 +10964,60 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>6001679442</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr"/>
+          <t>0041006367165</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>0323</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-03-05T13:25:25+01:00</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr"/>
+          <t>2026-03-05T13:53:18+01:00</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>,Switzerland</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:29+00:00</t>
+          <t>2026-03-06T05:03:28+00:00</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>JVGLOTC0109732872</t>
+          <t>06086432955679</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "0041006367165", "sales_office_id": "0323"}</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>REC000081158013</t>
+          <t>1ZR096K99010489136</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>ups-api</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -11011,7 +11027,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>6001679312</t>
+          <t>6001677201</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -11023,40 +11039,44 @@
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-03-06T13:55:00</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr"/>
+          <t>2026-03-06T11:55:38-08:00</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>REDLANDS, CA, 92374, US, United States</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-03-06T14:20:22+00:00</t>
+          <t>2026-03-06T20:01:23+00:00</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>REC000081158013</t>
+          <t>1ZR096K99010489136</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>REC000081128659</t>
+          <t>JVGLOTC0109732872</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -11066,7 +11086,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>6001676814</t>
+          <t>6001679442</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -11078,40 +11098,40 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-03-06T17:21:00</t>
+          <t>2026-03-05T13:25:25+01:00</t>
         </is>
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-03-06T17:20:27+00:00</t>
+          <t>2026-03-06T01:44:29+00:00</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>REC000081128659</t>
+          <t>JVGLOTC0109732872</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>REC000081129859</t>
+          <t>JJD149990121180197968</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>dhlparcel-nl</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>DHL Parcel NL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -11121,7 +11141,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>6001677522</t>
+          <t>6001677729</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -11133,30 +11153,30 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-03-06T17:18:00</t>
+          <t>2026-02-25T13:36:00+01:00</t>
         </is>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-03-06T17:20:27+00:00</t>
+          <t>2026-03-06T01:44:30+00:00</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>REC000081129859</t>
+          <t>JJD149990121180197968</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>REC000081130266</t>
+          <t>REC000081138277</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11176,7 +11196,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>6001677622</t>
+          <t>6001678531</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -11188,18 +11208,18 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-06T10:53:00</t>
+          <t>2026-03-06T11:19:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-03-06T12:19:58+00:00</t>
+          <t>2026-03-06T11:20:58+00:00</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>REC000081130266</t>
+          <t>REC000081138277</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -11211,7 +11231,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>REC000081136278</t>
+          <t>REC000081128659</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11231,7 +11251,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>6001678319</t>
+          <t>6001676814</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -11243,18 +11263,18 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-03-06T17:02:00</t>
+          <t>2026-03-06T17:21:00</t>
         </is>
       </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-03-06T16:19:04+00:00</t>
+          <t>2026-03-06T17:20:27+00:00</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>REC000081136278</t>
+          <t>REC000081128659</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -11266,7 +11286,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>REC000081138277</t>
+          <t>REC000081130266</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11286,7 +11306,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>6001678531</t>
+          <t>6001677622</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -11298,18 +11318,18 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-03-06T11:19:00</t>
+          <t>2026-03-06T10:53:00</t>
         </is>
       </c>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-03-06T11:20:58+00:00</t>
+          <t>2026-03-06T12:19:58+00:00</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>REC000081138277</t>
+          <t>REC000081130266</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -11321,7 +11341,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>REC000081128649</t>
+          <t>REC000081130037</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11341,7 +11361,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>6001676755</t>
+          <t>6001677571</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -11353,18 +11373,18 @@
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-03-06T16:02:00</t>
+          <t>2026-03-06T13:07:00</t>
         </is>
       </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-03-06T15:18:44+00:00</t>
+          <t>2026-03-06T12:19:58+00:00</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>REC000081128649</t>
+          <t>REC000081130037</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -11376,17 +11396,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>REC000081130037</t>
+          <t>996011434800779082</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>swiss-post</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Swiss Post</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11396,7 +11416,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>6001677571</t>
+          <t>6001676681</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -11408,30 +11428,34 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-03-06T13:07:00</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr"/>
+          <t>2026-03-06T08:36:12+01:00</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>CH, Switzerland</t>
+        </is>
+      </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-03-06T12:19:58+00:00</t>
+          <t>2026-03-06T09:14:42+00:00</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>REC000081130037</t>
+          <t>996011434800779082</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"courier": "swiss-post"}</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>REC000081135308</t>
+          <t>REC000081171766</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11451,7 +11475,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>6001678247</t>
+          <t>6001679761</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -11463,18 +11487,18 @@
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-03-06T14:21:00</t>
+          <t>2026-03-06T18:02:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-03-06T14:21:03+00:00</t>
+          <t>2026-03-06T17:20:27+00:00</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>REC000081135308</t>
+          <t>REC000081171766</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -11486,7 +11510,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>REC000081136256</t>
+          <t>REC000081128649</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11506,7 +11530,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>6001678322</t>
+          <t>6001676755</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -11518,18 +11542,18 @@
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-03-06T15:08:00</t>
+          <t>2026-03-06T16:02:00</t>
         </is>
       </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-03-06T14:20:42+00:00</t>
+          <t>2026-03-06T15:18:44+00:00</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>REC000081136256</t>
+          <t>REC000081128649</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -11541,7 +11565,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>REC000081138050</t>
+          <t>REC000081136256</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11561,7 +11585,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>6001678500</t>
+          <t>6001678322</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -11573,18 +11597,18 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-03-06T11:24:00</t>
+          <t>2026-03-06T15:08:00</t>
         </is>
       </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-03-06T11:20:58+00:00</t>
+          <t>2026-03-06T14:20:42+00:00</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>REC000081138050</t>
+          <t>REC000081136256</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -11596,7 +11620,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>REC000081171766</t>
+          <t>REC000081163581</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11616,7 +11640,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>6001679761</t>
+          <t>6001679526</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -11628,18 +11652,18 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-03-06T18:02:00</t>
+          <t>2026-03-06T13:29:00</t>
         </is>
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-03-06T17:20:27+00:00</t>
+          <t>2026-03-06T15:18:44+00:00</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>REC000081171766</t>
+          <t>REC000081163581</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -11651,7 +11675,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>REC000081163581</t>
+          <t>REC000081138050</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11671,7 +11695,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>6001679526</t>
+          <t>6001678500</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -11683,18 +11707,18 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-03-06T13:29:00</t>
+          <t>2026-03-06T11:24:00</t>
         </is>
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-03-06T15:18:44+00:00</t>
+          <t>2026-03-06T11:20:58+00:00</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>REC000081163581</t>
+          <t>REC000081138050</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -11706,17 +11730,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>996011434800779082</t>
+          <t>REC000081135308</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>swiss-post</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Swiss Post</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11726,7 +11750,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>6001676681</t>
+          <t>6001678247</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -11738,34 +11762,30 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-03-06T08:36:12+01:00</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>CH, Switzerland</t>
-        </is>
-      </c>
+          <t>2026-03-06T14:21:00</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:42+00:00</t>
+          <t>2026-03-06T14:21:03+00:00</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>996011434800779082</t>
+          <t>REC000081135308</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>{"courier": "swiss-post"}</t>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>REC000081137342</t>
+          <t>REC000081136278</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11785,7 +11805,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>6001678429</t>
+          <t>6001678319</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -11797,18 +11817,18 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-03-06T09:31:00</t>
+          <t>2026-03-06T17:02:00</t>
         </is>
       </c>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-03-06T09:21:15+00:00</t>
+          <t>2026-03-06T16:19:04+00:00</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>REC000081137342</t>
+          <t>REC000081136278</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -11820,7 +11840,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>REC000081145007</t>
+          <t>REC000081129859</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11840,7 +11860,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>6001678965</t>
+          <t>6001677522</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -11852,18 +11872,18 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-03-06T12:28:00</t>
+          <t>2026-03-06T17:18:00</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-03-06T12:19:38+00:00</t>
+          <t>2026-03-06T17:20:27+00:00</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>REC000081145007</t>
+          <t>REC000081129859</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -11875,7 +11895,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>REC000081129636</t>
+          <t>REC000081158013</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11895,7 +11915,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>6001677477</t>
+          <t>6001679312</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -11907,18 +11927,18 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-03-06T15:32:00</t>
+          <t>2026-03-06T13:55:00</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-03-06T15:19:03+00:00</t>
+          <t>2026-03-06T14:20:22+00:00</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>REC000081129636</t>
+          <t>REC000081158013</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -11930,7 +11950,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>REC000081128911</t>
+          <t>REC000081129636</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11950,7 +11970,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>6001677193</t>
+          <t>6001677477</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -11962,18 +11982,18 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-03-06T10:57:00</t>
+          <t>2026-03-06T15:32:00</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-03-06T11:20:39+00:00</t>
+          <t>2026-03-06T15:19:03+00:00</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>REC000081128911</t>
+          <t>REC000081129636</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -12040,17 +12060,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ZDDO3IST</t>
+          <t>REC000081128911</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -12060,7 +12080,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>6001679636</t>
+          <t>6001677193</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -12072,44 +12092,40 @@
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-02-12T14:00:00+01:00</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>DE, Germany</t>
-        </is>
-      </c>
+          <t>2026-03-06T10:57:00</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:20+00:00</t>
+          <t>2026-03-06T11:20:39+00:00</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>ZDDO3IST</t>
+          <t>REC000081128911</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ZDDO3ISS</t>
+          <t>REC000081145007</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -12119,7 +12135,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>6001679636</t>
+          <t>6001678965</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -12131,44 +12147,40 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-02-12T14:00:00+01:00</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>DE, Germany</t>
-        </is>
-      </c>
+          <t>2026-03-06T12:28:00</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:22+00:00</t>
+          <t>2026-03-06T12:19:38+00:00</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>ZDDO3ISS</t>
+          <t>REC000081145007</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Z7XDDA12</t>
+          <t>REC000081137342</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>spanish-seur-ftp</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12178,7 +12190,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>6001677260</t>
+          <t>6001678429</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -12190,44 +12202,40 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-02-20T13:00:19+01:00</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>AT, Austria</t>
-        </is>
-      </c>
+          <t>2026-03-06T09:31:00</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:21+00:00</t>
+          <t>2026-03-06T09:21:15+00:00</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Z7XDDA12</t>
+          <t>REC000081137342</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>05222069778589</t>
+          <t>ZDDO3IST</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12237,7 +12245,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>6001679888</t>
+          <t>6001679636</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -12249,44 +12257,44 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-03-04T17:48:49+01:00</t>
+          <t>2026-02-12T14:00:00+01:00</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Rijssen, NL, Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026-03-06T13:44:27+00:00</t>
+          <t>2026-03-06T01:44:20+00:00</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>05222069778589</t>
+          <t>ZDDO3IST</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>05222006538846</t>
+          <t>ZDDO3ISS</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12296,7 +12304,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>6001678746</t>
+          <t>6001679636</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -12308,44 +12316,44 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-03-05T15:35:36+01:00</t>
+          <t>2026-02-12T14:00:00+01:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Etten-Leur, NL, Netherlands</t>
+          <t>DE, Germany</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026-03-06T16:44:56+00:00</t>
+          <t>2026-03-06T01:44:22+00:00</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>05222006538846</t>
+          <t>ZDDO3ISS</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>05222006538848</t>
+          <t>Z7XDDA12</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>gls</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12355,7 +12363,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>6001678777</t>
+          <t>6001677260</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -12367,34 +12375,34 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-03-05T11:50:49+01:00</t>
+          <t>2026-02-20T13:00:19+01:00</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Berkel en Rodenrijs, NL, Netherlands</t>
+          <t>AT, Austria</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026-03-06T13:44:41+00:00</t>
+          <t>2026-03-06T01:44:21+00:00</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>05222006538848</t>
+          <t>Z7XDDA12</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>05222006538860</t>
+          <t>05222069732758</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12414,7 +12422,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>6001679075</t>
+          <t>6001679852</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -12426,22 +12434,22 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-03-05T13:55:37+01:00</t>
+          <t>2026-02-13T11:15:29+01:00</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Beverwijk, NL, Netherlands</t>
+          <t>Veenendaal, NL, Netherlands</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026-03-06T13:44:26+00:00</t>
+          <t>2026-03-06T01:44:16+00:00</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>05222006538860</t>
+          <t>05222069732758</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -12453,7 +12461,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>05222006538833</t>
+          <t>05222006538846</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12473,7 +12481,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>6001678501</t>
+          <t>6001678746</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -12485,22 +12493,22 @@
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-03-05T13:40:25+01:00</t>
+          <t>2026-03-05T15:35:36+01:00</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>Etten-Leur, NL, Netherlands</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:16+00:00</t>
+          <t>2026-03-06T16:44:56+00:00</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>05222006538833</t>
+          <t>05222006538846</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -12512,7 +12520,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>05222006538822</t>
+          <t>05222006538860</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12532,7 +12540,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>6001678246</t>
+          <t>6001679075</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -12544,22 +12552,22 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-03-05T16:09:16+01:00</t>
+          <t>2026-03-05T13:55:37+01:00</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Rijssen, NL, Netherlands</t>
+          <t>Beverwijk, NL, Netherlands</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-03-06T13:44:28+00:00</t>
+          <t>2026-03-06T13:44:26+00:00</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>05222006538822</t>
+          <t>05222006538860</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -12571,7 +12579,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>05222006538797</t>
+          <t>05222069732759</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12591,7 +12599,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>6001676888</t>
+          <t>6001679852</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -12603,22 +12611,22 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-03-06T09:46:27+01:00</t>
+          <t>2026-02-13T11:15:29+01:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Veenendaal, NL, Netherlands</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-03-06T10:48:17+00:00</t>
+          <t>2026-03-06T01:44:17+00:00</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>05222006538797</t>
+          <t>05222069732759</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -12630,7 +12638,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>05222069732759</t>
+          <t>05222006538833</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12650,7 +12658,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>6001679852</t>
+          <t>6001678501</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -12662,7 +12670,7 @@
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-02-13T11:15:29+01:00</t>
+          <t>2026-03-05T13:40:25+01:00</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12672,12 +12680,12 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:17+00:00</t>
+          <t>2026-03-06T01:44:16+00:00</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>05222069732759</t>
+          <t>05222006538833</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -12689,7 +12697,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>05222006538859</t>
+          <t>05222069778589</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12709,7 +12717,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>6001679057</t>
+          <t>6001679888</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -12721,22 +12729,22 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-03-05T16:54:18+01:00</t>
+          <t>2026-03-04T17:48:49+01:00</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Berkel en Rodenrijs, NL, Netherlands</t>
+          <t>Rijssen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-03-06T13:44:28+00:00</t>
+          <t>2026-03-06T13:44:27+00:00</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>05222006538859</t>
+          <t>05222069778589</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -12748,7 +12756,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>05222006538803</t>
+          <t>05222006538859</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12768,7 +12776,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>6001677237</t>
+          <t>6001679057</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -12780,22 +12788,22 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-03-06T11:34:03+01:00</t>
+          <t>2026-03-05T16:54:18+01:00</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Berkel en Rodenrijs, NL, Netherlands</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-03-06T10:48:14+00:00</t>
+          <t>2026-03-06T13:44:28+00:00</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>05222006538803</t>
+          <t>05222006538859</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -12807,7 +12815,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>05222069732758</t>
+          <t>05222006538814</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12827,7 +12835,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>6001679852</t>
+          <t>6001678060</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -12839,22 +12847,22 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-02-13T11:15:29+01:00</t>
+          <t>2026-03-06T18:28:00+01:00</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>Segeltorp, SE, Sweden</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:16+00:00</t>
+          <t>2026-03-06T19:48:49+00:00</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>05222069732758</t>
+          <t>05222006538814</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -1494,7 +1494,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05228742857143</t>
+          <t>05228742857200</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1530,7 +1530,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-06T12:43:14+01:00</t>
+          <t>2026-03-06T12:41:39+01:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-03-06T13:40:27+00:00</t>
+          <t>2026-03-06T13:40:39+00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>05228742857143</t>
+          <t>05228742857200</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05228742857200</t>
+          <t>05228742857143</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1593,7 +1593,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-06T12:41:39+01:00</t>
+          <t>2026-03-06T12:43:14+01:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-06T13:40:39+00:00</t>
+          <t>2026-03-06T13:40:27+00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>05228742857200</t>
+          <t>05228742857143</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01475240802746</t>
+          <t>01475240801614</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0049010275899</t>
+          <t>302-3422488-6889965</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1782,34 +1782,34 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-03-06T13:47:08+01:00</t>
+          <t>2026-03-06T13:22:38+01:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Mannheim (DE), Germany</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:49+00:00</t>
+          <t>2026-03-06T13:38:48+00:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>01475240802746</t>
+          <t>01475240801614</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275899", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "302-3422488-6889965", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01475240802747</t>
+          <t>01475240803436</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:47+00:00</t>
+          <t>2026-03-06T13:38:48+00:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>01475240802747</t>
+          <t>01475240803436</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1872,7 +1872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01475240801614</t>
+          <t>01475240802747</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>302-3422488-6889965</t>
+          <t>0049010275899</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1908,34 +1908,34 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-03-06T13:22:38+01:00</t>
+          <t>2026-03-06T13:47:08+01:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Mannheim (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:48+00:00</t>
+          <t>2026-03-06T13:38:47+00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>01475240801614</t>
+          <t>01475240802747</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>{"external_order_id": "302-3422488-6889965", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "0049010275899", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01475240803436</t>
+          <t>01475240802746</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:48+00:00</t>
+          <t>2026-03-06T13:38:49+00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>01475240803436</t>
+          <t>01475240802746</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>01475240800294</t>
+          <t>01475240800295</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:37+00:00</t>
+          <t>2026-03-06T13:38:36+00:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>01475240800294</t>
+          <t>01475240800295</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>01475240800295</t>
+          <t>01475240800293</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>01475240800295</t>
+          <t>01475240800293</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2250,7 +2250,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>01475240800293</t>
+          <t>01475240800294</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-03-06T13:38:36+00:00</t>
+          <t>2026-03-06T13:38:37+00:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>01475240800293</t>
+          <t>01475240800294</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06086432957836</t>
+          <t>06086432957837</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2790,7 +2790,7 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-06T14:47:42+01:00</t>
+          <t>2026-03-06T14:47:17+01:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-03-06T15:31:00+00:00</t>
+          <t>2026-03-07T04:31:39+00:00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>06086432957836</t>
+          <t>06086432957837</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2817,7 +2817,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06086432957837</t>
+          <t>06086432957836</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2853,7 +2853,7 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-06T14:47:17+01:00</t>
+          <t>2026-03-06T14:47:42+01:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-06T15:31:00+00:00</t>
+          <t>2026-03-07T03:31:38+00:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>06086432957837</t>
+          <t>06086432957836</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-03-06T15:31:00+00:00</t>
+          <t>2026-03-07T04:31:39+00:00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UTV728589289</t>
+          <t>UTV442010395</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3357,7 +3357,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-06T14:35:08+01:00</t>
+          <t>2026-03-06T14:35:34+01:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-06T14:36:59+00:00</t>
+          <t>2026-03-06T14:37:00+00:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>UTV728589289</t>
+          <t>UTV442010395</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3384,7 +3384,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UTV442010395</t>
+          <t>UTV728589289</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-06T14:35:34+01:00</t>
+          <t>2026-03-06T14:35:08+01:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-03-06T14:37:00+00:00</t>
+          <t>2026-03-06T14:36:59+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>UTV442010395</t>
+          <t>UTV728589289</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>01475240801282</t>
+          <t>01475240801922</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0049010269409</t>
+          <t>B2BDS11558406</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3672,34 +3672,34 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-06T11:46:00+01:00</t>
+          <t>2026-03-06T09:31:54+01:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Essen (DE), Germany</t>
+          <t>Wuppertal (DE), Germany</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-03-06T11:00:49+00:00</t>
+          <t>2026-03-06T09:00:49+00:00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>01475240801282</t>
+          <t>01475240801922</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010269409", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11558406", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01475240801922</t>
+          <t>01475240801282</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>B2BDS11558406</t>
+          <t>0049010269409</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3735,34 +3735,34 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-06T09:31:54+01:00</t>
+          <t>2026-03-06T11:46:00+01:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Wuppertal (DE), Germany</t>
+          <t>Essen (DE), Germany</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-06T09:00:49+00:00</t>
+          <t>2026-03-06T11:00:49+00:00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>01475240801922</t>
+          <t>01475240801282</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11558406", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010269409", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01475240801743</t>
+          <t>01475240803152</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0049010273679</t>
+          <t>1024941722-A</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3798,12 +3798,12 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-06T13:52:42+01:00</t>
+          <t>2026-03-06T13:19:04+01:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Malsch (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3813,19 +3813,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>01475240801743</t>
+          <t>01475240803152</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010273679", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "1024941722-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>01475240801771</t>
+          <t>01475240801418</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0049010275957</t>
+          <t>B2BDS11558406</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3861,34 +3861,34 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-03-06T13:07:12+01:00</t>
+          <t>2026-03-06T09:31:54+01:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Wuppertal (DE), Germany</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-03-06T13:00:52+00:00</t>
+          <t>2026-03-06T09:00:47+00:00</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>01475240801771</t>
+          <t>01475240801418</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275957", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11558406", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>01475240803152</t>
+          <t>01475240801771</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1024941722-A</t>
+          <t>0049010275957</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3924,34 +3924,34 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-06T13:19:04+01:00</t>
+          <t>2026-03-06T13:07:12+01:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-03-06T13:00:50+00:00</t>
+          <t>2026-03-06T13:00:52+00:00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>01475240803152</t>
+          <t>01475240801771</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024941722-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0049010275957", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01475240801418</t>
+          <t>01475240801743</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B2BDS11558406</t>
+          <t>0049010273679</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3987,27 +3987,27 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-03-06T09:31:54+01:00</t>
+          <t>2026-03-06T13:52:42+01:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Wuppertal (DE), Germany</t>
+          <t>Malsch (DE), Germany</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-03-06T09:00:47+00:00</t>
+          <t>2026-03-06T13:00:50+00:00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>01475240801418</t>
+          <t>01475240801743</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11558406", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010273679", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>01475240801471</t>
+          <t>01475240802618</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MPSEGD5</t>
+          <t>0049010276102</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4113,34 +4113,34 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-03-06T12:41:00+01:00</t>
+          <t>2026-03-06T11:41:28+01:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Aschaffenburg (DE), Germany</t>
+          <t>Obing (DE), Germany</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-03-06T12:00:47+00:00</t>
+          <t>2026-03-06T11:00:47+00:00</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>01475240801471</t>
+          <t>01475240802618</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>{"external_order_id": "MPSEGD5", "sales_office_id": "4286"}</t>
+          <t>{"external_order_id": "0049010276102", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>01475240802618</t>
+          <t>01475240801471</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0049010276102</t>
+          <t>MPSEGD5</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4176,34 +4176,34 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-03-06T11:41:28+01:00</t>
+          <t>2026-03-06T12:41:00+01:00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Obing (DE), Germany</t>
+          <t>Aschaffenburg (DE), Germany</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-03-06T11:00:47+00:00</t>
+          <t>2026-03-06T12:00:47+00:00</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>01475240802618</t>
+          <t>01475240801471</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276102", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "MPSEGD5", "sales_office_id": "4286"}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>01475240799676</t>
+          <t>01475240801533</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0049010265731</t>
+          <t>0049010276139</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4239,27 +4239,27 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-06T14:34:33+01:00</t>
+          <t>2026-03-06T13:16:36+01:00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Kesselsdorf (DE), Germany</t>
+          <t>Hamm (DE), Germany</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-03-06T14:00:47+00:00</t>
+          <t>2026-03-06T13:00:50+00:00</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>01475240799676</t>
+          <t>01475240801533</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010265731", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010276139", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>01475240801533</t>
+          <t>01475240799676</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0049010276139</t>
+          <t>0049010265731</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4365,27 +4365,27 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-03-06T13:16:36+01:00</t>
+          <t>2026-03-06T14:34:33+01:00</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Hamm (DE), Germany</t>
+          <t>Kesselsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-06T13:00:50+00:00</t>
+          <t>2026-03-06T14:00:47+00:00</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>01475240801533</t>
+          <t>01475240799676</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276139", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010265731", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>01475240801497</t>
+          <t>01475240803010</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0049010276139</t>
+          <t>0049010276463</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4491,7 +4491,7 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-06T13:16:36+01:00</t>
+          <t>2026-03-06T10:07:49+01:00</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4501,24 +4501,24 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-03-06T13:00:46+00:00</t>
+          <t>2026-03-06T10:00:42+00:00</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>01475240801497</t>
+          <t>01475240803010</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276139", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010276463", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>01475240803010</t>
+          <t>01475240801497</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0049010276463</t>
+          <t>0049010276139</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4554,7 +4554,7 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-03-06T10:07:49+01:00</t>
+          <t>2026-03-06T13:16:36+01:00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-03-06T10:00:42+00:00</t>
+          <t>2026-03-06T13:00:46+00:00</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>01475240803010</t>
+          <t>01475240801497</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276463", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010276139", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>01475240798966</t>
+          <t>01475240803100</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FR7ATKC</t>
+          <t>B2BDS11565258</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4680,34 +4680,34 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-06T10:12:01+01:00</t>
+          <t>2026-03-06T10:28:43+01:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Lübbenau/Spreewald (DE), Germany</t>
+          <t>Gudensberg (DE), Germany</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:58+00:00</t>
+          <t>2026-03-06T10:14:56+00:00</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>01475240798966</t>
+          <t>01475240803100</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>{"external_order_id": "FR7ATKC", "sales_office_id": "4326"}</t>
+          <t>{"external_order_id": "B2BDS11565258", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>01475240803100</t>
+          <t>01475240798966</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>B2BDS11565258</t>
+          <t>FR7ATKC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4743,27 +4743,27 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-06T10:28:43+01:00</t>
+          <t>2026-03-06T10:12:01+01:00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Gudensberg (DE), Germany</t>
+          <t>Lübbenau/Spreewald (DE), Germany</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:56+00:00</t>
+          <t>2026-03-06T10:14:58+00:00</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>01475240803100</t>
+          <t>01475240798966</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11565258", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "FR7ATKC", "sales_office_id": "4326"}</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>01475240802688</t>
+          <t>01475240802447</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>B2BDS11572044</t>
+          <t>0049010275462</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5499,27 +5499,27 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:02+01:00</t>
+          <t>2026-03-06T10:02:07+01:00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Marl (DE), Germany</t>
+          <t>Melle (DE), Germany</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:38+00:00</t>
+          <t>2026-03-06T09:14:34+00:00</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>01475240802688</t>
+          <t>01475240802447</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010275462", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5589,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>01475240802447</t>
+          <t>01475240802688</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0049010275462</t>
+          <t>B2BDS11572044</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5625,27 +5625,27 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-06T10:02:07+01:00</t>
+          <t>2026-03-06T10:44:02+01:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Melle (DE), Germany</t>
+          <t>Marl (DE), Germany</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:34+00:00</t>
+          <t>2026-03-06T10:14:38+00:00</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>01475240802447</t>
+          <t>01475240802688</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275462", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>01475240802278</t>
+          <t>01475240801976</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>B2BDS11572044</t>
+          <t>0049010271798</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5751,27 +5751,27 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:02+01:00</t>
+          <t>2026-03-06T11:40:51+01:00</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Marl (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:31+00:00</t>
+          <t>2026-03-06T12:14:31+00:00</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>01475240802278</t>
+          <t>01475240801976</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010271798", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>01475240801976</t>
+          <t>01475240802279</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0049010271798</t>
+          <t>B2BDS11572044</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5877,34 +5877,34 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-03-06T11:40:51+01:00</t>
+          <t>2026-03-06T10:44:02+01:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Marl (DE), Germany</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:31+00:00</t>
+          <t>2026-03-06T10:14:34+00:00</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>01475240801976</t>
+          <t>01475240802279</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271798", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>01475240802279</t>
+          <t>01475240802278</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:34+00:00</t>
+          <t>2026-03-06T10:14:31+00:00</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>01475240802279</t>
+          <t>01475240802278</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>01475240801457</t>
+          <t>01475240802254</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0049010275056</t>
+          <t>B2BDS11552798</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6003,34 +6003,34 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-03-06T11:13:46+01:00</t>
+          <t>2026-03-06T10:54:49+01:00</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>Altentreptow (DE), Germany</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:30+00:00</t>
+          <t>2026-03-06T10:19:51+00:00</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>01475240801457</t>
+          <t>01475240802254</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275056", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11552798", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>01475240802597</t>
+          <t>01475240801457</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>B2BDS11572044</t>
+          <t>0049010275056</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6066,34 +6066,34 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:02+01:00</t>
+          <t>2026-03-06T11:13:46+01:00</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Marl (DE), Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:28+00:00</t>
+          <t>2026-03-06T10:44:30+00:00</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>01475240802597</t>
+          <t>01475240801457</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010275056", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>01475240802254</t>
+          <t>01475240802597</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>B2BDS11552798</t>
+          <t>B2BDS11572044</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6129,34 +6129,34 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-03-06T10:54:49+01:00</t>
+          <t>2026-03-06T10:44:02+01:00</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Altentreptow (DE), Germany</t>
+          <t>Marl (DE), Germany</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-03-06T10:19:51+00:00</t>
+          <t>2026-03-06T10:14:28+00:00</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>01475240802254</t>
+          <t>01475240802597</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11552798", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11572044", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>01475240801290</t>
+          <t>01475240801287</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0049010275056</t>
+          <t>B2BDS11570004</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6192,34 +6192,34 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-06T11:13:46+01:00</t>
+          <t>2026-03-06T14:22:35+01:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>Marl (DE), Germany</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:27+00:00</t>
+          <t>2026-03-06T14:14:33+00:00</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>01475240801290</t>
+          <t>01475240801287</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275056", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11570004", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>01475240801287</t>
+          <t>01475240801290</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>B2BDS11570004</t>
+          <t>0049010275056</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6255,27 +6255,27 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-03-06T14:22:35+01:00</t>
+          <t>2026-03-06T11:13:46+01:00</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Marl (DE), Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:33+00:00</t>
+          <t>2026-03-06T11:14:27+00:00</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>01475240801287</t>
+          <t>01475240801290</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11570004", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010275056", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>01475240801566</t>
+          <t>01475240802714</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1024939145-D</t>
+          <t>B2BDS11552798</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6507,34 +6507,34 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-03-06T16:02:43+01:00</t>
+          <t>2026-03-06T10:54:49+01:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Staufenberg-Mainzlar (DE), Germany</t>
+          <t>Altentreptow (DE), Germany</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-03-06T15:44:34+00:00</t>
+          <t>2026-03-06T10:14:25+00:00</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>01475240801566</t>
+          <t>01475240802714</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024939145-D", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "B2BDS11552798", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>01475240802714</t>
+          <t>01475240801566</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>B2BDS11552798</t>
+          <t>1024939145-D</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6570,27 +6570,27 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-03-06T10:54:49+01:00</t>
+          <t>2026-03-06T16:02:43+01:00</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Altentreptow (DE), Germany</t>
+          <t>Staufenberg-Mainzlar (DE), Germany</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:25+00:00</t>
+          <t>2026-03-06T15:44:34+00:00</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>01475240802714</t>
+          <t>01475240801566</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11552798", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "1024939145-D", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>01475240801854</t>
+          <t>01475240800043</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0049010271706</t>
+          <t>0049010271156</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7011,34 +7011,34 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-03-06T11:50:32+01:00</t>
+          <t>2026-03-06T10:44:11+01:00</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Neuhof-Dorfborn (DE), Germany</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:26+00:00</t>
+          <t>2026-03-06T11:14:25+00:00</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>01475240801854</t>
+          <t>01475240800043</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271706", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010271156", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>01475240800043</t>
+          <t>01475240803541</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0049010271156</t>
+          <t>1024946909-A</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7074,34 +7074,34 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:11+01:00</t>
+          <t>2026-03-06T10:45:28+01:00</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Neuhof-Dorfborn (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:25+00:00</t>
+          <t>2026-03-06T10:14:26+00:00</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>01475240800043</t>
+          <t>01475240803541</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271156", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "1024946909-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>01475240803541</t>
+          <t>01475240801854</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1024946909-A</t>
+          <t>0049010271706</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7137,34 +7137,34 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-06T10:45:28+01:00</t>
+          <t>2026-03-06T11:50:32+01:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:26+00:00</t>
+          <t>2026-03-06T13:14:26+00:00</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>01475240803541</t>
+          <t>01475240801854</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024946909-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "0049010271706", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>01475240802170</t>
+          <t>01475240802694</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0049010275668</t>
+          <t>MCPPKD5</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7200,7 +7200,7 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-06T12:38:58+01:00</t>
+          <t>2026-03-06T14:30:44+01:00</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7210,17 +7210,17 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:24+00:00</t>
+          <t>2026-03-06T14:14:27+00:00</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>01475240802170</t>
+          <t>01475240802694</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275668", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "MCPPKD5", "sales_office_id": "4286"}</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7290,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>01475240802694</t>
+          <t>01475240802170</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MCPPKD5</t>
+          <t>0049010275668</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -7326,7 +7326,7 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-03-06T14:30:44+01:00</t>
+          <t>2026-03-06T12:38:58+01:00</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7336,17 +7336,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:27+00:00</t>
+          <t>2026-03-06T12:14:24+00:00</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>01475240802694</t>
+          <t>01475240802170</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>{"external_order_id": "MCPPKD5", "sales_office_id": "4286"}</t>
+          <t>{"external_order_id": "0049010275668", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>01475240802171</t>
+          <t>01475240802088</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0049010275668</t>
+          <t>0049010271450</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7452,34 +7452,34 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-06T12:38:58+01:00</t>
+          <t>2026-03-06T14:52:22+01:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Neuhof-Dorfborn (DE), Germany</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:29+00:00</t>
+          <t>2026-03-06T14:14:25+00:00</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>01475240802171</t>
+          <t>01475240802088</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275668", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010271450", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>01475240802088</t>
+          <t>01475240802171</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0049010271450</t>
+          <t>0049010275668</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7515,34 +7515,34 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-03-06T14:52:22+01:00</t>
+          <t>2026-03-06T12:38:58+01:00</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Neuhof-Dorfborn (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:25+00:00</t>
+          <t>2026-03-06T12:14:29+00:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>01475240802088</t>
+          <t>01475240802171</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271450", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010275668", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>01475240803697</t>
+          <t>01475240802074</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0049010274335</t>
+          <t>0049010271450</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7578,34 +7578,34 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-06T10:19:41+01:00</t>
+          <t>2026-03-06T14:52:22+01:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Neuhof-Dorfborn (DE), Germany</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:21+00:00</t>
+          <t>2026-03-06T14:14:24+00:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>01475240803697</t>
+          <t>01475240802074</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274335", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010271450", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>01475240799822</t>
+          <t>01475240801642</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0049010271004</t>
+          <t>0049010270235</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7641,34 +7641,34 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-03-06T14:19:51+01:00</t>
+          <t>2026-03-06T09:34:06+01:00</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Aschaffenburg (DE), Germany</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:27+00:00</t>
+          <t>2026-03-06T09:14:20+00:00</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>01475240799822</t>
+          <t>01475240801642</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271004", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010270235", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>01475240801642</t>
+          <t>01475240799822</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0049010270235</t>
+          <t>0049010271004</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7704,34 +7704,34 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-03-06T09:34:06+01:00</t>
+          <t>2026-03-06T14:19:51+01:00</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Aschaffenburg (DE), Germany</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:20+00:00</t>
+          <t>2026-03-06T14:14:27+00:00</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>01475240801642</t>
+          <t>01475240799822</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010270235", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010271004", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>01475240802074</t>
+          <t>01475240803697</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0049010271450</t>
+          <t>0049010274335</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7767,34 +7767,34 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-03-06T14:52:22+01:00</t>
+          <t>2026-03-06T10:19:41+01:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Neuhof-Dorfborn (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:24+00:00</t>
+          <t>2026-03-06T11:14:21+00:00</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>01475240802074</t>
+          <t>01475240803697</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271450", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010274335", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>01475240800214</t>
+          <t>01475240802270</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>305-9272397-9608321</t>
+          <t>B2BDS11561959</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7830,34 +7830,34 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-03-06T11:33:48+01:00</t>
+          <t>2026-03-06T08:34:02+01:00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Ludwigsburg (DE), Germany</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:25+00:00</t>
+          <t>2026-03-06T08:14:19+00:00</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>01475240800214</t>
+          <t>01475240802270</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>{"external_order_id": "305-9272397-9608321", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "B2BDS11561959", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>01475240800215</t>
+          <t>01475240800214</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:21+00:00</t>
+          <t>2026-03-06T11:14:25+00:00</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>01475240800215</t>
+          <t>01475240800214</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -7920,7 +7920,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>01475240802270</t>
+          <t>01475240800215</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>B2BDS11561959</t>
+          <t>305-9272397-9608321</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7956,34 +7956,34 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-03-06T08:34:02+01:00</t>
+          <t>2026-03-06T11:33:48+01:00</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Ludwigsburg (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-03-06T08:14:19+00:00</t>
+          <t>2026-03-06T11:14:21+00:00</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>01475240802270</t>
+          <t>01475240800215</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11561959", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "305-9272397-9608321", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>01475240801430</t>
+          <t>01475240802916</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>B2BDS11550954</t>
+          <t>1024942385-A</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8019,34 +8019,34 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-06T11:00:16+01:00</t>
+          <t>2026-03-06T10:40:07+01:00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Wuppertal (DE), Germany</t>
+          <t>Heilbronn (DE), Germany</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:20+00:00</t>
+          <t>2026-03-06T11:14:19+00:00</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>01475240801430</t>
+          <t>01475240802916</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11550954", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "1024942385-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>01475240802916</t>
+          <t>01475240801430</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1024942385-A</t>
+          <t>B2BDS11550954</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -8082,34 +8082,34 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-03-06T10:40:07+01:00</t>
+          <t>2026-03-06T11:00:16+01:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Heilbronn (DE), Germany</t>
+          <t>Wuppertal (DE), Germany</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:19+00:00</t>
+          <t>2026-03-06T10:44:20+00:00</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>01475240802916</t>
+          <t>01475240801430</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024942385-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "B2BDS11550954", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>01475240801934</t>
+          <t>01475240801104</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1024942385-A</t>
+          <t>B2BDS11563163</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8145,34 +8145,34 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-03-06T10:40:07+01:00</t>
+          <t>2026-03-06T13:36:34+01:00</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Heilbronn (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:16+00:00</t>
+          <t>2026-03-06T13:44:25+00:00</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>01475240801934</t>
+          <t>01475240801104</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024942385-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "B2BDS11563163", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>01475240801104</t>
+          <t>01475240801934</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>B2BDS11563163</t>
+          <t>1024942385-A</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -8208,34 +8208,34 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-03-06T13:36:34+01:00</t>
+          <t>2026-03-06T10:40:07+01:00</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Heilbronn (DE), Germany</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-03-06T13:44:25+00:00</t>
+          <t>2026-03-06T10:14:16+00:00</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>01475240801104</t>
+          <t>01475240801934</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11563163", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "1024942385-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>01475240800442</t>
+          <t>01475240802166</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>cbn4wmb36y</t>
+          <t>B2BDS11563858</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8271,34 +8271,34 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-03-06T13:35:17+01:00</t>
+          <t>2026-03-06T12:07:48+01:00</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Hagen (DE), Germany</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-03-06T12:44:26+00:00</t>
+          <t>2026-03-06T12:14:20+00:00</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>01475240800442</t>
+          <t>01475240802166</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "B2BDS11563858", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>01475240802166</t>
+          <t>01475240801768</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>B2BDS11563858</t>
+          <t>27-14293-38348</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8334,34 +8334,34 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-03-06T12:07:48+01:00</t>
+          <t>2026-03-06T10:14:06+01:00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Hagen (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:20+00:00</t>
+          <t>2026-03-06T10:14:15+00:00</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>01475240802166</t>
+          <t>01475240801768</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11563858", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "27-14293-38348", "sales_office_id": "4389"}</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>01475240801768</t>
+          <t>01475240800442</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>27-14293-38348</t>
+          <t>cbn4wmb36y</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -8397,34 +8397,34 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:06+01:00</t>
+          <t>2026-03-06T13:35:17+01:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:15+00:00</t>
+          <t>2026-03-06T12:44:26+00:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>01475240801768</t>
+          <t>01475240800442</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>{"external_order_id": "27-14293-38348", "sales_office_id": "4389"}</t>
+          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>01475240801103</t>
+          <t>01475240799764</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>B2BDS11563163</t>
+          <t>0049010267065</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -8460,34 +8460,34 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-03-06T13:36:34+01:00</t>
+          <t>2026-03-06T13:47:00+01:00</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Melsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:31+00:00</t>
+          <t>2026-03-06T13:14:20+00:00</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>01475240801103</t>
+          <t>01475240799764</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11563163", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010267065", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>01475240801102</t>
+          <t>01475240801103</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-03-06T12:44:19+00:00</t>
+          <t>2026-03-06T13:14:31+00:00</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>01475240801102</t>
+          <t>01475240801103</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -8550,7 +8550,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>01475240800759</t>
+          <t>01475240801102</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>cbn4wmb36y</t>
+          <t>B2BDS11563163</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8586,34 +8586,34 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-03-06T13:35:17+01:00</t>
+          <t>2026-03-06T13:36:34+01:00</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:22+00:00</t>
+          <t>2026-03-06T12:44:19+00:00</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>01475240800759</t>
+          <t>01475240801102</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "B2BDS11563163", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>01475240799764</t>
+          <t>01475240800759</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0049010267065</t>
+          <t>cbn4wmb36y</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8649,34 +8649,34 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-06T13:47:00+01:00</t>
+          <t>2026-03-06T13:35:17+01:00</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Melsdorf (DE), Germany</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:20+00:00</t>
+          <t>2026-03-06T13:14:22+00:00</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>01475240799764</t>
+          <t>01475240800759</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010267065", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>01475240802479</t>
+          <t>01475240801473</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>303-3833262-5777904</t>
+          <t>B2BDS11543346</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8712,7 +8712,7 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-03-06T14:08:03+01:00</t>
+          <t>2026-03-06T09:53:10+01:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:35+00:00</t>
+          <t>2026-03-06T10:14:15+00:00</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>01475240802479</t>
+          <t>01475240801473</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>{"external_order_id": "303-3833262-5777904", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "B2BDS11543346", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>01475240801678</t>
+          <t>01475240802479</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0049010276115</t>
+          <t>303-3833262-5777904</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8775,34 +8775,34 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-03-06T08:33:47+01:00</t>
+          <t>2026-03-06T14:08:03+01:00</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-03-06T08:14:13+00:00</t>
+          <t>2026-03-06T14:14:35+00:00</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>01475240801678</t>
+          <t>01475240802479</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276115", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "303-3833262-5777904", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>01475240800410</t>
+          <t>01475240801678</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>cbn4wmb36y</t>
+          <t>0049010276115</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8838,34 +8838,34 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-03-06T13:35:17+01:00</t>
+          <t>2026-03-06T08:33:47+01:00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-03-06T15:14:18+00:00</t>
+          <t>2026-03-06T08:14:13+00:00</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>01475240800410</t>
+          <t>01475240801678</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0049010276115", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>01475240801473</t>
+          <t>01475240800410</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>B2BDS11543346</t>
+          <t>cbn4wmb36y</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8901,34 +8901,34 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-03-06T09:53:10+01:00</t>
+          <t>2026-03-06T13:35:17+01:00</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:15+00:00</t>
+          <t>2026-03-06T15:14:18+00:00</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>01475240801473</t>
+          <t>01475240800410</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11543346", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "cbn4wmb36y", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>01475240801433</t>
+          <t>01475240799765</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>B2BDS11564552</t>
+          <t>0049010267065</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8964,27 +8964,27 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-06T09:10:30+01:00</t>
+          <t>2026-03-06T13:47:00+01:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Melsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:18+00:00</t>
+          <t>2026-03-06T13:14:18+00:00</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>01475240801433</t>
+          <t>01475240799765</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11564552", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010267065", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>01475240799765</t>
+          <t>01475240801433</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0049010267065</t>
+          <t>B2BDS11564552</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -9153,34 +9153,34 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-03-06T13:47:00+01:00</t>
+          <t>2026-03-06T09:10:30+01:00</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Melsdorf (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:18+00:00</t>
+          <t>2026-03-06T09:14:18+00:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>01475240799765</t>
+          <t>01475240801433</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010267065", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11564552", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>01475240798118</t>
+          <t>01475240802713</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0049010267065</t>
+          <t>0049010275891</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9216,34 +9216,34 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-06T13:47:00+01:00</t>
+          <t>2026-03-06T13:43:18+01:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Melsdorf (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-03-06T13:14:16+00:00</t>
+          <t>2026-03-06T14:14:25+00:00</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>01475240798118</t>
+          <t>01475240802713</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010267065", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010275891", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>01475240802713</t>
+          <t>01475240798118</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>0049010275891</t>
+          <t>0049010267065</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9279,27 +9279,27 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-06T13:43:18+01:00</t>
+          <t>2026-03-06T13:47:00+01:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Melsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-03-06T14:14:25+00:00</t>
+          <t>2026-03-06T13:14:16+00:00</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>01475240802713</t>
+          <t>01475240798118</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010275891", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010267065", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>01475240801119</t>
+          <t>01475240803419</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>0049010274049</t>
+          <t>0049010278629</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -9405,34 +9405,34 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-03-06T12:49:58+01:00</t>
+          <t>2026-03-06T10:11:50+01:00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Koblenz (DE), Germany</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:15+00:00</t>
+          <t>2026-03-06T10:14:11+00:00</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>01475240801119</t>
+          <t>01475240803419</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274049", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010278629", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>01475240803419</t>
+          <t>01475240801119</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>0049010278629</t>
+          <t>0049010274049</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9468,27 +9468,27 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-03-06T10:11:50+01:00</t>
+          <t>2026-03-06T12:49:58+01:00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Koblenz (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-03-06T10:14:11+00:00</t>
+          <t>2026-03-06T12:14:15+00:00</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>01475240803419</t>
+          <t>01475240801119</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010278629", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010274049", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>01475240802586</t>
+          <t>01475240801186</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0049010274446</t>
+          <t>0049010272958</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9846,34 +9846,34 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-03-06T09:35:58+01:00</t>
+          <t>2026-03-06T16:05:36+01:00</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Erftstadt-Lechenich (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:06+00:00</t>
+          <t>2026-03-06T15:44:11+00:00</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>01475240802586</t>
+          <t>01475240801186</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010274446", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010272958", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>01475240801186</t>
+          <t>01475240802586</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0049010272958</t>
+          <t>0049010274446</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9909,34 +9909,34 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-03-06T16:05:36+01:00</t>
+          <t>2026-03-06T09:35:58+01:00</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Erftstadt-Lechenich (DE), Germany</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-03-06T15:44:11+00:00</t>
+          <t>2026-03-06T09:14:06+00:00</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>01475240801186</t>
+          <t>01475240802586</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272958", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010274446", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>01475240802870</t>
+          <t>01475240801046</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PO-076-19546873674873714</t>
+          <t>0049010272609</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9972,34 +9972,34 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-03-06T10:44:12+01:00</t>
+          <t>2026-03-06T11:22:44+01:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Mannheim (DE), Germany</t>
+          <t>Lüneburg (DE), Germany</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-03-06T11:44:06+00:00</t>
+          <t>2026-03-06T12:14:12+00:00</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>01475240802870</t>
+          <t>01475240801046</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-076-19546873674873714", "sales_office_id": "4670"}</t>
+          <t>{"external_order_id": "0049010272609", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>01475240801046</t>
+          <t>01475240802870</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0049010272609</t>
+          <t>PO-076-19546873674873714</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -10035,27 +10035,27 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-03-06T11:22:44+01:00</t>
+          <t>2026-03-06T10:44:12+01:00</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Lüneburg (DE), Germany</t>
+          <t>Mannheim (DE), Germany</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:12+00:00</t>
+          <t>2026-03-06T11:44:06+00:00</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>01475240801046</t>
+          <t>01475240802870</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272609", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "PO-076-19546873674873714", "sales_office_id": "4670"}</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10314,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>01475240801168</t>
+          <t>01475240803333</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>B2BDS11411147</t>
+          <t>cbn4wmhhxm</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -10350,34 +10350,34 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-03-06T10:13:02+01:00</t>
+          <t>2026-03-06T12:43:19+01:00</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Duisburg (DE), Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-03-06T09:44:03+00:00</t>
+          <t>2026-03-06T12:14:02+00:00</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>01475240801168</t>
+          <t>01475240803333</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11411147", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "cbn4wmhhxm", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>01475240802625</t>
+          <t>01475240801168</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10397,12 +10397,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>0049010276252</t>
+          <t>B2BDS11411147</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -10413,34 +10413,34 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-06T11:33:48+01:00</t>
+          <t>2026-03-06T10:13:02+01:00</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Holzgünz (DE), Germany</t>
+          <t>Duisburg (DE), Germany</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:04+00:00</t>
+          <t>2026-03-06T09:44:03+00:00</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>01475240802625</t>
+          <t>01475240801168</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010276252", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2BDS11411147", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>01475240803333</t>
+          <t>01475240802625</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>cbn4wmhhxm</t>
+          <t>0049010276252</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -10476,27 +10476,27 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-03-06T12:43:19+01:00</t>
+          <t>2026-03-06T11:33:48+01:00</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>Holzgünz (DE), Germany</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:02+00:00</t>
+          <t>2026-03-06T11:14:04+00:00</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>01475240803333</t>
+          <t>01475240802625</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmhhxm", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0049010276252", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -10755,7 +10755,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>01475240802695</t>
+          <t>01475240802147</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>0049010271341</t>
+          <t>cbn4wmn8ws</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -10791,34 +10791,34 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-03-06T12:24:56+01:00</t>
+          <t>2026-03-06T11:45:31+01:00</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Duisburg (DE), Germany</t>
+          <t>Seddiner See (DE), Germany</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-03-06T12:14:01+00:00</t>
+          <t>2026-03-06T11:14:00+00:00</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>01475240802695</t>
+          <t>01475240802147</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010271341", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "cbn4wmn8ws", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>01475240802147</t>
+          <t>01475240802695</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>cbn4wmn8ws</t>
+          <t>0049010271341</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10854,27 +10854,27 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-06T11:45:31+01:00</t>
+          <t>2026-03-06T12:24:56+01:00</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Seddiner See (DE), Germany</t>
+          <t>Duisburg (DE), Germany</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-03-06T11:14:00+00:00</t>
+          <t>2026-03-06T12:14:01+00:00</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>01475240802147</t>
+          <t>01475240802695</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmn8ws", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0049010271341", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
@@ -10944,17 +10944,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>06086432955679</t>
+          <t>518157131962</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>dpd-ch-sftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DPD Switzerland</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>0041006367165</t>
+          <t>249-2193385-3826239</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0323</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10980,44 +10980,44 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-03-05T13:53:18+01:00</t>
+          <t>2026-03-07T12:27:00+09:00</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>,Switzerland</t>
+          <t>三多摩営業所, Japan</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-03-06T05:03:28+00:00</t>
+          <t>2026-03-07T04:04:00+00:00</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>06086432955679</t>
+          <t>518157131962</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0041006367165", "sales_office_id": "0323"}</t>
+          <t>{"external_order_id": "249-2193385-3826239", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1ZR096K99010489136</t>
+          <t>518157125205</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ups-api</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -11027,56 +11027,60 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>6001677201</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr"/>
+          <t>249-9361097-4916613</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-03-06T11:55:38-08:00</t>
+          <t>2026-03-07T10:41:00+09:00</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>REDLANDS, CA, 92374, US, United States</t>
+          <t>台東営業所, Japan</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-03-06T20:01:23+00:00</t>
+          <t>2026-03-07T02:03:47+00:00</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>1ZR096K99010489136</t>
+          <t>518157125205</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>{"courier": "UPS", "custom_1": "returns_ups"}</t>
+          <t>{"external_order_id": "249-9361097-4916613", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>JVGLOTC0109732872</t>
+          <t>518157125216</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -11086,52 +11090,60 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>6001679442</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr"/>
+          <t>249-9361097-4916613</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-03-05T13:25:25+01:00</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
+          <t>2026-03-07T10:41:00+09:00</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>台東営業所, Japan</t>
+        </is>
+      </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:29+00:00</t>
+          <t>2026-03-07T02:03:44+00:00</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>JVGLOTC0109732872</t>
+          <t>518157125216</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "249-9361097-4916613", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>JJD149990121180197968</t>
+          <t>06086432955679</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>dhlparcel-nl</t>
+          <t>dpd-ch-sftp</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DHL Parcel NL</t>
+          <t>DPD Switzerland</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -11141,52 +11153,60 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>6001677729</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr"/>
+          <t>0041006367165</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>0323</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-02-25T13:36:00+01:00</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr"/>
+          <t>2026-03-05T13:53:18+01:00</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>,Switzerland</t>
+        </is>
+      </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:30+00:00</t>
+          <t>2026-03-06T05:03:28+00:00</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>JJD149990121180197968</t>
+          <t>06086432955679</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"external_order_id": "0041006367165", "sales_office_id": "0323"}</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>REC000081138277</t>
+          <t>518157130982</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -11196,52 +11216,60 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>6001678531</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr"/>
+          <t>250-0198096-4911074</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-06T11:19:00</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
+          <t>2026-03-07T11:02:00+09:00</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>千葉南営業所, Japan</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-03-06T11:20:58+00:00</t>
+          <t>2026-03-07T02:33:50+00:00</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>REC000081138277</t>
+          <t>518157130982</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-0198096-4911074", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>REC000081128659</t>
+          <t>518157130971</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -11251,52 +11279,60 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>6001676814</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
+          <t>250-0198096-4911074</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-03-06T17:21:00</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr"/>
+          <t>2026-03-07T11:02:00+09:00</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>千葉南営業所, Japan</t>
+        </is>
+      </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-03-06T17:20:27+00:00</t>
+          <t>2026-03-07T02:33:42+00:00</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>REC000081128659</t>
+          <t>518157130971</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-0198096-4911074", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>REC000081130266</t>
+          <t>518157130960</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11306,52 +11342,60 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>6001677622</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr"/>
+          <t>250-0198096-4911074</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-03-06T10:53:00</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr"/>
+          <t>2026-03-07T11:02:00+09:00</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>千葉南営業所, Japan</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-03-06T12:19:58+00:00</t>
+          <t>2026-03-07T02:33:33+00:00</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>REC000081130266</t>
+          <t>518157130960</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-0198096-4911074", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>REC000081130037</t>
+          <t>518157132894</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11361,52 +11405,60 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>6001677571</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr"/>
+          <t>250-2703021-8828618</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-03-06T13:07:00</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr"/>
+          <t>2026-03-07T12:50:00+09:00</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>城西営業所, Japan</t>
+        </is>
+      </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-03-06T12:19:58+00:00</t>
+          <t>2026-03-07T04:20:15+00:00</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>REC000081130037</t>
+          <t>518157132894</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-2703021-8828618", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>996011434800779082</t>
+          <t>518157132931</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>swiss-post</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Swiss Post</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11416,56 +11468,60 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>6001676681</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr"/>
+          <t>B2BDS11592126</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-03-06T08:36:12+01:00</t>
+          <t>2026-03-07T10:16:00+09:00</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>CH, Switzerland</t>
+          <t>東松山営業所, Japan</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-03-06T09:14:42+00:00</t>
+          <t>2026-03-07T01:50:10+00:00</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>996011434800779082</t>
+          <t>518157132931</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>{"courier": "swiss-post"}</t>
+          <t>{"external_order_id": "B2BDS11592126", "sales_office_id": "4468"}</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>REC000081171766</t>
+          <t>518157133281</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11475,52 +11531,60 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>6001679761</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
+          <t>503-5829434-6046214</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-03-06T18:02:00</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr"/>
+          <t>2026-03-07T13:03:00+09:00</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>東京営業所, Japan</t>
+        </is>
+      </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-03-06T17:20:27+00:00</t>
+          <t>2026-03-07T04:20:13+00:00</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>REC000081171766</t>
+          <t>518157133281</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "503-5829434-6046214", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>REC000081128649</t>
+          <t>518157133056</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11530,52 +11594,60 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>6001676755</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr"/>
+          <t>250-9718461-0843855</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-03-06T16:02:00</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr"/>
+          <t>2026-03-07T11:33:00+09:00</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>伊賀営業所, Japan</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-03-06T15:18:44+00:00</t>
+          <t>2026-03-07T03:19:12+00:00</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>REC000081128649</t>
+          <t>518157133056</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-9718461-0843855", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>REC000081136256</t>
+          <t>518157133045</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11585,52 +11657,60 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>6001678322</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr"/>
+          <t>250-9718461-0843855</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-03-06T15:08:00</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr"/>
+          <t>2026-03-07T11:33:00+09:00</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>伊賀営業所, Japan</t>
+        </is>
+      </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-03-06T14:20:42+00:00</t>
+          <t>2026-03-07T03:19:08+00:00</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>REC000081136256</t>
+          <t>518157133045</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-9718461-0843855", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>REC000081163581</t>
+          <t>518157132835</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11640,52 +11720,60 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>6001679526</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
+          <t>250-7750128-6635051</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-03-06T13:29:00</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr"/>
+          <t>2026-03-07T09:30:00+09:00</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>羽生営業所, Japan</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-03-06T15:18:44+00:00</t>
+          <t>2026-03-07T00:47:56+00:00</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>REC000081163581</t>
+          <t>518157132835</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-7750128-6635051", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>REC000081138050</t>
+          <t>518157132846</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11695,52 +11783,60 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>6001678500</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
+          <t>250-7750128-6635051</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-03-06T11:24:00</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr"/>
+          <t>2026-03-07T09:30:00+09:00</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>羽生営業所, Japan</t>
+        </is>
+      </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-03-06T11:20:58+00:00</t>
+          <t>2026-03-07T00:47:58+00:00</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>REC000081138050</t>
+          <t>518157132846</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-7750128-6635051", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>REC000081135308</t>
+          <t>518157133292</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11750,52 +11846,60 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>6001678247</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr"/>
+          <t>B2BDS11592096</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-03-06T14:21:00</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr"/>
+          <t>2026-03-07T09:28:00+09:00</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>都留営業所, Japan</t>
+        </is>
+      </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-03-06T14:21:03+00:00</t>
+          <t>2026-03-07T00:47:59+00:00</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>REC000081135308</t>
+          <t>518157133292</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "B2BDS11592096", "sales_office_id": "4468"}</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>REC000081136278</t>
+          <t>518157132850</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11805,52 +11909,60 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>6001678319</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr"/>
+          <t>250-7750128-6635051</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-03-06T17:02:00</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr"/>
+          <t>2026-03-07T09:30:00+09:00</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>羽生営業所, Japan</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-03-06T16:19:04+00:00</t>
+          <t>2026-03-07T00:47:58+00:00</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>REC000081136278</t>
+          <t>518157132850</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-7750128-6635051", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>REC000081129859</t>
+          <t>518157132150</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11860,52 +11972,60 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>6001677522</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr"/>
+          <t>B2BDS11592096</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-03-06T17:18:00</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr"/>
+          <t>2026-03-07T09:28:00+09:00</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>都留営業所, Japan</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-03-06T17:20:27+00:00</t>
+          <t>2026-03-07T00:47:58+00:00</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>REC000081129859</t>
+          <t>518157132150</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "B2BDS11592096", "sales_office_id": "4468"}</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>REC000081158013</t>
+          <t>518157132345</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11915,52 +12035,60 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>6001679312</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr"/>
+          <t>250-7750128-6635051</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-03-06T13:55:00</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr"/>
+          <t>2026-03-07T09:31:00+09:00</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>羽生営業所, Japan</t>
+        </is>
+      </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-03-06T14:20:22+00:00</t>
+          <t>2026-03-07T00:47:56+00:00</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>REC000081158013</t>
+          <t>518157132345</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-7750128-6635051", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>REC000081129636</t>
+          <t>518157132780</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11970,52 +12098,60 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>6001677477</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr"/>
+          <t>250-6233951-0415803</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-03-06T15:32:00</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr"/>
+          <t>2026-03-07T12:22:00+09:00</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>郡山営業所, Japan</t>
+        </is>
+      </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-03-06T15:19:03+00:00</t>
+          <t>2026-03-07T03:47:59+00:00</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>REC000081129636</t>
+          <t>518157132780</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-6233951-0415803", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>REC000081128844</t>
+          <t>518157132883</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -12025,52 +12161,60 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>6001677136</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr"/>
+          <t>250-9272870-4024600</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-03-06T11:57:00</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr"/>
+          <t>2026-03-07T12:24:00+09:00</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>羽島営業所, Japan</t>
+        </is>
+      </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026-03-06T11:21:20+00:00</t>
+          <t>2026-03-07T03:46:45+00:00</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>REC000081128844</t>
+          <t>518157132883</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-9272870-4024600", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>REC000081128911</t>
+          <t>518157133034</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -12080,52 +12224,60 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>6001677193</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr"/>
+          <t>250-4449315-4343025</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-03-06T10:57:00</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr"/>
+          <t>2026-03-07T10:30:00+09:00</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>前橋営業所, Japan</t>
+        </is>
+      </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-03-06T11:20:39+00:00</t>
+          <t>2026-03-07T02:16:43+00:00</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>REC000081128911</t>
+          <t>518157133034</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-4449315-4343025", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>REC000081145007</t>
+          <t>518157132861</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -12135,52 +12287,60 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>6001678965</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr"/>
+          <t>250-5442263-3764608</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-03-06T12:28:00</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr"/>
+          <t>2026-03-07T10:17:00+09:00</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>丸岡営業所, Japan</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-03-06T12:19:38+00:00</t>
+          <t>2026-03-07T01:46:45+00:00</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>REC000081145007</t>
+          <t>518157132861</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-5442263-3764608", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>REC000081137342</t>
+          <t>518157133012</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>spanish-seur-ftp</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12190,52 +12350,60 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>6001678429</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr"/>
+          <t>250-3690112-3101468</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-03-06T09:31:00</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr"/>
+          <t>2026-03-07T12:21:00+09:00</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>姫路営業所, Japan</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-03-06T09:21:15+00:00</t>
+          <t>2026-03-07T03:46:45+00:00</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>REC000081137342</t>
+          <t>518157133012</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>{"courier": "spanish-seur-ftp", "custom_1": "Returns_spanish-seur"}</t>
+          <t>{"external_order_id": "250-3690112-3101468", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ZDDO3IST</t>
+          <t>518157132625</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12245,56 +12413,60 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>6001679636</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr"/>
+          <t>249-8682654-9359034</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-02-12T14:00:00+01:00</t>
+          <t>2026-03-07T09:51:00+09:00</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>大山崎営業所, Japan</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:20+00:00</t>
+          <t>2026-03-07T02:46:41+00:00</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>ZDDO3IST</t>
+          <t>518157132625</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "249-8682654-9359034", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ZDDO3ISS</t>
+          <t>518157132824</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12304,56 +12476,60 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>6001679636</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr"/>
+          <t>250-8760607-8118239</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-02-12T14:00:00+01:00</t>
+          <t>2026-03-07T12:07:00+09:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>DE, Germany</t>
+          <t>稲城営業所, Japan</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:22+00:00</t>
+          <t>2026-03-07T03:46:42+00:00</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>ZDDO3ISS</t>
+          <t>518157132824</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "250-8760607-8118239", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Z7XDDA12</t>
+          <t>518157132791</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>gls</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12363,56 +12539,60 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>6001677260</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr"/>
+          <t>250-3432684-5186255</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-02-20T13:00:19+01:00</t>
+          <t>2026-03-07T12:30:00+09:00</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>AT, Austria</t>
+          <t>豊橋営業所, Japan</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:21+00:00</t>
+          <t>2026-03-07T03:46:45+00:00</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Z7XDDA12</t>
+          <t>518157132791</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>{"courier": "GLS", "custom_1": "returns_gls"}</t>
+          <t>{"external_order_id": "250-3432684-5186255", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>05222069732758</t>
+          <t>518157132404</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12422,56 +12602,60 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>6001679852</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr"/>
+          <t>0081000027993</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-02-13T11:15:29+01:00</t>
+          <t>2026-03-07T10:23:00+09:00</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>白石営業所, Japan</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:16+00:00</t>
+          <t>2026-03-07T01:45:19+00:00</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>05222069732758</t>
+          <t>518157132404</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "0081000027993", "sales_office_id": "4414"}</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>05222006538846</t>
+          <t>518157132986</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12481,56 +12665,60 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>6001678746</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr"/>
+          <t>B2BDS11592013</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-03-05T15:35:36+01:00</t>
+          <t>2026-03-07T11:31:00+09:00</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Etten-Leur, NL, Netherlands</t>
+          <t>栃木営業所, Japan</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-03-06T16:44:56+00:00</t>
+          <t>2026-03-07T02:45:20+00:00</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>05222006538846</t>
+          <t>518157132986</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "B2BDS11592013", "sales_office_id": "4468"}</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>05222006538860</t>
+          <t>518157132813</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12540,56 +12728,60 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>6001679075</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr"/>
+          <t>503-2676929-5654204</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-03-05T13:55:37+01:00</t>
+          <t>2026-03-07T11:56:00+09:00</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Beverwijk, NL, Netherlands</t>
+          <t>須磨営業所, Japan</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-03-06T13:44:26+00:00</t>
+          <t>2026-03-07T03:15:21+00:00</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>05222006538860</t>
+          <t>518157132813</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "503-2676929-5654204", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>05222069732759</t>
+          <t>518157132360</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12599,56 +12791,60 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>6001679852</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr"/>
+          <t>B2BDS11591999</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-02-13T11:15:29+01:00</t>
+          <t>2026-03-07T13:09:00+09:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>三島営業所, Japan</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:17+00:00</t>
+          <t>2026-03-07T04:45:26+00:00</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>05222069732759</t>
+          <t>518157132360</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "B2BDS11591999", "sales_office_id": "4468"}</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>05222006538833</t>
+          <t>518157132371</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12658,56 +12854,60 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>6001678501</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr"/>
+          <t>250-5292186-6332612</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-03-05T13:40:25+01:00</t>
+          <t>2026-03-07T08:31:00+09:00</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Veenendaal, NL, Netherlands</t>
+          <t>杉並営業所, Japan</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-03-06T01:44:16+00:00</t>
+          <t>2026-03-06T23:45:18+00:00</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>05222006538833</t>
+          <t>518157132371</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "250-5292186-6332612", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>05222069778589</t>
+          <t>518157132356</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12717,56 +12917,60 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>6001679888</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr"/>
+          <t>503-2453334-4255036</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-03-04T17:48:49+01:00</t>
+          <t>2026-03-07T11:12:00+09:00</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Rijssen, NL, Netherlands</t>
+          <t>千葉北営業所, Japan</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-03-06T13:44:27+00:00</t>
+          <t>2026-03-07T02:45:23+00:00</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>05222069778589</t>
+          <t>518157132356</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "503-2453334-4255036", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>05222006538859</t>
+          <t>518157132802</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12776,56 +12980,60 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>6001679057</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr"/>
+          <t>250-9022065-7323057</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-03-05T16:54:18+01:00</t>
+          <t>2026-03-07T13:16:00+09:00</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Berkel en Rodenrijs, NL, Netherlands</t>
+          <t>名古屋営業所, Japan</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-03-06T13:44:28+00:00</t>
+          <t>2026-03-07T04:45:17+00:00</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>05222006538859</t>
+          <t>518157132802</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "250-9022065-7323057", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>05222006538814</t>
+          <t>518157132636</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>dpd</t>
+          <t>sagawa</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12835,39 +13043,43 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>6001678060</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr"/>
+          <t>503-5945974-2243848</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>csv_importer</t>
+          <t>api</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-03-06T18:28:00+01:00</t>
+          <t>2026-03-07T10:09:00+09:00</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Segeltorp, SE, Sweden</t>
+          <t>飯田営業所, Japan</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-03-06T19:48:49+00:00</t>
+          <t>2026-03-07T01:15:13+00:00</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>05222006538814</t>
+          <t>518157132636</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>{"courier": "dpd ", "custom_1": "returns_dpd"}</t>
+          <t>{"external_order_id": "503-5945974-2243848", "sales_office_id": "4564"}</t>
         </is>
       </c>
     </row>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-07T16:55:00+00:00</t>
+          <t>2026-03-07T20:55:00+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-07T16:55:00+00:00</t>
+          <t>2026-03-07T20:55:01+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-07T16:54:58+00:00</t>
+          <t>2026-03-07T20:54:59+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-07T16:55:01+00:00</t>
+          <t>2026-03-07T20:55:03+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-07T16:43:01+00:00</t>
+          <t>2026-03-07T20:43:04+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>889375930364</t>
+          <t>889375906131</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-07T15:57:10+00:00</t>
+          <t>2026-03-07T15:57:14+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>889375930364</t>
+          <t>889375906131</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>889375931430</t>
+          <t>889375930364</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-07T15:57:15+00:00</t>
+          <t>2026-03-07T15:57:10+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>889375931430</t>
+          <t>889375930364</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>889375906131</t>
+          <t>889375931430</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-07T15:57:14+00:00</t>
+          <t>2026-03-07T15:57:15+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>889375906131</t>
+          <t>889375931430</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1872,7 +1872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>889370024329</t>
+          <t>889370028644</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-03-07T14:57:18+00:00</t>
+          <t>2026-03-07T14:57:28+00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>889370024329</t>
+          <t>889370028644</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>889370028644</t>
+          <t>889370024329</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-07T14:57:28+00:00</t>
+          <t>2026-03-07T14:57:18+00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>889370028644</t>
+          <t>889370024329</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2565,17 +2565,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UTV920806812</t>
+          <t>01475240803969</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0031009999635</t>
+          <t>B2BDS11563973</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,44 +2601,44 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-07T15:15:36+01:00</t>
+          <t>2026-03-07T10:09:53+01:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Münster (DE), Germany</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-03-07T15:45:25+00:00</t>
+          <t>2026-03-07T09:45:23+00:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>UTV920806812</t>
+          <t>01475240803969</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999635", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11563973", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>01475240803969</t>
+          <t>UTV920806812</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>B2BDS11563973</t>
+          <t>0031009999635</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2664,27 +2664,27 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-07T10:09:53+01:00</t>
+          <t>2026-03-07T15:15:36+01:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Münster (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-07T09:45:23+00:00</t>
+          <t>2026-03-07T15:45:25+00:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>01475240803969</t>
+          <t>UTV920806812</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11563973", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009999635", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>889369951492</t>
+          <t>889369347714</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>114-1748278-1883409</t>
+          <t>CS641748295</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2853,34 +2853,34 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-07T09:26:25-05:00</t>
+          <t>2026-03-07T14:44:54-05:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>New York, NY, 10032, US, United States</t>
+          <t>Millersville, MD, 21108, US, United States</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-07T14:42:20+00:00</t>
+          <t>2026-03-07T20:44:37+00:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>889369951492</t>
+          <t>889369347714</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>{"external_order_id": "114-1748278-1883409", "sales_office_id": "4264"}</t>
+          <t>{"external_order_id": "CS641748295", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>889369636510</t>
+          <t>889370059058</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CS641786066</t>
+          <t>200014460667074</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2916,34 +2916,34 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-07T14:03:34-05:00</t>
+          <t>2026-03-07T17:34:41-05:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>West Hempstead, NY, 11552, US, United States</t>
+          <t>Sayreville, NJ, 08872, US, United States</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-03-07T19:42:28+00:00</t>
+          <t>2026-03-07T22:42:43+00:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>889369636510</t>
+          <t>889370059058</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641786066", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "200014460667074", "sales_office_id": "4260"}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>889369892504</t>
+          <t>889369636510</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CS641703351</t>
+          <t>CS641786066</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2979,34 +2979,34 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-07T10:52:25-05:00</t>
+          <t>2026-03-07T14:03:34-05:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>New York, NY, 10024, US, United States</t>
+          <t>West Hempstead, NY, 11552, US, United States</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-03-07T16:40:31+00:00</t>
+          <t>2026-03-07T19:42:28+00:00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>889369892504</t>
+          <t>889369636510</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641703351", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "CS641786066", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>889369374063</t>
+          <t>889369951492</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4726090450-A</t>
+          <t>114-1748278-1883409</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3042,34 +3042,34 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-07T13:18:36-05:00</t>
+          <t>2026-03-07T09:26:25-05:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Far Rockaway, NY, 11691, US, United States</t>
+          <t>New York, NY, 10032, US, United States</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-03-07T18:40:29+00:00</t>
+          <t>2026-03-07T14:42:20+00:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>889369374063</t>
+          <t>889369951492</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{"external_order_id": "4726090450-A", "sales_office_id": "4574"}</t>
+          <t>{"external_order_id": "114-1748278-1883409", "sales_office_id": "4264"}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>889368965530</t>
+          <t>889369374063</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CS641728450</t>
+          <t>4726090450-A</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3105,34 +3105,34 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-07T11:09:14-05:00</t>
+          <t>2026-03-07T13:18:36-05:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Kittanning, PA, 16201, US, United States</t>
+          <t>Far Rockaway, NY, 11691, US, United States</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-07T17:07:07+00:00</t>
+          <t>2026-03-07T18:40:29+00:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>889368965530</t>
+          <t>889369374063</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641728450", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "4726090450-A", "sales_office_id": "4574"}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>889368963515</t>
+          <t>889369892504</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS641728450</t>
+          <t>CS641703351</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3168,34 +3168,34 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-07T11:09:14-05:00</t>
+          <t>2026-03-07T10:52:25-05:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Kittanning, PA, 16201, US, United States</t>
+          <t>New York, NY, 10024, US, United States</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-07T17:07:09+00:00</t>
+          <t>2026-03-07T16:40:31+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>889368963515</t>
+          <t>889369892504</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641728450", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "CS641703351", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>889369055622</t>
+          <t>889369327285</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3215,12 +3215,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PO-211-11616517479032025</t>
+          <t>115638817-1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3231,34 +3231,34 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-07T11:28:48-05:00</t>
+          <t>2026-03-07T14:57:27-05:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Arlington, VA, 22206, US, United States</t>
+          <t>Old Forge, PA, 18518, US, United States</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-03-07T17:07:07+00:00</t>
+          <t>2026-03-07T20:40:34+00:00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>889369055622</t>
+          <t>889369327285</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11616517479032025", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "115638817-1", "sales_office_id": "4175"}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>889368569122</t>
+          <t>889368965530</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>B2BDS11577654</t>
+          <t>CS641728450</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3294,34 +3294,34 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-03-07T14:48:36-05:00</t>
+          <t>2026-03-07T11:09:14-05:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Washington, DC, 20007, US, United States</t>
+          <t>Kittanning, PA, 16201, US, United States</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-03-07T20:07:15+00:00</t>
+          <t>2026-03-07T17:07:07+00:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>889368569122</t>
+          <t>889368965530</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11577654", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "CS641728450", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>889367921898</t>
+          <t>889369055622</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CS641712082</t>
+          <t>PO-211-11616517479032025</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3357,34 +3357,34 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-07T10:06:57-05:00</t>
+          <t>2026-03-07T11:28:48-05:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>New York, NY, 10019, US, United States</t>
+          <t>Arlington, VA, 22206, US, United States</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:17+00:00</t>
+          <t>2026-03-07T17:07:07+00:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>889367921898</t>
+          <t>889369055622</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641712082", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "PO-211-11616517479032025", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>889367452437</t>
+          <t>889368963515</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PO-211-11647151544951712</t>
+          <t>CS641728450</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3420,34 +3420,34 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-07T14:06:42-05:00</t>
+          <t>2026-03-07T11:09:14-05:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Dover, PA, 17315, US, United States</t>
+          <t>Kittanning, PA, 16201, US, United States</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-03-07T19:36:31+00:00</t>
+          <t>2026-03-07T17:07:09+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>889367452437</t>
+          <t>889368963515</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11647151544951712", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "CS641728450", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>889367449327</t>
+          <t>889369056916</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PO-211-11647151544951712</t>
+          <t>PO-211-08829010944631039</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3483,34 +3483,34 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-07T14:06:42-05:00</t>
+          <t>2026-03-07T15:21:01-05:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Dover, PA, 17315, US, United States</t>
+          <t>Scottsville, VA, 24590, US, United States</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-03-07T19:36:31+00:00</t>
+          <t>2026-03-07T21:07:19+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>889367449327</t>
+          <t>889369056916</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11647151544951712", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "PO-211-08829010944631039", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>889367343999</t>
+          <t>889368569122</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GSU16R54C00MH0R</t>
+          <t>B2BDS11577654</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3546,34 +3546,34 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-03-07T11:57:45-05:00</t>
+          <t>2026-03-07T14:48:36-05:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>New York, NY, 10016, US, United States</t>
+          <t>Washington, DC, 20007, US, United States</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-03-07T17:36:24+00:00</t>
+          <t>2026-03-07T20:07:15+00:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>889367343999</t>
+          <t>889368569122</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{"external_order_id": "GSU16R54C00MH0R", "sales_office_id": "4684"}</t>
+          <t>{"external_order_id": "B2BDS11577654", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>889367409069</t>
+          <t>889367921898</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>B2BDS11668629</t>
+          <t>CS641712082</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3609,34 +3609,34 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-03-07T13:46:29-05:00</t>
+          <t>2026-03-07T10:06:57-05:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Catasauqua, PA, 18032, US, United States</t>
+          <t>New York, NY, 10019, US, United States</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-03-07T19:32:06+00:00</t>
+          <t>2026-03-07T15:43:17+00:00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>889367409069</t>
+          <t>889367921898</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11668629", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "CS641712082", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>889367609189</t>
+          <t>889367452437</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>B2BDS11422951</t>
+          <t>PO-211-11647151544951712</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3672,34 +3672,34 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-07T11:09:03-05:00</t>
+          <t>2026-03-07T14:06:42-05:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Stuyvesant, NY, 12173, US, United States</t>
+          <t>Dover, PA, 17315, US, United States</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-03-07T16:32:15+00:00</t>
+          <t>2026-03-07T19:36:31+00:00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>889367609189</t>
+          <t>889367452437</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11422951", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "PO-211-11647151544951712", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>889365955437</t>
+          <t>889367343999</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>902003315571451-8616666156</t>
+          <t>GSU16R54C00MH0R</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3735,34 +3735,34 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-07T09:52:25-05:00</t>
+          <t>2026-03-07T11:57:45-05:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Stony Point, NY, 10980, US, United States</t>
+          <t>New York, NY, 10016, US, United States</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-07T15:17:20+00:00</t>
+          <t>2026-03-07T17:36:24+00:00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>889365955437</t>
+          <t>889367343999</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{"external_order_id": "902003315571451-8616666156", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "GSU16R54C00MH0R", "sales_office_id": "4684"}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>889366694432</t>
+          <t>889367449327</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>200014689927435</t>
+          <t>PO-211-11647151544951712</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3798,34 +3798,34 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-07T13:48:25-05:00</t>
+          <t>2026-03-07T14:06:42-05:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, 20905, US, United States</t>
+          <t>Dover, PA, 17315, US, United States</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-07T19:12:07+00:00</t>
+          <t>2026-03-07T19:36:31+00:00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>889366694432</t>
+          <t>889367449327</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"external_order_id": "200014689927435", "sales_office_id": "4260"}</t>
+          <t>{"external_order_id": "PO-211-11647151544951712", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>889363123264</t>
+          <t>889360197440</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PO-211-00136208108152741</t>
+          <t>PO-211-11145473444472590</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3861,34 +3861,34 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-03-07T11:29:45-05:00</t>
+          <t>2026-03-07T14:07:16-08:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, 11208, US, United States</t>
+          <t>Corona, CA, 92881, US, United States</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-03-07T16:40:18+00:00</t>
+          <t>2026-03-07T22:35:54+00:00</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>889363123264</t>
+          <t>889360197440</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-00136208108152741", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "PO-211-11145473444472590", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>889361439898</t>
+          <t>889367609189</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>912003268384629-8596772382</t>
+          <t>B2BDS11422951</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3924,34 +3924,34 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-07T12:05:00-05:00</t>
+          <t>2026-03-07T11:09:03-05:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Millsboro, DE, 19966, US, United States</t>
+          <t>Stuyvesant, NY, 12173, US, United States</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-03-07T17:37:24+00:00</t>
+          <t>2026-03-07T16:32:15+00:00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>889361439898</t>
+          <t>889367609189</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{"external_order_id": "912003268384629-8596772382", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "B2BDS11422951", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>889364042068</t>
+          <t>889367409069</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>200014473356841</t>
+          <t>B2BDS11668629</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3987,34 +3987,34 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-03-07T13:40:11-05:00</t>
+          <t>2026-03-07T13:46:29-05:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Olyphant, PA, 18447, US, United States</t>
+          <t>Catasauqua, PA, 18032, US, United States</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-03-07T19:37:45+00:00</t>
+          <t>2026-03-07T19:32:06+00:00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>889364042068</t>
+          <t>889367409069</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{"external_order_id": "200014473356841", "sales_office_id": "4260"}</t>
+          <t>{"external_order_id": "B2BDS11668629", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>889363718592</t>
+          <t>889366861790</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>912003268384629-8596772382</t>
+          <t>912003143848324-8627456153</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4050,34 +4050,34 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-03-07T12:05:00-05:00</t>
+          <t>2026-03-07T13:10:49-08:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Millsboro, DE, 19966, US, United States</t>
+          <t>Placentia, CA, 92870, US, United States</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-07T17:37:28+00:00</t>
+          <t>2026-03-08T01:22:36+00:00</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>889363718592</t>
+          <t>889366861790</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>{"external_order_id": "912003268384629-8596772382", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "912003143848324-8627456153", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>889361334643</t>
+          <t>889365955437</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>912003268384629-8596772382</t>
+          <t>902003315571451-8616666156</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4113,34 +4113,34 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-03-07T12:05:00-05:00</t>
+          <t>2026-03-07T09:52:25-05:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Millsboro, DE, 19966, US, United States</t>
+          <t>Stony Point, NY, 10980, US, United States</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-03-07T17:37:18+00:00</t>
+          <t>2026-03-07T15:17:20+00:00</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>889361334643</t>
+          <t>889365955437</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>{"external_order_id": "912003268384629-8596772382", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "902003315571451-8616666156", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>889363964370</t>
+          <t>889366694432</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B2BDS11576312</t>
+          <t>200014689927435</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4176,44 +4176,44 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-03-07T12:35:41-05:00</t>
+          <t>2026-03-07T13:48:25-05:00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Rosedale, MD, 21237, US, United States</t>
+          <t>Silver Spring, MD, 20905, US, United States</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-03-07T18:10:30+00:00</t>
+          <t>2026-03-07T19:12:07+00:00</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>889363964370</t>
+          <t>889366694432</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11576312", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "200014689927435", "sales_office_id": "4260"}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>01475240807222</t>
+          <t>889363123264</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0049010281327</t>
+          <t>PO-211-00136208108152741</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4239,44 +4239,44 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-07T11:28:29+01:00</t>
+          <t>2026-03-07T11:29:45-05:00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Gudensberg (DE), Germany</t>
+          <t>Brooklyn, NY, 11208, US, United States</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-03-07T11:35:20+00:00</t>
+          <t>2026-03-07T16:40:18+00:00</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>01475240807222</t>
+          <t>889363123264</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010281327", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "PO-211-00136208108152741", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>01475240806589</t>
+          <t>889363718592</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0049010281990</t>
+          <t>912003268384629-8596772382</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4302,34 +4302,34 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-03-07T15:12:11+01:00</t>
+          <t>2026-03-07T12:05:00-05:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Hengersberg (DE), Germany</t>
+          <t>Millsboro, DE, 19966, US, United States</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-07T14:35:26+00:00</t>
+          <t>2026-03-07T17:37:28+00:00</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>01475240806589</t>
+          <t>889363718592</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010281990", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "912003268384629-8596772382", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>889363457146</t>
+          <t>889364042068</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>912003270086545-8627201215</t>
+          <t>200014473356841</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4365,44 +4365,44 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-03-07T11:50:48-05:00</t>
+          <t>2026-03-07T13:40:11-05:00</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>East Elmhurst, NY, 11369, US, United States</t>
+          <t>Olyphant, PA, 18447, US, United States</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-07T17:04:25+00:00</t>
+          <t>2026-03-07T19:37:45+00:00</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>889363457146</t>
+          <t>889364042068</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>{"external_order_id": "912003270086545-8627201215", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "200014473356841", "sales_office_id": "4260"}</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>01475240807187</t>
+          <t>889361439898</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>cbn4wm2pzc</t>
+          <t>912003268384629-8596772382</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4428,34 +4428,34 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-07T15:22:18+01:00</t>
+          <t>2026-03-07T12:05:00-05:00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Millsboro, DE, 19966, US, United States</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-03-07T15:00:24+00:00</t>
+          <t>2026-03-07T17:37:24+00:00</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>01475240807187</t>
+          <t>889361439898</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wm2pzc", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "912003268384629-8596772382", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>889362885633</t>
+          <t>889361334643</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PO-211-11215988347513258</t>
+          <t>912003268384629-8596772382</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4491,34 +4491,34 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-03-07T10:37:24-05:00</t>
+          <t>2026-03-07T12:05:00-05:00</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, 11211, US, United States</t>
+          <t>Millsboro, DE, 19966, US, United States</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-03-07T15:48:47+00:00</t>
+          <t>2026-03-07T17:37:18+00:00</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>889362885633</t>
+          <t>889361334643</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11215988347513258", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "912003268384629-8596772382", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>889363459973</t>
+          <t>889363964370</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PO-211-05872303473270295</t>
+          <t>B2BDS11576312</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4554,44 +4554,44 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-03-07T11:09:20-08:00</t>
+          <t>2026-03-07T12:35:41-05:00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Van Nuys, CA, 91405, US, United States</t>
+          <t>Rosedale, MD, 21237, US, United States</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-03-07T19:49:00+00:00</t>
+          <t>2026-03-07T18:10:30+00:00</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>889363459973</t>
+          <t>889363964370</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-05872303473270295", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "B2BDS11576312", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>889363196395</t>
+          <t>01475240807222</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CS641762034</t>
+          <t>0049010281327</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4617,44 +4617,44 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-03-07T11:42:00-05:00</t>
+          <t>2026-03-07T11:28:29+01:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, 07306, US, United States</t>
+          <t>Gudensberg (DE), Germany</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-03-07T16:48:51+00:00</t>
+          <t>2026-03-07T11:35:20+00:00</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>889363196395</t>
+          <t>01475240807222</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641762034", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "0049010281327", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UTV819828971</t>
+          <t>01475240806589</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0031009998003</t>
+          <t>0049010281990</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4680,34 +4680,34 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-07T08:44:10+01:00</t>
+          <t>2026-03-07T15:12:11+01:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Hengersberg (DE), Germany</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-03-07T09:48:20+00:00</t>
+          <t>2026-03-07T14:35:26+00:00</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>UTV819828971</t>
+          <t>01475240806589</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998003", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010281990", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>889363135257</t>
+          <t>889363457146</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CS641803948</t>
+          <t>912003270086545-8627201215</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4743,44 +4743,44 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-03-07T11:10:33-08:00</t>
+          <t>2026-03-07T11:50:48-05:00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Hacienda Heights, CA, 91745, US, United States</t>
+          <t>East Elmhurst, NY, 11369, US, United States</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-03-07T19:48:52+00:00</t>
+          <t>2026-03-07T17:04:25+00:00</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>889363135257</t>
+          <t>889363457146</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641803948", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "912003270086545-8627201215", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>UTV525664811</t>
+          <t>01475240807187</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0031010000448</t>
+          <t>cbn4wm2pzc</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4806,44 +4806,44 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-03-07T11:45:45+01:00</t>
+          <t>2026-03-07T15:22:18+01:00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-03-07T12:46:41+00:00</t>
+          <t>2026-03-07T15:00:24+00:00</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>UTV525664811</t>
+          <t>01475240807187</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000448", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "cbn4wm2pzc", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>UTV341853252</t>
+          <t>889362885633</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0031010000939</t>
+          <t>PO-211-11215988347513258</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4869,44 +4869,44 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-07T15:36:31+01:00</t>
+          <t>2026-03-07T10:37:24-05:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Brooklyn, NY, 11211, US, United States</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-03-07T15:45:53+00:00</t>
+          <t>2026-03-07T15:48:47+00:00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>UTV341853252</t>
+          <t>889362885633</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000939", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-211-11215988347513258", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>UTV517387442</t>
+          <t>889363194392</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0031009995883</t>
+          <t>PO-211-11266395935354046</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4932,44 +4932,44 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-07T17:21:24+01:00</t>
+          <t>2026-03-07T17:31:41-05:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Toms River, NJ, 08753, US, United States</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-03-07T18:45:55+00:00</t>
+          <t>2026-03-07T22:49:11+00:00</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>UTV517387442</t>
+          <t>889363194392</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995883", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-211-11266395935354046", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>UTV307033148</t>
+          <t>889363459973</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0031009995883</t>
+          <t>PO-211-05872303473270295</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4995,44 +4995,44 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-07T17:21:43+01:00</t>
+          <t>2026-03-07T11:09:20-08:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Van Nuys, CA, 91405, US, United States</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-03-07T18:45:54+00:00</t>
+          <t>2026-03-07T19:49:00+00:00</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>UTV307033148</t>
+          <t>889363459973</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995883", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-211-05872303473270295", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>UTV342835070</t>
+          <t>889363196395</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0031009990149</t>
+          <t>CS641762034</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5058,34 +5058,34 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-07T13:56:21+01:00</t>
+          <t>2026-03-07T11:42:00-05:00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Jersey City, NJ, 07306, US, United States</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-03-07T15:45:49+00:00</t>
+          <t>2026-03-07T16:48:51+00:00</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>UTV342835070</t>
+          <t>889363196395</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009990149", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "CS641762034", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>UTV098268709</t>
+          <t>UTV819828971</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0031009991082</t>
+          <t>0031009998003</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5121,7 +5121,7 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-07T10:25:09+01:00</t>
+          <t>2026-03-07T08:44:10+01:00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5131,34 +5131,34 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-03-07T09:44:18+00:00</t>
+          <t>2026-03-07T09:48:20+00:00</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>UTV098268709</t>
+          <t>UTV819828971</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009991082", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998003", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>UTV854730895</t>
+          <t>889363135257</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0031009990149</t>
+          <t>CS641803948</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5184,34 +5184,34 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-03-07T13:56:05+01:00</t>
+          <t>2026-03-07T11:10:33-08:00</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Hacienda Heights, CA, 91745, US, United States</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:25+00:00</t>
+          <t>2026-03-07T19:48:52+00:00</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>UTV854730895</t>
+          <t>889363135257</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009990149", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "CS641803948", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>UTV614952059</t>
+          <t>UTV525664811</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0031010000481</t>
+          <t>0031010000448</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5247,7 +5247,7 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-03-07T17:12:23+01:00</t>
+          <t>2026-03-07T11:45:45+01:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5257,24 +5257,24 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-03-07T18:44:22+00:00</t>
+          <t>2026-03-07T12:46:41+00:00</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>UTV614952059</t>
+          <t>UTV525664811</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000481", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031010000448", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>UTV429486735</t>
+          <t>UTV341853252</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0031010001068</t>
+          <t>0031010000939</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5310,7 +5310,7 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-03-07T17:26:04+01:00</t>
+          <t>2026-03-07T15:36:31+01:00</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5320,24 +5320,24 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-03-07T18:44:24+00:00</t>
+          <t>2026-03-07T15:45:53+00:00</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>UTV429486735</t>
+          <t>UTV341853252</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010001068", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031010000939", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>UTV233778652</t>
+          <t>UTV517387442</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>B2BDS11552552</t>
+          <t>0031009995883</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5373,7 +5373,7 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-03-07T18:39:15+01:00</t>
+          <t>2026-03-07T17:21:24+01:00</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5383,24 +5383,24 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-03-07T18:44:22+00:00</t>
+          <t>2026-03-07T18:45:55+00:00</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>UTV233778652</t>
+          <t>UTV517387442</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11552552", "sales_office_id": "4449"}</t>
+          <t>{"external_order_id": "0031009995883", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>UTV588822958</t>
+          <t>UTV307033148</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0031009990149</t>
+          <t>0031009995883</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5436,7 +5436,7 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-03-07T18:11:01+01:00</t>
+          <t>2026-03-07T17:21:43+01:00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5446,24 +5446,24 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-03-07T18:44:22+00:00</t>
+          <t>2026-03-07T18:45:54+00:00</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>UTV588822958</t>
+          <t>UTV307033148</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009990149", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009995883", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>UTV770128264</t>
+          <t>UTV342835070</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0031009991082</t>
+          <t>0031009990149</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5499,7 +5499,7 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-03-07T10:26:24+01:00</t>
+          <t>2026-03-07T13:56:21+01:00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5509,24 +5509,24 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-03-07T09:44:13+00:00</t>
+          <t>2026-03-07T15:45:49+00:00</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>UTV770128264</t>
+          <t>UTV342835070</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009991082", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009990149", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>UTV520382342</t>
+          <t>UTV098268709</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0031009997752</t>
+          <t>0031009991082</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5562,7 +5562,7 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-03-07T11:32:29+01:00</t>
+          <t>2026-03-07T10:25:09+01:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5572,24 +5572,24 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-03-07T12:44:19+00:00</t>
+          <t>2026-03-07T09:44:18+00:00</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>UTV520382342</t>
+          <t>UTV098268709</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009997752", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009991082", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>UTV189674431</t>
+          <t>UTV854730895</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0031009998979</t>
+          <t>0031009990149</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5625,7 +5625,7 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-07T11:46:20+01:00</t>
+          <t>2026-03-07T13:56:05+01:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5635,24 +5635,24 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-03-07T12:44:16+00:00</t>
+          <t>2026-03-07T15:44:25+00:00</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>UTV189674431</t>
+          <t>UTV854730895</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998979", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009990149", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>UTV037899235</t>
+          <t>UTV614952059</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PO-141-00240214113913081</t>
+          <t>0031010000481</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5688,7 +5688,7 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-03-07T14:42:05+01:00</t>
+          <t>2026-03-07T17:12:23+01:00</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:16+00:00</t>
+          <t>2026-03-07T18:44:22+00:00</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>UTV037899235</t>
+          <t>UTV614952059</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-141-00240214113913081", "sales_office_id": "4675"}</t>
+          <t>{"external_order_id": "0031010000481", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>UTV385243264</t>
+          <t>UTV429486735</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PO-141-00240214113913081</t>
+          <t>0031010001068</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5751,7 +5751,7 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-03-07T14:41:50+01:00</t>
+          <t>2026-03-07T17:26:04+01:00</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5761,24 +5761,24 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:12+00:00</t>
+          <t>2026-03-07T18:44:24+00:00</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>UTV385243264</t>
+          <t>UTV429486735</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-141-00240214113913081", "sales_office_id": "4675"}</t>
+          <t>{"external_order_id": "0031010001068", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UTV892064517</t>
+          <t>UTV588822958</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0031009996341</t>
+          <t>0031009990149</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5814,7 +5814,7 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-03-07T14:58:40+01:00</t>
+          <t>2026-03-07T18:11:01+01:00</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5824,24 +5824,24 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:12+00:00</t>
+          <t>2026-03-07T18:44:22+00:00</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>UTV892064517</t>
+          <t>UTV588822958</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009996341", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009990149", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UTV789874035</t>
+          <t>UTV233778652</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0031009997072</t>
+          <t>B2BDS11552552</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5877,7 +5877,7 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-03-07T15:01:08+01:00</t>
+          <t>2026-03-07T18:39:15+01:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5887,24 +5887,24 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:16+00:00</t>
+          <t>2026-03-07T22:44:22+00:00</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>UTV789874035</t>
+          <t>UTV233778652</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009997072", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11552552", "sales_office_id": "4449"}</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UTV267011146</t>
+          <t>UTV770128264</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0031009997072</t>
+          <t>0031009991082</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5940,7 +5940,7 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-03-07T15:01:25+01:00</t>
+          <t>2026-03-07T10:26:24+01:00</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5950,24 +5950,24 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:16+00:00</t>
+          <t>2026-03-07T09:44:13+00:00</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>UTV267011146</t>
+          <t>UTV770128264</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009997072", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009991082", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>UTV278587518</t>
+          <t>UTV520382342</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0031009991718</t>
+          <t>0031009997752</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6003,7 +6003,7 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:44+01:00</t>
+          <t>2026-03-07T11:32:29+01:00</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6013,24 +6013,24 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-03-07T12:44:03+00:00</t>
+          <t>2026-03-07T12:44:19+00:00</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>UTV278587518</t>
+          <t>UTV520382342</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009991718", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009997752", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>UTV485172073</t>
+          <t>UTV037899235</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0031009991718</t>
+          <t>PO-141-00240214113913081</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6066,7 +6066,7 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-03-06T11:39:17+01:00</t>
+          <t>2026-03-07T14:42:05+01:00</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6076,24 +6076,24 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-03-06T15:43:54+00:00</t>
+          <t>2026-03-07T15:44:16+00:00</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>UTV485172073</t>
+          <t>UTV037899235</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009991718", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-141-00240214113913081", "sales_office_id": "4675"}</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>UTV755196133</t>
+          <t>UTV189674431</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0031010000005</t>
+          <t>0031009998979</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6129,7 +6129,7 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-03-07T16:05:50+01:00</t>
+          <t>2026-03-07T11:46:20+01:00</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6139,24 +6139,24 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:00+00:00</t>
+          <t>2026-03-07T12:44:16+00:00</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>UTV755196133</t>
+          <t>UTV189674431</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000005", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998979", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>UTV816171166</t>
+          <t>UTV385243264</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0031009996624</t>
+          <t>PO-141-00240214113913081</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6192,7 +6192,7 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-03-07T07:41:05+01:00</t>
+          <t>2026-03-07T14:41:50+01:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6202,24 +6202,24 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-03-07T06:43:56+00:00</t>
+          <t>2026-03-07T15:44:12+00:00</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>UTV816171166</t>
+          <t>UTV385243264</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009996624", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "PO-141-00240214113913081", "sales_office_id": "4675"}</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>UTV793053659</t>
+          <t>UTV789874035</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0031010000005</t>
+          <t>0031009997072</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6255,7 +6255,7 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-03-07T16:05:35+01:00</t>
+          <t>2026-03-07T15:01:08+01:00</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:04+00:00</t>
+          <t>2026-03-07T15:44:16+00:00</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>UTV793053659</t>
+          <t>UTV789874035</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000005", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009997072", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>UTV190006080</t>
+          <t>UTV892064517</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0031010000005</t>
+          <t>0031009996341</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6318,7 +6318,7 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-03-07T16:06:05+01:00</t>
+          <t>2026-03-07T14:58:40+01:00</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6328,24 +6328,24 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:02+00:00</t>
+          <t>2026-03-07T15:44:12+00:00</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>UTV190006080</t>
+          <t>UTV892064517</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000005", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009996341", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>UTV190116875</t>
+          <t>UTV267011146</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0031009999110</t>
+          <t>0031009997072</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6381,7 +6381,7 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-03-07T10:14:46+01:00</t>
+          <t>2026-03-07T15:01:25+01:00</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6391,24 +6391,24 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:53+00:00</t>
+          <t>2026-03-07T15:44:16+00:00</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>UTV190116875</t>
+          <t>UTV267011146</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999110", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009997072", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UTV858435463</t>
+          <t>UTV485172073</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0031009997421</t>
+          <t>0031009991718</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6444,7 +6444,7 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-03-07T14:09:55+01:00</t>
+          <t>2026-03-06T11:39:17+01:00</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-03-07T19:43:54+00:00</t>
+          <t>2026-03-06T15:43:54+00:00</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>UTV858435463</t>
+          <t>UTV485172073</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009997421", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009991718", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>UTV315231289</t>
+          <t>UTV278587518</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0031009999110</t>
+          <t>0031009991718</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6507,7 +6507,7 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-03-07T10:14:21+01:00</t>
+          <t>2026-03-07T12:43:44+01:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6517,24 +6517,24 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:49+00:00</t>
+          <t>2026-03-07T12:44:03+00:00</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>UTV315231289</t>
+          <t>UTV278587518</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999110", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009991718", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>UTV000652207</t>
+          <t>UTV755196133</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>B2B25353172</t>
+          <t>0031010000005</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6570,7 +6570,7 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-03-07T11:12:05+01:00</t>
+          <t>2026-03-07T16:05:50+01:00</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6580,24 +6580,24 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:54+00:00</t>
+          <t>2026-03-07T15:44:00+00:00</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>UTV000652207</t>
+          <t>UTV755196133</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2B25353172", "sales_office_id": "4238"}</t>
+          <t>{"external_order_id": "0031010000005", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>UTV401731075</t>
+          <t>UTV793053659</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0031009995967</t>
+          <t>0031010000005</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6633,7 +6633,7 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-03-07T08:05:26+01:00</t>
+          <t>2026-03-07T16:05:35+01:00</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:45+00:00</t>
+          <t>2026-03-07T15:44:04+00:00</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>UTV401731075</t>
+          <t>UTV793053659</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031010000005", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UTV368379285</t>
+          <t>UTV816171166</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0031009999717</t>
+          <t>0031009996624</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6696,7 +6696,7 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-03-07T15:09:11+01:00</t>
+          <t>2026-03-07T07:41:05+01:00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6706,24 +6706,24 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:53+00:00</t>
+          <t>2026-03-07T06:43:56+00:00</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>UTV368379285</t>
+          <t>UTV816171166</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999717", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009996624", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UTV333185391</t>
+          <t>UTV190006080</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0031009995967</t>
+          <t>0031010000005</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6759,7 +6759,7 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-03-07T08:05:17+01:00</t>
+          <t>2026-03-07T16:06:05+01:00</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6769,24 +6769,24 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:45+00:00</t>
+          <t>2026-03-07T15:44:02+00:00</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>UTV333185391</t>
+          <t>UTV190006080</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031010000005", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>UTV465980823</t>
+          <t>UTV190116875</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0031009995967</t>
+          <t>0031009999110</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6822,7 +6822,7 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-03-07T08:05:08+01:00</t>
+          <t>2026-03-07T10:14:46+01:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6832,24 +6832,24 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:42+00:00</t>
+          <t>2026-03-07T09:43:53+00:00</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>UTV465980823</t>
+          <t>UTV190116875</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999110", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>UTV150206567</t>
+          <t>UTV858435463</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0031009999052</t>
+          <t>0031009997421</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6885,7 +6885,7 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-03-07T13:41:38+01:00</t>
+          <t>2026-03-07T14:09:55+01:00</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6895,24 +6895,24 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:51+00:00</t>
+          <t>2026-03-07T19:43:54+00:00</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>UTV150206567</t>
+          <t>UTV858435463</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999052", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009997421", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>UTV523884117</t>
+          <t>UTV315231289</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0031009999052</t>
+          <t>0031009999110</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6948,7 +6948,7 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-03-07T13:42:50+01:00</t>
+          <t>2026-03-07T10:14:21+01:00</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6958,24 +6958,24 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:46+00:00</t>
+          <t>2026-03-07T09:43:49+00:00</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>UTV523884117</t>
+          <t>UTV315231289</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999052", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999110", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>UTV583940173</t>
+          <t>UTV000652207</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0031009993377</t>
+          <t>B2B25353172</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7011,7 +7011,7 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-03-06T12:16:11+01:00</t>
+          <t>2026-03-07T11:12:05+01:00</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7021,24 +7021,24 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-03-06T15:45:18+00:00</t>
+          <t>2026-03-07T12:43:54+00:00</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>UTV583940173</t>
+          <t>UTV000652207</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009993377", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2B25353172", "sales_office_id": "4238"}</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>UTV666157586</t>
+          <t>UTV401731075</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0031009993377</t>
+          <t>0031009995967</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7074,7 +7074,7 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-03-06T12:16:32+01:00</t>
+          <t>2026-03-07T08:05:26+01:00</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7084,24 +7084,24 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-03-06T15:43:34+00:00</t>
+          <t>2026-03-07T09:43:45+00:00</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>UTV666157586</t>
+          <t>UTV401731075</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009993377", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>UTV037823638</t>
+          <t>UTV368379285</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0031009995967</t>
+          <t>0031009999717</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -7137,7 +7137,7 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-07T08:05:35+01:00</t>
+          <t>2026-03-07T15:09:11+01:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7147,24 +7147,24 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:41+00:00</t>
+          <t>2026-03-07T15:43:53+00:00</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>UTV037823638</t>
+          <t>UTV368379285</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999717", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UTV887843710</t>
+          <t>UTV333185391</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0031009993377</t>
+          <t>0031009995967</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7200,7 +7200,7 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-06T12:16:21+01:00</t>
+          <t>2026-03-07T08:05:17+01:00</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7210,24 +7210,24 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-03-06T15:43:33+00:00</t>
+          <t>2026-03-07T09:43:45+00:00</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>UTV887843710</t>
+          <t>UTV333185391</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009993377", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UTV684232150</t>
+          <t>UTV150206567</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0031010000617</t>
+          <t>0031009999052</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7263,7 +7263,7 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-03-07T12:31:22+01:00</t>
+          <t>2026-03-07T13:41:38+01:00</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7273,24 +7273,24 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:46+00:00</t>
+          <t>2026-03-07T12:43:51+00:00</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>UTV684232150</t>
+          <t>UTV150206567</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000617", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999052", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UTV323182364</t>
+          <t>UTV523884117</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0031010000617</t>
+          <t>0031009999052</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7326,7 +7326,7 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-03-07T12:31:13+01:00</t>
+          <t>2026-03-07T13:42:50+01:00</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7341,19 +7341,19 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>UTV323182364</t>
+          <t>UTV523884117</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000617", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999052", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>UTV692930235</t>
+          <t>UTV465980823</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0031010000617</t>
+          <t>0031009995967</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7389,7 +7389,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-03-07T12:31:32+01:00</t>
+          <t>2026-03-07T08:05:08+01:00</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7399,24 +7399,24 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:43+00:00</t>
+          <t>2026-03-07T09:43:42+00:00</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>UTV692930235</t>
+          <t>UTV465980823</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000617", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UTV869435335</t>
+          <t>UTV583940173</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0031009993802</t>
+          <t>0031009993377</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7452,7 +7452,7 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-07T15:16:42+01:00</t>
+          <t>2026-03-06T12:16:11+01:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7462,24 +7462,24 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:40+00:00</t>
+          <t>2026-03-06T15:45:18+00:00</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>UTV869435335</t>
+          <t>UTV583940173</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009993802", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009993377", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>UTV699841515</t>
+          <t>UTV037823638</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0031009993802</t>
+          <t>0031009995967</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7515,7 +7515,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-03-07T15:16:56+01:00</t>
+          <t>2026-03-07T08:05:35+01:00</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7525,24 +7525,24 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:44+00:00</t>
+          <t>2026-03-07T09:43:41+00:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>UTV699841515</t>
+          <t>UTV037823638</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009993802", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UTV833690635</t>
+          <t>UTV666157586</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0031009998483</t>
+          <t>0031009993377</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7578,7 +7578,7 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-07T10:31:48+01:00</t>
+          <t>2026-03-06T12:16:32+01:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7588,24 +7588,24 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:39+00:00</t>
+          <t>2026-03-06T15:43:34+00:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>UTV833690635</t>
+          <t>UTV666157586</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998483", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009993377", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>UTV374098129</t>
+          <t>UTV887843710</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0031009998574</t>
+          <t>0031009993377</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7641,7 +7641,7 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-03-07T12:32:26+01:00</t>
+          <t>2026-03-06T12:16:21+01:00</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7651,24 +7651,24 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:27+00:00</t>
+          <t>2026-03-06T15:43:33+00:00</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>UTV374098129</t>
+          <t>UTV887843710</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998574", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009993377", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UTV510907245</t>
+          <t>UTV323182364</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0031009998483</t>
+          <t>0031010000617</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7704,7 +7704,7 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-03-07T10:31:34+01:00</t>
+          <t>2026-03-07T12:31:13+01:00</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7714,24 +7714,24 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:25+00:00</t>
+          <t>2026-03-07T12:43:46+00:00</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>UTV510907245</t>
+          <t>UTV323182364</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998483", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031010000617", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UTV494135530</t>
+          <t>UTV684232150</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0031009999313</t>
+          <t>0031010000617</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-03-07T13:33:00+01:00</t>
+          <t>2026-03-07T12:31:22+01:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7777,24 +7777,24 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:42+00:00</t>
+          <t>2026-03-07T12:43:46+00:00</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>UTV494135530</t>
+          <t>UTV684232150</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999313", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031010000617", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UTV936544238</t>
+          <t>UTV692930235</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0031009996435</t>
+          <t>0031010000617</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -7830,7 +7830,7 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-03-07T11:43:30+01:00</t>
+          <t>2026-03-07T12:31:32+01:00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7840,24 +7840,24 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:34+00:00</t>
+          <t>2026-03-07T12:43:43+00:00</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>UTV936544238</t>
+          <t>UTV692930235</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009996435", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031010000617", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>UTV821301129</t>
+          <t>UTV869435335</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0031009991226</t>
+          <t>0031009993802</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7893,7 +7893,7 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-03-07T09:22:33+01:00</t>
+          <t>2026-03-07T15:16:42+01:00</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7903,24 +7903,24 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:37+00:00</t>
+          <t>2026-03-07T15:43:40+00:00</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>UTV821301129</t>
+          <t>UTV869435335</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009991226", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009993802", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UTV617244913</t>
+          <t>UTV699841515</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0031009999113</t>
+          <t>0031009993802</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7956,7 +7956,7 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-03-07T14:11:52+01:00</t>
+          <t>2026-03-07T15:16:56+01:00</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7966,24 +7966,24 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:11+00:00</t>
+          <t>2026-03-07T15:43:44+00:00</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>UTV617244913</t>
+          <t>UTV699841515</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999113", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009993802", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UTV476154311</t>
+          <t>UTV374098129</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0031009998346</t>
+          <t>0031009998574</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -8019,7 +8019,7 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-07T10:58:10+01:00</t>
+          <t>2026-03-07T12:32:26+01:00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8029,24 +8029,24 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:06+00:00</t>
+          <t>2026-03-07T12:43:27+00:00</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>UTV476154311</t>
+          <t>UTV374098129</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998346", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998574", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UTV344915468</t>
+          <t>UTV833690635</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>0031010000354</t>
+          <t>0031009998483</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -8082,7 +8082,7 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-03-07T14:21:39+01:00</t>
+          <t>2026-03-07T10:31:48+01:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8092,24 +8092,24 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-03-07T16:13:40+00:00</t>
+          <t>2026-03-07T09:43:39+00:00</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>UTV344915468</t>
+          <t>UTV833690635</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000354", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998483", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UTV557713650</t>
+          <t>UTV510907245</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>0031009999276</t>
+          <t>0031009998483</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -8145,7 +8145,7 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-03-07T08:28:25+01:00</t>
+          <t>2026-03-07T10:31:34+01:00</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8155,24 +8155,24 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:04+00:00</t>
+          <t>2026-03-07T09:43:25+00:00</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>UTV557713650</t>
+          <t>UTV510907245</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999276", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998483", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UTV181800985</t>
+          <t>UTV494135530</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>0031009991226</t>
+          <t>0031009999313</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -8208,7 +8208,7 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-03-07T09:21:27+01:00</t>
+          <t>2026-03-07T13:33:00+01:00</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8218,24 +8218,24 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-03-07T10:13:29+00:00</t>
+          <t>2026-03-08T00:43:46+00:00</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>UTV181800985</t>
+          <t>UTV494135530</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009991226", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999313", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>UTV087620692</t>
+          <t>UTV936544238</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>0031009998346</t>
+          <t>0031009996435</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -8271,7 +8271,7 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-03-07T10:58:39+01:00</t>
+          <t>2026-03-07T11:43:30+01:00</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8281,24 +8281,24 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-03-07T10:13:26+00:00</t>
+          <t>2026-03-07T12:43:34+00:00</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>UTV087620692</t>
+          <t>UTV936544238</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998346", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009996435", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>UTV458384249</t>
+          <t>UTV821301129</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>0031009998891</t>
+          <t>0031009991226</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8334,7 +8334,7 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-03-07T13:14:58+01:00</t>
+          <t>2026-03-07T09:22:33+01:00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8344,24 +8344,24 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-03-07T16:43:08+00:00</t>
+          <t>2026-03-07T09:43:37+00:00</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>UTV458384249</t>
+          <t>UTV821301129</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998891", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009991226", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>UTV193284768</t>
+          <t>UTV617244913</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>0031009998567</t>
+          <t>0031009999113</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8397,7 +8397,7 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-03-07T14:04:43+01:00</t>
+          <t>2026-03-07T14:11:52+01:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8407,24 +8407,24 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:07+00:00</t>
+          <t>2026-03-07T15:43:11+00:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>UTV193284768</t>
+          <t>UTV617244913</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999113", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>UTV058630911</t>
+          <t>UTV476154311</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0031009985429</t>
+          <t>0031009998346</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8460,7 +8460,7 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-03-05T15:44:55+01:00</t>
+          <t>2026-03-07T10:58:10+01:00</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8470,24 +8470,24 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-03-06T15:42:57+00:00</t>
+          <t>2026-03-07T12:43:06+00:00</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>UTV058630911</t>
+          <t>UTV476154311</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985429", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998346", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>UTV111163273</t>
+          <t>UTV181800985</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0031009998346</t>
+          <t>0031009991226</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8523,7 +8523,7 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-03-07T10:57:58+01:00</t>
+          <t>2026-03-07T09:21:27+01:00</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8533,24 +8533,24 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:03+00:00</t>
+          <t>2026-03-07T10:13:29+00:00</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>UTV111163273</t>
+          <t>UTV181800985</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998346", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009991226", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>UTV710144770</t>
+          <t>UTV087620692</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0031009998567</t>
+          <t>0031009998346</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8586,7 +8586,7 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-03-07T14:05:43+01:00</t>
+          <t>2026-03-07T10:58:39+01:00</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8596,24 +8596,24 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:04+00:00</t>
+          <t>2026-03-07T10:13:26+00:00</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>UTV710144770</t>
+          <t>UTV087620692</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998346", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>UTV422656399</t>
+          <t>UTV344915468</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0031009999276</t>
+          <t>0031010000354</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8649,7 +8649,7 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-07T08:28:07+01:00</t>
+          <t>2026-03-07T14:21:39+01:00</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8659,24 +8659,24 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-03-07T10:13:30+00:00</t>
+          <t>2026-03-07T16:13:40+00:00</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>UTV422656399</t>
+          <t>UTV344915468</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999276", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031010000354", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>UTV781809166</t>
+          <t>UTV557713650</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0031009998567</t>
+          <t>0031009999276</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8712,7 +8712,7 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-03-07T14:05:22+01:00</t>
+          <t>2026-03-07T08:28:25+01:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:04+00:00</t>
+          <t>2026-03-07T09:43:04+00:00</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>UTV781809166</t>
+          <t>UTV557713650</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999276", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>UTV513696790</t>
+          <t>UTV458384249</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0031009997143</t>
+          <t>0031009998891</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8775,7 +8775,7 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-03-07T15:08:05+01:00</t>
+          <t>2026-03-07T13:14:58+01:00</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8785,24 +8785,24 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-03-07T16:13:29+00:00</t>
+          <t>2026-03-08T00:43:10+00:00</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>UTV513696790</t>
+          <t>UTV458384249</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009997143", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998891", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UTV902477348</t>
+          <t>UTV111163273</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0031009998567</t>
+          <t>0031009998346</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8838,7 +8838,7 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-03-07T14:05:34+01:00</t>
+          <t>2026-03-07T10:57:58+01:00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8848,24 +8848,24 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-03-07T13:13:31+00:00</t>
+          <t>2026-03-07T12:43:03+00:00</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>UTV902477348</t>
+          <t>UTV111163273</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998346", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>UTV363882189</t>
+          <t>UTV058630911</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0031009998471</t>
+          <t>0031009985429</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8901,7 +8901,7 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-03-07T12:58:08+01:00</t>
+          <t>2026-03-05T15:44:55+01:00</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8911,24 +8911,24 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:06+00:00</t>
+          <t>2026-03-06T15:42:57+00:00</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>UTV363882189</t>
+          <t>UTV058630911</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998471", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009985429", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UTV339837582</t>
+          <t>UTV193284768</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>0031009996193</t>
+          <t>0031009998567</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8964,7 +8964,7 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-07T15:18:16+01:00</t>
+          <t>2026-03-07T14:04:43+01:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8974,24 +8974,24 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-03-07T15:42:57+00:00</t>
+          <t>2026-03-07T15:43:07+00:00</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>UTV339837582</t>
+          <t>UTV193284768</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009996193", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>UTV468080146</t>
+          <t>UTV710144770</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>0031009994397</t>
+          <t>0031009998567</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -9027,7 +9027,7 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-03-07T15:31:58+01:00</t>
+          <t>2026-03-07T14:05:43+01:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9037,24 +9037,24 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:00+00:00</t>
+          <t>2026-03-07T15:43:04+00:00</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>UTV468080146</t>
+          <t>UTV710144770</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009994397", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UTV366918661</t>
+          <t>UTV422656399</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>0031009994397</t>
+          <t>0031009999276</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9090,7 +9090,7 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-03-06T17:28:23+01:00</t>
+          <t>2026-03-07T08:28:07+01:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9100,24 +9100,24 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-03-06T18:42:45+00:00</t>
+          <t>2026-03-07T10:13:30+00:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>UTV366918661</t>
+          <t>UTV422656399</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009994397", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999276", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>UTV977400454</t>
+          <t>UTV781809166</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0031009997413</t>
+          <t>0031009998567</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -9153,7 +9153,7 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-03-07T10:34:42+01:00</t>
+          <t>2026-03-07T14:05:22+01:00</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9163,24 +9163,24 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-03-07T09:42:52+00:00</t>
+          <t>2026-03-07T15:43:04+00:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>UTV977400454</t>
+          <t>UTV781809166</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009997413", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>UTV310660604</t>
+          <t>UTV902477348</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0031009994397</t>
+          <t>0031009998567</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9216,7 +9216,7 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-06T17:28:36+01:00</t>
+          <t>2026-03-07T14:05:34+01:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9226,24 +9226,24 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-03-06T18:42:45+00:00</t>
+          <t>2026-03-07T13:13:31+00:00</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>UTV310660604</t>
+          <t>UTV902477348</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009994397", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>UTV644642092</t>
+          <t>UTV513696790</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>0031009992895</t>
+          <t>0031009997143</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9279,7 +9279,7 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-07T18:39:26+01:00</t>
+          <t>2026-03-07T15:08:05+01:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9289,34 +9289,34 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-03-07T18:43:04+00:00</t>
+          <t>2026-03-07T16:13:29+00:00</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>UTV644642092</t>
+          <t>UTV513696790</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009992895", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009997143", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>889362282844</t>
+          <t>UTV339837582</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>4725946539-E</t>
+          <t>0031009996193</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -9342,34 +9342,34 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-03-07T10:55:45-05:00</t>
+          <t>2026-03-07T15:18:16+01:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Salisbury, MD, 21801, US, United States</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-03-07T16:42:59+00:00</t>
+          <t>2026-03-07T15:42:57+00:00</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>889362282844</t>
+          <t>UTV339837582</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>{"external_order_id": "4725946539-E", "sales_office_id": "4574"}</t>
+          <t>{"external_order_id": "0031009996193", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>UTV108409911</t>
+          <t>UTV363882189</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>B2B25338794</t>
+          <t>0031009998471</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -9405,7 +9405,7 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-03-07T12:34:27+01:00</t>
+          <t>2026-03-07T12:58:08+01:00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9415,24 +9415,24 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-03-07T12:42:47+00:00</t>
+          <t>2026-03-07T12:43:06+00:00</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>UTV108409911</t>
+          <t>UTV363882189</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2B25338794", "sales_office_id": "4238"}</t>
+          <t>{"external_order_id": "0031009998471", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>UTV508978354</t>
+          <t>UTV468080146</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>B2B25338794</t>
+          <t>0031009994397</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -9468,7 +9468,7 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-03-07T12:34:40+01:00</t>
+          <t>2026-03-07T15:31:58+01:00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9478,24 +9478,24 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-03-07T12:42:50+00:00</t>
+          <t>2026-03-07T15:43:00+00:00</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>UTV508978354</t>
+          <t>UTV468080146</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2B25338794", "sales_office_id": "4238"}</t>
+          <t>{"external_order_id": "0031009994397", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>UTV974033873</t>
+          <t>UTV975027754</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>0031009996191</t>
+          <t>0031009995954</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9531,7 +9531,7 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-03-07T09:47:31+01:00</t>
+          <t>2026-03-07T20:35:20+01:00</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9541,34 +9541,34 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-03-07T09:42:44+00:00</t>
+          <t>2026-03-07T21:43:02+00:00</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>UTV974033873</t>
+          <t>UTV975027754</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009996191", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009995954", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>01475240806576</t>
+          <t>UTV366918661</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>0049010277729</t>
+          <t>0031009994397</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -9594,44 +9594,44 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-03-07T14:55:37+01:00</t>
+          <t>2026-03-06T17:28:23+01:00</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Walsrode (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-03-07T14:12:33+00:00</t>
+          <t>2026-03-06T18:42:45+00:00</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>01475240806576</t>
+          <t>UTV366918661</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010277729", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009994397", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>01475240806570</t>
+          <t>UTV977400454</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>0049010279709</t>
+          <t>0031009997413</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -9657,44 +9657,44 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-03-07T09:18:59+01:00</t>
+          <t>2026-03-07T10:34:42+01:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Mannheim (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-03-07T09:42:04+00:00</t>
+          <t>2026-03-07T09:42:52+00:00</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>01475240806570</t>
+          <t>UTV977400454</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010279709", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009997413", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>01475240804973</t>
+          <t>UTV247488610</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0049010279709</t>
+          <t>0031009995954</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -9720,44 +9720,44 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-03-07T09:18:59+01:00</t>
+          <t>2026-03-07T20:35:47+01:00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Mannheim (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-03-07T09:12:19+00:00</t>
+          <t>2026-03-07T21:42:57+00:00</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>01475240804973</t>
+          <t>UTV247488610</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010279709", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009995954", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>01475240805877</t>
+          <t>UTV310660604</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9767,12 +9767,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PO-076-00240645863033076</t>
+          <t>0031009994397</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -9783,44 +9783,44 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-03-07T11:21:57+01:00</t>
+          <t>2026-03-06T17:28:36+01:00</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Hamm (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-03-07T10:41:54+00:00</t>
+          <t>2026-03-06T18:42:45+00:00</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>01475240805877</t>
+          <t>UTV310660604</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-076-00240645863033076", "sales_office_id": "4670"}</t>
+          <t>{"external_order_id": "0031009994397", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>01475240804156</t>
+          <t>UTV644642092</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>cbn4wmt9q9</t>
+          <t>0031009992895</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -9846,44 +9846,44 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-03-07T13:50:29+01:00</t>
+          <t>2026-03-07T18:39:26+01:00</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Hengersberg (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-03-07T15:42:00+00:00</t>
+          <t>2026-03-07T22:42:58+00:00</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>01475240804156</t>
+          <t>UTV644642092</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmt9q9", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "0031009992895", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>01475240807183</t>
+          <t>UTV108409911</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>cbn4wmwjbr</t>
+          <t>B2B25338794</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9909,44 +9909,44 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-03-07T10:22:33+01:00</t>
+          <t>2026-03-07T12:34:27+01:00</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-03-07T09:41:53+00:00</t>
+          <t>2026-03-08T00:42:49+00:00</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>01475240807183</t>
+          <t>UTV108409911</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmwjbr", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "B2B25338794", "sales_office_id": "4238"}</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>01475240804898</t>
+          <t>889362282844</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0049010284398</t>
+          <t>4725946539-E</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9972,44 +9972,44 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-03-07T09:55:26+01:00</t>
+          <t>2026-03-07T10:55:45-05:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Obertraubling (DE), Germany</t>
+          <t>Salisbury, MD, 21801, US, United States</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-03-07T09:41:38+00:00</t>
+          <t>2026-03-07T16:42:59+00:00</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>01475240804898</t>
+          <t>889362282844</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010284398", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "4725946539-E", "sales_office_id": "4574"}</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>01475240804899</t>
+          <t>UTV508978354</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0049010284398</t>
+          <t>B2B25338794</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -10035,44 +10035,44 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-03-07T09:55:26+01:00</t>
+          <t>2026-03-07T12:34:40+01:00</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Obertraubling (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-03-07T09:41:38+00:00</t>
+          <t>2026-03-08T00:42:53+00:00</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>01475240804899</t>
+          <t>UTV508978354</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010284398", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "B2B25338794", "sales_office_id": "4238"}</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>01475240804516</t>
+          <t>UTV974033873</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>0049010279964</t>
+          <t>0031009996191</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -10098,34 +10098,34 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-03-07T13:05:06+01:00</t>
+          <t>2026-03-07T09:47:31+01:00</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Bad Bentheim (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-03-07T12:41:45+00:00</t>
+          <t>2026-03-07T09:42:44+00:00</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>01475240804516</t>
+          <t>UTV974033873</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010279964", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009996191", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>01475240804515</t>
+          <t>01475240806576</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>0049010279964</t>
+          <t>0049010277729</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -10161,34 +10161,34 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-03-07T13:05:06+01:00</t>
+          <t>2026-03-07T14:55:37+01:00</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Bad Bentheim (DE), Germany</t>
+          <t>Walsrode (DE), Germany</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-03-07T14:11:45+00:00</t>
+          <t>2026-03-07T14:12:33+00:00</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>01475240804515</t>
+          <t>01475240806576</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010279964", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010277729", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>01475240807368</t>
+          <t>01475240804973</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>306-1258323-7494713</t>
+          <t>0049010279709</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -10224,34 +10224,34 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-03-07T11:54:01+01:00</t>
+          <t>2026-03-07T09:18:59+01:00</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Mannheim (DE), Germany</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-03-07T11:11:41+00:00</t>
+          <t>2026-03-07T09:12:19+00:00</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>01475240807368</t>
+          <t>01475240804973</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>{"external_order_id": "306-1258323-7494713", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "0049010279709", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>01475240807301</t>
+          <t>01475240806570</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>306-1258323-7494713</t>
+          <t>0049010279709</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -10287,34 +10287,34 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-03-07T11:54:01+01:00</t>
+          <t>2026-03-07T09:18:59+01:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Mannheim (DE), Germany</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-03-07T11:41:41+00:00</t>
+          <t>2026-03-07T09:42:04+00:00</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>01475240807301</t>
+          <t>01475240806570</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>{"external_order_id": "306-1258323-7494713", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "0049010279709", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>01475240804986</t>
+          <t>01475240805877</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1024952660-A</t>
+          <t>PO-076-00240645863033076</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -10350,34 +10350,34 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-03-07T10:48:06+01:00</t>
+          <t>2026-03-07T11:21:57+01:00</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Hamm (DE), Germany</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-03-07T10:41:35+00:00</t>
+          <t>2026-03-07T10:41:54+00:00</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>01475240804986</t>
+          <t>01475240805877</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024952660-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "PO-076-00240645863033076", "sales_office_id": "4670"}</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>01475240805311</t>
+          <t>01475240807183</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10397,12 +10397,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1024952660-A</t>
+          <t>cbn4wmwjbr</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -10413,44 +10413,44 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-07T10:48:06+01:00</t>
+          <t>2026-03-07T10:22:33+01:00</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-03-07T10:41:40+00:00</t>
+          <t>2026-03-07T09:41:53+00:00</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>01475240805311</t>
+          <t>01475240807183</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024952660-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "cbn4wmwjbr", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>05228742866057</t>
+          <t>01475240804156</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>0031009995636</t>
+          <t>cbn4wmt9q9</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -10476,34 +10476,34 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-03-07T10:18:41+01:00</t>
+          <t>2026-03-07T13:50:29+01:00</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Vijfhuizen, NL, Netherlands</t>
+          <t>Hengersberg (DE), Germany</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-03-07T09:41:59+00:00</t>
+          <t>2026-03-07T15:42:00+00:00</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>05228742866057</t>
+          <t>01475240804156</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995636", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "cbn4wmt9q9", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>01475240801708</t>
+          <t>01475240804898</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>0049010272928</t>
+          <t>0049010284398</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10539,34 +10539,34 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-03-06T10:47:25+01:00</t>
+          <t>2026-03-07T09:55:26+01:00</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Obertraubling (DE), Germany</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-03-06T15:41:27+00:00</t>
+          <t>2026-03-07T09:41:38+00:00</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>01475240801708</t>
+          <t>01475240804898</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272928", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0049010284398", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>01475240806076</t>
+          <t>01475240804515</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>B2BDS11583779</t>
+          <t>0049010279964</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -10602,34 +10602,34 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-03-07T11:38:25+01:00</t>
+          <t>2026-03-07T13:05:06+01:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Bad Bentheim (DE), Germany</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-03-07T11:41:38+00:00</t>
+          <t>2026-03-07T14:11:45+00:00</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>01475240806076</t>
+          <t>01475240804515</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11583779", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010279964", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>01475240806647</t>
+          <t>01475240804899</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>B2BDS11595895</t>
+          <t>0049010284398</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -10665,44 +10665,44 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-03-07T11:29:26+01:00</t>
+          <t>2026-03-07T09:55:26+01:00</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Loxstedt (DE), Germany</t>
+          <t>Obertraubling (DE), Germany</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-03-07T11:11:37+00:00</t>
+          <t>2026-03-07T09:41:38+00:00</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>01475240806647</t>
+          <t>01475240804899</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11595895", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0049010284398", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>05228742865987</t>
+          <t>01475240804516</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>0031009998968</t>
+          <t>0049010279964</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -10728,44 +10728,44 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-03-07T11:22:32+01:00</t>
+          <t>2026-03-07T13:05:06+01:00</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Vijfhuizen, NL, Netherlands</t>
+          <t>Bad Bentheim (DE), Germany</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-03-07T10:42:06+00:00</t>
+          <t>2026-03-07T12:41:45+00:00</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>05228742865987</t>
+          <t>01475240804516</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998968", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010279964", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>05228742865949</t>
+          <t>01475240807301</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>0031009998377</t>
+          <t>306-1258323-7494713</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -10791,34 +10791,34 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-03-07T14:35:11+01:00</t>
+          <t>2026-03-07T11:54:01+01:00</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Berkel en Rodenrijs, NL, Netherlands</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-03-07T13:42:14+00:00</t>
+          <t>2026-03-07T11:41:41+00:00</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>05228742865949</t>
+          <t>01475240807301</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998377", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "306-1258323-7494713", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>01475240805088</t>
+          <t>01475240807368</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>0049010280772</t>
+          <t>306-1258323-7494713</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10854,7 +10854,7 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-07T10:42:01+01:00</t>
+          <t>2026-03-07T11:54:01+01:00</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10864,24 +10864,24 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-03-07T10:41:22+00:00</t>
+          <t>2026-03-07T11:11:41+00:00</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>01475240805088</t>
+          <t>01475240807368</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010280772", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "306-1258323-7494713", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>01475240806027</t>
+          <t>01475240804986</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10901,12 +10901,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1116551438-01</t>
+          <t>1024952660-A</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10917,7 +10917,7 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-03-07T10:16:48+01:00</t>
+          <t>2026-03-07T10:48:06+01:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10927,34 +10927,34 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-03-07T10:11:15+00:00</t>
+          <t>2026-03-07T10:41:35+00:00</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>01475240806027</t>
+          <t>01475240804986</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1116551438-01", "sales_office_id": "4677"}</t>
+          <t>{"external_order_id": "1024952660-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>05228742861288</t>
+          <t>01475240805311</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>0032005573112</t>
+          <t>1024952660-A</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10980,34 +10980,34 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-03-06T12:33:25+01:00</t>
+          <t>2026-03-07T10:48:06+01:00</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Aalter, BE, Belgium</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-03-06T15:41:08+00:00</t>
+          <t>2026-03-07T10:41:40+00:00</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>05228742861288</t>
+          <t>01475240805311</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005573112", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "1024952660-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>05228742861453</t>
+          <t>05228742866057</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>0032005573112</t>
+          <t>0031009995636</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -11043,44 +11043,44 @@
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-03-06T12:33:25+01:00</t>
+          <t>2026-03-07T10:18:41+01:00</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Aalter, BE, Belgium</t>
+          <t>Vijfhuizen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-03-06T15:41:09+00:00</t>
+          <t>2026-03-07T09:41:59+00:00</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>05228742861453</t>
+          <t>05228742866057</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0032005573112", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009995636", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>05228742866134</t>
+          <t>01475240801708</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0031009998447</t>
+          <t>0049010272928</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -11106,44 +11106,44 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-03-07T13:39:58+01:00</t>
+          <t>2026-03-06T10:47:25+01:00</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Goes, NL, Netherlands</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-03-07T16:42:25+00:00</t>
+          <t>2026-03-06T15:41:27+00:00</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>05228742866134</t>
+          <t>01475240801708</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998447", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010272928", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>05228742865874</t>
+          <t>01475240806076</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0031009996781</t>
+          <t>B2BDS11583779</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -11169,44 +11169,44 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-03-07T11:03:41+01:00</t>
+          <t>2026-03-07T11:38:25+01:00</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Vijfhuizen, NL, Netherlands</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-03-07T10:11:35+00:00</t>
+          <t>2026-03-07T11:41:38+00:00</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>05228742865874</t>
+          <t>01475240806076</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009996781", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11583779", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>05228742865875</t>
+          <t>01475240806647</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -11216,12 +11216,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0031009996781</t>
+          <t>B2BDS11595895</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -11232,34 +11232,34 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-07T11:03:40+01:00</t>
+          <t>2026-03-07T11:29:26+01:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Vijfhuizen, NL, Netherlands</t>
+          <t>Loxstedt (DE), Germany</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-03-07T10:11:52+00:00</t>
+          <t>2026-03-07T11:11:37+00:00</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>05228742865875</t>
+          <t>01475240806647</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009996781", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11595895", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>05228742865802</t>
+          <t>05228742865949</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0031009997882</t>
+          <t>0031009998377</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -11295,7 +11295,7 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-03-07T12:49:23+01:00</t>
+          <t>2026-03-07T14:35:11+01:00</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11305,34 +11305,34 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-03-07T12:11:54+00:00</t>
+          <t>2026-03-07T13:42:14+00:00</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>05228742865802</t>
+          <t>05228742865949</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009997882", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998377", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>889362849543</t>
+          <t>05228742865987</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PO-211-11065921301112104</t>
+          <t>0031009998968</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -11358,44 +11358,44 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-03-07T12:03:35-05:00</t>
+          <t>2026-03-07T11:22:32+01:00</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Wind Gap, PA, 18091, US, United States</t>
+          <t>Vijfhuizen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-03-07T17:40:45+00:00</t>
+          <t>2026-03-07T10:42:06+00:00</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>889362849543</t>
+          <t>05228742865987</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11065921301112104", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "0031009998968", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>889358374640</t>
+          <t>01475240805088</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11405,12 +11405,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PO-211-11065921301112104</t>
+          <t>0049010280772</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -11421,44 +11421,44 @@
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-03-07T12:03:35-05:00</t>
+          <t>2026-03-07T10:42:01+01:00</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Wind Gap, PA, 18091, US, United States</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-03-07T17:40:34+00:00</t>
+          <t>2026-03-07T10:41:22+00:00</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>889358374640</t>
+          <t>01475240805088</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11065921301112104", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "0049010280772", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>05228742864572</t>
+          <t>01475240806027</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11468,12 +11468,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>B2BDS11544152</t>
+          <t>1116551438-01</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -11484,34 +11484,34 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-03-07T11:11:08+01:00</t>
+          <t>2026-03-07T10:16:48+01:00</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Vemars, FR, France</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-03-07T12:40:08+00:00</t>
+          <t>2026-03-07T10:11:15+00:00</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>05228742864572</t>
+          <t>01475240806027</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11544152", "sales_office_id": "4452"}</t>
+          <t>{"external_order_id": "1116551438-01", "sales_office_id": "4677"}</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>05228742861583</t>
+          <t>05228742861288</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>406-1270775-4419547</t>
+          <t>0032005573112</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -11547,34 +11547,34 @@
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-03-07T11:34:43+01:00</t>
+          <t>2026-03-06T12:33:25+01:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Reims, FR, France</t>
+          <t>Aalter, BE, Belgium</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-03-07T12:39:27+00:00</t>
+          <t>2026-03-06T15:41:08+00:00</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>05228742861583</t>
+          <t>05228742861288</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>{"external_order_id": "406-1270775-4419547", "sales_office_id": "4561"}</t>
+          <t>{"external_order_id": "0032005573112", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>05228742862413</t>
+          <t>05228742861453</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>406-1270775-4419547</t>
+          <t>0032005573112</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -11610,44 +11610,44 @@
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-03-07T11:34:53+01:00</t>
+          <t>2026-03-06T12:33:25+01:00</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Reims, FR, France</t>
+          <t>Aalter, BE, Belgium</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-03-07T12:39:34+00:00</t>
+          <t>2026-03-06T15:41:09+00:00</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>05228742862413</t>
+          <t>05228742861453</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>{"external_order_id": "406-1270775-4419547", "sales_office_id": "4561"}</t>
+          <t>{"external_order_id": "0032005573112", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>889362121758</t>
+          <t>05228742866134</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11657,12 +11657,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>B2BDS11668533</t>
+          <t>0031009998447</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -11673,44 +11673,44 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-03-07T13:01:08-05:00</t>
+          <t>2026-03-07T13:39:58+01:00</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Canonsburg, PA, 15317, US, United States</t>
+          <t>Goes, NL, Netherlands</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-03-07T18:36:40+00:00</t>
+          <t>2026-03-07T16:42:25+00:00</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>889362121758</t>
+          <t>05228742866134</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11668533", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "0031009998447", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>01475240807143</t>
+          <t>05228742865875</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>B2BDS11333012</t>
+          <t>0031009996781</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -11736,44 +11736,44 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-03-07T11:38:26+01:00</t>
+          <t>2026-03-07T11:03:40+01:00</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Melle (DE), Germany</t>
+          <t>Vijfhuizen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-03-07T11:00:53+00:00</t>
+          <t>2026-03-07T10:11:52+00:00</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>01475240807143</t>
+          <t>05228742865875</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11333012", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009996781", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>01475240806676</t>
+          <t>05228742865874</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>186475899-A</t>
+          <t>0031009996781</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -11799,44 +11799,44 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-03-07T16:33:53+01:00</t>
+          <t>2026-03-07T11:03:41+01:00</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Vijfhuizen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-03-07T16:00:29+00:00</t>
+          <t>2026-03-07T10:11:35+00:00</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>01475240806676</t>
+          <t>05228742865874</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>{"external_order_id": "186475899-A", "sales_office_id": "4307"}</t>
+          <t>{"external_order_id": "0031009996781", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>889362520075</t>
+          <t>05228742865802</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11846,12 +11846,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>B2BDS11638259</t>
+          <t>0031009997882</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -11862,34 +11862,34 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-03-07T10:09:14-08:00</t>
+          <t>2026-03-07T12:49:23+01:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Murrieta, CA, 92563, US, United States</t>
+          <t>Berkel en Rodenrijs, NL, Netherlands</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-03-07T18:26:26+00:00</t>
+          <t>2026-03-07T12:11:54+00:00</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>889362520075</t>
+          <t>05228742865802</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11638259", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "0031009997882", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>889362581982</t>
+          <t>889362849543</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>4726054375-A</t>
+          <t>PO-211-11065921301112104</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -11925,44 +11925,44 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-03-07T10:45:55-08:00</t>
+          <t>2026-03-07T12:03:35-05:00</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Upland, CA, 91784, US, United States</t>
+          <t>Wind Gap, PA, 18091, US, United States</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-03-07T19:26:27+00:00</t>
+          <t>2026-03-07T17:40:45+00:00</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>889362581982</t>
+          <t>889362849543</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>{"external_order_id": "4726054375-A", "sales_office_id": "4574"}</t>
+          <t>{"external_order_id": "PO-211-11065921301112104", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>01475240807151</t>
+          <t>889358374640</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>028-1020951-0754752</t>
+          <t>PO-211-11065921301112104</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11988,44 +11988,44 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-03-07T10:43:39+01:00</t>
+          <t>2026-03-07T12:03:35-05:00</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Bad Bentheim (DE), Germany</t>
+          <t>Wind Gap, PA, 18091, US, United States</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-03-07T10:25:17+00:00</t>
+          <t>2026-03-07T17:40:34+00:00</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>01475240807151</t>
+          <t>889358374640</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>{"external_order_id": "028-1020951-0754752", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "PO-211-11065921301112104", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>889362519185</t>
+          <t>05228742864572</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -12035,12 +12035,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>200014402048537</t>
+          <t>B2BDS11544152</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -12051,44 +12051,44 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-03-07T10:45:25-08:00</t>
+          <t>2026-03-07T11:11:08+01:00</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Pasadena, CA, 91103, US, United States</t>
+          <t>Vemars, FR, France</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-03-07T19:24:37+00:00</t>
+          <t>2026-03-07T12:40:08+00:00</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>889362519185</t>
+          <t>05228742864572</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>{"external_order_id": "200014402048537", "sales_office_id": "4260"}</t>
+          <t>{"external_order_id": "B2BDS11544152", "sales_office_id": "4452"}</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>889362017579</t>
+          <t>05228742861583</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>PO-211-11482499625590711</t>
+          <t>406-1270775-4419547</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -12114,44 +12114,44 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-03-07T11:10:28-08:00</t>
+          <t>2026-03-07T11:34:43+01:00</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Atascadero, CA, 93422, US, United States</t>
+          <t>Reims, FR, France</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-03-07T19:22:33+00:00</t>
+          <t>2026-03-07T12:39:27+00:00</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>889362017579</t>
+          <t>05228742861583</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11482499625590711", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "406-1270775-4419547", "sales_office_id": "4561"}</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>889362015223</t>
+          <t>05228742862413</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PO-211-11482499625590711</t>
+          <t>406-1270775-4419547</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -12177,34 +12177,34 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-03-07T11:10:28-08:00</t>
+          <t>2026-03-07T11:34:53+01:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Atascadero, CA, 93422, US, United States</t>
+          <t>Reims, FR, France</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026-03-07T19:22:31+00:00</t>
+          <t>2026-03-07T12:39:34+00:00</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>889362015223</t>
+          <t>05228742862413</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11482499625590711", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "406-1270775-4419547", "sales_office_id": "4561"}</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>889362018943</t>
+          <t>889362121758</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12224,12 +12224,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PO-211-11482499625590711</t>
+          <t>B2BDS11668533</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -12240,44 +12240,44 @@
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-03-07T11:10:28-08:00</t>
+          <t>2026-03-07T13:01:08-05:00</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Atascadero, CA, 93422, US, United States</t>
+          <t>Canonsburg, PA, 15317, US, United States</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-03-07T19:22:30+00:00</t>
+          <t>2026-03-07T18:36:40+00:00</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>889362018943</t>
+          <t>889362121758</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11482499625590711", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "B2BDS11668533", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>889361871413</t>
+          <t>01475240807143</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>CS641805688</t>
+          <t>B2BDS11333012</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -12303,44 +12303,44 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-03-07T15:12:34-05:00</t>
+          <t>2026-03-07T11:38:26+01:00</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Bowie, MD, 20716, US, United States</t>
+          <t>Melle (DE), Germany</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-03-07T20:21:42+00:00</t>
+          <t>2026-03-07T11:00:53+00:00</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>889361871413</t>
+          <t>01475240807143</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641805688", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "B2BDS11333012", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>889360662943</t>
+          <t>01475240806676</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>fedex</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>FedEx®</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12350,12 +12350,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>B2BDS11656922</t>
+          <t>186475899-A</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -12366,34 +12366,34 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-03-07T12:14:17-05:00</t>
+          <t>2026-03-07T16:33:53+01:00</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Glen Rock, NJ, 07452, US, United States</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-03-07T17:21:18+00:00</t>
+          <t>2026-03-07T16:00:29+00:00</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>889360662943</t>
+          <t>01475240806676</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11656922", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "186475899-A", "sales_office_id": "4307"}</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>889361576299</t>
+          <t>889361127212</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12413,12 +12413,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PO-211-11228567235193313</t>
+          <t>B2BDS11580843</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -12429,34 +12429,34 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-03-07T11:52:23-05:00</t>
+          <t>2026-03-07T14:18:17-08:00</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Rochester, NY, 14622, US, United States</t>
+          <t>Agoura Hills, CA, 91301, US, United States</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026-03-07T17:21:21+00:00</t>
+          <t>2026-03-08T00:26:28+00:00</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>889361576299</t>
+          <t>889361127212</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11228567235193313", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "B2BDS11580843", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>889362245714</t>
+          <t>889362591961</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12476,12 +12476,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PO-211-11334555699833705</t>
+          <t>B2BDS11580843</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -12492,44 +12492,44 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-03-07T11:20:27-05:00</t>
+          <t>2026-03-07T14:18:17-08:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Schaghticoke, NY, 12154, US, United States</t>
+          <t>Agoura Hills, CA, 91301, US, United States</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026-03-07T16:21:20+00:00</t>
+          <t>2026-03-08T00:26:26+00:00</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>889362245714</t>
+          <t>889362591961</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11334555699833705", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "B2BDS11580843", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>05228742858322</t>
+          <t>889361126098</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>0031009985268</t>
+          <t>B2BDS11580843</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -12555,44 +12555,44 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-03-06T14:38:35+01:00</t>
+          <t>2026-03-07T14:18:17-08:00</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Berkel en Rodenrijs, NL, Netherlands</t>
+          <t>Agoura Hills, CA, 91301, US, United States</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026-03-06T15:19:20+00:00</t>
+          <t>2026-03-08T00:26:30+00:00</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>05228742858322</t>
+          <t>889361126098</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985268", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11580843", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>05228742857013</t>
+          <t>889362520075</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>0031009985268</t>
+          <t>B2BDS11638259</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -12618,44 +12618,44 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-03-06T11:35:00+01:00</t>
+          <t>2026-03-07T10:09:14-08:00</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Oirschot, NL, Netherlands</t>
+          <t>Murrieta, CA, 92563, US, United States</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026-03-06T15:19:17+00:00</t>
+          <t>2026-03-07T18:26:26+00:00</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>05228742857013</t>
+          <t>889362520075</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009985268", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11638259", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>01475240796877</t>
+          <t>889362581982</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>B2BDS11383175</t>
+          <t>4726054375-A</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -12681,34 +12681,34 @@
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-03-06T09:56:10+01:00</t>
+          <t>2026-03-07T10:45:55-08:00</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Föhren (DE), Germany</t>
+          <t>Upland, CA, 91784, US, United States</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-03-06T15:19:01+00:00</t>
+          <t>2026-03-07T19:26:27+00:00</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>01475240796877</t>
+          <t>889362581982</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11383175", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "4726054375-A", "sales_office_id": "4574"}</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>01475240795750</t>
+          <t>01475240807151</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>B2BDS11383175</t>
+          <t>028-1020951-0754752</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -12744,44 +12744,44 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-03-06T09:56:10+01:00</t>
+          <t>2026-03-07T10:43:39+01:00</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Föhren (DE), Germany</t>
+          <t>Bad Bentheim (DE), Germany</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-03-06T15:19:00+00:00</t>
+          <t>2026-03-07T10:25:17+00:00</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>01475240795750</t>
+          <t>01475240807151</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11383175", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "028-1020951-0754752", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>05228742861941</t>
+          <t>889362519185</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>fedex</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>FedEx®</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>171-3139604-3465107</t>
+          <t>200014402048537</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -12807,34 +12807,34 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-03-07T11:34:57+01:00</t>
+          <t>2026-03-07T10:45:25-08:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Séné, FR, France</t>
+          <t>Pasadena, CA, 91103, US, United States</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-03-07T16:20:00+00:00</t>
+          <t>2026-03-07T19:24:37+00:00</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>05228742861941</t>
+          <t>889362519185</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>{"external_order_id": "171-3139604-3465107", "sales_office_id": "4561"}</t>
+          <t>{"external_order_id": "200014402048537", "sales_office_id": "4260"}</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>889359482420</t>
+          <t>889362015223</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12854,12 +12854,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>113-6228141-0628203</t>
+          <t>PO-211-11482499625590711</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -12870,34 +12870,34 @@
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-03-07T10:23:24-05:00</t>
+          <t>2026-03-07T11:10:28-08:00</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Bayside, NY, 11361, US, United States</t>
+          <t>Atascadero, CA, 93422, US, United States</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-03-07T16:17:27+00:00</t>
+          <t>2026-03-07T19:22:31+00:00</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>889359482420</t>
+          <t>889362015223</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>{"external_order_id": "113-6228141-0628203", "sales_office_id": "4264"}</t>
+          <t>{"external_order_id": "PO-211-11482499625590711", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>889361463068</t>
+          <t>889362018943</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12917,12 +12917,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>B2BDS11609914</t>
+          <t>PO-211-11482499625590711</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -12933,34 +12933,34 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-03-07T13:08:51-05:00</t>
+          <t>2026-03-07T11:10:28-08:00</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Stroudsburg, PA, 18360, US, United States</t>
+          <t>Atascadero, CA, 93422, US, United States</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-03-07T19:08:31+00:00</t>
+          <t>2026-03-07T19:22:30+00:00</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>889361463068</t>
+          <t>889362018943</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11609914", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "PO-211-11482499625590711", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>889361465829</t>
+          <t>889362017579</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>B2BDS11656241</t>
+          <t>PO-211-11482499625590711</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -12996,34 +12996,34 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-03-07T10:09:41-05:00</t>
+          <t>2026-03-07T11:10:28-08:00</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Ashburn, VA, 20148, US, United States</t>
+          <t>Atascadero, CA, 93422, US, United States</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-03-07T16:08:17+00:00</t>
+          <t>2026-03-07T19:22:33+00:00</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>889361465829</t>
+          <t>889362017579</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11656241", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "PO-211-11482499625590711", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>889361265709</t>
+          <t>889361871413</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>PO-211-11107439227512819</t>
+          <t>CS641805688</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -13059,27 +13059,27 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-03-07T10:54:46-08:00</t>
+          <t>2026-03-07T15:12:34-05:00</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Bakersfield, CA, 93314, US, United States</t>
+          <t>Bowie, MD, 20716, US, United States</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-03-07T19:51:46+00:00</t>
+          <t>2026-03-07T20:21:42+00:00</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>889361265709</t>
+          <t>889361871413</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11107439227512819", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "CS641805688", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>

--- a/docs/data/returns_intransit.xlsx
+++ b/docs/data/returns_intransit.xlsx
@@ -549,7 +549,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>889248018557</t>
+          <t>889251541268</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,12 +569,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B2BDS11361523</t>
+          <t>PO-211-14167907912310065</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,34 +585,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-05T15:08:57-06:00</t>
+          <t>2026-03-05T12:26:21-05:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nashville, TN, 37207, US, United States</t>
+          <t>Tampa, FL, 33604, US, United States</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-03-07T20:55:01+00:00</t>
+          <t>2026-03-07T20:55:03+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>889248018557</t>
+          <t>889251541268</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11361523", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "PO-211-14167907912310065", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>889243093701</t>
+          <t>889248018557</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-07T20:54:59+00:00</t>
+          <t>2026-03-07T20:55:01+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>889243093701</t>
+          <t>889248018557</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>889251541268</t>
+          <t>889243093701</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PO-211-14167907912310065</t>
+          <t>B2BDS11361523</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -711,27 +711,27 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-05T12:26:21-05:00</t>
+          <t>2026-03-05T15:08:57-06:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Tampa, FL, 33604, US, United States</t>
+          <t>Nashville, TN, 37207, US, United States</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-03-07T20:55:03+00:00</t>
+          <t>2026-03-07T20:54:59+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>889251541268</t>
+          <t>889243093701</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-14167907912310065", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "B2BDS11361523", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>889375928294</t>
+          <t>889375930364</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-03-07T15:57:12+00:00</t>
+          <t>2026-03-07T15:57:10+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>889375928294</t>
+          <t>889375930364</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>889375906131</t>
+          <t>889375931430</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-07T15:57:14+00:00</t>
+          <t>2026-03-07T15:57:15+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>889375906131</t>
+          <t>889375931430</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>889375930364</t>
+          <t>889375928294</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-07T15:57:10+00:00</t>
+          <t>2026-03-07T15:57:12+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>889375930364</t>
+          <t>889375928294</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>889375931430</t>
+          <t>889375906131</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-07T15:57:15+00:00</t>
+          <t>2026-03-07T15:57:14+00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>889375931430</t>
+          <t>889375906131</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1872,7 +1872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>889370028644</t>
+          <t>889370024329</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-03-07T14:57:28+00:00</t>
+          <t>2026-03-07T14:57:18+00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>889370028644</t>
+          <t>889370024329</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>889370024329</t>
+          <t>889370028644</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-07T14:57:18+00:00</t>
+          <t>2026-03-07T14:57:28+00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>889370024329</t>
+          <t>889370028644</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>889370934611</t>
+          <t>889370932045</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PO-211-11675224310391611</t>
+          <t>PO-211-00243831706233123</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2223,34 +2223,34 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-03-07T11:11:46-05:00</t>
+          <t>2026-03-07T13:57:32-05:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Orange, NJ, 07050, US, United States</t>
+          <t>Patchogue, NY, 11772, US, United States</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-03-07T16:54:18+00:00</t>
+          <t>2026-03-07T19:54:26+00:00</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>889370934611</t>
+          <t>889370932045</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11675224310391611", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "PO-211-00243831706233123", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>889370932045</t>
+          <t>889370934611</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PO-211-00243831706233123</t>
+          <t>PO-211-11675224310391611</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2286,27 +2286,27 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-03-07T13:57:32-05:00</t>
+          <t>2026-03-07T11:11:46-05:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Patchogue, NY, 11772, US, United States</t>
+          <t>Orange, NJ, 07050, US, United States</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-03-07T19:54:26+00:00</t>
+          <t>2026-03-07T16:54:18+00:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>889370932045</t>
+          <t>889370934611</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-00243831706233123", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "PO-211-11675224310391611", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
@@ -2565,17 +2565,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>01475240803969</t>
+          <t>UTV920806812</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>Packs</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B2BDS11563973</t>
+          <t>0031009999635</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,44 +2601,44 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-03-07T10:09:53+01:00</t>
+          <t>2026-03-07T15:15:36+01:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Münster (DE), Germany</t>
+          <t>,Netherlands</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-03-07T09:45:23+00:00</t>
+          <t>2026-03-07T15:45:25+00:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>01475240803969</t>
+          <t>UTV920806812</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11563973", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "0031009999635", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UTV920806812</t>
+          <t>01475240803969</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Packs</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0031009999635</t>
+          <t>B2BDS11563973</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2664,27 +2664,27 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-07T15:15:36+01:00</t>
+          <t>2026-03-07T10:09:53+01:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>,Netherlands</t>
+          <t>Münster (DE), Germany</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-07T15:45:25+00:00</t>
+          <t>2026-03-07T09:45:23+00:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>UTV920806812</t>
+          <t>01475240803969</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999635", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "B2BDS11563973", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>889369636510</t>
+          <t>889369951492</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CS641786066</t>
+          <t>114-1748278-1883409</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2979,34 +2979,34 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-07T14:03:34-05:00</t>
+          <t>2026-03-07T09:26:25-05:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>West Hempstead, NY, 11552, US, United States</t>
+          <t>New York, NY, 10032, US, United States</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-03-07T19:42:28+00:00</t>
+          <t>2026-03-07T14:42:20+00:00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>889369636510</t>
+          <t>889369951492</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641786066", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "114-1748278-1883409", "sales_office_id": "4264"}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>889369951492</t>
+          <t>889369636510</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>114-1748278-1883409</t>
+          <t>CS641786066</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3042,34 +3042,34 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-07T09:26:25-05:00</t>
+          <t>2026-03-07T14:03:34-05:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>New York, NY, 10032, US, United States</t>
+          <t>West Hempstead, NY, 11552, US, United States</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-03-07T14:42:20+00:00</t>
+          <t>2026-03-07T19:42:28+00:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>889369951492</t>
+          <t>889369636510</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{"external_order_id": "114-1748278-1883409", "sales_office_id": "4264"}</t>
+          <t>{"external_order_id": "CS641786066", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>889369374063</t>
+          <t>889369892504</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4726090450-A</t>
+          <t>CS641703351</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3105,34 +3105,34 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-03-07T13:18:36-05:00</t>
+          <t>2026-03-07T10:52:25-05:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Far Rockaway, NY, 11691, US, United States</t>
+          <t>New York, NY, 10024, US, United States</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-07T18:40:29+00:00</t>
+          <t>2026-03-07T16:40:31+00:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>889369374063</t>
+          <t>889369892504</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{"external_order_id": "4726090450-A", "sales_office_id": "4574"}</t>
+          <t>{"external_order_id": "CS641703351", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>889369892504</t>
+          <t>889369374063</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS641703351</t>
+          <t>4726090450-A</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3168,27 +3168,27 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-07T10:52:25-05:00</t>
+          <t>2026-03-07T13:18:36-05:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>New York, NY, 10024, US, United States</t>
+          <t>Far Rockaway, NY, 11691, US, United States</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-07T16:40:31+00:00</t>
+          <t>2026-03-07T18:40:29+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>889369892504</t>
+          <t>889369374063</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641703351", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "4726090450-A", "sales_office_id": "4574"}</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>889369055622</t>
+          <t>889368963515</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PO-211-11616517479032025</t>
+          <t>CS641728450</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3357,34 +3357,34 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-03-07T11:28:48-05:00</t>
+          <t>2026-03-07T11:09:14-05:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Arlington, VA, 22206, US, United States</t>
+          <t>Kittanning, PA, 16201, US, United States</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-07T17:07:07+00:00</t>
+          <t>2026-03-07T17:07:09+00:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>889369055622</t>
+          <t>889368963515</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11616517479032025", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "CS641728450", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>889368963515</t>
+          <t>889369055622</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CS641728450</t>
+          <t>PO-211-11616517479032025</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3420,34 +3420,34 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-03-07T11:09:14-05:00</t>
+          <t>2026-03-07T11:28:48-05:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Kittanning, PA, 16201, US, United States</t>
+          <t>Arlington, VA, 22206, US, United States</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-03-07T17:07:09+00:00</t>
+          <t>2026-03-07T17:07:07+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>889368963515</t>
+          <t>889369055622</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641728450", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "PO-211-11616517479032025", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>889369056916</t>
+          <t>889368569122</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PO-211-08829010944631039</t>
+          <t>B2BDS11577654</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3483,34 +3483,34 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-03-07T15:21:01-05:00</t>
+          <t>2026-03-07T14:48:36-05:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Scottsville, VA, 24590, US, United States</t>
+          <t>Washington, DC, 20007, US, United States</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-03-07T21:07:19+00:00</t>
+          <t>2026-03-07T20:07:15+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>889369056916</t>
+          <t>889368569122</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-08829010944631039", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "B2BDS11577654", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>889368569122</t>
+          <t>889369056916</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>B2BDS11577654</t>
+          <t>PO-211-08829010944631039</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3546,27 +3546,27 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-03-07T14:48:36-05:00</t>
+          <t>2026-03-07T15:21:01-05:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Washington, DC, 20007, US, United States</t>
+          <t>Scottsville, VA, 24590, US, United States</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-03-07T20:07:15+00:00</t>
+          <t>2026-03-07T21:07:19+00:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>889368569122</t>
+          <t>889369056916</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11577654", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "PO-211-08829010944631039", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>889367343999</t>
+          <t>889367449327</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GSU16R54C00MH0R</t>
+          <t>PO-211-11647151544951712</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3735,34 +3735,34 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-07T11:57:45-05:00</t>
+          <t>2026-03-07T14:06:42-05:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>New York, NY, 10016, US, United States</t>
+          <t>Dover, PA, 17315, US, United States</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-03-07T17:36:24+00:00</t>
+          <t>2026-03-07T19:36:31+00:00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>889367343999</t>
+          <t>889367449327</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{"external_order_id": "GSU16R54C00MH0R", "sales_office_id": "4684"}</t>
+          <t>{"external_order_id": "PO-211-11647151544951712", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>889367449327</t>
+          <t>889367343999</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PO-211-11647151544951712</t>
+          <t>GSU16R54C00MH0R</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3798,27 +3798,27 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-07T14:06:42-05:00</t>
+          <t>2026-03-07T11:57:45-05:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Dover, PA, 17315, US, United States</t>
+          <t>New York, NY, 10016, US, United States</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-07T19:36:31+00:00</t>
+          <t>2026-03-07T17:36:24+00:00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>889367449327</t>
+          <t>889367343999</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11647151544951712", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "GSU16R54C00MH0R", "sales_office_id": "4684"}</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>889367609189</t>
+          <t>889367409069</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>B2BDS11422951</t>
+          <t>B2BDS11668629</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3924,34 +3924,34 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-03-07T11:09:03-05:00</t>
+          <t>2026-03-07T13:46:29-05:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Stuyvesant, NY, 12173, US, United States</t>
+          <t>Catasauqua, PA, 18032, US, United States</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-03-07T16:32:15+00:00</t>
+          <t>2026-03-07T19:32:06+00:00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>889367609189</t>
+          <t>889367409069</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11422951", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "B2BDS11668629", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>889367409069</t>
+          <t>889367609189</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B2BDS11668629</t>
+          <t>B2BDS11422951</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3987,27 +3987,27 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-03-07T13:46:29-05:00</t>
+          <t>2026-03-07T11:09:03-05:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Catasauqua, PA, 18032, US, United States</t>
+          <t>Stuyvesant, NY, 12173, US, United States</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-03-07T19:32:06+00:00</t>
+          <t>2026-03-07T16:32:15+00:00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>889367409069</t>
+          <t>889367609189</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11668629", "sales_office_id": "4461"}</t>
+          <t>{"external_order_id": "B2BDS11422951", "sales_office_id": "4461"}</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>889363718592</t>
+          <t>889361439898</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4312,12 +4312,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-07T17:37:28+00:00</t>
+          <t>2026-03-07T17:37:24+00:00</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>889363718592</t>
+          <t>889361439898</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>889364042068</t>
+          <t>889363718592</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>200014473356841</t>
+          <t>912003268384629-8596772382</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4365,34 +4365,34 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-03-07T13:40:11-05:00</t>
+          <t>2026-03-07T12:05:00-05:00</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Olyphant, PA, 18447, US, United States</t>
+          <t>Millsboro, DE, 19966, US, United States</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-07T19:37:45+00:00</t>
+          <t>2026-03-07T17:37:28+00:00</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>889364042068</t>
+          <t>889363718592</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>{"external_order_id": "200014473356841", "sales_office_id": "4260"}</t>
+          <t>{"external_order_id": "912003268384629-8596772382", "sales_office_id": "4362"}</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>889361439898</t>
+          <t>889364042068</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>912003268384629-8596772382</t>
+          <t>200014473356841</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4428,27 +4428,27 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-03-07T12:05:00-05:00</t>
+          <t>2026-03-07T13:40:11-05:00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Millsboro, DE, 19966, US, United States</t>
+          <t>Olyphant, PA, 18447, US, United States</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-03-07T17:37:24+00:00</t>
+          <t>2026-03-07T19:37:45+00:00</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>889361439898</t>
+          <t>889364042068</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>{"external_order_id": "912003268384629-8596772382", "sales_office_id": "4362"}</t>
+          <t>{"external_order_id": "200014473356841", "sales_office_id": "4260"}</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>889362885633</t>
+          <t>889363196395</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PO-211-11215988347513258</t>
+          <t>CS641762034</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4869,34 +4869,34 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-07T10:37:24-05:00</t>
+          <t>2026-03-07T11:42:00-05:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, 11211, US, United States</t>
+          <t>Jersey City, NJ, 07306, US, United States</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-03-07T15:48:47+00:00</t>
+          <t>2026-03-07T16:48:51+00:00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>889362885633</t>
+          <t>889363196395</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11215988347513258", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "CS641762034", "sales_office_id": "4310"}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>889363194392</t>
+          <t>889363459973</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PO-211-11266395935354046</t>
+          <t>PO-211-05872303473270295</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4932,34 +4932,34 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-03-07T17:31:41-05:00</t>
+          <t>2026-03-07T11:09:20-08:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Toms River, NJ, 08753, US, United States</t>
+          <t>Van Nuys, CA, 91405, US, United States</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-03-07T22:49:11+00:00</t>
+          <t>2026-03-07T19:49:00+00:00</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>889363194392</t>
+          <t>889363459973</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-11266395935354046", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "PO-211-05872303473270295", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>889363459973</t>
+          <t>889362885633</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PO-211-05872303473270295</t>
+          <t>PO-211-11215988347513258</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4995,34 +4995,34 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-07T11:09:20-08:00</t>
+          <t>2026-03-07T10:37:24-05:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Van Nuys, CA, 91405, US, United States</t>
+          <t>Brooklyn, NY, 11211, US, United States</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-03-07T19:49:00+00:00</t>
+          <t>2026-03-07T15:48:47+00:00</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>889363459973</t>
+          <t>889362885633</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>{"external_order_id": "PO-211-05872303473270295", "sales_office_id": "4676"}</t>
+          <t>{"external_order_id": "PO-211-11215988347513258", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>889363196395</t>
+          <t>889363194392</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CS641762034</t>
+          <t>PO-211-11266395935354046</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5058,27 +5058,27 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-03-07T11:42:00-05:00</t>
+          <t>2026-03-07T17:31:41-05:00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, 07306, US, United States</t>
+          <t>Toms River, NJ, 08753, US, United States</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-03-07T16:48:51+00:00</t>
+          <t>2026-03-07T22:49:11+00:00</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>889363196395</t>
+          <t>889363194392</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>{"external_order_id": "CS641762034", "sales_office_id": "4310"}</t>
+          <t>{"external_order_id": "PO-211-11266395935354046", "sales_office_id": "4676"}</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>UTV517387442</t>
+          <t>UTV307033148</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5373,7 +5373,7 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-03-07T17:21:24+01:00</t>
+          <t>2026-03-07T17:21:43+01:00</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-03-07T18:45:55+00:00</t>
+          <t>2026-03-07T18:45:54+00:00</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>UTV517387442</t>
+          <t>UTV307033148</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>UTV307033148</t>
+          <t>UTV517387442</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5436,7 +5436,7 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-03-07T17:21:43+01:00</t>
+          <t>2026-03-07T17:21:24+01:00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-03-07T18:45:54+00:00</t>
+          <t>2026-03-07T18:45:55+00:00</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>UTV307033148</t>
+          <t>UTV517387442</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>UTV098268709</t>
+          <t>UTV854730895</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0031009991082</t>
+          <t>0031009990149</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5562,7 +5562,7 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-03-07T10:25:09+01:00</t>
+          <t>2026-03-07T13:56:05+01:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5572,24 +5572,24 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-03-07T09:44:18+00:00</t>
+          <t>2026-03-07T15:44:25+00:00</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>UTV098268709</t>
+          <t>UTV854730895</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009991082", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009990149", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>UTV854730895</t>
+          <t>UTV098268709</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0031009990149</t>
+          <t>0031009991082</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5625,7 +5625,7 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-03-07T13:56:05+01:00</t>
+          <t>2026-03-07T10:25:09+01:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:25+00:00</t>
+          <t>2026-03-07T09:44:18+00:00</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>UTV854730895</t>
+          <t>UTV098268709</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009990149", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009991082", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>UTV789874035</t>
+          <t>UTV892064517</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0031009997072</t>
+          <t>0031009996341</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6255,7 +6255,7 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-03-07T15:01:08+01:00</t>
+          <t>2026-03-07T14:58:40+01:00</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:16+00:00</t>
+          <t>2026-03-07T15:44:12+00:00</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>UTV789874035</t>
+          <t>UTV892064517</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009997072", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009996341", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>UTV892064517</t>
+          <t>UTV789874035</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0031009996341</t>
+          <t>0031009997072</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6318,7 +6318,7 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-03-07T14:58:40+01:00</t>
+          <t>2026-03-07T15:01:08+01:00</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6328,17 +6328,17 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-03-07T15:44:12+00:00</t>
+          <t>2026-03-07T15:44:16+00:00</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>UTV892064517</t>
+          <t>UTV789874035</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009996341", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009997072", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UTV485172073</t>
+          <t>UTV278587518</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6444,7 +6444,7 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-03-06T11:39:17+01:00</t>
+          <t>2026-03-07T12:43:44+01:00</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-03-06T15:43:54+00:00</t>
+          <t>2026-03-07T12:44:03+00:00</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>UTV485172073</t>
+          <t>UTV278587518</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6471,7 +6471,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>UTV278587518</t>
+          <t>UTV485172073</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6507,7 +6507,7 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:44+01:00</t>
+          <t>2026-03-06T11:39:17+01:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-03-07T12:44:03+00:00</t>
+          <t>2026-03-06T15:43:54+00:00</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>UTV278587518</t>
+          <t>UTV485172073</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7227,7 +7227,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UTV150206567</t>
+          <t>UTV523884117</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7263,7 +7263,7 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-03-07T13:41:38+01:00</t>
+          <t>2026-03-07T13:42:50+01:00</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:51+00:00</t>
+          <t>2026-03-07T12:43:46+00:00</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>UTV150206567</t>
+          <t>UTV523884117</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UTV523884117</t>
+          <t>UTV465980823</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0031009999052</t>
+          <t>0031009995967</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7326,7 +7326,7 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-03-07T13:42:50+01:00</t>
+          <t>2026-03-07T08:05:08+01:00</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7336,24 +7336,24 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:46+00:00</t>
+          <t>2026-03-07T09:43:42+00:00</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>UTV523884117</t>
+          <t>UTV465980823</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999052", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>UTV465980823</t>
+          <t>UTV150206567</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0031009995967</t>
+          <t>0031009999052</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7389,7 +7389,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-03-07T08:05:08+01:00</t>
+          <t>2026-03-07T13:41:38+01:00</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7399,17 +7399,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:42+00:00</t>
+          <t>2026-03-07T12:43:51+00:00</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>UTV465980823</t>
+          <t>UTV150206567</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999052", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>UTV037823638</t>
+          <t>UTV666157586</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0031009995967</t>
+          <t>0031009993377</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7515,7 +7515,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-03-07T08:05:35+01:00</t>
+          <t>2026-03-06T12:16:32+01:00</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7525,24 +7525,24 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:41+00:00</t>
+          <t>2026-03-06T15:43:34+00:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>UTV037823638</t>
+          <t>UTV666157586</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009993377", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UTV666157586</t>
+          <t>UTV037823638</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0031009993377</t>
+          <t>0031009995967</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7578,7 +7578,7 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-03-06T12:16:32+01:00</t>
+          <t>2026-03-07T08:05:35+01:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7588,17 +7588,17 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-03-06T15:43:34+00:00</t>
+          <t>2026-03-07T09:43:41+00:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>UTV666157586</t>
+          <t>UTV037823638</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009993377", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009995967", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UTV323182364</t>
+          <t>UTV684232150</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7704,7 +7704,7 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-03-07T12:31:13+01:00</t>
+          <t>2026-03-07T12:31:22+01:00</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>UTV323182364</t>
+          <t>UTV684232150</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -7731,7 +7731,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UTV684232150</t>
+          <t>UTV323182364</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-03-07T12:31:22+01:00</t>
+          <t>2026-03-07T12:31:13+01:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>UTV684232150</t>
+          <t>UTV323182364</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -7983,7 +7983,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UTV374098129</t>
+          <t>UTV833690635</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0031009998574</t>
+          <t>0031009998483</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -8019,7 +8019,7 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-03-07T12:32:26+01:00</t>
+          <t>2026-03-07T10:31:48+01:00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8029,24 +8029,24 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:27+00:00</t>
+          <t>2026-03-07T09:43:39+00:00</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>UTV374098129</t>
+          <t>UTV833690635</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998574", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998483", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UTV833690635</t>
+          <t>UTV374098129</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>0031009998483</t>
+          <t>0031009998574</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -8082,7 +8082,7 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-03-07T10:31:48+01:00</t>
+          <t>2026-03-07T12:32:26+01:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8092,17 +8092,17 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:39+00:00</t>
+          <t>2026-03-07T12:43:27+00:00</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>UTV833690635</t>
+          <t>UTV374098129</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998483", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998574", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>UTV821301129</t>
+          <t>UTV617244913</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>0031009991226</t>
+          <t>0031009999113</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8334,7 +8334,7 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-03-07T09:22:33+01:00</t>
+          <t>2026-03-07T14:11:52+01:00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8344,24 +8344,24 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-03-07T09:43:37+00:00</t>
+          <t>2026-03-07T15:43:11+00:00</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>UTV821301129</t>
+          <t>UTV617244913</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009991226", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999113", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>UTV617244913</t>
+          <t>UTV821301129</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>0031009999113</t>
+          <t>0031009991226</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8397,7 +8397,7 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-03-07T14:11:52+01:00</t>
+          <t>2026-03-07T09:22:33+01:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8407,17 +8407,17 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:11+00:00</t>
+          <t>2026-03-07T09:43:37+00:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>UTV617244913</t>
+          <t>UTV821301129</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999113", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009991226", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>UTV181800985</t>
+          <t>UTV344915468</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0031009991226</t>
+          <t>0031010000354</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8523,7 +8523,7 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-03-07T09:21:27+01:00</t>
+          <t>2026-03-07T14:21:39+01:00</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8533,17 +8533,17 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-03-07T10:13:29+00:00</t>
+          <t>2026-03-07T16:13:40+00:00</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>UTV181800985</t>
+          <t>UTV344915468</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009991226", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031010000354", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>UTV344915468</t>
+          <t>UTV181800985</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0031010000354</t>
+          <t>0031009991226</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8649,7 +8649,7 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-07T14:21:39+01:00</t>
+          <t>2026-03-07T09:21:27+01:00</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8659,17 +8659,17 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-03-07T16:13:40+00:00</t>
+          <t>2026-03-07T10:13:29+00:00</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>UTV344915468</t>
+          <t>UTV181800985</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031010000354", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009991226", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UTV111163273</t>
+          <t>UTV193284768</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0031009998346</t>
+          <t>0031009998567</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8838,7 +8838,7 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-03-07T10:57:58+01:00</t>
+          <t>2026-03-07T14:04:43+01:00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8848,17 +8848,17 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-03-07T12:43:03+00:00</t>
+          <t>2026-03-07T15:43:07+00:00</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>UTV111163273</t>
+          <t>UTV193284768</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998346", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -8928,7 +8928,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UTV193284768</t>
+          <t>UTV111163273</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>0031009998567</t>
+          <t>0031009998346</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8964,7 +8964,7 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-07T14:04:43+01:00</t>
+          <t>2026-03-07T10:57:58+01:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8974,24 +8974,24 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:07+00:00</t>
+          <t>2026-03-07T12:43:03+00:00</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>UTV193284768</t>
+          <t>UTV111163273</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998346", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>UTV710144770</t>
+          <t>UTV422656399</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>0031009998567</t>
+          <t>0031009999276</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -9027,7 +9027,7 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-03-07T14:05:43+01:00</t>
+          <t>2026-03-07T08:28:07+01:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9037,24 +9037,24 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-03-07T15:43:04+00:00</t>
+          <t>2026-03-07T10:13:30+00:00</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>UTV710144770</t>
+          <t>UTV422656399</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009999276", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UTV422656399</t>
+          <t>UTV710144770</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>0031009999276</t>
+          <t>0031009998567</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9090,7 +9090,7 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-03-07T08:28:07+01:00</t>
+          <t>2026-03-07T14:05:43+01:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9100,17 +9100,17 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-03-07T10:13:30+00:00</t>
+          <t>2026-03-07T15:43:04+00:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>UTV422656399</t>
+          <t>UTV710144770</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009999276", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009998567", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>UTV247488610</t>
+          <t>UTV310660604</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0031009995954</t>
+          <t>0031009994397</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9720,7 +9720,7 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-03-07T20:35:47+01:00</t>
+          <t>2026-03-06T17:28:36+01:00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9730,24 +9730,24 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-03-07T21:42:57+00:00</t>
+          <t>2026-03-06T18:42:45+00:00</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>UTV247488610</t>
+          <t>UTV310660604</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995954", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009994397", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>UTV310660604</t>
+          <t>UTV644642092</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0031009994397</t>
+          <t>0031009992895</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9783,7 +9783,7 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-03-06T17:28:36+01:00</t>
+          <t>2026-03-07T18:39:26+01:00</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9793,24 +9793,24 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-03-06T18:42:45+00:00</t>
+          <t>2026-03-07T22:42:58+00:00</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>UTV310660604</t>
+          <t>UTV644642092</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009994397", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009992895", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>UTV644642092</t>
+          <t>UTV247488610</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0031009992895</t>
+          <t>0031009995954</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9846,7 +9846,7 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-03-07T18:39:26+01:00</t>
+          <t>2026-03-07T20:35:47+01:00</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9856,17 +9856,17 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-03-07T22:42:58+00:00</t>
+          <t>2026-03-07T21:42:57+00:00</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>UTV644642092</t>
+          <t>UTV247488610</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009992895", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0031009995954", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10188,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>01475240804973</t>
+          <t>01475240806570</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-03-07T09:12:19+00:00</t>
+          <t>2026-03-07T09:42:04+00:00</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>01475240804973</t>
+          <t>01475240806570</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -10251,7 +10251,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>01475240806570</t>
+          <t>01475240804973</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10297,12 +10297,12 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-03-07T09:42:04+00:00</t>
+          <t>2026-03-07T09:12:19+00:00</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>01475240806570</t>
+          <t>01475240804973</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -10377,7 +10377,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>01475240807183</t>
+          <t>01475240804156</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>cbn4wmwjbr</t>
+          <t>cbn4wmt9q9</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10413,34 +10413,34 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-07T10:22:33+01:00</t>
+          <t>2026-03-07T13:50:29+01:00</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Vlotho (DE), Germany</t>
+          <t>Hengersberg (DE), Germany</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-03-07T09:41:53+00:00</t>
+          <t>2026-03-07T15:42:00+00:00</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>01475240807183</t>
+          <t>01475240804156</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmwjbr", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "cbn4wmt9q9", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>01475240804156</t>
+          <t>01475240807183</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>cbn4wmt9q9</t>
+          <t>cbn4wmwjbr</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10476,27 +10476,27 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-03-07T13:50:29+01:00</t>
+          <t>2026-03-07T10:22:33+01:00</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Hengersberg (DE), Germany</t>
+          <t>Vlotho (DE), Germany</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-03-07T15:42:00+00:00</t>
+          <t>2026-03-07T09:41:53+00:00</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>01475240804156</t>
+          <t>01475240807183</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>{"external_order_id": "cbn4wmt9q9", "sales_office_id": "4316"}</t>
+          <t>{"external_order_id": "cbn4wmwjbr", "sales_office_id": "4316"}</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>01475240804515</t>
+          <t>01475240804516</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10612,12 +10612,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-03-07T14:11:45+00:00</t>
+          <t>2026-03-07T12:41:45+00:00</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>01475240804515</t>
+          <t>01475240804516</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -10692,7 +10692,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>01475240804516</t>
+          <t>01475240804515</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10738,12 +10738,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-03-07T12:41:45+00:00</t>
+          <t>2026-03-07T14:11:45+00:00</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>01475240804516</t>
+          <t>01475240804515</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -10755,7 +10755,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>01475240807301</t>
+          <t>01475240807368</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10801,12 +10801,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-03-07T11:41:41+00:00</t>
+          <t>2026-03-07T11:11:41+00:00</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>01475240807301</t>
+          <t>01475240807368</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -10818,7 +10818,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>01475240807368</t>
+          <t>01475240804986</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>306-1258323-7494713</t>
+          <t>1024952660-A</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10854,34 +10854,34 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-07T11:54:01+01:00</t>
+          <t>2026-03-07T10:48:06+01:00</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Salzgitter (DE), Germany</t>
+          <t>Wilnsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-03-07T11:11:41+00:00</t>
+          <t>2026-03-07T10:41:35+00:00</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>01475240807368</t>
+          <t>01475240804986</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>{"external_order_id": "306-1258323-7494713", "sales_office_id": "4263"}</t>
+          <t>{"external_order_id": "1024952660-A", "sales_office_id": "4074"}</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>01475240804986</t>
+          <t>01475240807301</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10901,12 +10901,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1024952660-A</t>
+          <t>306-1258323-7494713</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10917,27 +10917,27 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-03-07T10:48:06+01:00</t>
+          <t>2026-03-07T11:54:01+01:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Wilnsdorf (DE), Germany</t>
+          <t>Salzgitter (DE), Germany</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-03-07T10:41:35+00:00</t>
+          <t>2026-03-07T11:41:41+00:00</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>01475240804986</t>
+          <t>01475240807301</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>{"external_order_id": "1024952660-A", "sales_office_id": "4074"}</t>
+          <t>{"external_order_id": "306-1258323-7494713", "sales_office_id": "4263"}</t>
         </is>
       </c>
     </row>
@@ -11007,17 +11007,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>05228742866057</t>
+          <t>01475240801708</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>dpd-api</t>
+          <t>dpd-de</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DPD</t>
+          <t>DPD Germany</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -11027,12 +11027,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>0031009995636</t>
+          <t>0049010272928</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -11043,44 +11043,44 @@
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-03-07T10:18:41+01:00</t>
+          <t>2026-03-06T10:47:25+01:00</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Vijfhuizen, NL, Netherlands</t>
+          <t>Raunheim (DE), Germany</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-03-07T09:41:59+00:00</t>
+          <t>2026-03-06T15:41:27+00:00</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>05228742866057</t>
+          <t>01475240801708</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0031009995636", "sales_office_id": "0303"}</t>
+          <t>{"external_order_id": "0049010272928", "sales_office_id": "0301"}</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>01475240801708</t>
+          <t>05228742866057</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>dpd-de</t>
+          <t>dpd-api</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DPD Germany</t>
+          <t>DPD</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0049010272928</t>
+          <t>0031009995636</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -11106,34 +11106,34 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-03-06T10:47:25+01:00</t>
+          <t>2026-03-07T10:18:41+01:00</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Raunheim (DE), Germany</t>
+          <t>Vijfhuizen, NL, Netherlands</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-03-06T15:41:27+00:00</t>
+          <t>2026-03-07T09:41:59+00:00</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>01475240801708</t>
+          <t>05228742866057</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>{"external_order_id": "0049010272928", "sales_office_id": "0301"}</t>
+          <t>{"external_order_id": "0031009995636", "sales_office_id": "0303"}</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>01475240806076</t>
+          <t>01475240806647</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>B2BDS11583779</t>
+          <t>B2BDS11595895</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -11169,34 +11169,34 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-03-07T11:38:25+01:00</t>
+          <t>2026-03-07T11:29:26+01:00</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Hermsdorf (DE), Germany</t>
+          <t>Loxstedt (DE), Germany</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-03-07T11:41:38+00:00</t>
+          <t>2026-03-07T11:11:37+00:00</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>01475240806076</t>
+          <t>01475240806647</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11583779", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11595895", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>01475240806647</t>
+          <t>01475240806076</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>B2BDS11595895</t>
+          <t>B2BDS11583779</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -11232,27 +11232,27 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-07T11:29:26+01:00</t>
+          <t>2026-03-07T11:38:25+01:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Loxstedt (DE), Germany</t>
+          <t>Hermsdorf (DE), Germany</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-03-07T11:11:37+00:00</t>
+          <t>2026-03-07T11:41:38+00:00</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>01475240806647</t>
+          <t>01475240806076</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>{"external_order_id": "B2BDS11595895", "sales_office_id": "4436"}</t>
+          <t>{"external_order_id": "B2BDS11583779", "sales_office_id": "4436"}</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>05228742865875</t>
+          <t>05228742865874</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11736,7 +11736,7 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-03-07T11:03:40+01:00</t>
+          <t>2026-03-07T11:03:41+01:00</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-03-07T10:11:52+00:00</t>
+          <t>2026-03-07T10:11:35+00:00</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>05228742865875</t>
+          <t>05228742865874</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -11763,7 +11763,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>05228742865874</t>
+          <t>05228742865875</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11799,7 +11799,7 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-03-07T11:03:41+01:00</t>
+          <t>2026-03-07T11:03:40+01:00</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11809,12 +11809,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-03-07T10:11:35+00:00</t>
+          <t>2026-03-07T10:11:52+00:00</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>05228742865874</t>
+          <t>05228742865875</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -12834,7 +12834,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>889362015223</t>
+      